--- a/clang-x64/Running erasure.xlsx
+++ b/clang-x64/Running erasure.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>19.5712</v>
+        <v>18.1649</v>
       </c>
       <c r="C2" t="n">
-        <v>32.4169</v>
+        <v>13.1199</v>
       </c>
       <c r="D2" t="n">
-        <v>32.3548</v>
+        <v>31.2195</v>
       </c>
       <c r="E2" t="n">
-        <v>13.7134</v>
+        <v>12.4241</v>
       </c>
       <c r="F2" t="n">
-        <v>26.1729</v>
+        <v>25.5751</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>19.5468</v>
+        <v>17.9267</v>
       </c>
       <c r="C3" t="n">
-        <v>31.8743</v>
+        <v>13.2544</v>
       </c>
       <c r="D3" t="n">
-        <v>32.3259</v>
+        <v>31.3683</v>
       </c>
       <c r="E3" t="n">
-        <v>13.2515</v>
+        <v>12.4286</v>
       </c>
       <c r="F3" t="n">
-        <v>25.8568</v>
+        <v>25.2832</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>18.8916</v>
+        <v>17.6123</v>
       </c>
       <c r="C4" t="n">
-        <v>31.8579</v>
+        <v>13.6223</v>
       </c>
       <c r="D4" t="n">
-        <v>32.351</v>
+        <v>31.4701</v>
       </c>
       <c r="E4" t="n">
-        <v>13.2091</v>
+        <v>12.3612</v>
       </c>
       <c r="F4" t="n">
-        <v>25.8044</v>
+        <v>25.1731</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>18.3889</v>
+        <v>17.1899</v>
       </c>
       <c r="C5" t="n">
-        <v>31.0955</v>
+        <v>13.7743</v>
       </c>
       <c r="D5" t="n">
-        <v>32.4596</v>
+        <v>31.507</v>
       </c>
       <c r="E5" t="n">
-        <v>13.2821</v>
+        <v>11.8174</v>
       </c>
       <c r="F5" t="n">
-        <v>25.988</v>
+        <v>25.3553</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>17.7598</v>
+        <v>16.7161</v>
       </c>
       <c r="C6" t="n">
-        <v>31.1922</v>
+        <v>14.1039</v>
       </c>
       <c r="D6" t="n">
-        <v>32.5839</v>
+        <v>31.5241</v>
       </c>
       <c r="E6" t="n">
-        <v>12.9202</v>
+        <v>11.5245</v>
       </c>
       <c r="F6" t="n">
-        <v>25.7892</v>
+        <v>24.5978</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>17.0245</v>
+        <v>16.0838</v>
       </c>
       <c r="C7" t="n">
-        <v>29.3642</v>
+        <v>14.3737</v>
       </c>
       <c r="D7" t="n">
-        <v>31.8394</v>
+        <v>30.8271</v>
       </c>
       <c r="E7" t="n">
-        <v>12.7819</v>
+        <v>11.2704</v>
       </c>
       <c r="F7" t="n">
-        <v>25.3473</v>
+        <v>24.5152</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>16.1128</v>
+        <v>15.7641</v>
       </c>
       <c r="C8" t="n">
-        <v>29.2507</v>
+        <v>15.9177</v>
       </c>
       <c r="D8" t="n">
-        <v>31.7849</v>
+        <v>30.93</v>
       </c>
       <c r="E8" t="n">
-        <v>12.7526</v>
+        <v>11.1835</v>
       </c>
       <c r="F8" t="n">
-        <v>24.9575</v>
+        <v>23.8778</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>15.1663</v>
+        <v>15.0223</v>
       </c>
       <c r="C9" t="n">
-        <v>28.0698</v>
+        <v>16.0947</v>
       </c>
       <c r="D9" t="n">
-        <v>31.972</v>
+        <v>30.8595</v>
       </c>
       <c r="E9" t="n">
-        <v>18.8149</v>
+        <v>18.1357</v>
       </c>
       <c r="F9" t="n">
-        <v>29.4978</v>
+        <v>28.615</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>23.1245</v>
+        <v>22.096</v>
       </c>
       <c r="C10" t="n">
-        <v>35.6823</v>
+        <v>16.081</v>
       </c>
       <c r="D10" t="n">
-        <v>31.9343</v>
+        <v>31.0329</v>
       </c>
       <c r="E10" t="n">
-        <v>18.2956</v>
+        <v>17.8009</v>
       </c>
       <c r="F10" t="n">
-        <v>29.2042</v>
+        <v>28.3862</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>22.7276</v>
+        <v>21.5427</v>
       </c>
       <c r="C11" t="n">
-        <v>35.4801</v>
+        <v>16.1712</v>
       </c>
       <c r="D11" t="n">
-        <v>32.1228</v>
+        <v>31.136</v>
       </c>
       <c r="E11" t="n">
-        <v>17.9469</v>
+        <v>17.3088</v>
       </c>
       <c r="F11" t="n">
-        <v>29.0085</v>
+        <v>28.1436</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>22.4395</v>
+        <v>21.1584</v>
       </c>
       <c r="C12" t="n">
-        <v>35.1832</v>
+        <v>16.3599</v>
       </c>
       <c r="D12" t="n">
-        <v>32.079</v>
+        <v>31.1369</v>
       </c>
       <c r="E12" t="n">
-        <v>17.5639</v>
+        <v>16.9088</v>
       </c>
       <c r="F12" t="n">
-        <v>28.5731</v>
+        <v>27.8771</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>22.1276</v>
+        <v>20.8588</v>
       </c>
       <c r="C13" t="n">
-        <v>34.5253</v>
+        <v>16.2817</v>
       </c>
       <c r="D13" t="n">
-        <v>32.1647</v>
+        <v>31.2478</v>
       </c>
       <c r="E13" t="n">
-        <v>17.0586</v>
+        <v>16.8409</v>
       </c>
       <c r="F13" t="n">
-        <v>28.4366</v>
+        <v>27.6361</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>21.8952</v>
+        <v>20.4948</v>
       </c>
       <c r="C14" t="n">
-        <v>34.1336</v>
+        <v>16.3276</v>
       </c>
       <c r="D14" t="n">
-        <v>32.2961</v>
+        <v>31.231</v>
       </c>
       <c r="E14" t="n">
-        <v>16.8871</v>
+        <v>16.2413</v>
       </c>
       <c r="F14" t="n">
-        <v>28.1186</v>
+        <v>27.2463</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>21.4727</v>
+        <v>20.197</v>
       </c>
       <c r="C15" t="n">
-        <v>33.8685</v>
+        <v>16.4072</v>
       </c>
       <c r="D15" t="n">
-        <v>32.387</v>
+        <v>31.6648</v>
       </c>
       <c r="E15" t="n">
-        <v>16.6152</v>
+        <v>15.9324</v>
       </c>
       <c r="F15" t="n">
-        <v>27.5503</v>
+        <v>26.9708</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>21.1944</v>
+        <v>19.8942</v>
       </c>
       <c r="C16" t="n">
-        <v>33.2539</v>
+        <v>16.4818</v>
       </c>
       <c r="D16" t="n">
-        <v>32.5546</v>
+        <v>31.7549</v>
       </c>
       <c r="E16" t="n">
-        <v>16.1838</v>
+        <v>15.6917</v>
       </c>
       <c r="F16" t="n">
-        <v>27.209</v>
+        <v>26.6826</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>20.8012</v>
+        <v>19.4758</v>
       </c>
       <c r="C17" t="n">
-        <v>32.68</v>
+        <v>16.4722</v>
       </c>
       <c r="D17" t="n">
-        <v>32.7433</v>
+        <v>31.8593</v>
       </c>
       <c r="E17" t="n">
-        <v>15.9017</v>
+        <v>15.4828</v>
       </c>
       <c r="F17" t="n">
-        <v>27.1776</v>
+        <v>26.2925</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>20.207</v>
+        <v>19.0279</v>
       </c>
       <c r="C18" t="n">
-        <v>32.3858</v>
+        <v>16.4737</v>
       </c>
       <c r="D18" t="n">
-        <v>32.6731</v>
+        <v>31.8791</v>
       </c>
       <c r="E18" t="n">
-        <v>15.5843</v>
+        <v>15.0345</v>
       </c>
       <c r="F18" t="n">
-        <v>26.7096</v>
+        <v>26.0432</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>19.6907</v>
+        <v>18.5368</v>
       </c>
       <c r="C19" t="n">
-        <v>31.6282</v>
+        <v>16.6511</v>
       </c>
       <c r="D19" t="n">
-        <v>32.9088</v>
+        <v>32.0341</v>
       </c>
       <c r="E19" t="n">
-        <v>15.188</v>
+        <v>14.3257</v>
       </c>
       <c r="F19" t="n">
-        <v>26.9191</v>
+        <v>26.182</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>19.1122</v>
+        <v>18.1204</v>
       </c>
       <c r="C20" t="n">
-        <v>30.9681</v>
+        <v>16.6053</v>
       </c>
       <c r="D20" t="n">
-        <v>32.9973</v>
+        <v>32.1096</v>
       </c>
       <c r="E20" t="n">
-        <v>14.9034</v>
+        <v>14.4674</v>
       </c>
       <c r="F20" t="n">
-        <v>26.1324</v>
+        <v>25.4358</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>18.4477</v>
+        <v>17.5466</v>
       </c>
       <c r="C21" t="n">
-        <v>30.9473</v>
+        <v>16.6071</v>
       </c>
       <c r="D21" t="n">
-        <v>32.5488</v>
+        <v>31.2539</v>
       </c>
       <c r="E21" t="n">
-        <v>14.5431</v>
+        <v>14.1013</v>
       </c>
       <c r="F21" t="n">
-        <v>25.7132</v>
+        <v>25.3389</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>17.4643</v>
+        <v>16.8943</v>
       </c>
       <c r="C22" t="n">
-        <v>29.5201</v>
+        <v>18.03</v>
       </c>
       <c r="D22" t="n">
-        <v>32.6324</v>
+        <v>31.3076</v>
       </c>
       <c r="E22" t="n">
-        <v>14.1624</v>
+        <v>13.7474</v>
       </c>
       <c r="F22" t="n">
-        <v>25.279</v>
+        <v>24.6478</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>16.5627</v>
+        <v>16.1921</v>
       </c>
       <c r="C23" t="n">
-        <v>28.4764</v>
+        <v>17.8246</v>
       </c>
       <c r="D23" t="n">
-        <v>32.4175</v>
+        <v>31.3589</v>
       </c>
       <c r="E23" t="n">
-        <v>19.476</v>
+        <v>18.8899</v>
       </c>
       <c r="F23" t="n">
-        <v>30.1618</v>
+        <v>29.2582</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>24.2479</v>
+        <v>22.8023</v>
       </c>
       <c r="C24" t="n">
-        <v>35.6339</v>
+        <v>17.7785</v>
       </c>
       <c r="D24" t="n">
-        <v>32.3946</v>
+        <v>31.2342</v>
       </c>
       <c r="E24" t="n">
-        <v>18.9346</v>
+        <v>18.6623</v>
       </c>
       <c r="F24" t="n">
-        <v>29.6991</v>
+        <v>28.9466</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>23.832</v>
+        <v>22.3267</v>
       </c>
       <c r="C25" t="n">
-        <v>35.182</v>
+        <v>17.7365</v>
       </c>
       <c r="D25" t="n">
-        <v>32.5553</v>
+        <v>31.6939</v>
       </c>
       <c r="E25" t="n">
-        <v>18.6036</v>
+        <v>18.1185</v>
       </c>
       <c r="F25" t="n">
-        <v>29.3291</v>
+        <v>28.5494</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>23.4682</v>
+        <v>22.0173</v>
       </c>
       <c r="C26" t="n">
-        <v>34.7727</v>
+        <v>17.746</v>
       </c>
       <c r="D26" t="n">
-        <v>32.5087</v>
+        <v>31.8216</v>
       </c>
       <c r="E26" t="n">
-        <v>18.1545</v>
+        <v>17.7991</v>
       </c>
       <c r="F26" t="n">
-        <v>29.1399</v>
+        <v>28.2956</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>23.1299</v>
+        <v>21.7219</v>
       </c>
       <c r="C27" t="n">
-        <v>34.3529</v>
+        <v>17.756</v>
       </c>
       <c r="D27" t="n">
-        <v>32.5235</v>
+        <v>31.7776</v>
       </c>
       <c r="E27" t="n">
-        <v>17.8374</v>
+        <v>16.8777</v>
       </c>
       <c r="F27" t="n">
-        <v>29.2104</v>
+        <v>28.3926</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>22.8336</v>
+        <v>21.2838</v>
       </c>
       <c r="C28" t="n">
-        <v>33.9868</v>
+        <v>17.6227</v>
       </c>
       <c r="D28" t="n">
-        <v>32.527</v>
+        <v>31.7009</v>
       </c>
       <c r="E28" t="n">
-        <v>17.4272</v>
+        <v>16.5796</v>
       </c>
       <c r="F28" t="n">
-        <v>28.8166</v>
+        <v>28.1401</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>22.2167</v>
+        <v>20.8533</v>
       </c>
       <c r="C29" t="n">
-        <v>33.5239</v>
+        <v>17.6078</v>
       </c>
       <c r="D29" t="n">
-        <v>32.7323</v>
+        <v>31.7841</v>
       </c>
       <c r="E29" t="n">
-        <v>17.1515</v>
+        <v>16.1333</v>
       </c>
       <c r="F29" t="n">
-        <v>28.5845</v>
+        <v>27.8871</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>21.754</v>
+        <v>20.4578</v>
       </c>
       <c r="C30" t="n">
-        <v>32.7259</v>
+        <v>17.4479</v>
       </c>
       <c r="D30" t="n">
-        <v>32.9192</v>
+        <v>31.8248</v>
       </c>
       <c r="E30" t="n">
-        <v>16.8113</v>
+        <v>15.8689</v>
       </c>
       <c r="F30" t="n">
-        <v>28.2802</v>
+        <v>27.7028</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>21.3296</v>
+        <v>19.9913</v>
       </c>
       <c r="C31" t="n">
-        <v>32.6791</v>
+        <v>17.3981</v>
       </c>
       <c r="D31" t="n">
-        <v>32.7623</v>
+        <v>31.8539</v>
       </c>
       <c r="E31" t="n">
-        <v>16.494</v>
+        <v>15.9741</v>
       </c>
       <c r="F31" t="n">
-        <v>27.4813</v>
+        <v>26.7818</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>20.9157</v>
+        <v>19.5734</v>
       </c>
       <c r="C32" t="n">
-        <v>32.5328</v>
+        <v>17.2669</v>
       </c>
       <c r="D32" t="n">
-        <v>32.9132</v>
+        <v>32.0997</v>
       </c>
       <c r="E32" t="n">
-        <v>16.0821</v>
+        <v>15.6749</v>
       </c>
       <c r="F32" t="n">
-        <v>27.1039</v>
+        <v>26.4331</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>20.316</v>
+        <v>19.0334</v>
       </c>
       <c r="C33" t="n">
-        <v>31.3534</v>
+        <v>17.249</v>
       </c>
       <c r="D33" t="n">
-        <v>33.2063</v>
+        <v>32.2559</v>
       </c>
       <c r="E33" t="n">
-        <v>15.7456</v>
+        <v>15.4075</v>
       </c>
       <c r="F33" t="n">
-        <v>26.7529</v>
+        <v>26.1474</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>19.7228</v>
+        <v>18.5063</v>
       </c>
       <c r="C34" t="n">
-        <v>31.1103</v>
+        <v>17.2496</v>
       </c>
       <c r="D34" t="n">
-        <v>33.2326</v>
+        <v>32.4027</v>
       </c>
       <c r="E34" t="n">
-        <v>15.4802</v>
+        <v>14.5306</v>
       </c>
       <c r="F34" t="n">
-        <v>26.9235</v>
+        <v>26.2908</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>18.8534</v>
+        <v>17.9952</v>
       </c>
       <c r="C35" t="n">
-        <v>30.6415</v>
+        <v>17.0966</v>
       </c>
       <c r="D35" t="n">
-        <v>32.7393</v>
+        <v>32.0863</v>
       </c>
       <c r="E35" t="n">
-        <v>15.0878</v>
+        <v>14.7897</v>
       </c>
       <c r="F35" t="n">
-        <v>26.0212</v>
+        <v>25.3595</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>18.1225</v>
+        <v>17.3979</v>
       </c>
       <c r="C36" t="n">
-        <v>29.8632</v>
+        <v>17.0872</v>
       </c>
       <c r="D36" t="n">
-        <v>32.8623</v>
+        <v>31.7374</v>
       </c>
       <c r="E36" t="n">
-        <v>14.7045</v>
+        <v>14.3336</v>
       </c>
       <c r="F36" t="n">
-        <v>25.7651</v>
+        <v>24.9919</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>17.2218</v>
+        <v>16.6646</v>
       </c>
       <c r="C37" t="n">
-        <v>28.3407</v>
+        <v>18.367</v>
       </c>
       <c r="D37" t="n">
-        <v>32.7656</v>
+        <v>31.9617</v>
       </c>
       <c r="E37" t="n">
-        <v>19.716</v>
+        <v>18.8891</v>
       </c>
       <c r="F37" t="n">
-        <v>30.7043</v>
+        <v>29.7543</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>24.9509</v>
+        <v>23.0508</v>
       </c>
       <c r="C38" t="n">
-        <v>35.7345</v>
+        <v>18.2663</v>
       </c>
       <c r="D38" t="n">
-        <v>32.6992</v>
+        <v>31.9625</v>
       </c>
       <c r="E38" t="n">
-        <v>19.3737</v>
+        <v>18.3858</v>
       </c>
       <c r="F38" t="n">
-        <v>30.3253</v>
+        <v>29.4634</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>24.3047</v>
+        <v>22.7891</v>
       </c>
       <c r="C39" t="n">
-        <v>35.3776</v>
+        <v>18.2614</v>
       </c>
       <c r="D39" t="n">
-        <v>32.6813</v>
+        <v>31.9226</v>
       </c>
       <c r="E39" t="n">
-        <v>18.8359</v>
+        <v>18.4874</v>
       </c>
       <c r="F39" t="n">
-        <v>29.6419</v>
+        <v>28.8168</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>23.8396</v>
+        <v>22.4121</v>
       </c>
       <c r="C40" t="n">
-        <v>35.0695</v>
+        <v>18.1162</v>
       </c>
       <c r="D40" t="n">
-        <v>32.7753</v>
+        <v>31.7576</v>
       </c>
       <c r="E40" t="n">
-        <v>18.4569</v>
+        <v>17.9234</v>
       </c>
       <c r="F40" t="n">
-        <v>29.2622</v>
+        <v>28.4065</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>23.558</v>
+        <v>22.0319</v>
       </c>
       <c r="C41" t="n">
-        <v>34.5741</v>
+        <v>17.9511</v>
       </c>
       <c r="D41" t="n">
-        <v>32.8035</v>
+        <v>31.9123</v>
       </c>
       <c r="E41" t="n">
-        <v>17.9301</v>
+        <v>17.5961</v>
       </c>
       <c r="F41" t="n">
-        <v>28.9127</v>
+        <v>28.1463</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>23.1962</v>
+        <v>21.6225</v>
       </c>
       <c r="C42" t="n">
-        <v>34.206</v>
+        <v>17.9055</v>
       </c>
       <c r="D42" t="n">
-        <v>32.7936</v>
+        <v>31.9342</v>
       </c>
       <c r="E42" t="n">
-        <v>17.5664</v>
+        <v>17.2123</v>
       </c>
       <c r="F42" t="n">
-        <v>28.6283</v>
+        <v>27.8691</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>22.6496</v>
+        <v>21.2173</v>
       </c>
       <c r="C43" t="n">
-        <v>33.6492</v>
+        <v>17.7847</v>
       </c>
       <c r="D43" t="n">
-        <v>32.8061</v>
+        <v>31.96</v>
       </c>
       <c r="E43" t="n">
-        <v>17.1585</v>
+        <v>16.9356</v>
       </c>
       <c r="F43" t="n">
-        <v>28.3096</v>
+        <v>27.6263</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>22.1581</v>
+        <v>20.7627</v>
       </c>
       <c r="C44" t="n">
-        <v>33.6725</v>
+        <v>17.7243</v>
       </c>
       <c r="D44" t="n">
-        <v>32.8267</v>
+        <v>32.2076</v>
       </c>
       <c r="E44" t="n">
-        <v>16.8763</v>
+        <v>16.6159</v>
       </c>
       <c r="F44" t="n">
-        <v>27.9949</v>
+        <v>27.3339</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>21.6812</v>
+        <v>20.3156</v>
       </c>
       <c r="C45" t="n">
-        <v>33.4763</v>
+        <v>17.6123</v>
       </c>
       <c r="D45" t="n">
-        <v>33.1476</v>
+        <v>32.3024</v>
       </c>
       <c r="E45" t="n">
-        <v>16.5358</v>
+        <v>16.2508</v>
       </c>
       <c r="F45" t="n">
-        <v>27.5976</v>
+        <v>26.8886</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>21.1514</v>
+        <v>19.7434</v>
       </c>
       <c r="C46" t="n">
-        <v>32.5623</v>
+        <v>17.5094</v>
       </c>
       <c r="D46" t="n">
-        <v>33.0779</v>
+        <v>32.3851</v>
       </c>
       <c r="E46" t="n">
-        <v>16.1624</v>
+        <v>15.9162</v>
       </c>
       <c r="F46" t="n">
-        <v>27.2651</v>
+        <v>26.627</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>20.7</v>
+        <v>19.3099</v>
       </c>
       <c r="C47" t="n">
-        <v>32.5888</v>
+        <v>17.4083</v>
       </c>
       <c r="D47" t="n">
-        <v>33.2753</v>
+        <v>32.5082</v>
       </c>
       <c r="E47" t="n">
-        <v>16.0495</v>
+        <v>15.0738</v>
       </c>
       <c r="F47" t="n">
-        <v>27.512</v>
+        <v>26.8194</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>20.0144</v>
+        <v>18.7168</v>
       </c>
       <c r="C48" t="n">
-        <v>30.9826</v>
+        <v>17.3153</v>
       </c>
       <c r="D48" t="n">
-        <v>33.3254</v>
+        <v>32.65</v>
       </c>
       <c r="E48" t="n">
-        <v>15.6986</v>
+        <v>14.8159</v>
       </c>
       <c r="F48" t="n">
-        <v>27.1207</v>
+        <v>26.4582</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>19.3033</v>
+        <v>18.1636</v>
       </c>
       <c r="C49" t="n">
-        <v>30.7402</v>
+        <v>17.2409</v>
       </c>
       <c r="D49" t="n">
-        <v>33.7205</v>
+        <v>32.7463</v>
       </c>
       <c r="E49" t="n">
-        <v>15.353</v>
+        <v>14.4323</v>
       </c>
       <c r="F49" t="n">
-        <v>26.7924</v>
+        <v>26.1144</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>18.5182</v>
+        <v>17.6124</v>
       </c>
       <c r="C50" t="n">
-        <v>30.0531</v>
+        <v>17.1992</v>
       </c>
       <c r="D50" t="n">
-        <v>33.0372</v>
+        <v>32.1235</v>
       </c>
       <c r="E50" t="n">
-        <v>14.9978</v>
+        <v>14.0744</v>
       </c>
       <c r="F50" t="n">
-        <v>25.8824</v>
+        <v>25.2246</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>17.6294</v>
+        <v>16.7553</v>
       </c>
       <c r="C51" t="n">
-        <v>29.5188</v>
+        <v>18.7548</v>
       </c>
       <c r="D51" t="n">
-        <v>33.1005</v>
+        <v>32.2574</v>
       </c>
       <c r="E51" t="n">
-        <v>19.8417</v>
+        <v>19.5773</v>
       </c>
       <c r="F51" t="n">
-        <v>30.3999</v>
+        <v>29.5736</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>16.6311</v>
+        <v>16.1302</v>
       </c>
       <c r="C52" t="n">
-        <v>28.4781</v>
+        <v>18.5352</v>
       </c>
       <c r="D52" t="n">
-        <v>33.2693</v>
+        <v>32.345</v>
       </c>
       <c r="E52" t="n">
-        <v>19.4498</v>
+        <v>19.0997</v>
       </c>
       <c r="F52" t="n">
-        <v>30.0282</v>
+        <v>29.1793</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>24.5514</v>
+        <v>22.9623</v>
       </c>
       <c r="C53" t="n">
-        <v>35.6754</v>
+        <v>18.4054</v>
       </c>
       <c r="D53" t="n">
-        <v>33.4358</v>
+        <v>32.5911</v>
       </c>
       <c r="E53" t="n">
-        <v>18.9822</v>
+        <v>18.7357</v>
       </c>
       <c r="F53" t="n">
-        <v>29.7171</v>
+        <v>28.8465</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>24.1786</v>
+        <v>22.6592</v>
       </c>
       <c r="C54" t="n">
-        <v>34.7604</v>
+        <v>18.2396</v>
       </c>
       <c r="D54" t="n">
-        <v>33.3312</v>
+        <v>32.8437</v>
       </c>
       <c r="E54" t="n">
-        <v>18.6404</v>
+        <v>18.2221</v>
       </c>
       <c r="F54" t="n">
-        <v>29.3512</v>
+        <v>28.5186</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>23.9842</v>
+        <v>22.2626</v>
       </c>
       <c r="C55" t="n">
-        <v>35.0489</v>
+        <v>18.1205</v>
       </c>
       <c r="D55" t="n">
-        <v>33.6221</v>
+        <v>32.853</v>
       </c>
       <c r="E55" t="n">
-        <v>18.171</v>
+        <v>17.8063</v>
       </c>
       <c r="F55" t="n">
-        <v>28.9388</v>
+        <v>28.1812</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>23.4567</v>
+        <v>21.8107</v>
       </c>
       <c r="C56" t="n">
-        <v>34.6781</v>
+        <v>17.9559</v>
       </c>
       <c r="D56" t="n">
-        <v>33.7555</v>
+        <v>33.1263</v>
       </c>
       <c r="E56" t="n">
-        <v>17.6863</v>
+        <v>17.4829</v>
       </c>
       <c r="F56" t="n">
-        <v>28.7557</v>
+        <v>27.958</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>22.9974</v>
+        <v>21.3934</v>
       </c>
       <c r="C57" t="n">
-        <v>34.2725</v>
+        <v>17.8392</v>
       </c>
       <c r="D57" t="n">
-        <v>33.9131</v>
+        <v>33.3352</v>
       </c>
       <c r="E57" t="n">
-        <v>17.4118</v>
+        <v>17.1654</v>
       </c>
       <c r="F57" t="n">
-        <v>28.4453</v>
+        <v>27.6652</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>22.3513</v>
+        <v>20.9203</v>
       </c>
       <c r="C58" t="n">
-        <v>35.8665</v>
+        <v>17.7082</v>
       </c>
       <c r="D58" t="n">
-        <v>33.9714</v>
+        <v>33.3734</v>
       </c>
       <c r="E58" t="n">
-        <v>17.0327</v>
+        <v>16.7665</v>
       </c>
       <c r="F58" t="n">
-        <v>28.113</v>
+        <v>27.3561</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>21.9546</v>
+        <v>20.5229</v>
       </c>
       <c r="C59" t="n">
-        <v>33.4465</v>
+        <v>17.682</v>
       </c>
       <c r="D59" t="n">
-        <v>34.0639</v>
+        <v>33.2964</v>
       </c>
       <c r="E59" t="n">
-        <v>16.6929</v>
+        <v>16.4346</v>
       </c>
       <c r="F59" t="n">
-        <v>27.7821</v>
+        <v>27.0643</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>21.3973</v>
+        <v>20.0016</v>
       </c>
       <c r="C60" t="n">
-        <v>33.806</v>
+        <v>17.6078</v>
       </c>
       <c r="D60" t="n">
-        <v>34.3362</v>
+        <v>33.426</v>
       </c>
       <c r="E60" t="n">
-        <v>16.3676</v>
+        <v>16.1424</v>
       </c>
       <c r="F60" t="n">
-        <v>27.4355</v>
+        <v>26.7707</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>20.7814</v>
+        <v>19.429</v>
       </c>
       <c r="C61" t="n">
-        <v>35.2562</v>
+        <v>17.504</v>
       </c>
       <c r="D61" t="n">
-        <v>34.984</v>
+        <v>33.7261</v>
       </c>
       <c r="E61" t="n">
-        <v>16.196</v>
+        <v>15.8328</v>
       </c>
       <c r="F61" t="n">
-        <v>27.1314</v>
+        <v>26.4513</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>20.1692</v>
+        <v>19.0116</v>
       </c>
       <c r="C62" t="n">
-        <v>32.1153</v>
+        <v>17.4306</v>
       </c>
       <c r="D62" t="n">
-        <v>35.3885</v>
+        <v>34.1577</v>
       </c>
       <c r="E62" t="n">
-        <v>15.7177</v>
+        <v>15.6116</v>
       </c>
       <c r="F62" t="n">
-        <v>26.7996</v>
+        <v>26.145</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>19.5521</v>
+        <v>18.4182</v>
       </c>
       <c r="C63" t="n">
-        <v>34.8917</v>
+        <v>17.3575</v>
       </c>
       <c r="D63" t="n">
-        <v>35.6502</v>
+        <v>34.3247</v>
       </c>
       <c r="E63" t="n">
-        <v>15.3981</v>
+        <v>15.1741</v>
       </c>
       <c r="F63" t="n">
-        <v>26.4801</v>
+        <v>25.7969</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>18.7407</v>
+        <v>17.8085</v>
       </c>
       <c r="C64" t="n">
-        <v>32.3849</v>
+        <v>17.2436</v>
       </c>
       <c r="D64" t="n">
-        <v>39.9336</v>
+        <v>38.9061</v>
       </c>
       <c r="E64" t="n">
-        <v>15.1033</v>
+        <v>14.8448</v>
       </c>
       <c r="F64" t="n">
-        <v>26.1012</v>
+        <v>25.3947</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>17.8233</v>
+        <v>17.1783</v>
       </c>
       <c r="C65" t="n">
-        <v>31.8501</v>
+        <v>18.9956</v>
       </c>
       <c r="D65" t="n">
-        <v>39.8078</v>
+        <v>39.3455</v>
       </c>
       <c r="E65" t="n">
-        <v>14.8033</v>
+        <v>13.936</v>
       </c>
       <c r="F65" t="n">
-        <v>25.7464</v>
+        <v>25.0543</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>16.9602</v>
+        <v>16.4502</v>
       </c>
       <c r="C66" t="n">
-        <v>31.4454</v>
+        <v>18.697</v>
       </c>
       <c r="D66" t="n">
-        <v>40.0481</v>
+        <v>39.8596</v>
       </c>
       <c r="E66" t="n">
-        <v>20.144</v>
+        <v>20.2061</v>
       </c>
       <c r="F66" t="n">
-        <v>30.2031</v>
+        <v>29.2967</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>24.7985</v>
+        <v>23.1694</v>
       </c>
       <c r="C67" t="n">
-        <v>39.5392</v>
+        <v>18.5445</v>
       </c>
       <c r="D67" t="n">
-        <v>40.1726</v>
+        <v>40.1401</v>
       </c>
       <c r="E67" t="n">
-        <v>19.4835</v>
+        <v>19.7251</v>
       </c>
       <c r="F67" t="n">
-        <v>29.8278</v>
+        <v>28.9614</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>24.3981</v>
+        <v>22.7717</v>
       </c>
       <c r="C68" t="n">
-        <v>38.8802</v>
+        <v>18.3673</v>
       </c>
       <c r="D68" t="n">
-        <v>40.1715</v>
+        <v>39.9438</v>
       </c>
       <c r="E68" t="n">
-        <v>18.9949</v>
+        <v>19.1971</v>
       </c>
       <c r="F68" t="n">
-        <v>29.5116</v>
+        <v>28.7337</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>23.9581</v>
+        <v>22.3866</v>
       </c>
       <c r="C69" t="n">
-        <v>38.5758</v>
+        <v>18.2174</v>
       </c>
       <c r="D69" t="n">
-        <v>40.475</v>
+        <v>40.0688</v>
       </c>
       <c r="E69" t="n">
-        <v>18.5598</v>
+        <v>18.5423</v>
       </c>
       <c r="F69" t="n">
-        <v>29.1397</v>
+        <v>28.4231</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>23.537</v>
+        <v>21.9892</v>
       </c>
       <c r="C70" t="n">
-        <v>38.2454</v>
+        <v>18.0762</v>
       </c>
       <c r="D70" t="n">
-        <v>40.4642</v>
+        <v>40.0966</v>
       </c>
       <c r="E70" t="n">
-        <v>17.9604</v>
+        <v>17.8981</v>
       </c>
       <c r="F70" t="n">
-        <v>28.8427</v>
+        <v>28.1528</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>23.0793</v>
+        <v>21.5547</v>
       </c>
       <c r="C71" t="n">
-        <v>37.9353</v>
+        <v>17.9972</v>
       </c>
       <c r="D71" t="n">
-        <v>40.5336</v>
+        <v>40.3956</v>
       </c>
       <c r="E71" t="n">
-        <v>17.796</v>
+        <v>16.8735</v>
       </c>
       <c r="F71" t="n">
-        <v>28.9924</v>
+        <v>28.3493</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>22.5449</v>
+        <v>21.0809</v>
       </c>
       <c r="C72" t="n">
-        <v>36.3626</v>
+        <v>17.8461</v>
       </c>
       <c r="D72" t="n">
-        <v>40.5347</v>
+        <v>40.3522</v>
       </c>
       <c r="E72" t="n">
-        <v>17.4378</v>
+        <v>16.4194</v>
       </c>
       <c r="F72" t="n">
-        <v>28.7218</v>
+        <v>28.0723</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>21.9661</v>
+        <v>20.6142</v>
       </c>
       <c r="C73" t="n">
-        <v>46.5634</v>
+        <v>17.747</v>
       </c>
       <c r="D73" t="n">
-        <v>40.7337</v>
+        <v>40.5137</v>
       </c>
       <c r="E73" t="n">
-        <v>16.9797</v>
+        <v>16.0374</v>
       </c>
       <c r="F73" t="n">
-        <v>28.3568</v>
+        <v>27.7541</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>21.5434</v>
+        <v>20.1363</v>
       </c>
       <c r="C74" t="n">
-        <v>45.0506</v>
+        <v>17.6129</v>
       </c>
       <c r="D74" t="n">
-        <v>40.9405</v>
+        <v>40.5953</v>
       </c>
       <c r="E74" t="n">
-        <v>16.6379</v>
+        <v>16.233</v>
       </c>
       <c r="F74" t="n">
-        <v>27.5474</v>
+        <v>26.9354</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>21.018</v>
+        <v>19.6556</v>
       </c>
       <c r="C75" t="n">
-        <v>49.341</v>
+        <v>17.5175</v>
       </c>
       <c r="D75" t="n">
-        <v>40.6678</v>
+        <v>40.3265</v>
       </c>
       <c r="E75" t="n">
-        <v>16.3104</v>
+        <v>15.372</v>
       </c>
       <c r="F75" t="n">
-        <v>27.7196</v>
+        <v>27.1623</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>20.3884</v>
+        <v>19.1217</v>
       </c>
       <c r="C76" t="n">
-        <v>49.24</v>
+        <v>17.4289</v>
       </c>
       <c r="D76" t="n">
-        <v>40.7984</v>
+        <v>40.3276</v>
       </c>
       <c r="E76" t="n">
-        <v>16.0069</v>
+        <v>15.581</v>
       </c>
       <c r="F76" t="n">
-        <v>26.8326</v>
+        <v>26.3088</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>19.6827</v>
+        <v>18.5257</v>
       </c>
       <c r="C77" t="n">
-        <v>44.1783</v>
+        <v>17.3518</v>
       </c>
       <c r="D77" t="n">
-        <v>40.7573</v>
+        <v>40.5803</v>
       </c>
       <c r="E77" t="n">
-        <v>15.6441</v>
+        <v>15.3226</v>
       </c>
       <c r="F77" t="n">
-        <v>26.5199</v>
+        <v>25.9717</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>19.0707</v>
+        <v>18.0175</v>
       </c>
       <c r="C78" t="n">
-        <v>40.2342</v>
+        <v>17.2698</v>
       </c>
       <c r="D78" t="n">
-        <v>47.7113</v>
+        <v>47.6148</v>
       </c>
       <c r="E78" t="n">
-        <v>15.2637</v>
+        <v>15.0282</v>
       </c>
       <c r="F78" t="n">
-        <v>26.1832</v>
+        <v>25.6434</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>18.0947</v>
+        <v>17.317</v>
       </c>
       <c r="C79" t="n">
-        <v>41.1563</v>
+        <v>19.1826</v>
       </c>
       <c r="D79" t="n">
-        <v>46.637</v>
+        <v>47.5704</v>
       </c>
       <c r="E79" t="n">
-        <v>14.9546</v>
+        <v>14.0986</v>
       </c>
       <c r="F79" t="n">
-        <v>26.3568</v>
+        <v>25.7773</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>17.1725</v>
+        <v>16.5954</v>
       </c>
       <c r="C80" t="n">
-        <v>43.5658</v>
+        <v>18.9689</v>
       </c>
       <c r="D80" t="n">
-        <v>46.7636</v>
+        <v>46.4766</v>
       </c>
       <c r="E80" t="n">
-        <v>19.8751</v>
+        <v>19.0297</v>
       </c>
       <c r="F80" t="n">
-        <v>30.678</v>
+        <v>29.8955</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>24.7729</v>
+        <v>23.2629</v>
       </c>
       <c r="C81" t="n">
-        <v>38.0679</v>
+        <v>18.7464</v>
       </c>
       <c r="D81" t="n">
-        <v>46.1846</v>
+        <v>46.187</v>
       </c>
       <c r="E81" t="n">
-        <v>19.3938</v>
+        <v>18.5659</v>
       </c>
       <c r="F81" t="n">
-        <v>30.2356</v>
+        <v>29.578</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>24.498</v>
+        <v>22.8727</v>
       </c>
       <c r="C82" t="n">
-        <v>37.8147</v>
+        <v>18.5727</v>
       </c>
       <c r="D82" t="n">
-        <v>45.8033</v>
+        <v>45.7675</v>
       </c>
       <c r="E82" t="n">
-        <v>18.9958</v>
+        <v>18.6986</v>
       </c>
       <c r="F82" t="n">
-        <v>29.5245</v>
+        <v>28.7856</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>24.1218</v>
+        <v>22.5013</v>
       </c>
       <c r="C83" t="n">
-        <v>37.378</v>
+        <v>18.4165</v>
       </c>
       <c r="D83" t="n">
-        <v>45.0658</v>
+        <v>45.1114</v>
       </c>
       <c r="E83" t="n">
-        <v>18.564</v>
+        <v>18.1835</v>
       </c>
       <c r="F83" t="n">
-        <v>29.1573</v>
+        <v>28.3952</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>23.6631</v>
+        <v>22.1253</v>
       </c>
       <c r="C84" t="n">
-        <v>36.7839</v>
+        <v>18.1916</v>
       </c>
       <c r="D84" t="n">
-        <v>44.8205</v>
+        <v>44.3671</v>
       </c>
       <c r="E84" t="n">
-        <v>18.235</v>
+        <v>17.2981</v>
       </c>
       <c r="F84" t="n">
-        <v>29.268</v>
+        <v>28.382</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>23.2387</v>
+        <v>21.6998</v>
       </c>
       <c r="C85" t="n">
-        <v>36.2141</v>
+        <v>18.0837</v>
       </c>
       <c r="D85" t="n">
-        <v>44.2662</v>
+        <v>44.0648</v>
       </c>
       <c r="E85" t="n">
-        <v>17.8392</v>
+        <v>16.9904</v>
       </c>
       <c r="F85" t="n">
-        <v>28.9824</v>
+        <v>28.1605</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>22.7905</v>
+        <v>21.2388</v>
       </c>
       <c r="C86" t="n">
-        <v>35.6414</v>
+        <v>17.9331</v>
       </c>
       <c r="D86" t="n">
-        <v>44.5199</v>
+        <v>43.5787</v>
       </c>
       <c r="E86" t="n">
-        <v>17.4852</v>
+        <v>16.5549</v>
       </c>
       <c r="F86" t="n">
-        <v>28.6771</v>
+        <v>27.8912</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>22.2938</v>
+        <v>20.7184</v>
       </c>
       <c r="C87" t="n">
-        <v>41.0958</v>
+        <v>17.8254</v>
       </c>
       <c r="D87" t="n">
-        <v>43.884</v>
+        <v>42.8417</v>
       </c>
       <c r="E87" t="n">
-        <v>17.155</v>
+        <v>16.1834</v>
       </c>
       <c r="F87" t="n">
-        <v>28.4066</v>
+        <v>27.6014</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>21.6964</v>
+        <v>20.2399</v>
       </c>
       <c r="C88" t="n">
-        <v>38.4834</v>
+        <v>17.72</v>
       </c>
       <c r="D88" t="n">
-        <v>43.285</v>
+        <v>43.1535</v>
       </c>
       <c r="E88" t="n">
-        <v>16.8245</v>
+        <v>15.8834</v>
       </c>
       <c r="F88" t="n">
-        <v>28.0772</v>
+        <v>27.2888</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>21.0801</v>
+        <v>19.7075</v>
       </c>
       <c r="C89" t="n">
-        <v>43.992</v>
+        <v>17.5807</v>
       </c>
       <c r="D89" t="n">
-        <v>43.0234</v>
+        <v>42.96</v>
       </c>
       <c r="E89" t="n">
-        <v>16.5184</v>
+        <v>15.4757</v>
       </c>
       <c r="F89" t="n">
-        <v>27.7644</v>
+        <v>26.9806</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>20.5829</v>
+        <v>19.2007</v>
       </c>
       <c r="C90" t="n">
-        <v>42.4696</v>
+        <v>17.4941</v>
       </c>
       <c r="D90" t="n">
-        <v>42.8962</v>
+        <v>42.1403</v>
       </c>
       <c r="E90" t="n">
-        <v>16.1357</v>
+        <v>15.1864</v>
       </c>
       <c r="F90" t="n">
-        <v>27.4611</v>
+        <v>26.6826</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>19.9441</v>
+        <v>18.7094</v>
       </c>
       <c r="C91" t="n">
-        <v>43.2677</v>
+        <v>17.3949</v>
       </c>
       <c r="D91" t="n">
-        <v>42.6316</v>
+        <v>42.4161</v>
       </c>
       <c r="E91" t="n">
-        <v>15.802</v>
+        <v>14.8645</v>
       </c>
       <c r="F91" t="n">
-        <v>27.1273</v>
+        <v>26.369</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>19.2061</v>
+        <v>18.1886</v>
       </c>
       <c r="C92" t="n">
-        <v>35.4075</v>
+        <v>17.3105</v>
       </c>
       <c r="D92" t="n">
-        <v>48.4803</v>
+        <v>47.9311</v>
       </c>
       <c r="E92" t="n">
-        <v>15.3993</v>
+        <v>14.5938</v>
       </c>
       <c r="F92" t="n">
-        <v>26.2933</v>
+        <v>25.7144</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>18.3427</v>
+        <v>17.6503</v>
       </c>
       <c r="C93" t="n">
-        <v>42.3115</v>
+        <v>17.2144</v>
       </c>
       <c r="D93" t="n">
-        <v>48.1255</v>
+        <v>47.3067</v>
       </c>
       <c r="E93" t="n">
-        <v>15.0396</v>
+        <v>14.7523</v>
       </c>
       <c r="F93" t="n">
-        <v>25.9528</v>
+        <v>25.232</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>17.4327</v>
+        <v>16.7593</v>
       </c>
       <c r="C94" t="n">
-        <v>36.4795</v>
+        <v>18.8911</v>
       </c>
       <c r="D94" t="n">
-        <v>47.6274</v>
+        <v>47.5108</v>
       </c>
       <c r="E94" t="n">
-        <v>19.7809</v>
+        <v>19.6557</v>
       </c>
       <c r="F94" t="n">
-        <v>30.1657</v>
+        <v>29.3733</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>24.9666</v>
+        <v>23.3419</v>
       </c>
       <c r="C95" t="n">
-        <v>43.4046</v>
+        <v>18.6952</v>
       </c>
       <c r="D95" t="n">
-        <v>46.9377</v>
+        <v>46.682</v>
       </c>
       <c r="E95" t="n">
-        <v>19.2969</v>
+        <v>19.1925</v>
       </c>
       <c r="F95" t="n">
-        <v>29.8223</v>
+        <v>29.1389</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>24.5728</v>
+        <v>22.9803</v>
       </c>
       <c r="C96" t="n">
-        <v>45.9442</v>
+        <v>18.484</v>
       </c>
       <c r="D96" t="n">
-        <v>45.9897</v>
+        <v>45.9611</v>
       </c>
       <c r="E96" t="n">
-        <v>18.8623</v>
+        <v>18.7051</v>
       </c>
       <c r="F96" t="n">
-        <v>29.48</v>
+        <v>29.0456</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>24.1939</v>
+        <v>22.5912</v>
       </c>
       <c r="C97" t="n">
-        <v>36.2093</v>
+        <v>18.3987</v>
       </c>
       <c r="D97" t="n">
-        <v>45.4968</v>
+        <v>45.2926</v>
       </c>
       <c r="E97" t="n">
-        <v>18.4648</v>
+        <v>18.2747</v>
       </c>
       <c r="F97" t="n">
-        <v>29.134</v>
+        <v>28.4951</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>23.7915</v>
+        <v>22.1761</v>
       </c>
       <c r="C98" t="n">
-        <v>35.7504</v>
+        <v>18.2393</v>
       </c>
       <c r="D98" t="n">
-        <v>44.8651</v>
+        <v>44.7372</v>
       </c>
       <c r="E98" t="n">
-        <v>18.0868</v>
+        <v>17.8038</v>
       </c>
       <c r="F98" t="n">
-        <v>29.1044</v>
+        <v>28.1309</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>23.3405</v>
+        <v>21.7488</v>
       </c>
       <c r="C99" t="n">
-        <v>35.2682</v>
+        <v>18.0331</v>
       </c>
       <c r="D99" t="n">
-        <v>44.8137</v>
+        <v>44.2357</v>
       </c>
       <c r="E99" t="n">
-        <v>17.7023</v>
+        <v>17.5453</v>
       </c>
       <c r="F99" t="n">
-        <v>28.7723</v>
+        <v>27.8615</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>22.8547</v>
+        <v>21.2723</v>
       </c>
       <c r="C100" t="n">
-        <v>34.7828</v>
+        <v>17.9461</v>
       </c>
       <c r="D100" t="n">
-        <v>43.8497</v>
+        <v>43.7461</v>
       </c>
       <c r="E100" t="n">
-        <v>17.3846</v>
+        <v>17.0357</v>
       </c>
       <c r="F100" t="n">
-        <v>28.2088</v>
+        <v>27.568</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>22.3505</v>
+        <v>20.8266</v>
       </c>
       <c r="C101" t="n">
-        <v>41.2985</v>
+        <v>17.8257</v>
       </c>
       <c r="D101" t="n">
-        <v>43.6172</v>
+        <v>43.4296</v>
       </c>
       <c r="E101" t="n">
-        <v>17.0743</v>
+        <v>16.6828</v>
       </c>
       <c r="F101" t="n">
-        <v>27.9611</v>
+        <v>27.3069</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>21.8716</v>
+        <v>20.3481</v>
       </c>
       <c r="C102" t="n">
-        <v>48.8424</v>
+        <v>17.6867</v>
       </c>
       <c r="D102" t="n">
-        <v>43.0829</v>
+        <v>43.0619</v>
       </c>
       <c r="E102" t="n">
-        <v>16.8578</v>
+        <v>15.926</v>
       </c>
       <c r="F102" t="n">
-        <v>27.9836</v>
+        <v>27.4135</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>21.3341</v>
+        <v>19.8979</v>
       </c>
       <c r="C103" t="n">
-        <v>43.8491</v>
+        <v>17.5798</v>
       </c>
       <c r="D103" t="n">
-        <v>42.6893</v>
+        <v>42.6634</v>
       </c>
       <c r="E103" t="n">
-        <v>16.5543</v>
+        <v>16.0969</v>
       </c>
       <c r="F103" t="n">
-        <v>27.2342</v>
+        <v>26.6873</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>20.7362</v>
+        <v>19.3496</v>
       </c>
       <c r="C104" t="n">
-        <v>39.2879</v>
+        <v>17.5009</v>
       </c>
       <c r="D104" t="n">
-        <v>42.5543</v>
+        <v>42.0305</v>
       </c>
       <c r="E104" t="n">
-        <v>16.067</v>
+        <v>15.8111</v>
       </c>
       <c r="F104" t="n">
-        <v>26.9126</v>
+        <v>26.3562</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>20.0587</v>
+        <v>18.843</v>
       </c>
       <c r="C105" t="n">
-        <v>38.6168</v>
+        <v>17.3964</v>
       </c>
       <c r="D105" t="n">
-        <v>42.2223</v>
+        <v>41.7991</v>
       </c>
       <c r="E105" t="n">
-        <v>15.7065</v>
+        <v>15.4477</v>
       </c>
       <c r="F105" t="n">
-        <v>26.5732</v>
+        <v>26.0475</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>19.4144</v>
+        <v>18.2432</v>
       </c>
       <c r="C106" t="n">
-        <v>41.6184</v>
+        <v>17.3225</v>
       </c>
       <c r="D106" t="n">
-        <v>41.6851</v>
+        <v>41.6231</v>
       </c>
       <c r="E106" t="n">
-        <v>15.4296</v>
+        <v>15.1481</v>
       </c>
       <c r="F106" t="n">
-        <v>26.2862</v>
+        <v>25.7139</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>18.645</v>
+        <v>17.649</v>
       </c>
       <c r="C107" t="n">
-        <v>41.1232</v>
+        <v>17.2269</v>
       </c>
       <c r="D107" t="n">
-        <v>45.7117</v>
+        <v>44.9042</v>
       </c>
       <c r="E107" t="n">
-        <v>15.1173</v>
+        <v>14.83</v>
       </c>
       <c r="F107" t="n">
-        <v>25.9159</v>
+        <v>25.326</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>17.73</v>
+        <v>16.9921</v>
       </c>
       <c r="C108" t="n">
-        <v>39.7261</v>
+        <v>18.9325</v>
       </c>
       <c r="D108" t="n">
-        <v>45.0375</v>
+        <v>44.885</v>
       </c>
       <c r="E108" t="n">
-        <v>19.941</v>
+        <v>19.7326</v>
       </c>
       <c r="F108" t="n">
-        <v>30.284</v>
+        <v>29.4285</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>16.5706</v>
+        <v>16.1787</v>
       </c>
       <c r="C109" t="n">
-        <v>34.5568</v>
+        <v>18.7486</v>
       </c>
       <c r="D109" t="n">
-        <v>44.604</v>
+        <v>44.1365</v>
       </c>
       <c r="E109" t="n">
-        <v>19.477</v>
+        <v>19.2067</v>
       </c>
       <c r="F109" t="n">
-        <v>29.8372</v>
+        <v>29.1021</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>24.6493</v>
+        <v>23.0641</v>
       </c>
       <c r="C110" t="n">
-        <v>47.3106</v>
+        <v>18.6088</v>
       </c>
       <c r="D110" t="n">
-        <v>44.1602</v>
+        <v>43.7129</v>
       </c>
       <c r="E110" t="n">
-        <v>19.0662</v>
+        <v>18.832</v>
       </c>
       <c r="F110" t="n">
-        <v>29.4317</v>
+        <v>28.8322</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>24.3087</v>
+        <v>22.6802</v>
       </c>
       <c r="C111" t="n">
-        <v>47.1031</v>
+        <v>18.4377</v>
       </c>
       <c r="D111" t="n">
-        <v>43.7971</v>
+        <v>43.6402</v>
       </c>
       <c r="E111" t="n">
-        <v>18.7691</v>
+        <v>17.909</v>
       </c>
       <c r="F111" t="n">
-        <v>29.6169</v>
+        <v>28.8938</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>23.9121</v>
+        <v>22.2827</v>
       </c>
       <c r="C112" t="n">
-        <v>46.7761</v>
+        <v>18.2658</v>
       </c>
       <c r="D112" t="n">
-        <v>43.3579</v>
+        <v>43.1177</v>
       </c>
       <c r="E112" t="n">
-        <v>18.4003</v>
+        <v>17.4786</v>
       </c>
       <c r="F112" t="n">
-        <v>29.3137</v>
+        <v>28.5629</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>23.4407</v>
+        <v>21.8459</v>
       </c>
       <c r="C113" t="n">
-        <v>46.3358</v>
+        <v>18.1407</v>
       </c>
       <c r="D113" t="n">
-        <v>42.8394</v>
+        <v>42.5585</v>
       </c>
       <c r="E113" t="n">
-        <v>17.8656</v>
+        <v>17.4347</v>
       </c>
       <c r="F113" t="n">
-        <v>28.4405</v>
+        <v>27.9016</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>22.9575</v>
+        <v>21.399</v>
       </c>
       <c r="C114" t="n">
-        <v>45.9384</v>
+        <v>17.9822</v>
       </c>
       <c r="D114" t="n">
-        <v>42.3028</v>
+        <v>42.1495</v>
       </c>
       <c r="E114" t="n">
-        <v>17.449</v>
+        <v>17.0921</v>
       </c>
       <c r="F114" t="n">
-        <v>28.3465</v>
+        <v>27.6085</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>22.4449</v>
+        <v>20.9195</v>
       </c>
       <c r="C115" t="n">
-        <v>44.928</v>
+        <v>17.8807</v>
       </c>
       <c r="D115" t="n">
-        <v>42.462</v>
+        <v>41.9272</v>
       </c>
       <c r="E115" t="n">
-        <v>17.1134</v>
+        <v>16.7606</v>
       </c>
       <c r="F115" t="n">
-        <v>28.0643</v>
+        <v>27.3377</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>21.9173</v>
+        <v>20.4481</v>
       </c>
       <c r="C116" t="n">
-        <v>46.0291</v>
+        <v>17.7573</v>
       </c>
       <c r="D116" t="n">
-        <v>42.1717</v>
+        <v>41.5845</v>
       </c>
       <c r="E116" t="n">
-        <v>16.7985</v>
+        <v>16.4489</v>
       </c>
       <c r="F116" t="n">
-        <v>27.7308</v>
+        <v>27.0226</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>21.4298</v>
+        <v>19.9611</v>
       </c>
       <c r="C117" t="n">
-        <v>33.6264</v>
+        <v>17.6255</v>
       </c>
       <c r="D117" t="n">
-        <v>41.4614</v>
+        <v>41.4676</v>
       </c>
       <c r="E117" t="n">
-        <v>16.464</v>
+        <v>16.1411</v>
       </c>
       <c r="F117" t="n">
-        <v>27.2688</v>
+        <v>26.702</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>20.83</v>
+        <v>19.4453</v>
       </c>
       <c r="C118" t="n">
-        <v>43.1671</v>
+        <v>17.4923</v>
       </c>
       <c r="D118" t="n">
-        <v>40.8368</v>
+        <v>41.3421</v>
       </c>
       <c r="E118" t="n">
-        <v>16.133</v>
+        <v>15.8204</v>
       </c>
       <c r="F118" t="n">
-        <v>27.1081</v>
+        <v>26.402</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>20.2286</v>
+        <v>18.9764</v>
       </c>
       <c r="C119" t="n">
-        <v>44.0286</v>
+        <v>17.4248</v>
       </c>
       <c r="D119" t="n">
-        <v>40.6895</v>
+        <v>41.0816</v>
       </c>
       <c r="E119" t="n">
-        <v>15.8211</v>
+        <v>15.5107</v>
       </c>
       <c r="F119" t="n">
-        <v>26.7287</v>
+        <v>26.0845</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>19.5705</v>
+        <v>18.4145</v>
       </c>
       <c r="C120" t="n">
-        <v>43.4949</v>
+        <v>17.3335</v>
       </c>
       <c r="D120" t="n">
-        <v>40.5487</v>
+        <v>40.8797</v>
       </c>
       <c r="E120" t="n">
-        <v>15.5225</v>
+        <v>15.173</v>
       </c>
       <c r="F120" t="n">
-        <v>26.3722</v>
+        <v>25.7178</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>18.8434</v>
+        <v>17.8342</v>
       </c>
       <c r="C121" t="n">
-        <v>39.0923</v>
+        <v>17.2716</v>
       </c>
       <c r="D121" t="n">
-        <v>49.2164</v>
+        <v>47.8076</v>
       </c>
       <c r="E121" t="n">
-        <v>15.1968</v>
+        <v>14.8429</v>
       </c>
       <c r="F121" t="n">
-        <v>25.9225</v>
+        <v>25.3421</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>17.8388</v>
+        <v>17.1897</v>
       </c>
       <c r="C122" t="n">
-        <v>33.4795</v>
+        <v>18.9638</v>
       </c>
       <c r="D122" t="n">
-        <v>47.7135</v>
+        <v>47.3333</v>
       </c>
       <c r="E122" t="n">
-        <v>14.8866</v>
+        <v>14.4645</v>
       </c>
       <c r="F122" t="n">
-        <v>25.6542</v>
+        <v>25.0195</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>16.9398</v>
+        <v>16.4236</v>
       </c>
       <c r="C123" t="n">
-        <v>35.4697</v>
+        <v>18.7536</v>
       </c>
       <c r="D123" t="n">
-        <v>47.2358</v>
+        <v>46.8136</v>
       </c>
       <c r="E123" t="n">
-        <v>19.6585</v>
+        <v>18.8937</v>
       </c>
       <c r="F123" t="n">
-        <v>30.3674</v>
+        <v>29.5792</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>24.6935</v>
+        <v>23.1596</v>
       </c>
       <c r="C124" t="n">
-        <v>49.9706</v>
+        <v>18.5812</v>
       </c>
       <c r="D124" t="n">
-        <v>46.6411</v>
+        <v>46.3622</v>
       </c>
       <c r="E124" t="n">
-        <v>19.2058</v>
+        <v>18.4092</v>
       </c>
       <c r="F124" t="n">
-        <v>30.036</v>
+        <v>29.2384</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>24.3612</v>
+        <v>22.7995</v>
       </c>
       <c r="C125" t="n">
-        <v>38.4729</v>
+        <v>18.3855</v>
       </c>
       <c r="D125" t="n">
-        <v>46.338</v>
+        <v>45.991</v>
       </c>
       <c r="E125" t="n">
-        <v>18.8093</v>
+        <v>17.9795</v>
       </c>
       <c r="F125" t="n">
-        <v>29.5232</v>
+        <v>29.1089</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>23.9507</v>
+        <v>22.4251</v>
       </c>
       <c r="C126" t="n">
-        <v>46.3768</v>
+        <v>18.245</v>
       </c>
       <c r="D126" t="n">
-        <v>45.8176</v>
+        <v>45.7547</v>
       </c>
       <c r="E126" t="n">
-        <v>18.4147</v>
+        <v>17.5476</v>
       </c>
       <c r="F126" t="n">
-        <v>29.3357</v>
+        <v>28.5446</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>23.4916</v>
+        <v>21.9481</v>
       </c>
       <c r="C127" t="n">
-        <v>39.9525</v>
+        <v>18.0963</v>
       </c>
       <c r="D127" t="n">
-        <v>44.7338</v>
+        <v>44.816</v>
       </c>
       <c r="E127" t="n">
-        <v>18.05</v>
+        <v>17.1661</v>
       </c>
       <c r="F127" t="n">
-        <v>28.9398</v>
+        <v>28.1473</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>22.9943</v>
+        <v>21.5009</v>
       </c>
       <c r="C128" t="n">
-        <v>52.4676</v>
+        <v>17.951</v>
       </c>
       <c r="D128" t="n">
-        <v>44.1402</v>
+        <v>44.5159</v>
       </c>
       <c r="E128" t="n">
-        <v>17.6843</v>
+        <v>16.7798</v>
       </c>
       <c r="F128" t="n">
-        <v>28.6539</v>
+        <v>27.9444</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>22.5479</v>
+        <v>21.0077</v>
       </c>
       <c r="C129" t="n">
-        <v>38.9497</v>
+        <v>17.8372</v>
       </c>
       <c r="D129" t="n">
-        <v>44.0648</v>
+        <v>43.7455</v>
       </c>
       <c r="E129" t="n">
-        <v>17.3302</v>
+        <v>16.4425</v>
       </c>
       <c r="F129" t="n">
-        <v>28.2447</v>
+        <v>27.8001</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>22.0373</v>
+        <v>20.5275</v>
       </c>
       <c r="C130" t="n">
-        <v>40.1513</v>
+        <v>17.7401</v>
       </c>
       <c r="D130" t="n">
-        <v>43.606</v>
+        <v>43.3611</v>
       </c>
       <c r="E130" t="n">
-        <v>17.0439</v>
+        <v>16.0818</v>
       </c>
       <c r="F130" t="n">
-        <v>27.9897</v>
+        <v>27.5256</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>21.4737</v>
+        <v>20.0371</v>
       </c>
       <c r="C131" t="n">
-        <v>44.7993</v>
+        <v>17.6364</v>
       </c>
       <c r="D131" t="n">
-        <v>43.2044</v>
+        <v>42.8893</v>
       </c>
       <c r="E131" t="n">
-        <v>16.7075</v>
+        <v>15.7487</v>
       </c>
       <c r="F131" t="n">
-        <v>27.6738</v>
+        <v>27.2262</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>20.9603</v>
+        <v>19.5951</v>
       </c>
       <c r="C132" t="n">
-        <v>46.5666</v>
+        <v>17.5264</v>
       </c>
       <c r="D132" t="n">
-        <v>42.8387</v>
+        <v>42.3679</v>
       </c>
       <c r="E132" t="n">
-        <v>16.4042</v>
+        <v>15.4119</v>
       </c>
       <c r="F132" t="n">
-        <v>27.5071</v>
+        <v>26.9278</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>20.385</v>
+        <v>19.0369</v>
       </c>
       <c r="C133" t="n">
-        <v>41.7332</v>
+        <v>17.4251</v>
       </c>
       <c r="D133" t="n">
-        <v>42.3428</v>
+        <v>42.0208</v>
       </c>
       <c r="E133" t="n">
-        <v>16.016</v>
+        <v>15.0771</v>
       </c>
       <c r="F133" t="n">
-        <v>27.1476</v>
+        <v>26.6198</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>19.7507</v>
+        <v>18.4999</v>
       </c>
       <c r="C134" t="n">
-        <v>40.8705</v>
+        <v>17.3471</v>
       </c>
       <c r="D134" t="n">
-        <v>41.9811</v>
+        <v>41.5718</v>
       </c>
       <c r="E134" t="n">
-        <v>15.5362</v>
+        <v>15.2567</v>
       </c>
       <c r="F134" t="n">
-        <v>26.3644</v>
+        <v>25.8225</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>19.006</v>
+        <v>17.9527</v>
       </c>
       <c r="C135" t="n">
-        <v>44.7118</v>
+        <v>17.2782</v>
       </c>
       <c r="D135" t="n">
-        <v>49.3347</v>
+        <v>49.6665</v>
       </c>
       <c r="E135" t="n">
-        <v>15.2287</v>
+        <v>14.9431</v>
       </c>
       <c r="F135" t="n">
-        <v>26.1137</v>
+        <v>25.4938</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>18.1019</v>
+        <v>17.3149</v>
       </c>
       <c r="C136" t="n">
-        <v>42.9698</v>
+        <v>19.0147</v>
       </c>
       <c r="D136" t="n">
-        <v>48.754</v>
+        <v>49.0351</v>
       </c>
       <c r="E136" t="n">
-        <v>14.9431</v>
+        <v>14.5584</v>
       </c>
       <c r="F136" t="n">
-        <v>25.6994</v>
+        <v>25.1494</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>17.0961</v>
+        <v>16.5964</v>
       </c>
       <c r="C137" t="n">
-        <v>41.4858</v>
+        <v>18.8053</v>
       </c>
       <c r="D137" t="n">
-        <v>48.4306</v>
+        <v>47.348</v>
       </c>
       <c r="E137" t="n">
-        <v>19.7482</v>
+        <v>19.1009</v>
       </c>
       <c r="F137" t="n">
-        <v>29.8856</v>
+        <v>29.218</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>24.7895</v>
+        <v>23.2116</v>
       </c>
       <c r="C138" t="n">
-        <v>51.4396</v>
+        <v>18.6362</v>
       </c>
       <c r="D138" t="n">
-        <v>47.2498</v>
+        <v>47.6538</v>
       </c>
       <c r="E138" t="n">
-        <v>19.3092</v>
+        <v>18.6246</v>
       </c>
       <c r="F138" t="n">
-        <v>29.5197</v>
+        <v>28.9491</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>24.4365</v>
+        <v>22.8789</v>
       </c>
       <c r="C139" t="n">
-        <v>49.8608</v>
+        <v>18.4567</v>
       </c>
       <c r="D139" t="n">
-        <v>46.6299</v>
+        <v>46.8022</v>
       </c>
       <c r="E139" t="n">
-        <v>18.9007</v>
+        <v>18.2141</v>
       </c>
       <c r="F139" t="n">
-        <v>29.2037</v>
+        <v>28.6203</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>24.0389</v>
+        <v>22.4539</v>
       </c>
       <c r="C140" t="n">
-        <v>40.4231</v>
+        <v>18.2888</v>
       </c>
       <c r="D140" t="n">
-        <v>45.9415</v>
+        <v>46.2852</v>
       </c>
       <c r="E140" t="n">
-        <v>18.4768</v>
+        <v>17.5789</v>
       </c>
       <c r="F140" t="n">
-        <v>29.1965</v>
+        <v>28.4348</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>23.6121</v>
+        <v>22.0076</v>
       </c>
       <c r="C141" t="n">
-        <v>44.7031</v>
+        <v>18.1356</v>
       </c>
       <c r="D141" t="n">
-        <v>45.3649</v>
+        <v>45.5134</v>
       </c>
       <c r="E141" t="n">
-        <v>18.1169</v>
+        <v>17.2011</v>
       </c>
       <c r="F141" t="n">
-        <v>28.7669</v>
+        <v>28.0058</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>23.143</v>
+        <v>21.5668</v>
       </c>
       <c r="C142" t="n">
-        <v>51.5054</v>
+        <v>18.0042</v>
       </c>
       <c r="D142" t="n">
-        <v>44.8422</v>
+        <v>45.0897</v>
       </c>
       <c r="E142" t="n">
-        <v>17.7571</v>
+        <v>16.8171</v>
       </c>
       <c r="F142" t="n">
-        <v>28.5487</v>
+        <v>27.7835</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>22.6567</v>
+        <v>21.1124</v>
       </c>
       <c r="C143" t="n">
-        <v>49.8344</v>
+        <v>17.8607</v>
       </c>
       <c r="D143" t="n">
-        <v>44.3619</v>
+        <v>44.2488</v>
       </c>
       <c r="E143" t="n">
-        <v>17.3911</v>
+        <v>16.4441</v>
       </c>
       <c r="F143" t="n">
-        <v>28.4385</v>
+        <v>27.525</v>
       </c>
     </row>
   </sheetData>

--- a/clang-x64/Running erasure.xlsx
+++ b/clang-x64/Running erasure.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>18.5266</v>
+        <v>18.3565</v>
       </c>
       <c r="C2" t="n">
-        <v>13.1055</v>
+        <v>13.1645</v>
       </c>
       <c r="D2" t="n">
-        <v>30.2619</v>
+        <v>29.8558</v>
       </c>
       <c r="E2" t="n">
-        <v>13.1217</v>
+        <v>13.0541</v>
       </c>
       <c r="F2" t="n">
-        <v>25.6374</v>
+        <v>25.6326</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>18.1931</v>
+        <v>18.1416</v>
       </c>
       <c r="C3" t="n">
-        <v>13.2656</v>
+        <v>13.2216</v>
       </c>
       <c r="D3" t="n">
-        <v>30.1165</v>
+        <v>30.0601</v>
       </c>
       <c r="E3" t="n">
-        <v>12.8569</v>
+        <v>12.9403</v>
       </c>
       <c r="F3" t="n">
-        <v>25.2785</v>
+        <v>25.4452</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>17.6757</v>
+        <v>17.5619</v>
       </c>
       <c r="C4" t="n">
-        <v>13.5074</v>
+        <v>13.4295</v>
       </c>
       <c r="D4" t="n">
-        <v>30.195</v>
+        <v>30.2483</v>
       </c>
       <c r="E4" t="n">
-        <v>12.7148</v>
+        <v>12.7755</v>
       </c>
       <c r="F4" t="n">
-        <v>25.1563</v>
+        <v>25.1504</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>17.0368</v>
+        <v>17.1037</v>
       </c>
       <c r="C5" t="n">
-        <v>13.5266</v>
+        <v>13.5375</v>
       </c>
       <c r="D5" t="n">
-        <v>30.3464</v>
+        <v>30.3997</v>
       </c>
       <c r="E5" t="n">
-        <v>12.4555</v>
+        <v>12.3853</v>
       </c>
       <c r="F5" t="n">
-        <v>25.35</v>
+        <v>25.2698</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>16.6517</v>
+        <v>16.6607</v>
       </c>
       <c r="C6" t="n">
-        <v>13.8428</v>
+        <v>13.8019</v>
       </c>
       <c r="D6" t="n">
-        <v>30.4589</v>
+        <v>30.3702</v>
       </c>
       <c r="E6" t="n">
-        <v>12.5271</v>
+        <v>12.5602</v>
       </c>
       <c r="F6" t="n">
-        <v>25.1931</v>
+        <v>25.3383</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>16.3016</v>
+        <v>16.0268</v>
       </c>
       <c r="C7" t="n">
-        <v>14.0699</v>
+        <v>14.0108</v>
       </c>
       <c r="D7" t="n">
-        <v>29.5601</v>
+        <v>29.5475</v>
       </c>
       <c r="E7" t="n">
-        <v>12.2662</v>
+        <v>19.3719</v>
       </c>
       <c r="F7" t="n">
-        <v>24.5536</v>
+        <v>30.1791</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>15.5684</v>
+        <v>15.7683</v>
       </c>
       <c r="C8" t="n">
-        <v>15.4189</v>
+        <v>15.4346</v>
       </c>
       <c r="D8" t="n">
-        <v>29.6183</v>
+        <v>29.7138</v>
       </c>
       <c r="E8" t="n">
-        <v>12.0498</v>
+        <v>18.5584</v>
       </c>
       <c r="F8" t="n">
-        <v>24.2031</v>
+        <v>29.7722</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>14.7887</v>
+        <v>15.1549</v>
       </c>
       <c r="C9" t="n">
-        <v>15.7656</v>
+        <v>15.6645</v>
       </c>
       <c r="D9" t="n">
-        <v>29.9021</v>
+        <v>29.7378</v>
       </c>
       <c r="E9" t="n">
-        <v>18.4382</v>
+        <v>18.2995</v>
       </c>
       <c r="F9" t="n">
-        <v>29.5488</v>
+        <v>29.5554</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>21.7807</v>
+        <v>21.6547</v>
       </c>
       <c r="C10" t="n">
-        <v>15.7179</v>
+        <v>15.6912</v>
       </c>
       <c r="D10" t="n">
-        <v>29.7395</v>
+        <v>29.8229</v>
       </c>
       <c r="E10" t="n">
-        <v>18.0268</v>
+        <v>17.9449</v>
       </c>
       <c r="F10" t="n">
-        <v>29.1318</v>
+        <v>29.1289</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>21.4945</v>
+        <v>21.3898</v>
       </c>
       <c r="C11" t="n">
-        <v>15.8651</v>
+        <v>15.7893</v>
       </c>
       <c r="D11" t="n">
-        <v>29.8883</v>
+        <v>29.9437</v>
       </c>
       <c r="E11" t="n">
-        <v>17.6289</v>
+        <v>17.4105</v>
       </c>
       <c r="F11" t="n">
-        <v>28.8941</v>
+        <v>28.9758</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>21.1568</v>
+        <v>21.105</v>
       </c>
       <c r="C12" t="n">
-        <v>15.9127</v>
+        <v>15.9422</v>
       </c>
       <c r="D12" t="n">
-        <v>30.0416</v>
+        <v>30.0244</v>
       </c>
       <c r="E12" t="n">
-        <v>17.2482</v>
+        <v>17.1416</v>
       </c>
       <c r="F12" t="n">
-        <v>28.6649</v>
+        <v>28.6708</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>20.9473</v>
+        <v>20.9606</v>
       </c>
       <c r="C13" t="n">
-        <v>16.0652</v>
+        <v>16.0807</v>
       </c>
       <c r="D13" t="n">
-        <v>30.2872</v>
+        <v>30.1545</v>
       </c>
       <c r="E13" t="n">
-        <v>16.8849</v>
+        <v>16.8854</v>
       </c>
       <c r="F13" t="n">
-        <v>28.4705</v>
+        <v>28.5868</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>20.605</v>
+        <v>20.5226</v>
       </c>
       <c r="C14" t="n">
-        <v>16.2579</v>
+        <v>16.2731</v>
       </c>
       <c r="D14" t="n">
-        <v>30.3586</v>
+        <v>30.2434</v>
       </c>
       <c r="E14" t="n">
-        <v>16.5701</v>
+        <v>16.6475</v>
       </c>
       <c r="F14" t="n">
-        <v>28.1005</v>
+        <v>27.9213</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>20.1682</v>
+        <v>20.1913</v>
       </c>
       <c r="C15" t="n">
-        <v>16.3702</v>
+        <v>16.186</v>
       </c>
       <c r="D15" t="n">
-        <v>30.4251</v>
+        <v>30.2854</v>
       </c>
       <c r="E15" t="n">
-        <v>16.2367</v>
+        <v>16.3286</v>
       </c>
       <c r="F15" t="n">
-        <v>27.5718</v>
+        <v>27.5622</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>19.7026</v>
+        <v>19.8475</v>
       </c>
       <c r="C16" t="n">
-        <v>16.3802</v>
+        <v>16.317</v>
       </c>
       <c r="D16" t="n">
-        <v>30.4895</v>
+        <v>30.4054</v>
       </c>
       <c r="E16" t="n">
-        <v>16.0252</v>
+        <v>15.9633</v>
       </c>
       <c r="F16" t="n">
-        <v>27.2569</v>
+        <v>27.0622</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>19.3109</v>
+        <v>19.3034</v>
       </c>
       <c r="C17" t="n">
-        <v>16.1891</v>
+        <v>16.2672</v>
       </c>
       <c r="D17" t="n">
-        <v>30.7255</v>
+        <v>30.6716</v>
       </c>
       <c r="E17" t="n">
-        <v>15.7027</v>
+        <v>15.6559</v>
       </c>
       <c r="F17" t="n">
-        <v>26.8071</v>
+        <v>26.8119</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>18.9883</v>
+        <v>18.9116</v>
       </c>
       <c r="C18" t="n">
-        <v>16.1969</v>
+        <v>16.3177</v>
       </c>
       <c r="D18" t="n">
-        <v>31.0906</v>
+        <v>30.8793</v>
       </c>
       <c r="E18" t="n">
-        <v>15.385</v>
+        <v>15.4516</v>
       </c>
       <c r="F18" t="n">
-        <v>26.5378</v>
+        <v>26.5299</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>18.3766</v>
+        <v>18.4012</v>
       </c>
       <c r="C19" t="n">
-        <v>16.4034</v>
+        <v>16.4507</v>
       </c>
       <c r="D19" t="n">
-        <v>31.1306</v>
+        <v>30.9599</v>
       </c>
       <c r="E19" t="n">
-        <v>15.0789</v>
+        <v>15.0455</v>
       </c>
       <c r="F19" t="n">
-        <v>26.2087</v>
+        <v>26.144</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>17.9047</v>
+        <v>17.8758</v>
       </c>
       <c r="C20" t="n">
-        <v>16.2757</v>
+        <v>16.209</v>
       </c>
       <c r="D20" t="n">
-        <v>31.2015</v>
+        <v>31.0737</v>
       </c>
       <c r="E20" t="n">
-        <v>14.6512</v>
+        <v>14.6414</v>
       </c>
       <c r="F20" t="n">
-        <v>25.8341</v>
+        <v>25.8434</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>17.3469</v>
+        <v>17.3178</v>
       </c>
       <c r="C21" t="n">
-        <v>16.1979</v>
+        <v>16.2159</v>
       </c>
       <c r="D21" t="n">
-        <v>30.3837</v>
+        <v>30.2988</v>
       </c>
       <c r="E21" t="n">
-        <v>14.3342</v>
+        <v>20.4899</v>
       </c>
       <c r="F21" t="n">
-        <v>25.4318</v>
+        <v>30.8193</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>16.68</v>
+        <v>16.6635</v>
       </c>
       <c r="C22" t="n">
-        <v>17.7673</v>
+        <v>17.6437</v>
       </c>
       <c r="D22" t="n">
-        <v>30.3446</v>
+        <v>30.0183</v>
       </c>
       <c r="E22" t="n">
-        <v>14.1177</v>
+        <v>19.9819</v>
       </c>
       <c r="F22" t="n">
-        <v>25.007</v>
+        <v>30.3746</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>15.9901</v>
+        <v>16.0141</v>
       </c>
       <c r="C23" t="n">
-        <v>17.7015</v>
+        <v>17.6274</v>
       </c>
       <c r="D23" t="n">
-        <v>30.4306</v>
+        <v>30.1593</v>
       </c>
       <c r="E23" t="n">
-        <v>19.5399</v>
+        <v>19.4704</v>
       </c>
       <c r="F23" t="n">
-        <v>30.1937</v>
+        <v>30.1025</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>22.573</v>
+        <v>22.527</v>
       </c>
       <c r="C24" t="n">
-        <v>17.5247</v>
+        <v>17.4965</v>
       </c>
       <c r="D24" t="n">
-        <v>30.5516</v>
+        <v>30.1786</v>
       </c>
       <c r="E24" t="n">
-        <v>19.0629</v>
+        <v>18.9964</v>
       </c>
       <c r="F24" t="n">
-        <v>29.832</v>
+        <v>29.8042</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>22.297</v>
+        <v>22.2712</v>
       </c>
       <c r="C25" t="n">
-        <v>17.4877</v>
+        <v>17.3882</v>
       </c>
       <c r="D25" t="n">
-        <v>30.5299</v>
+        <v>30.4941</v>
       </c>
       <c r="E25" t="n">
-        <v>18.6069</v>
+        <v>18.6233</v>
       </c>
       <c r="F25" t="n">
-        <v>29.4686</v>
+        <v>29.3626</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>21.9512</v>
+        <v>21.9002</v>
       </c>
       <c r="C26" t="n">
-        <v>17.3865</v>
+        <v>17.3812</v>
       </c>
       <c r="D26" t="n">
-        <v>30.6075</v>
+        <v>30.4738</v>
       </c>
       <c r="E26" t="n">
-        <v>18.1431</v>
+        <v>18.3502</v>
       </c>
       <c r="F26" t="n">
-        <v>29.1188</v>
+        <v>28.9463</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>21.4993</v>
+        <v>21.6332</v>
       </c>
       <c r="C27" t="n">
-        <v>17.2972</v>
+        <v>17.2121</v>
       </c>
       <c r="D27" t="n">
-        <v>30.5014</v>
+        <v>30.4826</v>
       </c>
       <c r="E27" t="n">
-        <v>17.754</v>
+        <v>17.6591</v>
       </c>
       <c r="F27" t="n">
-        <v>28.8316</v>
+        <v>28.6544</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>21.1875</v>
+        <v>21.2788</v>
       </c>
       <c r="C28" t="n">
-        <v>17.1972</v>
+        <v>17.175</v>
       </c>
       <c r="D28" t="n">
-        <v>30.6606</v>
+        <v>30.5915</v>
       </c>
       <c r="E28" t="n">
-        <v>17.3289</v>
+        <v>17.3568</v>
       </c>
       <c r="F28" t="n">
-        <v>28.3852</v>
+        <v>28.1722</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>20.8189</v>
+        <v>20.7753</v>
       </c>
       <c r="C29" t="n">
-        <v>17.1244</v>
+        <v>17.1852</v>
       </c>
       <c r="D29" t="n">
-        <v>30.6915</v>
+        <v>30.6904</v>
       </c>
       <c r="E29" t="n">
-        <v>17.0486</v>
+        <v>16.9445</v>
       </c>
       <c r="F29" t="n">
-        <v>27.9299</v>
+        <v>27.9261</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>20.5004</v>
+        <v>20.4481</v>
       </c>
       <c r="C30" t="n">
-        <v>17.166</v>
+        <v>17.1081</v>
       </c>
       <c r="D30" t="n">
-        <v>30.6852</v>
+        <v>30.6246</v>
       </c>
       <c r="E30" t="n">
-        <v>16.5969</v>
+        <v>16.6104</v>
       </c>
       <c r="F30" t="n">
-        <v>27.7494</v>
+        <v>27.7002</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>19.9706</v>
+        <v>20.0151</v>
       </c>
       <c r="C31" t="n">
-        <v>17.0386</v>
+        <v>17.1522</v>
       </c>
       <c r="D31" t="n">
-        <v>30.6745</v>
+        <v>30.7591</v>
       </c>
       <c r="E31" t="n">
-        <v>16.2905</v>
+        <v>16.2422</v>
       </c>
       <c r="F31" t="n">
-        <v>27.3035</v>
+        <v>27.2466</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>19.4146</v>
+        <v>19.4693</v>
       </c>
       <c r="C32" t="n">
-        <v>17.0077</v>
+        <v>16.9839</v>
       </c>
       <c r="D32" t="n">
-        <v>30.8208</v>
+        <v>30.839</v>
       </c>
       <c r="E32" t="n">
-        <v>15.9323</v>
+        <v>15.8859</v>
       </c>
       <c r="F32" t="n">
-        <v>26.9116</v>
+        <v>26.8389</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>18.8764</v>
+        <v>18.9378</v>
       </c>
       <c r="C33" t="n">
-        <v>16.8794</v>
+        <v>16.9271</v>
       </c>
       <c r="D33" t="n">
-        <v>31.0864</v>
+        <v>31.0605</v>
       </c>
       <c r="E33" t="n">
-        <v>15.5704</v>
+        <v>15.6105</v>
       </c>
       <c r="F33" t="n">
-        <v>26.5251</v>
+        <v>26.5591</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>18.4646</v>
+        <v>18.4565</v>
       </c>
       <c r="C34" t="n">
-        <v>16.8893</v>
+        <v>16.8471</v>
       </c>
       <c r="D34" t="n">
-        <v>31.2353</v>
+        <v>31.2876</v>
       </c>
       <c r="E34" t="n">
-        <v>15.2594</v>
+        <v>15.255</v>
       </c>
       <c r="F34" t="n">
-        <v>26.1973</v>
+        <v>26.2249</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>17.8831</v>
+        <v>17.8665</v>
       </c>
       <c r="C35" t="n">
-        <v>16.8495</v>
+        <v>16.8098</v>
       </c>
       <c r="D35" t="n">
-        <v>30.5493</v>
+        <v>30.6466</v>
       </c>
       <c r="E35" t="n">
-        <v>14.9228</v>
+        <v>20.795</v>
       </c>
       <c r="F35" t="n">
-        <v>25.7487</v>
+        <v>31.0727</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>17.2748</v>
+        <v>17.3027</v>
       </c>
       <c r="C36" t="n">
-        <v>16.7788</v>
+        <v>16.7692</v>
       </c>
       <c r="D36" t="n">
-        <v>30.6125</v>
+        <v>30.8248</v>
       </c>
       <c r="E36" t="n">
-        <v>14.61</v>
+        <v>20.2225</v>
       </c>
       <c r="F36" t="n">
-        <v>25.3718</v>
+        <v>30.8048</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>16.6176</v>
+        <v>16.7591</v>
       </c>
       <c r="C37" t="n">
-        <v>18.1362</v>
+        <v>18.27</v>
       </c>
       <c r="D37" t="n">
-        <v>30.7685</v>
+        <v>30.6935</v>
       </c>
       <c r="E37" t="n">
-        <v>19.6345</v>
+        <v>19.5965</v>
       </c>
       <c r="F37" t="n">
-        <v>30.3546</v>
+        <v>30.2733</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>22.9774</v>
+        <v>23.0657</v>
       </c>
       <c r="C38" t="n">
-        <v>18.0324</v>
+        <v>18.1571</v>
       </c>
       <c r="D38" t="n">
-        <v>30.8452</v>
+        <v>30.7751</v>
       </c>
       <c r="E38" t="n">
-        <v>19.1838</v>
+        <v>19.2592</v>
       </c>
       <c r="F38" t="n">
-        <v>29.9826</v>
+        <v>30.0247</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>22.8108</v>
+        <v>22.8131</v>
       </c>
       <c r="C39" t="n">
-        <v>17.8774</v>
+        <v>17.9673</v>
       </c>
       <c r="D39" t="n">
-        <v>30.7728</v>
+        <v>30.7058</v>
       </c>
       <c r="E39" t="n">
-        <v>18.6716</v>
+        <v>18.6581</v>
       </c>
       <c r="F39" t="n">
-        <v>29.6209</v>
+        <v>29.6378</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>22.5082</v>
+        <v>22.4528</v>
       </c>
       <c r="C40" t="n">
-        <v>17.7571</v>
+        <v>17.7213</v>
       </c>
       <c r="D40" t="n">
-        <v>30.6355</v>
+        <v>30.8659</v>
       </c>
       <c r="E40" t="n">
-        <v>18.2434</v>
+        <v>18.3322</v>
       </c>
       <c r="F40" t="n">
-        <v>29.2485</v>
+        <v>29.2723</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>22.1043</v>
+        <v>22.0943</v>
       </c>
       <c r="C41" t="n">
-        <v>17.6261</v>
+        <v>17.6521</v>
       </c>
       <c r="D41" t="n">
-        <v>30.755</v>
+        <v>30.8946</v>
       </c>
       <c r="E41" t="n">
-        <v>17.8901</v>
+        <v>17.927</v>
       </c>
       <c r="F41" t="n">
-        <v>28.9267</v>
+        <v>28.9128</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>21.6001</v>
+        <v>21.653</v>
       </c>
       <c r="C42" t="n">
-        <v>17.5373</v>
+        <v>17.5314</v>
       </c>
       <c r="D42" t="n">
-        <v>30.7231</v>
+        <v>30.9487</v>
       </c>
       <c r="E42" t="n">
-        <v>17.5498</v>
+        <v>17.6283</v>
       </c>
       <c r="F42" t="n">
-        <v>28.482</v>
+        <v>28.4349</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>21.1809</v>
+        <v>21.2208</v>
       </c>
       <c r="C43" t="n">
-        <v>17.4194</v>
+        <v>17.4426</v>
       </c>
       <c r="D43" t="n">
-        <v>30.8147</v>
+        <v>31.0149</v>
       </c>
       <c r="E43" t="n">
-        <v>17.1961</v>
+        <v>17.2227</v>
       </c>
       <c r="F43" t="n">
-        <v>28.1615</v>
+        <v>28.0224</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>20.7232</v>
+        <v>20.725</v>
       </c>
       <c r="C44" t="n">
-        <v>17.3565</v>
+        <v>17.3186</v>
       </c>
       <c r="D44" t="n">
-        <v>30.9992</v>
+        <v>31.1898</v>
       </c>
       <c r="E44" t="n">
-        <v>16.9191</v>
+        <v>16.8958</v>
       </c>
       <c r="F44" t="n">
-        <v>27.8191</v>
+        <v>27.7112</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>20.2682</v>
+        <v>20.2409</v>
       </c>
       <c r="C45" t="n">
-        <v>17.2854</v>
+        <v>17.2801</v>
       </c>
       <c r="D45" t="n">
-        <v>31.1158</v>
+        <v>31.1817</v>
       </c>
       <c r="E45" t="n">
-        <v>16.5359</v>
+        <v>16.5518</v>
       </c>
       <c r="F45" t="n">
-        <v>27.489</v>
+        <v>27.346</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>19.8733</v>
+        <v>19.8912</v>
       </c>
       <c r="C46" t="n">
-        <v>17.2014</v>
+        <v>17.2079</v>
       </c>
       <c r="D46" t="n">
-        <v>31.1491</v>
+        <v>31.4594</v>
       </c>
       <c r="E46" t="n">
-        <v>16.1845</v>
+        <v>16.1836</v>
       </c>
       <c r="F46" t="n">
-        <v>27.1692</v>
+        <v>27.1086</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>19.3573</v>
+        <v>19.3317</v>
       </c>
       <c r="C47" t="n">
-        <v>17.134</v>
+        <v>17.0561</v>
       </c>
       <c r="D47" t="n">
-        <v>31.3242</v>
+        <v>31.4178</v>
       </c>
       <c r="E47" t="n">
-        <v>15.8803</v>
+        <v>15.847</v>
       </c>
       <c r="F47" t="n">
-        <v>26.7805</v>
+        <v>26.708</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>18.9032</v>
+        <v>18.8334</v>
       </c>
       <c r="C48" t="n">
-        <v>16.9848</v>
+        <v>16.9964</v>
       </c>
       <c r="D48" t="n">
-        <v>31.4896</v>
+        <v>31.5075</v>
       </c>
       <c r="E48" t="n">
-        <v>15.5628</v>
+        <v>15.5423</v>
       </c>
       <c r="F48" t="n">
-        <v>26.4455</v>
+        <v>26.3471</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>18.2913</v>
+        <v>18.2296</v>
       </c>
       <c r="C49" t="n">
-        <v>17.0021</v>
+        <v>16.9709</v>
       </c>
       <c r="D49" t="n">
-        <v>31.4342</v>
+        <v>31.6952</v>
       </c>
       <c r="E49" t="n">
-        <v>15.1939</v>
+        <v>15.179</v>
       </c>
       <c r="F49" t="n">
-        <v>26.0589</v>
+        <v>25.9915</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>17.6641</v>
+        <v>17.6432</v>
       </c>
       <c r="C50" t="n">
-        <v>16.9329</v>
+        <v>16.9249</v>
       </c>
       <c r="D50" t="n">
-        <v>31.4166</v>
+        <v>31.2257</v>
       </c>
       <c r="E50" t="n">
-        <v>14.8095</v>
+        <v>20.3313</v>
       </c>
       <c r="F50" t="n">
-        <v>25.6181</v>
+        <v>30.8117</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>16.9024</v>
+        <v>16.9366</v>
       </c>
       <c r="C51" t="n">
-        <v>18.3291</v>
+        <v>18.3161</v>
       </c>
       <c r="D51" t="n">
-        <v>31.4211</v>
+        <v>31.2286</v>
       </c>
       <c r="E51" t="n">
-        <v>19.887</v>
+        <v>19.7912</v>
       </c>
       <c r="F51" t="n">
-        <v>30.4714</v>
+        <v>30.4574</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>16.1097</v>
+        <v>16.0855</v>
       </c>
       <c r="C52" t="n">
-        <v>18.1997</v>
+        <v>18.185</v>
       </c>
       <c r="D52" t="n">
-        <v>31.4647</v>
+        <v>31.3408</v>
       </c>
       <c r="E52" t="n">
-        <v>19.3288</v>
+        <v>19.3278</v>
       </c>
       <c r="F52" t="n">
-        <v>30.082</v>
+        <v>30.054</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>23.0375</v>
+        <v>22.9579</v>
       </c>
       <c r="C53" t="n">
-        <v>18.0751</v>
+        <v>18.0505</v>
       </c>
       <c r="D53" t="n">
-        <v>31.7279</v>
+        <v>31.4346</v>
       </c>
       <c r="E53" t="n">
-        <v>18.8988</v>
+        <v>18.9943</v>
       </c>
       <c r="F53" t="n">
-        <v>29.6934</v>
+        <v>29.6641</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>22.6283</v>
+        <v>22.6531</v>
       </c>
       <c r="C54" t="n">
-        <v>17.9265</v>
+        <v>17.8866</v>
       </c>
       <c r="D54" t="n">
-        <v>31.9197</v>
+        <v>31.4977</v>
       </c>
       <c r="E54" t="n">
-        <v>18.5291</v>
+        <v>18.4964</v>
       </c>
       <c r="F54" t="n">
-        <v>29.3749</v>
+        <v>29.3552</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>22.3214</v>
+        <v>22.2683</v>
       </c>
       <c r="C55" t="n">
-        <v>17.7952</v>
+        <v>17.7764</v>
       </c>
       <c r="D55" t="n">
-        <v>31.8636</v>
+        <v>31.713</v>
       </c>
       <c r="E55" t="n">
-        <v>18.151</v>
+        <v>18.2269</v>
       </c>
       <c r="F55" t="n">
-        <v>29.0515</v>
+        <v>29.0103</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>21.8474</v>
+        <v>21.844</v>
       </c>
       <c r="C56" t="n">
-        <v>17.6513</v>
+        <v>17.6309</v>
       </c>
       <c r="D56" t="n">
-        <v>32.0947</v>
+        <v>31.919</v>
       </c>
       <c r="E56" t="n">
-        <v>17.802</v>
+        <v>17.7855</v>
       </c>
       <c r="F56" t="n">
-        <v>28.6427</v>
+        <v>28.6162</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>21.3992</v>
+        <v>21.3845</v>
       </c>
       <c r="C57" t="n">
-        <v>17.5954</v>
+        <v>17.5823</v>
       </c>
       <c r="D57" t="n">
-        <v>32.354</v>
+        <v>32.0142</v>
       </c>
       <c r="E57" t="n">
-        <v>17.4224</v>
+        <v>17.3947</v>
       </c>
       <c r="F57" t="n">
-        <v>28.2249</v>
+        <v>28.2628</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>20.9876</v>
+        <v>20.9576</v>
       </c>
       <c r="C58" t="n">
-        <v>17.4536</v>
+        <v>17.4567</v>
       </c>
       <c r="D58" t="n">
-        <v>32.4293</v>
+        <v>32.3056</v>
       </c>
       <c r="E58" t="n">
-        <v>17.0921</v>
+        <v>17.059</v>
       </c>
       <c r="F58" t="n">
-        <v>27.9111</v>
+        <v>27.8748</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>20.4578</v>
+        <v>20.4711</v>
       </c>
       <c r="C59" t="n">
-        <v>17.3871</v>
+        <v>17.3939</v>
       </c>
       <c r="D59" t="n">
-        <v>32.6146</v>
+        <v>32.6037</v>
       </c>
       <c r="E59" t="n">
-        <v>16.7419</v>
+        <v>16.7175</v>
       </c>
       <c r="F59" t="n">
-        <v>27.6221</v>
+        <v>27.5298</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>20.0315</v>
+        <v>20.0148</v>
       </c>
       <c r="C60" t="n">
-        <v>17.333</v>
+        <v>17.3156</v>
       </c>
       <c r="D60" t="n">
-        <v>32.9972</v>
+        <v>32.9718</v>
       </c>
       <c r="E60" t="n">
-        <v>16.4323</v>
+        <v>16.4382</v>
       </c>
       <c r="F60" t="n">
-        <v>27.3159</v>
+        <v>27.2576</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>19.5192</v>
+        <v>19.489</v>
       </c>
       <c r="C61" t="n">
-        <v>17.2138</v>
+        <v>17.178</v>
       </c>
       <c r="D61" t="n">
-        <v>33.2773</v>
+        <v>33.21</v>
       </c>
       <c r="E61" t="n">
-        <v>16.1236</v>
+        <v>16.0692</v>
       </c>
       <c r="F61" t="n">
-        <v>26.9745</v>
+        <v>26.8663</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>18.97</v>
+        <v>18.9657</v>
       </c>
       <c r="C62" t="n">
-        <v>17.1294</v>
+        <v>17.1256</v>
       </c>
       <c r="D62" t="n">
-        <v>33.5994</v>
+        <v>33.6402</v>
       </c>
       <c r="E62" t="n">
-        <v>15.7297</v>
+        <v>15.6783</v>
       </c>
       <c r="F62" t="n">
-        <v>26.567</v>
+        <v>26.4723</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>18.4254</v>
+        <v>18.4055</v>
       </c>
       <c r="C63" t="n">
-        <v>17.1</v>
+        <v>17.1579</v>
       </c>
       <c r="D63" t="n">
-        <v>33.84</v>
+        <v>33.8837</v>
       </c>
       <c r="E63" t="n">
-        <v>15.4345</v>
+        <v>15.3661</v>
       </c>
       <c r="F63" t="n">
-        <v>26.1949</v>
+        <v>26.1399</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>17.9077</v>
+        <v>17.8666</v>
       </c>
       <c r="C64" t="n">
-        <v>16.9832</v>
+        <v>16.9932</v>
       </c>
       <c r="D64" t="n">
-        <v>38.2507</v>
+        <v>38.3726</v>
       </c>
       <c r="E64" t="n">
-        <v>15.0452</v>
+        <v>21.4971</v>
       </c>
       <c r="F64" t="n">
-        <v>25.4149</v>
+        <v>30.9381</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>17.2417</v>
+        <v>17.1392</v>
       </c>
       <c r="C65" t="n">
-        <v>18.6392</v>
+        <v>18.5855</v>
       </c>
       <c r="D65" t="n">
-        <v>38.3322</v>
+        <v>37.9651</v>
       </c>
       <c r="E65" t="n">
-        <v>14.6785</v>
+        <v>20.769</v>
       </c>
       <c r="F65" t="n">
-        <v>25.3871</v>
+        <v>30.5605</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>16.3859</v>
+        <v>16.3124</v>
       </c>
       <c r="C66" t="n">
-        <v>18.4123</v>
+        <v>18.4736</v>
       </c>
       <c r="D66" t="n">
-        <v>38.6967</v>
+        <v>38.2096</v>
       </c>
       <c r="E66" t="n">
-        <v>20.1143</v>
+        <v>20.5709</v>
       </c>
       <c r="F66" t="n">
-        <v>30.1755</v>
+        <v>30.1678</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>23.1467</v>
+        <v>23.1497</v>
       </c>
       <c r="C67" t="n">
-        <v>18.2145</v>
+        <v>18.2037</v>
       </c>
       <c r="D67" t="n">
-        <v>38.9741</v>
+        <v>38.605</v>
       </c>
       <c r="E67" t="n">
-        <v>20.033</v>
+        <v>19.9273</v>
       </c>
       <c r="F67" t="n">
-        <v>29.8159</v>
+        <v>29.771</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>22.7849</v>
+        <v>22.8098</v>
       </c>
       <c r="C68" t="n">
-        <v>18.0358</v>
+        <v>18.0718</v>
       </c>
       <c r="D68" t="n">
-        <v>38.8693</v>
+        <v>38.8405</v>
       </c>
       <c r="E68" t="n">
-        <v>19.202</v>
+        <v>19.3199</v>
       </c>
       <c r="F68" t="n">
-        <v>29.5063</v>
+        <v>29.4403</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>22.4078</v>
+        <v>22.3989</v>
       </c>
       <c r="C69" t="n">
-        <v>17.8898</v>
+        <v>17.914</v>
       </c>
       <c r="D69" t="n">
-        <v>38.76</v>
+        <v>39.3574</v>
       </c>
       <c r="E69" t="n">
-        <v>18.6862</v>
+        <v>18.8251</v>
       </c>
       <c r="F69" t="n">
-        <v>29.0838</v>
+        <v>29.0875</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>22.0182</v>
+        <v>21.9977</v>
       </c>
       <c r="C70" t="n">
-        <v>17.8968</v>
+        <v>17.8507</v>
       </c>
       <c r="D70" t="n">
-        <v>39.0134</v>
+        <v>39.3728</v>
       </c>
       <c r="E70" t="n">
-        <v>18.2046</v>
+        <v>18.1584</v>
       </c>
       <c r="F70" t="n">
-        <v>28.7922</v>
+        <v>28.6991</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>21.497</v>
+        <v>21.5281</v>
       </c>
       <c r="C71" t="n">
-        <v>17.7517</v>
+        <v>17.7114</v>
       </c>
       <c r="D71" t="n">
-        <v>39.2351</v>
+        <v>39.2595</v>
       </c>
       <c r="E71" t="n">
-        <v>17.6289</v>
+        <v>17.7234</v>
       </c>
       <c r="F71" t="n">
-        <v>28.3655</v>
+        <v>28.3483</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>21.1092</v>
+        <v>21.0743</v>
       </c>
       <c r="C72" t="n">
-        <v>17.6138</v>
+        <v>17.5507</v>
       </c>
       <c r="D72" t="n">
-        <v>39.4358</v>
+        <v>39.4784</v>
       </c>
       <c r="E72" t="n">
-        <v>17.2761</v>
+        <v>17.2646</v>
       </c>
       <c r="F72" t="n">
-        <v>28.0073</v>
+        <v>28.0308</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>20.6048</v>
+        <v>20.6029</v>
       </c>
       <c r="C73" t="n">
-        <v>17.4905</v>
+        <v>17.5081</v>
       </c>
       <c r="D73" t="n">
-        <v>39.3374</v>
+        <v>39.3317</v>
       </c>
       <c r="E73" t="n">
-        <v>16.8725</v>
+        <v>16.9123</v>
       </c>
       <c r="F73" t="n">
-        <v>27.7122</v>
+        <v>27.6859</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>20.1583</v>
+        <v>20.1463</v>
       </c>
       <c r="C74" t="n">
-        <v>17.3544</v>
+        <v>17.3666</v>
       </c>
       <c r="D74" t="n">
-        <v>39.2737</v>
+        <v>39.53</v>
       </c>
       <c r="E74" t="n">
-        <v>16.5853</v>
+        <v>16.6045</v>
       </c>
       <c r="F74" t="n">
-        <v>27.4085</v>
+        <v>27.3867</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>19.6774</v>
+        <v>19.5877</v>
       </c>
       <c r="C75" t="n">
-        <v>17.3065</v>
+        <v>17.3049</v>
       </c>
       <c r="D75" t="n">
-        <v>39.3279</v>
+        <v>39.5256</v>
       </c>
       <c r="E75" t="n">
-        <v>16.2351</v>
+        <v>16.2065</v>
       </c>
       <c r="F75" t="n">
-        <v>27.0511</v>
+        <v>27.0084</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>19.1801</v>
+        <v>19.1406</v>
       </c>
       <c r="C76" t="n">
-        <v>17.2449</v>
+        <v>17.1743</v>
       </c>
       <c r="D76" t="n">
-        <v>39.2498</v>
+        <v>39.8295</v>
       </c>
       <c r="E76" t="n">
-        <v>15.8929</v>
+        <v>15.8754</v>
       </c>
       <c r="F76" t="n">
-        <v>26.7318</v>
+        <v>26.6394</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>18.5866</v>
+        <v>18.6038</v>
       </c>
       <c r="C77" t="n">
-        <v>17.1214</v>
+        <v>17.0907</v>
       </c>
       <c r="D77" t="n">
-        <v>39.377</v>
+        <v>39.3565</v>
       </c>
       <c r="E77" t="n">
-        <v>15.5414</v>
+        <v>15.5635</v>
       </c>
       <c r="F77" t="n">
-        <v>26.3616</v>
+        <v>26.3199</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>18.0158</v>
+        <v>17.9901</v>
       </c>
       <c r="C78" t="n">
-        <v>17.0567</v>
+        <v>17.0226</v>
       </c>
       <c r="D78" t="n">
-        <v>46.1245</v>
+        <v>46.3727</v>
       </c>
       <c r="E78" t="n">
-        <v>15.235</v>
+        <v>20.8185</v>
       </c>
       <c r="F78" t="n">
-        <v>26.1016</v>
+        <v>31.1153</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>17.3683</v>
+        <v>17.3048</v>
       </c>
       <c r="C79" t="n">
-        <v>18.8781</v>
+        <v>18.8299</v>
       </c>
       <c r="D79" t="n">
-        <v>45.6487</v>
+        <v>46.3616</v>
       </c>
       <c r="E79" t="n">
-        <v>14.8841</v>
+        <v>20.312</v>
       </c>
       <c r="F79" t="n">
-        <v>25.7486</v>
+        <v>30.7454</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>16.6109</v>
+        <v>16.573</v>
       </c>
       <c r="C80" t="n">
-        <v>18.6203</v>
+        <v>18.5806</v>
       </c>
       <c r="D80" t="n">
-        <v>45.4386</v>
+        <v>45.8918</v>
       </c>
       <c r="E80" t="n">
-        <v>19.8205</v>
+        <v>19.8195</v>
       </c>
       <c r="F80" t="n">
-        <v>30.5125</v>
+        <v>30.3465</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>23.2726</v>
+        <v>23.2955</v>
       </c>
       <c r="C81" t="n">
-        <v>18.4509</v>
+        <v>18.4189</v>
       </c>
       <c r="D81" t="n">
-        <v>44.5641</v>
+        <v>45.1713</v>
       </c>
       <c r="E81" t="n">
-        <v>19.3938</v>
+        <v>19.3321</v>
       </c>
       <c r="F81" t="n">
-        <v>30.1835</v>
+        <v>29.9867</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>22.9203</v>
+        <v>22.9082</v>
       </c>
       <c r="C82" t="n">
-        <v>18.2204</v>
+        <v>18.241</v>
       </c>
       <c r="D82" t="n">
-        <v>44.1935</v>
+        <v>44.7325</v>
       </c>
       <c r="E82" t="n">
-        <v>18.8846</v>
+        <v>18.9525</v>
       </c>
       <c r="F82" t="n">
-        <v>29.7855</v>
+        <v>29.6017</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>22.5588</v>
+        <v>22.5462</v>
       </c>
       <c r="C83" t="n">
-        <v>18.0876</v>
+        <v>18.0727</v>
       </c>
       <c r="D83" t="n">
-        <v>43.779</v>
+        <v>44.3896</v>
       </c>
       <c r="E83" t="n">
-        <v>18.5511</v>
+        <v>18.5461</v>
       </c>
       <c r="F83" t="n">
-        <v>29.4113</v>
+        <v>29.2526</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>22.1572</v>
+        <v>22.1207</v>
       </c>
       <c r="C84" t="n">
-        <v>17.9863</v>
+        <v>17.9377</v>
       </c>
       <c r="D84" t="n">
-        <v>43.229</v>
+        <v>43.9035</v>
       </c>
       <c r="E84" t="n">
-        <v>18.1673</v>
+        <v>18.1091</v>
       </c>
       <c r="F84" t="n">
-        <v>29.0176</v>
+        <v>28.8647</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>21.6693</v>
+        <v>21.6665</v>
       </c>
       <c r="C85" t="n">
-        <v>17.7933</v>
+        <v>17.7703</v>
       </c>
       <c r="D85" t="n">
-        <v>42.914</v>
+        <v>43.8908</v>
       </c>
       <c r="E85" t="n">
-        <v>17.7649</v>
+        <v>17.8089</v>
       </c>
       <c r="F85" t="n">
-        <v>28.2055</v>
+        <v>28.4574</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>21.1762</v>
+        <v>21.2388</v>
       </c>
       <c r="C86" t="n">
-        <v>17.6666</v>
+        <v>17.6921</v>
       </c>
       <c r="D86" t="n">
-        <v>42.2766</v>
+        <v>42.564</v>
       </c>
       <c r="E86" t="n">
-        <v>17.4428</v>
+        <v>17.4052</v>
       </c>
       <c r="F86" t="n">
-        <v>27.8194</v>
+        <v>28.1353</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>20.7437</v>
+        <v>20.7617</v>
       </c>
       <c r="C87" t="n">
-        <v>17.5376</v>
+        <v>17.5426</v>
       </c>
       <c r="D87" t="n">
-        <v>42.1857</v>
+        <v>42.4335</v>
       </c>
       <c r="E87" t="n">
-        <v>17.105</v>
+        <v>17.1147</v>
       </c>
       <c r="F87" t="n">
-        <v>27.4856</v>
+        <v>27.8369</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>20.2636</v>
+        <v>20.2679</v>
       </c>
       <c r="C88" t="n">
-        <v>17.444</v>
+        <v>17.4562</v>
       </c>
       <c r="D88" t="n">
-        <v>41.754</v>
+        <v>42.7443</v>
       </c>
       <c r="E88" t="n">
-        <v>16.6964</v>
+        <v>16.7327</v>
       </c>
       <c r="F88" t="n">
-        <v>27.1608</v>
+        <v>27.4881</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>19.7511</v>
+        <v>19.714</v>
       </c>
       <c r="C89" t="n">
-        <v>17.3258</v>
+        <v>17.3411</v>
       </c>
       <c r="D89" t="n">
-        <v>42.2894</v>
+        <v>40.9248</v>
       </c>
       <c r="E89" t="n">
-        <v>16.361</v>
+        <v>16.4105</v>
       </c>
       <c r="F89" t="n">
-        <v>26.8309</v>
+        <v>26.8787</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>19.2585</v>
+        <v>19.3077</v>
       </c>
       <c r="C90" t="n">
-        <v>17.2339</v>
+        <v>17.2394</v>
       </c>
       <c r="D90" t="n">
-        <v>42.0206</v>
+        <v>40.7278</v>
       </c>
       <c r="E90" t="n">
-        <v>16.0286</v>
+        <v>16.0523</v>
       </c>
       <c r="F90" t="n">
-        <v>26.4851</v>
+        <v>26.4859</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>18.7051</v>
+        <v>18.7221</v>
       </c>
       <c r="C91" t="n">
-        <v>17.1336</v>
+        <v>17.1297</v>
       </c>
       <c r="D91" t="n">
-        <v>41.3835</v>
+        <v>40.7875</v>
       </c>
       <c r="E91" t="n">
-        <v>15.6914</v>
+        <v>15.717</v>
       </c>
       <c r="F91" t="n">
-        <v>26.107</v>
+        <v>26.1027</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>18.1653</v>
+        <v>18.1798</v>
       </c>
       <c r="C92" t="n">
-        <v>17.0576</v>
+        <v>17.0554</v>
       </c>
       <c r="D92" t="n">
-        <v>47.0005</v>
+        <v>45.5614</v>
       </c>
       <c r="E92" t="n">
-        <v>15.3511</v>
+        <v>21.059</v>
       </c>
       <c r="F92" t="n">
-        <v>25.7665</v>
+        <v>30.7784</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>17.5623</v>
+        <v>17.5178</v>
       </c>
       <c r="C93" t="n">
-        <v>16.9896</v>
+        <v>16.9918</v>
       </c>
       <c r="D93" t="n">
-        <v>46.4686</v>
+        <v>44.8403</v>
       </c>
       <c r="E93" t="n">
-        <v>15.017</v>
+        <v>20.5103</v>
       </c>
       <c r="F93" t="n">
-        <v>25.3688</v>
+        <v>30.337</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>16.7973</v>
+        <v>16.8378</v>
       </c>
       <c r="C94" t="n">
-        <v>18.623</v>
+        <v>18.5934</v>
       </c>
       <c r="D94" t="n">
-        <v>46.1649</v>
+        <v>44.1537</v>
       </c>
       <c r="E94" t="n">
-        <v>20.0118</v>
+        <v>19.9862</v>
       </c>
       <c r="F94" t="n">
-        <v>30.0668</v>
+        <v>30.0722</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>23.3307</v>
+        <v>23.3534</v>
       </c>
       <c r="C95" t="n">
-        <v>18.3948</v>
+        <v>18.3896</v>
       </c>
       <c r="D95" t="n">
-        <v>45.585</v>
+        <v>43.5997</v>
       </c>
       <c r="E95" t="n">
-        <v>19.5133</v>
+        <v>19.5561</v>
       </c>
       <c r="F95" t="n">
-        <v>29.7039</v>
+        <v>29.6004</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>22.9977</v>
+        <v>23.0004</v>
       </c>
       <c r="C96" t="n">
-        <v>18.223</v>
+        <v>18.2254</v>
       </c>
       <c r="D96" t="n">
-        <v>44.9966</v>
+        <v>43.1782</v>
       </c>
       <c r="E96" t="n">
-        <v>19.0887</v>
+        <v>19.096</v>
       </c>
       <c r="F96" t="n">
-        <v>29.9735</v>
+        <v>29.9035</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>22.5854</v>
+        <v>22.5962</v>
       </c>
       <c r="C97" t="n">
-        <v>18.065</v>
+        <v>18.0631</v>
       </c>
       <c r="D97" t="n">
-        <v>44.225</v>
+        <v>42.9315</v>
       </c>
       <c r="E97" t="n">
-        <v>18.6354</v>
+        <v>18.742</v>
       </c>
       <c r="F97" t="n">
-        <v>29.3874</v>
+        <v>29.3762</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>22.1661</v>
+        <v>22.197</v>
       </c>
       <c r="C98" t="n">
-        <v>17.9158</v>
+        <v>17.9127</v>
       </c>
       <c r="D98" t="n">
-        <v>43.7718</v>
+        <v>42.419</v>
       </c>
       <c r="E98" t="n">
-        <v>18.2352</v>
+        <v>18.2589</v>
       </c>
       <c r="F98" t="n">
-        <v>28.9768</v>
+        <v>28.921</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>21.7401</v>
+        <v>21.7681</v>
       </c>
       <c r="C99" t="n">
-        <v>17.7839</v>
+        <v>17.7971</v>
       </c>
       <c r="D99" t="n">
-        <v>43.4045</v>
+        <v>41.8857</v>
       </c>
       <c r="E99" t="n">
-        <v>17.8371</v>
+        <v>17.8674</v>
       </c>
       <c r="F99" t="n">
-        <v>28.5471</v>
+        <v>28.532</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>21.3046</v>
+        <v>21.3324</v>
       </c>
       <c r="C100" t="n">
-        <v>17.7117</v>
+        <v>17.7507</v>
       </c>
       <c r="D100" t="n">
-        <v>42.7536</v>
+        <v>41.7781</v>
       </c>
       <c r="E100" t="n">
-        <v>17.4663</v>
+        <v>17.5207</v>
       </c>
       <c r="F100" t="n">
-        <v>28.2001</v>
+        <v>28.1479</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>20.7911</v>
+        <v>20.8081</v>
       </c>
       <c r="C101" t="n">
-        <v>17.6067</v>
+        <v>17.6236</v>
       </c>
       <c r="D101" t="n">
-        <v>42.4325</v>
+        <v>41.3668</v>
       </c>
       <c r="E101" t="n">
-        <v>17.1104</v>
+        <v>17.1525</v>
       </c>
       <c r="F101" t="n">
-        <v>27.8837</v>
+        <v>27.7957</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>20.3392</v>
+        <v>20.3524</v>
       </c>
       <c r="C102" t="n">
-        <v>17.4844</v>
+        <v>17.4585</v>
       </c>
       <c r="D102" t="n">
-        <v>41.8492</v>
+        <v>41.0283</v>
       </c>
       <c r="E102" t="n">
-        <v>16.7612</v>
+        <v>16.8019</v>
       </c>
       <c r="F102" t="n">
-        <v>27.555</v>
+        <v>27.4829</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>19.8533</v>
+        <v>19.8692</v>
       </c>
       <c r="C103" t="n">
-        <v>17.3416</v>
+        <v>17.3597</v>
       </c>
       <c r="D103" t="n">
-        <v>41.6121</v>
+        <v>40.8453</v>
       </c>
       <c r="E103" t="n">
-        <v>16.4163</v>
+        <v>16.4896</v>
       </c>
       <c r="F103" t="n">
-        <v>27.1875</v>
+        <v>27.1684</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>19.3622</v>
+        <v>19.3663</v>
       </c>
       <c r="C104" t="n">
-        <v>17.2469</v>
+        <v>17.2291</v>
       </c>
       <c r="D104" t="n">
-        <v>41.204</v>
+        <v>40.4249</v>
       </c>
       <c r="E104" t="n">
-        <v>16.1016</v>
+        <v>16.1249</v>
       </c>
       <c r="F104" t="n">
-        <v>26.8307</v>
+        <v>26.827</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>18.871</v>
+        <v>18.8867</v>
       </c>
       <c r="C105" t="n">
-        <v>17.1632</v>
+        <v>17.1553</v>
       </c>
       <c r="D105" t="n">
-        <v>40.945</v>
+        <v>40.3173</v>
       </c>
       <c r="E105" t="n">
-        <v>15.7663</v>
+        <v>15.7883</v>
       </c>
       <c r="F105" t="n">
-        <v>26.5073</v>
+        <v>26.4476</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>18.3094</v>
+        <v>18.3062</v>
       </c>
       <c r="C106" t="n">
-        <v>17.1019</v>
+        <v>17.0647</v>
       </c>
       <c r="D106" t="n">
-        <v>40.4736</v>
+        <v>40.0104</v>
       </c>
       <c r="E106" t="n">
-        <v>15.4584</v>
+        <v>15.4654</v>
       </c>
       <c r="F106" t="n">
-        <v>26.1349</v>
+        <v>26.0874</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>17.7558</v>
+        <v>17.703</v>
       </c>
       <c r="C107" t="n">
-        <v>17.0001</v>
+        <v>16.9781</v>
       </c>
       <c r="D107" t="n">
-        <v>43.7811</v>
+        <v>43.338</v>
       </c>
       <c r="E107" t="n">
-        <v>15.111</v>
+        <v>20.5822</v>
       </c>
       <c r="F107" t="n">
-        <v>25.7455</v>
+        <v>30.8497</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>17.049</v>
+        <v>17.0331</v>
       </c>
       <c r="C108" t="n">
-        <v>18.7464</v>
+        <v>18.7418</v>
       </c>
       <c r="D108" t="n">
-        <v>43.6148</v>
+        <v>43.2162</v>
       </c>
       <c r="E108" t="n">
-        <v>20.0823</v>
+        <v>20.0864</v>
       </c>
       <c r="F108" t="n">
-        <v>30.5024</v>
+        <v>30.4457</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>16.144</v>
+        <v>16.1588</v>
       </c>
       <c r="C109" t="n">
-        <v>18.5414</v>
+        <v>18.5567</v>
       </c>
       <c r="D109" t="n">
-        <v>42.9856</v>
+        <v>42.5907</v>
       </c>
       <c r="E109" t="n">
-        <v>19.6336</v>
+        <v>19.6254</v>
       </c>
       <c r="F109" t="n">
-        <v>30.1045</v>
+        <v>30.0543</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>23.0653</v>
+        <v>23.1166</v>
       </c>
       <c r="C110" t="n">
-        <v>18.2731</v>
+        <v>18.2851</v>
       </c>
       <c r="D110" t="n">
-        <v>42.5874</v>
+        <v>42.0862</v>
       </c>
       <c r="E110" t="n">
-        <v>19.1338</v>
+        <v>19.1601</v>
       </c>
       <c r="F110" t="n">
-        <v>29.8136</v>
+        <v>29.3432</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>22.7142</v>
+        <v>22.721</v>
       </c>
       <c r="C111" t="n">
-        <v>18.2145</v>
+        <v>18.2293</v>
       </c>
       <c r="D111" t="n">
-        <v>42.4641</v>
+        <v>41.5601</v>
       </c>
       <c r="E111" t="n">
-        <v>18.7272</v>
+        <v>18.7604</v>
       </c>
       <c r="F111" t="n">
-        <v>28.9446</v>
+        <v>28.9563</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>22.2607</v>
+        <v>22.2927</v>
       </c>
       <c r="C112" t="n">
-        <v>18.0577</v>
+        <v>18.0715</v>
       </c>
       <c r="D112" t="n">
-        <v>41.9083</v>
+        <v>41.2496</v>
       </c>
       <c r="E112" t="n">
-        <v>18.3086</v>
+        <v>18.3706</v>
       </c>
       <c r="F112" t="n">
-        <v>28.6571</v>
+        <v>28.6666</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>21.8333</v>
+        <v>21.8578</v>
       </c>
       <c r="C113" t="n">
-        <v>17.9153</v>
+        <v>17.9252</v>
       </c>
       <c r="D113" t="n">
-        <v>41.551</v>
+        <v>40.8648</v>
       </c>
       <c r="E113" t="n">
-        <v>17.9135</v>
+        <v>17.9467</v>
       </c>
       <c r="F113" t="n">
-        <v>28.2083</v>
+        <v>28.2501</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>21.385</v>
+        <v>21.4213</v>
       </c>
       <c r="C114" t="n">
-        <v>17.6892</v>
+        <v>17.7281</v>
       </c>
       <c r="D114" t="n">
-        <v>41.1922</v>
+        <v>40.0838</v>
       </c>
       <c r="E114" t="n">
-        <v>17.557</v>
+        <v>17.6144</v>
       </c>
       <c r="F114" t="n">
-        <v>27.8602</v>
+        <v>27.9178</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>20.944</v>
+        <v>20.917</v>
       </c>
       <c r="C115" t="n">
-        <v>17.5769</v>
+        <v>17.6009</v>
       </c>
       <c r="D115" t="n">
-        <v>40.9381</v>
+        <v>39.7897</v>
       </c>
       <c r="E115" t="n">
-        <v>17.2234</v>
+        <v>17.2539</v>
       </c>
       <c r="F115" t="n">
-        <v>27.5151</v>
+        <v>27.6135</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>20.4384</v>
+        <v>20.4597</v>
       </c>
       <c r="C116" t="n">
-        <v>17.5461</v>
+        <v>17.5551</v>
       </c>
       <c r="D116" t="n">
-        <v>40.7653</v>
+        <v>39.3513</v>
       </c>
       <c r="E116" t="n">
-        <v>16.8571</v>
+        <v>16.8878</v>
       </c>
       <c r="F116" t="n">
-        <v>27.5515</v>
+        <v>27.6017</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>19.9796</v>
+        <v>19.9702</v>
       </c>
       <c r="C117" t="n">
-        <v>17.4012</v>
+        <v>17.4111</v>
       </c>
       <c r="D117" t="n">
-        <v>40.4774</v>
+        <v>39.091</v>
       </c>
       <c r="E117" t="n">
-        <v>16.5216</v>
+        <v>16.5229</v>
       </c>
       <c r="F117" t="n">
-        <v>27.2253</v>
+        <v>27.2845</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>19.5074</v>
+        <v>19.5025</v>
       </c>
       <c r="C118" t="n">
-        <v>17.2868</v>
+        <v>17.2752</v>
       </c>
       <c r="D118" t="n">
-        <v>40.1628</v>
+        <v>38.7224</v>
       </c>
       <c r="E118" t="n">
-        <v>16.1739</v>
+        <v>16.1709</v>
       </c>
       <c r="F118" t="n">
-        <v>26.902</v>
+        <v>26.9489</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>18.9954</v>
+        <v>18.9834</v>
       </c>
       <c r="C119" t="n">
-        <v>17.1938</v>
+        <v>17.191</v>
       </c>
       <c r="D119" t="n">
-        <v>39.9484</v>
+        <v>38.398</v>
       </c>
       <c r="E119" t="n">
-        <v>15.8399</v>
+        <v>15.8568</v>
       </c>
       <c r="F119" t="n">
-        <v>26.5331</v>
+        <v>26.5712</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>18.4899</v>
+        <v>18.4597</v>
       </c>
       <c r="C120" t="n">
-        <v>17.1152</v>
+        <v>17.0808</v>
       </c>
       <c r="D120" t="n">
-        <v>39.7589</v>
+        <v>38.2197</v>
       </c>
       <c r="E120" t="n">
-        <v>15.5009</v>
+        <v>15.5126</v>
       </c>
       <c r="F120" t="n">
-        <v>26.1851</v>
+        <v>26.221</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>17.9068</v>
+        <v>17.8706</v>
       </c>
       <c r="C121" t="n">
-        <v>17.0228</v>
+        <v>17.0219</v>
       </c>
       <c r="D121" t="n">
-        <v>47.2038</v>
+        <v>45.8619</v>
       </c>
       <c r="E121" t="n">
-        <v>15.1705</v>
+        <v>20.6873</v>
       </c>
       <c r="F121" t="n">
-        <v>25.4968</v>
+        <v>30.5176</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>17.2268</v>
+        <v>17.1948</v>
       </c>
       <c r="C122" t="n">
-        <v>18.6972</v>
+        <v>18.705</v>
       </c>
       <c r="D122" t="n">
-        <v>46.4366</v>
+        <v>45.1618</v>
       </c>
       <c r="E122" t="n">
-        <v>14.8169</v>
+        <v>20.2115</v>
       </c>
       <c r="F122" t="n">
-        <v>25.034</v>
+        <v>30.5332</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>16.4002</v>
+        <v>16.3424</v>
       </c>
       <c r="C123" t="n">
-        <v>18.4985</v>
+        <v>18.4951</v>
       </c>
       <c r="D123" t="n">
-        <v>45.9065</v>
+        <v>44.9331</v>
       </c>
       <c r="E123" t="n">
-        <v>19.6551</v>
+        <v>19.6895</v>
       </c>
       <c r="F123" t="n">
-        <v>30.2099</v>
+        <v>29.7095</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>23.1545</v>
+        <v>23.1673</v>
       </c>
       <c r="C124" t="n">
-        <v>18.3129</v>
+        <v>18.3234</v>
       </c>
       <c r="D124" t="n">
-        <v>45.114</v>
+        <v>44.2349</v>
       </c>
       <c r="E124" t="n">
-        <v>19.1995</v>
+        <v>19.2304</v>
       </c>
       <c r="F124" t="n">
-        <v>29.7087</v>
+        <v>29.3824</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>22.7646</v>
+        <v>22.7706</v>
       </c>
       <c r="C125" t="n">
-        <v>18.149</v>
+        <v>18.1647</v>
       </c>
       <c r="D125" t="n">
-        <v>44.8422</v>
+        <v>43.7723</v>
       </c>
       <c r="E125" t="n">
-        <v>18.7679</v>
+        <v>18.8181</v>
       </c>
       <c r="F125" t="n">
-        <v>29.1135</v>
+        <v>28.9261</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>22.341</v>
+        <v>22.3577</v>
       </c>
       <c r="C126" t="n">
-        <v>18.0008</v>
+        <v>17.9955</v>
       </c>
       <c r="D126" t="n">
-        <v>44.1174</v>
+        <v>43.0109</v>
       </c>
       <c r="E126" t="n">
-        <v>18.3685</v>
+        <v>18.3659</v>
       </c>
       <c r="F126" t="n">
-        <v>28.6698</v>
+        <v>28.6306</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>21.921</v>
+        <v>21.9174</v>
       </c>
       <c r="C127" t="n">
-        <v>17.8554</v>
+        <v>17.8552</v>
       </c>
       <c r="D127" t="n">
-        <v>43.6059</v>
+        <v>42.3875</v>
       </c>
       <c r="E127" t="n">
-        <v>17.9788</v>
+        <v>17.9515</v>
       </c>
       <c r="F127" t="n">
-        <v>28.2863</v>
+        <v>28.3253</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>21.4961</v>
+        <v>21.5023</v>
       </c>
       <c r="C128" t="n">
-        <v>17.7362</v>
+        <v>17.7543</v>
       </c>
       <c r="D128" t="n">
-        <v>42.3949</v>
+        <v>42.2719</v>
       </c>
       <c r="E128" t="n">
-        <v>17.6557</v>
+        <v>17.6007</v>
       </c>
       <c r="F128" t="n">
-        <v>27.9901</v>
+        <v>27.984</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>21.0424</v>
+        <v>21.0374</v>
       </c>
       <c r="C129" t="n">
-        <v>17.5824</v>
+        <v>17.6031</v>
       </c>
       <c r="D129" t="n">
-        <v>41.4086</v>
+        <v>41.7879</v>
       </c>
       <c r="E129" t="n">
-        <v>17.3182</v>
+        <v>17.2705</v>
       </c>
       <c r="F129" t="n">
-        <v>27.6705</v>
+        <v>27.6371</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>20.5496</v>
+        <v>20.5593</v>
       </c>
       <c r="C130" t="n">
-        <v>17.4875</v>
+        <v>17.4843</v>
       </c>
       <c r="D130" t="n">
-        <v>40.9574</v>
+        <v>41.4405</v>
       </c>
       <c r="E130" t="n">
-        <v>16.9398</v>
+        <v>16.9525</v>
       </c>
       <c r="F130" t="n">
-        <v>27.6712</v>
+        <v>27.609</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>20.056</v>
+        <v>20.0877</v>
       </c>
       <c r="C131" t="n">
-        <v>17.3732</v>
+        <v>17.3806</v>
       </c>
       <c r="D131" t="n">
-        <v>40.5314</v>
+        <v>40.9456</v>
       </c>
       <c r="E131" t="n">
-        <v>16.599</v>
+        <v>16.5816</v>
       </c>
       <c r="F131" t="n">
-        <v>27.3375</v>
+        <v>27.2866</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>19.5794</v>
+        <v>19.5949</v>
       </c>
       <c r="C132" t="n">
-        <v>17.2735</v>
+        <v>17.2733</v>
       </c>
       <c r="D132" t="n">
-        <v>40.214</v>
+        <v>40.6227</v>
       </c>
       <c r="E132" t="n">
-        <v>16.2913</v>
+        <v>16.2737</v>
       </c>
       <c r="F132" t="n">
-        <v>26.9936</v>
+        <v>26.9543</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>19.0652</v>
+        <v>19.0879</v>
       </c>
       <c r="C133" t="n">
-        <v>17.2025</v>
+        <v>17.21</v>
       </c>
       <c r="D133" t="n">
-        <v>39.8864</v>
+        <v>40.3934</v>
       </c>
       <c r="E133" t="n">
-        <v>15.9306</v>
+        <v>15.92</v>
       </c>
       <c r="F133" t="n">
-        <v>26.6654</v>
+        <v>26.6306</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>18.5593</v>
+        <v>18.5698</v>
       </c>
       <c r="C134" t="n">
-        <v>17.1019</v>
+        <v>17.0953</v>
       </c>
       <c r="D134" t="n">
-        <v>39.5386</v>
+        <v>40.1089</v>
       </c>
       <c r="E134" t="n">
-        <v>15.5981</v>
+        <v>15.6099</v>
       </c>
       <c r="F134" t="n">
-        <v>26.2994</v>
+        <v>26.2752</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>17.9755</v>
+        <v>17.9923</v>
       </c>
       <c r="C135" t="n">
-        <v>17.0178</v>
+        <v>17.0191</v>
       </c>
       <c r="D135" t="n">
-        <v>46.5627</v>
+        <v>46.3368</v>
       </c>
       <c r="E135" t="n">
-        <v>15.2665</v>
+        <v>20.7515</v>
       </c>
       <c r="F135" t="n">
-        <v>25.619</v>
+        <v>30.9002</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>17.356</v>
+        <v>17.3554</v>
       </c>
       <c r="C136" t="n">
-        <v>18.7655</v>
+        <v>18.7493</v>
       </c>
       <c r="D136" t="n">
-        <v>45.9996</v>
+        <v>45.9559</v>
       </c>
       <c r="E136" t="n">
-        <v>14.908</v>
+        <v>20.2598</v>
       </c>
       <c r="F136" t="n">
-        <v>24.8936</v>
+        <v>30.1763</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>16.5901</v>
+        <v>16.5043</v>
       </c>
       <c r="C137" t="n">
-        <v>18.5605</v>
+        <v>18.513</v>
       </c>
       <c r="D137" t="n">
-        <v>44.8781</v>
+        <v>44.9926</v>
       </c>
       <c r="E137" t="n">
-        <v>19.8222</v>
+        <v>19.7404</v>
       </c>
       <c r="F137" t="n">
-        <v>30.2022</v>
+        <v>30.1638</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>23.2506</v>
+        <v>23.2525</v>
       </c>
       <c r="C138" t="n">
-        <v>18.3406</v>
+        <v>18.3541</v>
       </c>
       <c r="D138" t="n">
-        <v>44.7639</v>
+        <v>44.6721</v>
       </c>
       <c r="E138" t="n">
-        <v>19.3389</v>
+        <v>19.2794</v>
       </c>
       <c r="F138" t="n">
-        <v>29.7809</v>
+        <v>29.8439</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>22.8873</v>
+        <v>22.8926</v>
       </c>
       <c r="C139" t="n">
-        <v>18.1677</v>
+        <v>18.1665</v>
       </c>
       <c r="D139" t="n">
-        <v>44.1494</v>
+        <v>44.2461</v>
       </c>
       <c r="E139" t="n">
-        <v>18.886</v>
+        <v>18.8382</v>
       </c>
       <c r="F139" t="n">
-        <v>29.0727</v>
+        <v>29.0409</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>22.4937</v>
+        <v>22.4918</v>
       </c>
       <c r="C140" t="n">
-        <v>18.0162</v>
+        <v>18.0054</v>
       </c>
       <c r="D140" t="n">
-        <v>43.5106</v>
+        <v>43.7456</v>
       </c>
       <c r="E140" t="n">
-        <v>18.4907</v>
+        <v>18.4503</v>
       </c>
       <c r="F140" t="n">
-        <v>28.705</v>
+        <v>28.7125</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>22.0511</v>
+        <v>22.0594</v>
       </c>
       <c r="C141" t="n">
-        <v>17.8636</v>
+        <v>17.8688</v>
       </c>
       <c r="D141" t="n">
-        <v>42.7985</v>
+        <v>43.186</v>
       </c>
       <c r="E141" t="n">
-        <v>18.0995</v>
+        <v>18.0581</v>
       </c>
       <c r="F141" t="n">
-        <v>28.4006</v>
+        <v>28.3463</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>21.601</v>
+        <v>21.6383</v>
       </c>
       <c r="C142" t="n">
-        <v>17.7408</v>
+        <v>17.7761</v>
       </c>
       <c r="D142" t="n">
-        <v>42.4473</v>
+        <v>42.5047</v>
       </c>
       <c r="E142" t="n">
-        <v>17.7371</v>
+        <v>17.685</v>
       </c>
       <c r="F142" t="n">
-        <v>28.359</v>
+        <v>28.4359</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>21.1173</v>
+        <v>21.1391</v>
       </c>
       <c r="C143" t="n">
-        <v>17.6113</v>
+        <v>17.6171</v>
       </c>
       <c r="D143" t="n">
-        <v>41.8692</v>
+        <v>41.9699</v>
       </c>
       <c r="E143" t="n">
-        <v>17.3722</v>
+        <v>17.3657</v>
       </c>
       <c r="F143" t="n">
-        <v>28.0245</v>
+        <v>28.0644</v>
       </c>
     </row>
   </sheetData>

--- a/clang-x64/Running erasure.xlsx
+++ b/clang-x64/Running erasure.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>18.3565</v>
+        <v>17.916</v>
       </c>
       <c r="C2" t="n">
-        <v>13.1645</v>
+        <v>13.1601</v>
       </c>
       <c r="D2" t="n">
-        <v>29.8558</v>
+        <v>29.8729</v>
       </c>
       <c r="E2" t="n">
-        <v>13.0541</v>
+        <v>13.0642</v>
       </c>
       <c r="F2" t="n">
-        <v>25.6326</v>
+        <v>25.2402</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>18.1416</v>
+        <v>18.2083</v>
       </c>
       <c r="C3" t="n">
-        <v>13.2216</v>
+        <v>13.2301</v>
       </c>
       <c r="D3" t="n">
-        <v>30.0601</v>
+        <v>30.012</v>
       </c>
       <c r="E3" t="n">
-        <v>12.9403</v>
+        <v>12.8382</v>
       </c>
       <c r="F3" t="n">
-        <v>25.4452</v>
+        <v>25.0351</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>17.5619</v>
+        <v>17.5409</v>
       </c>
       <c r="C4" t="n">
-        <v>13.4295</v>
+        <v>13.5695</v>
       </c>
       <c r="D4" t="n">
-        <v>30.2483</v>
+        <v>30.3008</v>
       </c>
       <c r="E4" t="n">
-        <v>12.7755</v>
+        <v>12.5547</v>
       </c>
       <c r="F4" t="n">
-        <v>25.1504</v>
+        <v>24.7482</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>17.1037</v>
+        <v>16.943</v>
       </c>
       <c r="C5" t="n">
-        <v>13.5375</v>
+        <v>13.6708</v>
       </c>
       <c r="D5" t="n">
-        <v>30.3997</v>
+        <v>30.398</v>
       </c>
       <c r="E5" t="n">
-        <v>12.3853</v>
+        <v>12.7854</v>
       </c>
       <c r="F5" t="n">
-        <v>25.2698</v>
+        <v>24.9031</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>16.6607</v>
+        <v>16.5741</v>
       </c>
       <c r="C6" t="n">
-        <v>13.8019</v>
+        <v>13.7094</v>
       </c>
       <c r="D6" t="n">
-        <v>30.3702</v>
+        <v>30.4179</v>
       </c>
       <c r="E6" t="n">
-        <v>12.5602</v>
+        <v>12.9507</v>
       </c>
       <c r="F6" t="n">
-        <v>25.3383</v>
+        <v>24.8869</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>16.0268</v>
+        <v>16.2387</v>
       </c>
       <c r="C7" t="n">
-        <v>14.0108</v>
+        <v>14.0992</v>
       </c>
       <c r="D7" t="n">
-        <v>29.5475</v>
+        <v>29.5917</v>
       </c>
       <c r="E7" t="n">
-        <v>19.3719</v>
+        <v>19.6527</v>
       </c>
       <c r="F7" t="n">
-        <v>30.1791</v>
+        <v>29.1323</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>15.7683</v>
+        <v>15.6529</v>
       </c>
       <c r="C8" t="n">
-        <v>15.4346</v>
+        <v>15.4978</v>
       </c>
       <c r="D8" t="n">
-        <v>29.7138</v>
+        <v>29.6386</v>
       </c>
       <c r="E8" t="n">
-        <v>18.5584</v>
+        <v>19.1504</v>
       </c>
       <c r="F8" t="n">
-        <v>29.7722</v>
+        <v>28.5949</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>15.1549</v>
+        <v>14.99</v>
       </c>
       <c r="C9" t="n">
-        <v>15.6645</v>
+        <v>15.5776</v>
       </c>
       <c r="D9" t="n">
-        <v>29.7378</v>
+        <v>29.6938</v>
       </c>
       <c r="E9" t="n">
-        <v>18.2995</v>
+        <v>18.7161</v>
       </c>
       <c r="F9" t="n">
-        <v>29.5554</v>
+        <v>28.324</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>21.6547</v>
+        <v>21.6787</v>
       </c>
       <c r="C10" t="n">
-        <v>15.6912</v>
+        <v>15.7578</v>
       </c>
       <c r="D10" t="n">
-        <v>29.8229</v>
+        <v>29.6643</v>
       </c>
       <c r="E10" t="n">
-        <v>17.9449</v>
+        <v>18.3027</v>
       </c>
       <c r="F10" t="n">
-        <v>29.1289</v>
+        <v>28.2004</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>21.3898</v>
+        <v>21.4668</v>
       </c>
       <c r="C11" t="n">
-        <v>15.7893</v>
+        <v>15.861</v>
       </c>
       <c r="D11" t="n">
-        <v>29.9437</v>
+        <v>29.762</v>
       </c>
       <c r="E11" t="n">
-        <v>17.4105</v>
+        <v>18.0535</v>
       </c>
       <c r="F11" t="n">
-        <v>28.9758</v>
+        <v>27.8296</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>21.105</v>
+        <v>21.155</v>
       </c>
       <c r="C12" t="n">
-        <v>15.9422</v>
+        <v>15.9372</v>
       </c>
       <c r="D12" t="n">
-        <v>30.0244</v>
+        <v>30.1145</v>
       </c>
       <c r="E12" t="n">
-        <v>17.1416</v>
+        <v>17.5445</v>
       </c>
       <c r="F12" t="n">
-        <v>28.6708</v>
+        <v>27.9629</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>20.9606</v>
+        <v>20.7869</v>
       </c>
       <c r="C13" t="n">
-        <v>16.0807</v>
+        <v>16.2754</v>
       </c>
       <c r="D13" t="n">
-        <v>30.1545</v>
+        <v>30.1818</v>
       </c>
       <c r="E13" t="n">
-        <v>16.8854</v>
+        <v>17.1383</v>
       </c>
       <c r="F13" t="n">
-        <v>28.5868</v>
+        <v>27.7166</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>20.5226</v>
+        <v>20.4643</v>
       </c>
       <c r="C14" t="n">
-        <v>16.2731</v>
+        <v>16.4162</v>
       </c>
       <c r="D14" t="n">
-        <v>30.2434</v>
+        <v>30.255</v>
       </c>
       <c r="E14" t="n">
-        <v>16.6475</v>
+        <v>16.8324</v>
       </c>
       <c r="F14" t="n">
-        <v>27.9213</v>
+        <v>27.606</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>20.1913</v>
+        <v>20.1091</v>
       </c>
       <c r="C15" t="n">
-        <v>16.186</v>
+        <v>16.2589</v>
       </c>
       <c r="D15" t="n">
-        <v>30.2854</v>
+        <v>30.4466</v>
       </c>
       <c r="E15" t="n">
-        <v>16.3286</v>
+        <v>16.5539</v>
       </c>
       <c r="F15" t="n">
-        <v>27.5622</v>
+        <v>26.8738</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>19.8475</v>
+        <v>19.7621</v>
       </c>
       <c r="C16" t="n">
-        <v>16.317</v>
+        <v>16.3263</v>
       </c>
       <c r="D16" t="n">
-        <v>30.4054</v>
+        <v>30.5175</v>
       </c>
       <c r="E16" t="n">
-        <v>15.9633</v>
+        <v>16.3513</v>
       </c>
       <c r="F16" t="n">
-        <v>27.0622</v>
+        <v>26.6769</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>19.3034</v>
+        <v>19.4163</v>
       </c>
       <c r="C17" t="n">
-        <v>16.2672</v>
+        <v>16.3506</v>
       </c>
       <c r="D17" t="n">
-        <v>30.6716</v>
+        <v>30.8041</v>
       </c>
       <c r="E17" t="n">
-        <v>15.6559</v>
+        <v>15.9038</v>
       </c>
       <c r="F17" t="n">
-        <v>26.8119</v>
+        <v>26.3262</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>18.9116</v>
+        <v>18.9649</v>
       </c>
       <c r="C18" t="n">
-        <v>16.3177</v>
+        <v>16.3774</v>
       </c>
       <c r="D18" t="n">
-        <v>30.8793</v>
+        <v>30.9885</v>
       </c>
       <c r="E18" t="n">
-        <v>15.4516</v>
+        <v>15.6581</v>
       </c>
       <c r="F18" t="n">
-        <v>26.5299</v>
+        <v>26.0774</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>18.4012</v>
+        <v>18.4809</v>
       </c>
       <c r="C19" t="n">
-        <v>16.4507</v>
+        <v>16.4093</v>
       </c>
       <c r="D19" t="n">
-        <v>30.9599</v>
+        <v>30.9315</v>
       </c>
       <c r="E19" t="n">
-        <v>15.0455</v>
+        <v>15.1616</v>
       </c>
       <c r="F19" t="n">
-        <v>26.144</v>
+        <v>25.7744</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>17.8758</v>
+        <v>17.9417</v>
       </c>
       <c r="C20" t="n">
-        <v>16.209</v>
+        <v>16.2541</v>
       </c>
       <c r="D20" t="n">
-        <v>31.0737</v>
+        <v>30.9932</v>
       </c>
       <c r="E20" t="n">
-        <v>14.6414</v>
+        <v>14.8636</v>
       </c>
       <c r="F20" t="n">
-        <v>25.8434</v>
+        <v>25.5554</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>17.3178</v>
+        <v>17.3662</v>
       </c>
       <c r="C21" t="n">
-        <v>16.2159</v>
+        <v>16.2489</v>
       </c>
       <c r="D21" t="n">
-        <v>30.2988</v>
+        <v>30.4139</v>
       </c>
       <c r="E21" t="n">
-        <v>20.4899</v>
+        <v>20.944</v>
       </c>
       <c r="F21" t="n">
-        <v>30.8193</v>
+        <v>29.9141</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>16.6635</v>
+        <v>16.7078</v>
       </c>
       <c r="C22" t="n">
-        <v>17.6437</v>
+        <v>17.7515</v>
       </c>
       <c r="D22" t="n">
-        <v>30.0183</v>
+        <v>30.1386</v>
       </c>
       <c r="E22" t="n">
-        <v>19.9819</v>
+        <v>20.3959</v>
       </c>
       <c r="F22" t="n">
-        <v>30.3746</v>
+        <v>29.5898</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>16.0141</v>
+        <v>16.0106</v>
       </c>
       <c r="C23" t="n">
-        <v>17.6274</v>
+        <v>17.6163</v>
       </c>
       <c r="D23" t="n">
-        <v>30.1593</v>
+        <v>30.4217</v>
       </c>
       <c r="E23" t="n">
-        <v>19.4704</v>
+        <v>19.92</v>
       </c>
       <c r="F23" t="n">
-        <v>30.1025</v>
+        <v>29.2425</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>22.527</v>
+        <v>22.4943</v>
       </c>
       <c r="C24" t="n">
-        <v>17.4965</v>
+        <v>17.5422</v>
       </c>
       <c r="D24" t="n">
-        <v>30.1786</v>
+        <v>30.4072</v>
       </c>
       <c r="E24" t="n">
-        <v>18.9964</v>
+        <v>19.454</v>
       </c>
       <c r="F24" t="n">
-        <v>29.8042</v>
+        <v>29.0103</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>22.2712</v>
+        <v>22.3155</v>
       </c>
       <c r="C25" t="n">
-        <v>17.3882</v>
+        <v>17.4907</v>
       </c>
       <c r="D25" t="n">
-        <v>30.4941</v>
+        <v>30.7077</v>
       </c>
       <c r="E25" t="n">
-        <v>18.6233</v>
+        <v>18.9775</v>
       </c>
       <c r="F25" t="n">
-        <v>29.3626</v>
+        <v>28.6146</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>21.9002</v>
+        <v>21.9288</v>
       </c>
       <c r="C26" t="n">
-        <v>17.3812</v>
+        <v>17.4048</v>
       </c>
       <c r="D26" t="n">
-        <v>30.4738</v>
+        <v>30.8035</v>
       </c>
       <c r="E26" t="n">
-        <v>18.3502</v>
+        <v>18.4967</v>
       </c>
       <c r="F26" t="n">
-        <v>28.9463</v>
+        <v>28.292</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>21.6332</v>
+        <v>21.5484</v>
       </c>
       <c r="C27" t="n">
-        <v>17.2121</v>
+        <v>17.2887</v>
       </c>
       <c r="D27" t="n">
-        <v>30.4826</v>
+        <v>30.6346</v>
       </c>
       <c r="E27" t="n">
-        <v>17.6591</v>
+        <v>18.107</v>
       </c>
       <c r="F27" t="n">
-        <v>28.6544</v>
+        <v>28.0942</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>21.2788</v>
+        <v>21.2514</v>
       </c>
       <c r="C28" t="n">
-        <v>17.175</v>
+        <v>17.2617</v>
       </c>
       <c r="D28" t="n">
-        <v>30.5915</v>
+        <v>30.8268</v>
       </c>
       <c r="E28" t="n">
-        <v>17.3568</v>
+        <v>17.7016</v>
       </c>
       <c r="F28" t="n">
-        <v>28.1722</v>
+        <v>27.7493</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>20.7753</v>
+        <v>20.9307</v>
       </c>
       <c r="C29" t="n">
-        <v>17.1852</v>
+        <v>17.2133</v>
       </c>
       <c r="D29" t="n">
-        <v>30.6904</v>
+        <v>30.8372</v>
       </c>
       <c r="E29" t="n">
-        <v>16.9445</v>
+        <v>17.2863</v>
       </c>
       <c r="F29" t="n">
-        <v>27.9261</v>
+        <v>27.473</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>20.4481</v>
+        <v>20.4823</v>
       </c>
       <c r="C30" t="n">
-        <v>17.1081</v>
+        <v>17.1376</v>
       </c>
       <c r="D30" t="n">
-        <v>30.6246</v>
+        <v>30.9175</v>
       </c>
       <c r="E30" t="n">
-        <v>16.6104</v>
+        <v>16.9702</v>
       </c>
       <c r="F30" t="n">
-        <v>27.7002</v>
+        <v>27.1461</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>20.0151</v>
+        <v>19.9838</v>
       </c>
       <c r="C31" t="n">
-        <v>17.1522</v>
+        <v>17.094</v>
       </c>
       <c r="D31" t="n">
-        <v>30.7591</v>
+        <v>30.9929</v>
       </c>
       <c r="E31" t="n">
-        <v>16.2422</v>
+        <v>16.5964</v>
       </c>
       <c r="F31" t="n">
-        <v>27.2466</v>
+        <v>26.8319</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>19.4693</v>
+        <v>19.5186</v>
       </c>
       <c r="C32" t="n">
-        <v>16.9839</v>
+        <v>17.0295</v>
       </c>
       <c r="D32" t="n">
-        <v>30.839</v>
+        <v>31.0509</v>
       </c>
       <c r="E32" t="n">
-        <v>15.8859</v>
+        <v>16.1345</v>
       </c>
       <c r="F32" t="n">
-        <v>26.8389</v>
+        <v>26.5971</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>18.9378</v>
+        <v>18.9547</v>
       </c>
       <c r="C33" t="n">
-        <v>16.9271</v>
+        <v>16.9069</v>
       </c>
       <c r="D33" t="n">
-        <v>31.0605</v>
+        <v>31.3634</v>
       </c>
       <c r="E33" t="n">
-        <v>15.6105</v>
+        <v>16.0068</v>
       </c>
       <c r="F33" t="n">
-        <v>26.5591</v>
+        <v>26.2216</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>18.4565</v>
+        <v>18.5146</v>
       </c>
       <c r="C34" t="n">
-        <v>16.8471</v>
+        <v>16.8371</v>
       </c>
       <c r="D34" t="n">
-        <v>31.2876</v>
+        <v>31.5057</v>
       </c>
       <c r="E34" t="n">
-        <v>15.255</v>
+        <v>15.6392</v>
       </c>
       <c r="F34" t="n">
-        <v>26.2249</v>
+        <v>25.9153</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>17.8665</v>
+        <v>17.8573</v>
       </c>
       <c r="C35" t="n">
-        <v>16.8098</v>
+        <v>16.8158</v>
       </c>
       <c r="D35" t="n">
-        <v>30.6466</v>
+        <v>30.938</v>
       </c>
       <c r="E35" t="n">
-        <v>20.795</v>
+        <v>21.1626</v>
       </c>
       <c r="F35" t="n">
-        <v>31.0727</v>
+        <v>30.4331</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>17.3027</v>
+        <v>17.259</v>
       </c>
       <c r="C36" t="n">
-        <v>16.7692</v>
+        <v>16.7604</v>
       </c>
       <c r="D36" t="n">
-        <v>30.8248</v>
+        <v>30.9228</v>
       </c>
       <c r="E36" t="n">
-        <v>20.2225</v>
+        <v>20.5991</v>
       </c>
       <c r="F36" t="n">
-        <v>30.8048</v>
+        <v>29.6333</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>16.7591</v>
+        <v>16.6773</v>
       </c>
       <c r="C37" t="n">
-        <v>18.27</v>
+        <v>18.1869</v>
       </c>
       <c r="D37" t="n">
-        <v>30.6935</v>
+        <v>30.6801</v>
       </c>
       <c r="E37" t="n">
-        <v>19.5965</v>
+        <v>20.031</v>
       </c>
       <c r="F37" t="n">
-        <v>30.2733</v>
+        <v>29.3087</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>23.0657</v>
+        <v>23.0606</v>
       </c>
       <c r="C38" t="n">
-        <v>18.1571</v>
+        <v>18.0181</v>
       </c>
       <c r="D38" t="n">
-        <v>30.7751</v>
+        <v>30.7144</v>
       </c>
       <c r="E38" t="n">
-        <v>19.2592</v>
+        <v>19.5351</v>
       </c>
       <c r="F38" t="n">
-        <v>30.0247</v>
+        <v>28.8987</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>22.8131</v>
+        <v>22.7806</v>
       </c>
       <c r="C39" t="n">
-        <v>17.9673</v>
+        <v>17.8442</v>
       </c>
       <c r="D39" t="n">
-        <v>30.7058</v>
+        <v>30.6742</v>
       </c>
       <c r="E39" t="n">
-        <v>18.6581</v>
+        <v>19.1341</v>
       </c>
       <c r="F39" t="n">
-        <v>29.6378</v>
+        <v>28.54</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>22.4528</v>
+        <v>22.4717</v>
       </c>
       <c r="C40" t="n">
-        <v>17.7213</v>
+        <v>17.6776</v>
       </c>
       <c r="D40" t="n">
-        <v>30.8659</v>
+        <v>30.8939</v>
       </c>
       <c r="E40" t="n">
-        <v>18.3322</v>
+        <v>18.7956</v>
       </c>
       <c r="F40" t="n">
-        <v>29.2723</v>
+        <v>28.2278</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>22.0943</v>
+        <v>22.1394</v>
       </c>
       <c r="C41" t="n">
-        <v>17.6521</v>
+        <v>17.6128</v>
       </c>
       <c r="D41" t="n">
-        <v>30.8946</v>
+        <v>30.9894</v>
       </c>
       <c r="E41" t="n">
-        <v>17.927</v>
+        <v>18.3314</v>
       </c>
       <c r="F41" t="n">
-        <v>28.9128</v>
+        <v>27.9573</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>21.653</v>
+        <v>21.7344</v>
       </c>
       <c r="C42" t="n">
-        <v>17.5314</v>
+        <v>17.5597</v>
       </c>
       <c r="D42" t="n">
-        <v>30.9487</v>
+        <v>30.9742</v>
       </c>
       <c r="E42" t="n">
-        <v>17.6283</v>
+        <v>17.9766</v>
       </c>
       <c r="F42" t="n">
-        <v>28.4349</v>
+        <v>27.6238</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>21.2208</v>
+        <v>21.274</v>
       </c>
       <c r="C43" t="n">
-        <v>17.4426</v>
+        <v>17.4617</v>
       </c>
       <c r="D43" t="n">
-        <v>31.0149</v>
+        <v>30.971</v>
       </c>
       <c r="E43" t="n">
-        <v>17.2227</v>
+        <v>17.6026</v>
       </c>
       <c r="F43" t="n">
-        <v>28.0224</v>
+        <v>27.3061</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>20.725</v>
+        <v>20.7816</v>
       </c>
       <c r="C44" t="n">
-        <v>17.3186</v>
+        <v>17.3232</v>
       </c>
       <c r="D44" t="n">
-        <v>31.1898</v>
+        <v>31.1525</v>
       </c>
       <c r="E44" t="n">
-        <v>16.8958</v>
+        <v>17.2722</v>
       </c>
       <c r="F44" t="n">
-        <v>27.7112</v>
+        <v>26.9664</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>20.2409</v>
+        <v>20.2812</v>
       </c>
       <c r="C45" t="n">
-        <v>17.2801</v>
+        <v>17.2827</v>
       </c>
       <c r="D45" t="n">
-        <v>31.1817</v>
+        <v>31.2365</v>
       </c>
       <c r="E45" t="n">
-        <v>16.5518</v>
+        <v>16.8255</v>
       </c>
       <c r="F45" t="n">
-        <v>27.346</v>
+        <v>26.6925</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>19.8912</v>
+        <v>19.8386</v>
       </c>
       <c r="C46" t="n">
-        <v>17.2079</v>
+        <v>17.214</v>
       </c>
       <c r="D46" t="n">
-        <v>31.4594</v>
+        <v>31.2183</v>
       </c>
       <c r="E46" t="n">
-        <v>16.1836</v>
+        <v>16.4928</v>
       </c>
       <c r="F46" t="n">
-        <v>27.1086</v>
+        <v>26.3244</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>19.3317</v>
+        <v>19.337</v>
       </c>
       <c r="C47" t="n">
-        <v>17.0561</v>
+        <v>17.0782</v>
       </c>
       <c r="D47" t="n">
-        <v>31.4178</v>
+        <v>31.4154</v>
       </c>
       <c r="E47" t="n">
-        <v>15.847</v>
+        <v>16.2659</v>
       </c>
       <c r="F47" t="n">
-        <v>26.708</v>
+        <v>25.9521</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>18.8334</v>
+        <v>18.8595</v>
       </c>
       <c r="C48" t="n">
-        <v>16.9964</v>
+        <v>17.0031</v>
       </c>
       <c r="D48" t="n">
-        <v>31.5075</v>
+        <v>31.4984</v>
       </c>
       <c r="E48" t="n">
-        <v>15.5423</v>
+        <v>15.8571</v>
       </c>
       <c r="F48" t="n">
-        <v>26.3471</v>
+        <v>25.6579</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>18.2296</v>
+        <v>18.2495</v>
       </c>
       <c r="C49" t="n">
-        <v>16.9709</v>
+        <v>16.9654</v>
       </c>
       <c r="D49" t="n">
-        <v>31.6952</v>
+        <v>31.4449</v>
       </c>
       <c r="E49" t="n">
-        <v>15.179</v>
+        <v>15.3809</v>
       </c>
       <c r="F49" t="n">
-        <v>25.9915</v>
+        <v>25.6997</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>17.6432</v>
+        <v>17.6661</v>
       </c>
       <c r="C50" t="n">
-        <v>16.9249</v>
+        <v>16.9139</v>
       </c>
       <c r="D50" t="n">
-        <v>31.2257</v>
+        <v>31.1869</v>
       </c>
       <c r="E50" t="n">
-        <v>20.3313</v>
+        <v>20.7514</v>
       </c>
       <c r="F50" t="n">
-        <v>30.8117</v>
+        <v>29.9717</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>16.9366</v>
+        <v>16.9071</v>
       </c>
       <c r="C51" t="n">
-        <v>18.3161</v>
+        <v>18.3285</v>
       </c>
       <c r="D51" t="n">
-        <v>31.2286</v>
+        <v>31.323</v>
       </c>
       <c r="E51" t="n">
-        <v>19.7912</v>
+        <v>20.233</v>
       </c>
       <c r="F51" t="n">
-        <v>30.4574</v>
+        <v>29.2412</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>16.0855</v>
+        <v>16.1251</v>
       </c>
       <c r="C52" t="n">
-        <v>18.185</v>
+        <v>18.2122</v>
       </c>
       <c r="D52" t="n">
-        <v>31.3408</v>
+        <v>31.4347</v>
       </c>
       <c r="E52" t="n">
-        <v>19.3278</v>
+        <v>19.7995</v>
       </c>
       <c r="F52" t="n">
-        <v>30.054</v>
+        <v>29.0067</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>22.9579</v>
+        <v>22.9515</v>
       </c>
       <c r="C53" t="n">
-        <v>18.0505</v>
+        <v>18.0387</v>
       </c>
       <c r="D53" t="n">
-        <v>31.4346</v>
+        <v>31.4673</v>
       </c>
       <c r="E53" t="n">
-        <v>18.9943</v>
+        <v>19.2906</v>
       </c>
       <c r="F53" t="n">
-        <v>29.6641</v>
+        <v>28.9962</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>22.6531</v>
+        <v>22.6665</v>
       </c>
       <c r="C54" t="n">
-        <v>17.8866</v>
+        <v>17.896</v>
       </c>
       <c r="D54" t="n">
-        <v>31.4977</v>
+        <v>31.5152</v>
       </c>
       <c r="E54" t="n">
-        <v>18.4964</v>
+        <v>18.8206</v>
       </c>
       <c r="F54" t="n">
-        <v>29.3552</v>
+        <v>28.8965</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>22.2683</v>
+        <v>22.3095</v>
       </c>
       <c r="C55" t="n">
-        <v>17.7764</v>
+        <v>17.7689</v>
       </c>
       <c r="D55" t="n">
-        <v>31.713</v>
+        <v>31.7337</v>
       </c>
       <c r="E55" t="n">
-        <v>18.2269</v>
+        <v>18.0483</v>
       </c>
       <c r="F55" t="n">
-        <v>29.0103</v>
+        <v>28.5472</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>21.844</v>
+        <v>21.8621</v>
       </c>
       <c r="C56" t="n">
-        <v>17.6309</v>
+        <v>17.6556</v>
       </c>
       <c r="D56" t="n">
-        <v>31.919</v>
+        <v>31.8968</v>
       </c>
       <c r="E56" t="n">
-        <v>17.7855</v>
+        <v>18.0408</v>
       </c>
       <c r="F56" t="n">
-        <v>28.6162</v>
+        <v>28.1836</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>21.3845</v>
+        <v>21.4341</v>
       </c>
       <c r="C57" t="n">
-        <v>17.5823</v>
+        <v>17.6092</v>
       </c>
       <c r="D57" t="n">
-        <v>32.0142</v>
+        <v>32.257</v>
       </c>
       <c r="E57" t="n">
-        <v>17.3947</v>
+        <v>17.6606</v>
       </c>
       <c r="F57" t="n">
-        <v>28.2628</v>
+        <v>27.8317</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>20.9576</v>
+        <v>20.9663</v>
       </c>
       <c r="C58" t="n">
-        <v>17.4567</v>
+        <v>17.4996</v>
       </c>
       <c r="D58" t="n">
-        <v>32.3056</v>
+        <v>32.3517</v>
       </c>
       <c r="E58" t="n">
-        <v>17.059</v>
+        <v>17.3143</v>
       </c>
       <c r="F58" t="n">
-        <v>27.8748</v>
+        <v>27.556</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>20.4711</v>
+        <v>20.511</v>
       </c>
       <c r="C59" t="n">
-        <v>17.3939</v>
+        <v>17.3789</v>
       </c>
       <c r="D59" t="n">
-        <v>32.6037</v>
+        <v>32.4721</v>
       </c>
       <c r="E59" t="n">
-        <v>16.7175</v>
+        <v>17.0397</v>
       </c>
       <c r="F59" t="n">
-        <v>27.5298</v>
+        <v>27.2907</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>20.0148</v>
+        <v>20.0662</v>
       </c>
       <c r="C60" t="n">
-        <v>17.3156</v>
+        <v>17.3194</v>
       </c>
       <c r="D60" t="n">
-        <v>32.9718</v>
+        <v>32.8432</v>
       </c>
       <c r="E60" t="n">
-        <v>16.4382</v>
+        <v>16.6877</v>
       </c>
       <c r="F60" t="n">
-        <v>27.2576</v>
+        <v>26.9322</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>19.489</v>
+        <v>19.472</v>
       </c>
       <c r="C61" t="n">
-        <v>17.178</v>
+        <v>17.1835</v>
       </c>
       <c r="D61" t="n">
-        <v>33.21</v>
+        <v>33.2414</v>
       </c>
       <c r="E61" t="n">
-        <v>16.0692</v>
+        <v>16.4098</v>
       </c>
       <c r="F61" t="n">
-        <v>26.8663</v>
+        <v>26.7035</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>18.9657</v>
+        <v>18.9313</v>
       </c>
       <c r="C62" t="n">
-        <v>17.1256</v>
+        <v>17.1279</v>
       </c>
       <c r="D62" t="n">
-        <v>33.6402</v>
+        <v>33.3842</v>
       </c>
       <c r="E62" t="n">
-        <v>15.6783</v>
+        <v>15.9467</v>
       </c>
       <c r="F62" t="n">
-        <v>26.4723</v>
+        <v>26.3101</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>18.4055</v>
+        <v>18.4032</v>
       </c>
       <c r="C63" t="n">
-        <v>17.1579</v>
+        <v>17.1124</v>
       </c>
       <c r="D63" t="n">
-        <v>33.8837</v>
+        <v>33.751</v>
       </c>
       <c r="E63" t="n">
-        <v>15.3661</v>
+        <v>15.5548</v>
       </c>
       <c r="F63" t="n">
-        <v>26.1399</v>
+        <v>25.9722</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>17.8666</v>
+        <v>17.8217</v>
       </c>
       <c r="C64" t="n">
-        <v>16.9932</v>
+        <v>16.9838</v>
       </c>
       <c r="D64" t="n">
-        <v>38.3726</v>
+        <v>38.3786</v>
       </c>
       <c r="E64" t="n">
-        <v>21.4971</v>
+        <v>21.644</v>
       </c>
       <c r="F64" t="n">
-        <v>30.9381</v>
+        <v>29.8267</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>17.1392</v>
+        <v>17.151</v>
       </c>
       <c r="C65" t="n">
-        <v>18.5855</v>
+        <v>18.604</v>
       </c>
       <c r="D65" t="n">
-        <v>37.9651</v>
+        <v>37.9296</v>
       </c>
       <c r="E65" t="n">
-        <v>20.769</v>
+        <v>21.3841</v>
       </c>
       <c r="F65" t="n">
-        <v>30.5605</v>
+        <v>29.4643</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>16.3124</v>
+        <v>16.3807</v>
       </c>
       <c r="C66" t="n">
-        <v>18.4736</v>
+        <v>18.3641</v>
       </c>
       <c r="D66" t="n">
-        <v>38.2096</v>
+        <v>38.0348</v>
       </c>
       <c r="E66" t="n">
-        <v>20.5709</v>
+        <v>20.786</v>
       </c>
       <c r="F66" t="n">
-        <v>30.1678</v>
+        <v>29.0659</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>23.1497</v>
+        <v>23.1663</v>
       </c>
       <c r="C67" t="n">
-        <v>18.2037</v>
+        <v>18.302</v>
       </c>
       <c r="D67" t="n">
-        <v>38.605</v>
+        <v>38.5404</v>
       </c>
       <c r="E67" t="n">
-        <v>19.9273</v>
+        <v>20.2802</v>
       </c>
       <c r="F67" t="n">
-        <v>29.771</v>
+        <v>28.7429</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>22.8098</v>
+        <v>22.8132</v>
       </c>
       <c r="C68" t="n">
-        <v>18.0718</v>
+        <v>18.0528</v>
       </c>
       <c r="D68" t="n">
-        <v>38.8405</v>
+        <v>38.8671</v>
       </c>
       <c r="E68" t="n">
-        <v>19.3199</v>
+        <v>19.5381</v>
       </c>
       <c r="F68" t="n">
-        <v>29.4403</v>
+        <v>28.4048</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>22.3989</v>
+        <v>22.4326</v>
       </c>
       <c r="C69" t="n">
-        <v>17.914</v>
+        <v>17.908</v>
       </c>
       <c r="D69" t="n">
-        <v>39.3574</v>
+        <v>39.3651</v>
       </c>
       <c r="E69" t="n">
-        <v>18.8251</v>
+        <v>19.0199</v>
       </c>
       <c r="F69" t="n">
-        <v>29.0875</v>
+        <v>28.0628</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>21.9977</v>
+        <v>22.0008</v>
       </c>
       <c r="C70" t="n">
-        <v>17.8507</v>
+        <v>17.8604</v>
       </c>
       <c r="D70" t="n">
-        <v>39.3728</v>
+        <v>39.3116</v>
       </c>
       <c r="E70" t="n">
-        <v>18.1584</v>
+        <v>18.491</v>
       </c>
       <c r="F70" t="n">
-        <v>28.6991</v>
+        <v>27.6721</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>21.5281</v>
+        <v>21.5167</v>
       </c>
       <c r="C71" t="n">
-        <v>17.7114</v>
+        <v>17.7174</v>
       </c>
       <c r="D71" t="n">
-        <v>39.2595</v>
+        <v>39.5046</v>
       </c>
       <c r="E71" t="n">
-        <v>17.7234</v>
+        <v>18.0139</v>
       </c>
       <c r="F71" t="n">
-        <v>28.3483</v>
+        <v>27.3845</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>21.0743</v>
+        <v>21.0736</v>
       </c>
       <c r="C72" t="n">
-        <v>17.5507</v>
+        <v>17.6053</v>
       </c>
       <c r="D72" t="n">
-        <v>39.4784</v>
+        <v>39.2583</v>
       </c>
       <c r="E72" t="n">
-        <v>17.2646</v>
+        <v>17.4598</v>
       </c>
       <c r="F72" t="n">
-        <v>28.0308</v>
+        <v>27.7266</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>20.6029</v>
+        <v>20.5909</v>
       </c>
       <c r="C73" t="n">
-        <v>17.5081</v>
+        <v>17.4733</v>
       </c>
       <c r="D73" t="n">
-        <v>39.3317</v>
+        <v>39.5968</v>
       </c>
       <c r="E73" t="n">
-        <v>16.9123</v>
+        <v>17.122</v>
       </c>
       <c r="F73" t="n">
-        <v>27.6859</v>
+        <v>27.45</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>20.1463</v>
+        <v>20.1381</v>
       </c>
       <c r="C74" t="n">
-        <v>17.3666</v>
+        <v>17.3491</v>
       </c>
       <c r="D74" t="n">
-        <v>39.53</v>
+        <v>39.5996</v>
       </c>
       <c r="E74" t="n">
-        <v>16.6045</v>
+        <v>16.7441</v>
       </c>
       <c r="F74" t="n">
-        <v>27.3867</v>
+        <v>27.1785</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>19.5877</v>
+        <v>19.5981</v>
       </c>
       <c r="C75" t="n">
-        <v>17.3049</v>
+        <v>17.2667</v>
       </c>
       <c r="D75" t="n">
-        <v>39.5256</v>
+        <v>39.5394</v>
       </c>
       <c r="E75" t="n">
-        <v>16.2065</v>
+        <v>16.4348</v>
       </c>
       <c r="F75" t="n">
-        <v>27.0084</v>
+        <v>26.7814</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>19.1406</v>
+        <v>19.1353</v>
       </c>
       <c r="C76" t="n">
-        <v>17.1743</v>
+        <v>17.2275</v>
       </c>
       <c r="D76" t="n">
-        <v>39.8295</v>
+        <v>39.7359</v>
       </c>
       <c r="E76" t="n">
-        <v>15.8754</v>
+        <v>16.0639</v>
       </c>
       <c r="F76" t="n">
-        <v>26.6394</v>
+        <v>26.5612</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>18.6038</v>
+        <v>18.6267</v>
       </c>
       <c r="C77" t="n">
-        <v>17.0907</v>
+        <v>17.1161</v>
       </c>
       <c r="D77" t="n">
-        <v>39.3565</v>
+        <v>39.445</v>
       </c>
       <c r="E77" t="n">
-        <v>15.5635</v>
+        <v>15.704</v>
       </c>
       <c r="F77" t="n">
-        <v>26.3199</v>
+        <v>26.1471</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>17.9901</v>
+        <v>17.9847</v>
       </c>
       <c r="C78" t="n">
-        <v>17.0226</v>
+        <v>17.0441</v>
       </c>
       <c r="D78" t="n">
-        <v>46.3727</v>
+        <v>46.3449</v>
       </c>
       <c r="E78" t="n">
-        <v>20.8185</v>
+        <v>21.1882</v>
       </c>
       <c r="F78" t="n">
-        <v>31.1153</v>
+        <v>30.4529</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>17.3048</v>
+        <v>17.3689</v>
       </c>
       <c r="C79" t="n">
-        <v>18.8299</v>
+        <v>18.8606</v>
       </c>
       <c r="D79" t="n">
-        <v>46.3616</v>
+        <v>46.2429</v>
       </c>
       <c r="E79" t="n">
-        <v>20.312</v>
+        <v>20.6825</v>
       </c>
       <c r="F79" t="n">
-        <v>30.7454</v>
+        <v>30.0422</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>16.573</v>
+        <v>16.6196</v>
       </c>
       <c r="C80" t="n">
-        <v>18.5806</v>
+        <v>18.6116</v>
       </c>
       <c r="D80" t="n">
-        <v>45.8918</v>
+        <v>45.7913</v>
       </c>
       <c r="E80" t="n">
-        <v>19.8195</v>
+        <v>19.7214</v>
       </c>
       <c r="F80" t="n">
-        <v>30.3465</v>
+        <v>29.8123</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>23.2955</v>
+        <v>23.2878</v>
       </c>
       <c r="C81" t="n">
-        <v>18.4189</v>
+        <v>18.4552</v>
       </c>
       <c r="D81" t="n">
-        <v>45.1713</v>
+        <v>45.2576</v>
       </c>
       <c r="E81" t="n">
-        <v>19.3321</v>
+        <v>19.2968</v>
       </c>
       <c r="F81" t="n">
-        <v>29.9867</v>
+        <v>29.4402</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>22.9082</v>
+        <v>22.925</v>
       </c>
       <c r="C82" t="n">
-        <v>18.241</v>
+        <v>18.2381</v>
       </c>
       <c r="D82" t="n">
-        <v>44.7325</v>
+        <v>44.6284</v>
       </c>
       <c r="E82" t="n">
-        <v>18.9525</v>
+        <v>18.8146</v>
       </c>
       <c r="F82" t="n">
-        <v>29.6017</v>
+        <v>29.0799</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>22.5462</v>
+        <v>22.551</v>
       </c>
       <c r="C83" t="n">
-        <v>18.0727</v>
+        <v>18.1004</v>
       </c>
       <c r="D83" t="n">
-        <v>44.3896</v>
+        <v>44.304</v>
       </c>
       <c r="E83" t="n">
-        <v>18.5461</v>
+        <v>18.3757</v>
       </c>
       <c r="F83" t="n">
-        <v>29.2526</v>
+        <v>28.7754</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>22.1207</v>
+        <v>22.1239</v>
       </c>
       <c r="C84" t="n">
-        <v>17.9377</v>
+        <v>17.9575</v>
       </c>
       <c r="D84" t="n">
-        <v>43.9035</v>
+        <v>44.0131</v>
       </c>
       <c r="E84" t="n">
-        <v>18.1091</v>
+        <v>18.0238</v>
       </c>
       <c r="F84" t="n">
-        <v>28.8647</v>
+        <v>28.4704</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>21.6665</v>
+        <v>21.6707</v>
       </c>
       <c r="C85" t="n">
-        <v>17.7703</v>
+        <v>17.7841</v>
       </c>
       <c r="D85" t="n">
-        <v>43.8908</v>
+        <v>42.9708</v>
       </c>
       <c r="E85" t="n">
-        <v>17.8089</v>
+        <v>17.6014</v>
       </c>
       <c r="F85" t="n">
-        <v>28.4574</v>
+        <v>28.176</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>21.2388</v>
+        <v>21.2341</v>
       </c>
       <c r="C86" t="n">
-        <v>17.6921</v>
+        <v>17.6913</v>
       </c>
       <c r="D86" t="n">
-        <v>42.564</v>
+        <v>43.3301</v>
       </c>
       <c r="E86" t="n">
-        <v>17.4052</v>
+        <v>17.1912</v>
       </c>
       <c r="F86" t="n">
-        <v>28.1353</v>
+        <v>27.8937</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>20.7617</v>
+        <v>20.7379</v>
       </c>
       <c r="C87" t="n">
-        <v>17.5426</v>
+        <v>17.5634</v>
       </c>
       <c r="D87" t="n">
-        <v>42.4335</v>
+        <v>42.9872</v>
       </c>
       <c r="E87" t="n">
-        <v>17.1147</v>
+        <v>16.8322</v>
       </c>
       <c r="F87" t="n">
-        <v>27.8369</v>
+        <v>27.6036</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>20.2679</v>
+        <v>20.2498</v>
       </c>
       <c r="C88" t="n">
-        <v>17.4562</v>
+        <v>17.4765</v>
       </c>
       <c r="D88" t="n">
-        <v>42.7443</v>
+        <v>42.5708</v>
       </c>
       <c r="E88" t="n">
-        <v>16.7327</v>
+        <v>16.4807</v>
       </c>
       <c r="F88" t="n">
-        <v>27.4881</v>
+        <v>27.2688</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>19.714</v>
+        <v>19.7215</v>
       </c>
       <c r="C89" t="n">
-        <v>17.3411</v>
+        <v>17.3419</v>
       </c>
       <c r="D89" t="n">
-        <v>40.9248</v>
+        <v>41.5391</v>
       </c>
       <c r="E89" t="n">
-        <v>16.4105</v>
+        <v>16.1253</v>
       </c>
       <c r="F89" t="n">
-        <v>26.8787</v>
+        <v>26.952</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>19.3077</v>
+        <v>19.2306</v>
       </c>
       <c r="C90" t="n">
-        <v>17.2394</v>
+        <v>17.2338</v>
       </c>
       <c r="D90" t="n">
-        <v>40.7278</v>
+        <v>41.2561</v>
       </c>
       <c r="E90" t="n">
-        <v>16.0523</v>
+        <v>15.7084</v>
       </c>
       <c r="F90" t="n">
-        <v>26.4859</v>
+        <v>26.6794</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>18.7221</v>
+        <v>18.7216</v>
       </c>
       <c r="C91" t="n">
-        <v>17.1297</v>
+        <v>17.1301</v>
       </c>
       <c r="D91" t="n">
-        <v>40.7875</v>
+        <v>41.135</v>
       </c>
       <c r="E91" t="n">
-        <v>15.717</v>
+        <v>15.3102</v>
       </c>
       <c r="F91" t="n">
-        <v>26.1027</v>
+        <v>26.3186</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>18.1798</v>
+        <v>18.1945</v>
       </c>
       <c r="C92" t="n">
-        <v>17.0554</v>
+        <v>17.0504</v>
       </c>
       <c r="D92" t="n">
-        <v>45.5614</v>
+        <v>47.3313</v>
       </c>
       <c r="E92" t="n">
-        <v>21.059</v>
+        <v>21.1266</v>
       </c>
       <c r="F92" t="n">
-        <v>30.7784</v>
+        <v>30.5523</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>17.5178</v>
+        <v>17.5405</v>
       </c>
       <c r="C93" t="n">
-        <v>16.9918</v>
+        <v>16.9945</v>
       </c>
       <c r="D93" t="n">
-        <v>44.8403</v>
+        <v>46.6133</v>
       </c>
       <c r="E93" t="n">
-        <v>20.5103</v>
+        <v>20.5437</v>
       </c>
       <c r="F93" t="n">
-        <v>30.337</v>
+        <v>29.7707</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>16.8378</v>
+        <v>16.8626</v>
       </c>
       <c r="C94" t="n">
-        <v>18.5934</v>
+        <v>18.6004</v>
       </c>
       <c r="D94" t="n">
-        <v>44.1537</v>
+        <v>45.5271</v>
       </c>
       <c r="E94" t="n">
-        <v>19.9862</v>
+        <v>19.9823</v>
       </c>
       <c r="F94" t="n">
-        <v>30.0722</v>
+        <v>29.4185</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>23.3534</v>
+        <v>23.3422</v>
       </c>
       <c r="C95" t="n">
-        <v>18.3896</v>
+        <v>18.398</v>
       </c>
       <c r="D95" t="n">
-        <v>43.5997</v>
+        <v>45.1164</v>
       </c>
       <c r="E95" t="n">
-        <v>19.5561</v>
+        <v>19.4786</v>
       </c>
       <c r="F95" t="n">
-        <v>29.6004</v>
+        <v>29.0638</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>23.0004</v>
+        <v>23.0002</v>
       </c>
       <c r="C96" t="n">
-        <v>18.2254</v>
+        <v>18.2299</v>
       </c>
       <c r="D96" t="n">
-        <v>43.1782</v>
+        <v>44.5656</v>
       </c>
       <c r="E96" t="n">
-        <v>19.096</v>
+        <v>19.4947</v>
       </c>
       <c r="F96" t="n">
-        <v>29.9035</v>
+        <v>28.7452</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>22.5962</v>
+        <v>22.6105</v>
       </c>
       <c r="C97" t="n">
-        <v>18.0631</v>
+        <v>18.0728</v>
       </c>
       <c r="D97" t="n">
-        <v>42.9315</v>
+        <v>44.3278</v>
       </c>
       <c r="E97" t="n">
-        <v>18.742</v>
+        <v>19.0278</v>
       </c>
       <c r="F97" t="n">
-        <v>29.3762</v>
+        <v>28.1936</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>22.197</v>
+        <v>22.1731</v>
       </c>
       <c r="C98" t="n">
-        <v>17.9127</v>
+        <v>17.9193</v>
       </c>
       <c r="D98" t="n">
-        <v>42.419</v>
+        <v>43.8596</v>
       </c>
       <c r="E98" t="n">
-        <v>18.2589</v>
+        <v>18.5448</v>
       </c>
       <c r="F98" t="n">
-        <v>28.921</v>
+        <v>27.8685</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>21.7681</v>
+        <v>21.7379</v>
       </c>
       <c r="C99" t="n">
-        <v>17.7971</v>
+        <v>17.7904</v>
       </c>
       <c r="D99" t="n">
-        <v>41.8857</v>
+        <v>43.223</v>
       </c>
       <c r="E99" t="n">
-        <v>17.8674</v>
+        <v>18.1287</v>
       </c>
       <c r="F99" t="n">
-        <v>28.532</v>
+        <v>27.5177</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>21.3324</v>
+        <v>21.3198</v>
       </c>
       <c r="C100" t="n">
-        <v>17.7507</v>
+        <v>17.7047</v>
       </c>
       <c r="D100" t="n">
-        <v>41.7781</v>
+        <v>43.1034</v>
       </c>
       <c r="E100" t="n">
-        <v>17.5207</v>
+        <v>17.8433</v>
       </c>
       <c r="F100" t="n">
-        <v>28.1479</v>
+        <v>27.2042</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>20.8081</v>
+        <v>20.7806</v>
       </c>
       <c r="C101" t="n">
-        <v>17.6236</v>
+        <v>17.6203</v>
       </c>
       <c r="D101" t="n">
-        <v>41.3668</v>
+        <v>42.5903</v>
       </c>
       <c r="E101" t="n">
-        <v>17.1525</v>
+        <v>17.4757</v>
       </c>
       <c r="F101" t="n">
-        <v>27.7957</v>
+        <v>26.9155</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>20.3524</v>
+        <v>20.3397</v>
       </c>
       <c r="C102" t="n">
-        <v>17.4585</v>
+        <v>17.4826</v>
       </c>
       <c r="D102" t="n">
-        <v>41.0283</v>
+        <v>42.175</v>
       </c>
       <c r="E102" t="n">
-        <v>16.8019</v>
+        <v>17.1404</v>
       </c>
       <c r="F102" t="n">
-        <v>27.4829</v>
+        <v>26.6322</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>19.8692</v>
+        <v>19.8315</v>
       </c>
       <c r="C103" t="n">
-        <v>17.3597</v>
+        <v>17.3336</v>
       </c>
       <c r="D103" t="n">
-        <v>40.8453</v>
+        <v>42.1206</v>
       </c>
       <c r="E103" t="n">
-        <v>16.4896</v>
+        <v>16.6525</v>
       </c>
       <c r="F103" t="n">
-        <v>27.1684</v>
+        <v>26.3038</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>19.3663</v>
+        <v>19.362</v>
       </c>
       <c r="C104" t="n">
-        <v>17.2291</v>
+        <v>17.234</v>
       </c>
       <c r="D104" t="n">
-        <v>40.4249</v>
+        <v>41.5797</v>
       </c>
       <c r="E104" t="n">
-        <v>16.1249</v>
+        <v>16.3268</v>
       </c>
       <c r="F104" t="n">
-        <v>26.827</v>
+        <v>26.0263</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>18.8867</v>
+        <v>18.8665</v>
       </c>
       <c r="C105" t="n">
-        <v>17.1553</v>
+        <v>17.1698</v>
       </c>
       <c r="D105" t="n">
-        <v>40.3173</v>
+        <v>41.573</v>
       </c>
       <c r="E105" t="n">
-        <v>15.7883</v>
+        <v>15.9519</v>
       </c>
       <c r="F105" t="n">
-        <v>26.4476</v>
+        <v>25.6884</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>18.3062</v>
+        <v>18.2944</v>
       </c>
       <c r="C106" t="n">
-        <v>17.0647</v>
+        <v>17.0833</v>
       </c>
       <c r="D106" t="n">
-        <v>40.0104</v>
+        <v>40.9729</v>
       </c>
       <c r="E106" t="n">
-        <v>15.4654</v>
+        <v>15.6226</v>
       </c>
       <c r="F106" t="n">
-        <v>26.0874</v>
+        <v>25.5534</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>17.703</v>
+        <v>17.7271</v>
       </c>
       <c r="C107" t="n">
-        <v>16.9781</v>
+        <v>16.9925</v>
       </c>
       <c r="D107" t="n">
-        <v>43.338</v>
+        <v>44.1436</v>
       </c>
       <c r="E107" t="n">
-        <v>20.5822</v>
+        <v>20.9786</v>
       </c>
       <c r="F107" t="n">
-        <v>30.8497</v>
+        <v>29.5564</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>17.0331</v>
+        <v>17.0473</v>
       </c>
       <c r="C108" t="n">
-        <v>18.7418</v>
+        <v>18.7272</v>
       </c>
       <c r="D108" t="n">
-        <v>43.2162</v>
+        <v>43.9386</v>
       </c>
       <c r="E108" t="n">
-        <v>20.0864</v>
+        <v>20.4325</v>
       </c>
       <c r="F108" t="n">
-        <v>30.4457</v>
+        <v>29.2431</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>16.1588</v>
+        <v>16.143</v>
       </c>
       <c r="C109" t="n">
-        <v>18.5567</v>
+        <v>18.5527</v>
       </c>
       <c r="D109" t="n">
-        <v>42.5907</v>
+        <v>43.4686</v>
       </c>
       <c r="E109" t="n">
-        <v>19.6254</v>
+        <v>20.0068</v>
       </c>
       <c r="F109" t="n">
-        <v>30.0543</v>
+        <v>28.8963</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>23.1166</v>
+        <v>23.0693</v>
       </c>
       <c r="C110" t="n">
-        <v>18.2851</v>
+        <v>18.285</v>
       </c>
       <c r="D110" t="n">
-        <v>42.0862</v>
+        <v>42.9026</v>
       </c>
       <c r="E110" t="n">
-        <v>19.1601</v>
+        <v>19.0411</v>
       </c>
       <c r="F110" t="n">
-        <v>29.3432</v>
+        <v>29.1022</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>22.721</v>
+        <v>22.6899</v>
       </c>
       <c r="C111" t="n">
-        <v>18.2293</v>
+        <v>18.2229</v>
       </c>
       <c r="D111" t="n">
-        <v>41.5601</v>
+        <v>42.4083</v>
       </c>
       <c r="E111" t="n">
-        <v>18.7604</v>
+        <v>18.5971</v>
       </c>
       <c r="F111" t="n">
-        <v>28.9563</v>
+        <v>28.7893</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>22.2927</v>
+        <v>22.2682</v>
       </c>
       <c r="C112" t="n">
-        <v>18.0715</v>
+        <v>18.0538</v>
       </c>
       <c r="D112" t="n">
-        <v>41.2496</v>
+        <v>41.8383</v>
       </c>
       <c r="E112" t="n">
-        <v>18.3706</v>
+        <v>18.1545</v>
       </c>
       <c r="F112" t="n">
-        <v>28.6666</v>
+        <v>28.4369</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>21.8578</v>
+        <v>21.8432</v>
       </c>
       <c r="C113" t="n">
-        <v>17.9252</v>
+        <v>17.9078</v>
       </c>
       <c r="D113" t="n">
-        <v>40.8648</v>
+        <v>41.6023</v>
       </c>
       <c r="E113" t="n">
-        <v>17.9467</v>
+        <v>17.7491</v>
       </c>
       <c r="F113" t="n">
-        <v>28.2501</v>
+        <v>28.1475</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>21.4213</v>
+        <v>21.4375</v>
       </c>
       <c r="C114" t="n">
-        <v>17.7281</v>
+        <v>17.7102</v>
       </c>
       <c r="D114" t="n">
-        <v>40.0838</v>
+        <v>40.8833</v>
       </c>
       <c r="E114" t="n">
-        <v>17.6144</v>
+        <v>17.3295</v>
       </c>
       <c r="F114" t="n">
-        <v>27.9178</v>
+        <v>27.8415</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>20.917</v>
+        <v>20.9</v>
       </c>
       <c r="C115" t="n">
-        <v>17.6009</v>
+        <v>17.6691</v>
       </c>
       <c r="D115" t="n">
-        <v>39.7897</v>
+        <v>40.5114</v>
       </c>
       <c r="E115" t="n">
-        <v>17.2539</v>
+        <v>17.0189</v>
       </c>
       <c r="F115" t="n">
-        <v>27.6135</v>
+        <v>27.5443</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>20.4597</v>
+        <v>20.4308</v>
       </c>
       <c r="C116" t="n">
-        <v>17.5551</v>
+        <v>17.5424</v>
       </c>
       <c r="D116" t="n">
-        <v>39.3513</v>
+        <v>40.0544</v>
       </c>
       <c r="E116" t="n">
-        <v>16.8878</v>
+        <v>17.1822</v>
       </c>
       <c r="F116" t="n">
-        <v>27.6017</v>
+        <v>26.6842</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>19.9702</v>
+        <v>19.9574</v>
       </c>
       <c r="C117" t="n">
-        <v>17.4111</v>
+        <v>17.402</v>
       </c>
       <c r="D117" t="n">
-        <v>39.091</v>
+        <v>39.7982</v>
       </c>
       <c r="E117" t="n">
-        <v>16.5229</v>
+        <v>16.8074</v>
       </c>
       <c r="F117" t="n">
-        <v>27.2845</v>
+        <v>26.4039</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>19.5025</v>
+        <v>19.4962</v>
       </c>
       <c r="C118" t="n">
-        <v>17.2752</v>
+        <v>17.3046</v>
       </c>
       <c r="D118" t="n">
-        <v>38.7224</v>
+        <v>39.442</v>
       </c>
       <c r="E118" t="n">
-        <v>16.1709</v>
+        <v>16.5124</v>
       </c>
       <c r="F118" t="n">
-        <v>26.9489</v>
+        <v>26.0748</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>18.9834</v>
+        <v>19.0077</v>
       </c>
       <c r="C119" t="n">
-        <v>17.191</v>
+        <v>17.1878</v>
       </c>
       <c r="D119" t="n">
-        <v>38.398</v>
+        <v>39.1788</v>
       </c>
       <c r="E119" t="n">
-        <v>15.8568</v>
+        <v>16.0508</v>
       </c>
       <c r="F119" t="n">
-        <v>26.5712</v>
+        <v>25.7755</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>18.4597</v>
+        <v>18.4835</v>
       </c>
       <c r="C120" t="n">
-        <v>17.0808</v>
+        <v>17.1339</v>
       </c>
       <c r="D120" t="n">
-        <v>38.2197</v>
+        <v>38.927</v>
       </c>
       <c r="E120" t="n">
-        <v>15.5126</v>
+        <v>15.688</v>
       </c>
       <c r="F120" t="n">
-        <v>26.221</v>
+        <v>25.5902</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>17.8706</v>
+        <v>17.8648</v>
       </c>
       <c r="C121" t="n">
-        <v>17.0219</v>
+        <v>17.0298</v>
       </c>
       <c r="D121" t="n">
-        <v>45.8619</v>
+        <v>47.4013</v>
       </c>
       <c r="E121" t="n">
-        <v>20.6873</v>
+        <v>20.607</v>
       </c>
       <c r="F121" t="n">
-        <v>30.5176</v>
+        <v>29.6879</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>17.1948</v>
+        <v>17.177</v>
       </c>
       <c r="C122" t="n">
-        <v>18.705</v>
+        <v>18.7149</v>
       </c>
       <c r="D122" t="n">
-        <v>45.1618</v>
+        <v>46.7413</v>
       </c>
       <c r="E122" t="n">
-        <v>20.2115</v>
+        <v>20.3194</v>
       </c>
       <c r="F122" t="n">
-        <v>30.5332</v>
+        <v>29.2945</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>16.3424</v>
+        <v>16.3349</v>
       </c>
       <c r="C123" t="n">
-        <v>18.4951</v>
+        <v>18.5041</v>
       </c>
       <c r="D123" t="n">
-        <v>44.9331</v>
+        <v>46.5408</v>
       </c>
       <c r="E123" t="n">
-        <v>19.6895</v>
+        <v>19.5998</v>
       </c>
       <c r="F123" t="n">
-        <v>29.7095</v>
+        <v>29.12</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>23.1673</v>
+        <v>23.1802</v>
       </c>
       <c r="C124" t="n">
-        <v>18.3234</v>
+        <v>18.31</v>
       </c>
       <c r="D124" t="n">
-        <v>44.2349</v>
+        <v>45.351</v>
       </c>
       <c r="E124" t="n">
-        <v>19.2304</v>
+        <v>19.1051</v>
       </c>
       <c r="F124" t="n">
-        <v>29.3824</v>
+        <v>28.7268</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>22.7706</v>
+        <v>22.7665</v>
       </c>
       <c r="C125" t="n">
-        <v>18.1647</v>
+        <v>18.1496</v>
       </c>
       <c r="D125" t="n">
-        <v>43.7723</v>
+        <v>44.7686</v>
       </c>
       <c r="E125" t="n">
-        <v>18.8181</v>
+        <v>18.6741</v>
       </c>
       <c r="F125" t="n">
-        <v>28.9261</v>
+        <v>28.3412</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>22.3577</v>
+        <v>22.3537</v>
       </c>
       <c r="C126" t="n">
-        <v>17.9955</v>
+        <v>17.9874</v>
       </c>
       <c r="D126" t="n">
-        <v>43.0109</v>
+        <v>44.4467</v>
       </c>
       <c r="E126" t="n">
-        <v>18.3659</v>
+        <v>18.2277</v>
       </c>
       <c r="F126" t="n">
-        <v>28.6306</v>
+        <v>28.0641</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>21.9174</v>
+        <v>21.9228</v>
       </c>
       <c r="C127" t="n">
-        <v>17.8552</v>
+        <v>17.8465</v>
       </c>
       <c r="D127" t="n">
-        <v>42.3875</v>
+        <v>43.8967</v>
       </c>
       <c r="E127" t="n">
-        <v>17.9515</v>
+        <v>17.7579</v>
       </c>
       <c r="F127" t="n">
-        <v>28.3253</v>
+        <v>27.7717</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>21.5023</v>
+        <v>21.4963</v>
       </c>
       <c r="C128" t="n">
-        <v>17.7543</v>
+        <v>17.744</v>
       </c>
       <c r="D128" t="n">
-        <v>42.2719</v>
+        <v>43.2852</v>
       </c>
       <c r="E128" t="n">
-        <v>17.6007</v>
+        <v>17.4373</v>
       </c>
       <c r="F128" t="n">
-        <v>27.984</v>
+        <v>27.9019</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>21.0374</v>
+        <v>20.9973</v>
       </c>
       <c r="C129" t="n">
-        <v>17.6031</v>
+        <v>17.6066</v>
       </c>
       <c r="D129" t="n">
-        <v>41.7879</v>
+        <v>42.8574</v>
       </c>
       <c r="E129" t="n">
-        <v>17.2705</v>
+        <v>17.1082</v>
       </c>
       <c r="F129" t="n">
-        <v>27.6371</v>
+        <v>27.5955</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>20.5593</v>
+        <v>20.5333</v>
       </c>
       <c r="C130" t="n">
-        <v>17.4843</v>
+        <v>17.4893</v>
       </c>
       <c r="D130" t="n">
-        <v>41.4405</v>
+        <v>42.4483</v>
       </c>
       <c r="E130" t="n">
-        <v>16.9525</v>
+        <v>17.2588</v>
       </c>
       <c r="F130" t="n">
-        <v>27.609</v>
+        <v>26.7858</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>20.0877</v>
+        <v>20.0671</v>
       </c>
       <c r="C131" t="n">
-        <v>17.3806</v>
+        <v>17.3744</v>
       </c>
       <c r="D131" t="n">
-        <v>40.9456</v>
+        <v>42.0044</v>
       </c>
       <c r="E131" t="n">
-        <v>16.5816</v>
+        <v>16.9117</v>
       </c>
       <c r="F131" t="n">
-        <v>27.2866</v>
+        <v>26.4139</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>19.5949</v>
+        <v>19.5866</v>
       </c>
       <c r="C132" t="n">
-        <v>17.2733</v>
+        <v>17.2745</v>
       </c>
       <c r="D132" t="n">
-        <v>40.6227</v>
+        <v>41.5538</v>
       </c>
       <c r="E132" t="n">
-        <v>16.2737</v>
+        <v>16.4698</v>
       </c>
       <c r="F132" t="n">
-        <v>26.9543</v>
+        <v>26.1123</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>19.0879</v>
+        <v>19.0732</v>
       </c>
       <c r="C133" t="n">
-        <v>17.21</v>
+        <v>17.2298</v>
       </c>
       <c r="D133" t="n">
-        <v>40.3934</v>
+        <v>41.3408</v>
       </c>
       <c r="E133" t="n">
-        <v>15.92</v>
+        <v>16.1504</v>
       </c>
       <c r="F133" t="n">
-        <v>26.6306</v>
+        <v>25.8075</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>18.5698</v>
+        <v>18.5774</v>
       </c>
       <c r="C134" t="n">
-        <v>17.0953</v>
+        <v>17.1371</v>
       </c>
       <c r="D134" t="n">
-        <v>40.1089</v>
+        <v>41.1186</v>
       </c>
       <c r="E134" t="n">
-        <v>15.6099</v>
+        <v>15.7775</v>
       </c>
       <c r="F134" t="n">
-        <v>26.2752</v>
+        <v>26.0491</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>17.9923</v>
+        <v>17.9795</v>
       </c>
       <c r="C135" t="n">
-        <v>17.0191</v>
+        <v>17.0296</v>
       </c>
       <c r="D135" t="n">
-        <v>46.3368</v>
+        <v>48.1407</v>
       </c>
       <c r="E135" t="n">
-        <v>20.7515</v>
+        <v>21.1629</v>
       </c>
       <c r="F135" t="n">
-        <v>30.9002</v>
+        <v>29.7465</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>17.3554</v>
+        <v>17.3422</v>
       </c>
       <c r="C136" t="n">
-        <v>18.7493</v>
+        <v>18.7672</v>
       </c>
       <c r="D136" t="n">
-        <v>45.9559</v>
+        <v>47.7784</v>
       </c>
       <c r="E136" t="n">
-        <v>20.2598</v>
+        <v>20.173</v>
       </c>
       <c r="F136" t="n">
-        <v>30.1763</v>
+        <v>29.4118</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>16.5043</v>
+        <v>16.5269</v>
       </c>
       <c r="C137" t="n">
-        <v>18.513</v>
+        <v>18.531</v>
       </c>
       <c r="D137" t="n">
-        <v>44.9926</v>
+        <v>46.3308</v>
       </c>
       <c r="E137" t="n">
-        <v>19.7404</v>
+        <v>19.9844</v>
       </c>
       <c r="F137" t="n">
-        <v>30.1638</v>
+        <v>29.0268</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>23.2525</v>
+        <v>23.2345</v>
       </c>
       <c r="C138" t="n">
-        <v>18.3541</v>
+        <v>18.3618</v>
       </c>
       <c r="D138" t="n">
-        <v>44.6721</v>
+        <v>46.4146</v>
       </c>
       <c r="E138" t="n">
-        <v>19.2794</v>
+        <v>19.246</v>
       </c>
       <c r="F138" t="n">
-        <v>29.8439</v>
+        <v>28.6652</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>22.8926</v>
+        <v>22.8793</v>
       </c>
       <c r="C139" t="n">
-        <v>18.1665</v>
+        <v>18.173</v>
       </c>
       <c r="D139" t="n">
-        <v>44.2461</v>
+        <v>45.7022</v>
       </c>
       <c r="E139" t="n">
-        <v>18.8382</v>
+        <v>18.7407</v>
       </c>
       <c r="F139" t="n">
-        <v>29.0409</v>
+        <v>28.4462</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>22.4918</v>
+        <v>22.4759</v>
       </c>
       <c r="C140" t="n">
-        <v>18.0054</v>
+        <v>18.0057</v>
       </c>
       <c r="D140" t="n">
-        <v>43.7456</v>
+        <v>45.0141</v>
       </c>
       <c r="E140" t="n">
-        <v>18.4503</v>
+        <v>18.3118</v>
       </c>
       <c r="F140" t="n">
-        <v>28.7125</v>
+        <v>28.099</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>22.0594</v>
+        <v>22.0273</v>
       </c>
       <c r="C141" t="n">
-        <v>17.8688</v>
+        <v>17.8665</v>
       </c>
       <c r="D141" t="n">
-        <v>43.186</v>
+        <v>44.3041</v>
       </c>
       <c r="E141" t="n">
-        <v>18.0581</v>
+        <v>17.8718</v>
       </c>
       <c r="F141" t="n">
-        <v>28.3463</v>
+        <v>27.7741</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>21.6383</v>
+        <v>21.6078</v>
       </c>
       <c r="C142" t="n">
-        <v>17.7761</v>
+        <v>17.7736</v>
       </c>
       <c r="D142" t="n">
-        <v>42.5047</v>
+        <v>43.8013</v>
       </c>
       <c r="E142" t="n">
-        <v>17.685</v>
+        <v>17.5134</v>
       </c>
       <c r="F142" t="n">
-        <v>28.4359</v>
+        <v>27.4435</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>21.1391</v>
+        <v>21.1235</v>
       </c>
       <c r="C143" t="n">
-        <v>17.6171</v>
+        <v>17.6016</v>
       </c>
       <c r="D143" t="n">
-        <v>41.9699</v>
+        <v>43.4251</v>
       </c>
       <c r="E143" t="n">
-        <v>17.3657</v>
+        <v>17.6278</v>
       </c>
       <c r="F143" t="n">
-        <v>28.0644</v>
+        <v>27.1701</v>
       </c>
     </row>
   </sheetData>

--- a/clang-x64/Running erasure.xlsx
+++ b/clang-x64/Running erasure.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>17.916</v>
+        <v>18.1873</v>
       </c>
       <c r="C2" t="n">
-        <v>13.1601</v>
+        <v>13.0642</v>
       </c>
       <c r="D2" t="n">
-        <v>29.8729</v>
+        <v>30.7265</v>
       </c>
       <c r="E2" t="n">
-        <v>13.0642</v>
+        <v>12.6225</v>
       </c>
       <c r="F2" t="n">
-        <v>25.2402</v>
+        <v>26.374</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>18.2083</v>
+        <v>18.2427</v>
       </c>
       <c r="C3" t="n">
-        <v>13.2301</v>
+        <v>13.2708</v>
       </c>
       <c r="D3" t="n">
-        <v>30.012</v>
+        <v>30.8356</v>
       </c>
       <c r="E3" t="n">
-        <v>12.8382</v>
+        <v>12.6275</v>
       </c>
       <c r="F3" t="n">
-        <v>25.0351</v>
+        <v>26.4565</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>17.5409</v>
+        <v>17.5995</v>
       </c>
       <c r="C4" t="n">
-        <v>13.5695</v>
+        <v>13.4329</v>
       </c>
       <c r="D4" t="n">
-        <v>30.3008</v>
+        <v>30.9713</v>
       </c>
       <c r="E4" t="n">
-        <v>12.5547</v>
+        <v>12.3454</v>
       </c>
       <c r="F4" t="n">
-        <v>24.7482</v>
+        <v>25.9954</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>16.943</v>
+        <v>16.942</v>
       </c>
       <c r="C5" t="n">
-        <v>13.6708</v>
+        <v>13.7699</v>
       </c>
       <c r="D5" t="n">
-        <v>30.398</v>
+        <v>31.187</v>
       </c>
       <c r="E5" t="n">
-        <v>12.7854</v>
+        <v>12.1402</v>
       </c>
       <c r="F5" t="n">
-        <v>24.9031</v>
+        <v>25.1504</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>16.5741</v>
+        <v>16.6406</v>
       </c>
       <c r="C6" t="n">
-        <v>13.7094</v>
+        <v>13.8739</v>
       </c>
       <c r="D6" t="n">
-        <v>30.4179</v>
+        <v>31.2468</v>
       </c>
       <c r="E6" t="n">
-        <v>12.9507</v>
+        <v>12.2599</v>
       </c>
       <c r="F6" t="n">
-        <v>24.8869</v>
+        <v>25.4634</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>16.2387</v>
+        <v>16.3569</v>
       </c>
       <c r="C7" t="n">
-        <v>14.0992</v>
+        <v>14.1519</v>
       </c>
       <c r="D7" t="n">
-        <v>29.5917</v>
+        <v>30.1633</v>
       </c>
       <c r="E7" t="n">
-        <v>19.6527</v>
+        <v>18.7929</v>
       </c>
       <c r="F7" t="n">
-        <v>29.1323</v>
+        <v>30.1421</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>15.6529</v>
+        <v>15.8323</v>
       </c>
       <c r="C8" t="n">
-        <v>15.4978</v>
+        <v>15.4549</v>
       </c>
       <c r="D8" t="n">
-        <v>29.6386</v>
+        <v>30.1855</v>
       </c>
       <c r="E8" t="n">
-        <v>19.1504</v>
+        <v>18.2929</v>
       </c>
       <c r="F8" t="n">
-        <v>28.5949</v>
+        <v>29.6575</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>14.99</v>
+        <v>15.0955</v>
       </c>
       <c r="C9" t="n">
-        <v>15.5776</v>
+        <v>15.6332</v>
       </c>
       <c r="D9" t="n">
-        <v>29.6938</v>
+        <v>30.3665</v>
       </c>
       <c r="E9" t="n">
-        <v>18.7161</v>
+        <v>17.9145</v>
       </c>
       <c r="F9" t="n">
-        <v>28.324</v>
+        <v>29.4536</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>21.6787</v>
+        <v>21.6752</v>
       </c>
       <c r="C10" t="n">
-        <v>15.7578</v>
+        <v>15.7451</v>
       </c>
       <c r="D10" t="n">
-        <v>29.6643</v>
+        <v>30.3455</v>
       </c>
       <c r="E10" t="n">
-        <v>18.3027</v>
+        <v>17.3887</v>
       </c>
       <c r="F10" t="n">
-        <v>28.2004</v>
+        <v>29.2156</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>21.4668</v>
+        <v>21.4626</v>
       </c>
       <c r="C11" t="n">
-        <v>15.861</v>
+        <v>15.8403</v>
       </c>
       <c r="D11" t="n">
-        <v>29.762</v>
+        <v>30.5487</v>
       </c>
       <c r="E11" t="n">
-        <v>18.0535</v>
+        <v>17.0878</v>
       </c>
       <c r="F11" t="n">
-        <v>27.8296</v>
+        <v>28.9029</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>21.155</v>
+        <v>21.1014</v>
       </c>
       <c r="C12" t="n">
-        <v>15.9372</v>
+        <v>15.9239</v>
       </c>
       <c r="D12" t="n">
-        <v>30.1145</v>
+        <v>30.6801</v>
       </c>
       <c r="E12" t="n">
-        <v>17.5445</v>
+        <v>16.5877</v>
       </c>
       <c r="F12" t="n">
-        <v>27.9629</v>
+        <v>28.0793</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>20.7869</v>
+        <v>20.8414</v>
       </c>
       <c r="C13" t="n">
-        <v>16.2754</v>
+        <v>16.1338</v>
       </c>
       <c r="D13" t="n">
-        <v>30.1818</v>
+        <v>31.0641</v>
       </c>
       <c r="E13" t="n">
-        <v>17.1383</v>
+        <v>16.4181</v>
       </c>
       <c r="F13" t="n">
-        <v>27.7166</v>
+        <v>27.8941</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>20.4643</v>
+        <v>20.3972</v>
       </c>
       <c r="C14" t="n">
-        <v>16.4162</v>
+        <v>16.4019</v>
       </c>
       <c r="D14" t="n">
-        <v>30.255</v>
+        <v>31.1088</v>
       </c>
       <c r="E14" t="n">
-        <v>16.8324</v>
+        <v>16.1298</v>
       </c>
       <c r="F14" t="n">
-        <v>27.606</v>
+        <v>27.7083</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>20.1091</v>
+        <v>19.969</v>
       </c>
       <c r="C15" t="n">
-        <v>16.2589</v>
+        <v>16.3327</v>
       </c>
       <c r="D15" t="n">
-        <v>30.4466</v>
+        <v>31.3103</v>
       </c>
       <c r="E15" t="n">
-        <v>16.5539</v>
+        <v>15.8517</v>
       </c>
       <c r="F15" t="n">
-        <v>26.8738</v>
+        <v>27.2218</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>19.7621</v>
+        <v>19.7977</v>
       </c>
       <c r="C16" t="n">
-        <v>16.3263</v>
+        <v>16.382</v>
       </c>
       <c r="D16" t="n">
-        <v>30.5175</v>
+        <v>31.5602</v>
       </c>
       <c r="E16" t="n">
-        <v>16.3513</v>
+        <v>15.5319</v>
       </c>
       <c r="F16" t="n">
-        <v>26.6769</v>
+        <v>27.0629</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>19.4163</v>
+        <v>19.2976</v>
       </c>
       <c r="C17" t="n">
-        <v>16.3506</v>
+        <v>16.4805</v>
       </c>
       <c r="D17" t="n">
-        <v>30.8041</v>
+        <v>31.6391</v>
       </c>
       <c r="E17" t="n">
-        <v>15.9038</v>
+        <v>15.2668</v>
       </c>
       <c r="F17" t="n">
-        <v>26.3262</v>
+        <v>26.6807</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>18.9649</v>
+        <v>19.0571</v>
       </c>
       <c r="C18" t="n">
-        <v>16.3774</v>
+        <v>16.4857</v>
       </c>
       <c r="D18" t="n">
-        <v>30.9885</v>
+        <v>31.935</v>
       </c>
       <c r="E18" t="n">
-        <v>15.6581</v>
+        <v>14.9616</v>
       </c>
       <c r="F18" t="n">
-        <v>26.0774</v>
+        <v>26.3869</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>18.4809</v>
+        <v>18.3642</v>
       </c>
       <c r="C19" t="n">
-        <v>16.4093</v>
+        <v>16.5577</v>
       </c>
       <c r="D19" t="n">
-        <v>30.9315</v>
+        <v>32.0637</v>
       </c>
       <c r="E19" t="n">
-        <v>15.1616</v>
+        <v>14.5992</v>
       </c>
       <c r="F19" t="n">
-        <v>25.7744</v>
+        <v>26.2361</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>17.9417</v>
+        <v>17.9687</v>
       </c>
       <c r="C20" t="n">
-        <v>16.2541</v>
+        <v>16.6791</v>
       </c>
       <c r="D20" t="n">
-        <v>30.9932</v>
+        <v>32.2281</v>
       </c>
       <c r="E20" t="n">
-        <v>14.8636</v>
+        <v>14.3105</v>
       </c>
       <c r="F20" t="n">
-        <v>25.5554</v>
+        <v>25.9073</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>17.3662</v>
+        <v>17.3414</v>
       </c>
       <c r="C21" t="n">
-        <v>16.2489</v>
+        <v>16.6892</v>
       </c>
       <c r="D21" t="n">
-        <v>30.4139</v>
+        <v>31.1621</v>
       </c>
       <c r="E21" t="n">
-        <v>20.944</v>
+        <v>20.0684</v>
       </c>
       <c r="F21" t="n">
-        <v>29.9141</v>
+        <v>30.8248</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>16.7078</v>
+        <v>16.7941</v>
       </c>
       <c r="C22" t="n">
-        <v>17.7515</v>
+        <v>17.9257</v>
       </c>
       <c r="D22" t="n">
-        <v>30.1386</v>
+        <v>31.0915</v>
       </c>
       <c r="E22" t="n">
-        <v>20.3959</v>
+        <v>19.478</v>
       </c>
       <c r="F22" t="n">
-        <v>29.5898</v>
+        <v>29.8566</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>16.0106</v>
+        <v>16.0409</v>
       </c>
       <c r="C23" t="n">
-        <v>17.6163</v>
+        <v>17.9015</v>
       </c>
       <c r="D23" t="n">
-        <v>30.4217</v>
+        <v>31.1165</v>
       </c>
       <c r="E23" t="n">
-        <v>19.92</v>
+        <v>18.8929</v>
       </c>
       <c r="F23" t="n">
-        <v>29.2425</v>
+        <v>29.6297</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>22.4943</v>
+        <v>22.5232</v>
       </c>
       <c r="C24" t="n">
-        <v>17.5422</v>
+        <v>17.8172</v>
       </c>
       <c r="D24" t="n">
-        <v>30.4072</v>
+        <v>31.0443</v>
       </c>
       <c r="E24" t="n">
-        <v>19.454</v>
+        <v>18.4688</v>
       </c>
       <c r="F24" t="n">
-        <v>29.0103</v>
+        <v>29.2735</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>22.3155</v>
+        <v>22.228</v>
       </c>
       <c r="C25" t="n">
-        <v>17.4907</v>
+        <v>17.8205</v>
       </c>
       <c r="D25" t="n">
-        <v>30.7077</v>
+        <v>31.502</v>
       </c>
       <c r="E25" t="n">
-        <v>18.9775</v>
+        <v>17.9924</v>
       </c>
       <c r="F25" t="n">
-        <v>28.6146</v>
+        <v>28.9404</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>21.9288</v>
+        <v>21.8047</v>
       </c>
       <c r="C26" t="n">
-        <v>17.4048</v>
+        <v>17.6822</v>
       </c>
       <c r="D26" t="n">
-        <v>30.8035</v>
+        <v>31.5042</v>
       </c>
       <c r="E26" t="n">
-        <v>18.4967</v>
+        <v>17.5367</v>
       </c>
       <c r="F26" t="n">
-        <v>28.292</v>
+        <v>28.5199</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>21.5484</v>
+        <v>21.5134</v>
       </c>
       <c r="C27" t="n">
-        <v>17.2887</v>
+        <v>17.5489</v>
       </c>
       <c r="D27" t="n">
-        <v>30.6346</v>
+        <v>31.6337</v>
       </c>
       <c r="E27" t="n">
-        <v>18.107</v>
+        <v>17.0983</v>
       </c>
       <c r="F27" t="n">
-        <v>28.0942</v>
+        <v>28.2751</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>21.2514</v>
+        <v>21.2112</v>
       </c>
       <c r="C28" t="n">
-        <v>17.2617</v>
+        <v>17.5222</v>
       </c>
       <c r="D28" t="n">
-        <v>30.8268</v>
+        <v>31.6887</v>
       </c>
       <c r="E28" t="n">
-        <v>17.7016</v>
+        <v>16.8427</v>
       </c>
       <c r="F28" t="n">
-        <v>27.7493</v>
+        <v>27.8447</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>20.9307</v>
+        <v>20.8033</v>
       </c>
       <c r="C29" t="n">
-        <v>17.2133</v>
+        <v>17.3968</v>
       </c>
       <c r="D29" t="n">
-        <v>30.8372</v>
+        <v>31.7795</v>
       </c>
       <c r="E29" t="n">
-        <v>17.2863</v>
+        <v>16.462</v>
       </c>
       <c r="F29" t="n">
-        <v>27.473</v>
+        <v>27.6815</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>20.4823</v>
+        <v>20.3748</v>
       </c>
       <c r="C30" t="n">
-        <v>17.1376</v>
+        <v>17.4377</v>
       </c>
       <c r="D30" t="n">
-        <v>30.9175</v>
+        <v>31.3997</v>
       </c>
       <c r="E30" t="n">
-        <v>16.9702</v>
+        <v>16.1314</v>
       </c>
       <c r="F30" t="n">
-        <v>27.1461</v>
+        <v>27.4711</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>19.9838</v>
+        <v>19.9867</v>
       </c>
       <c r="C31" t="n">
-        <v>17.094</v>
+        <v>17.3735</v>
       </c>
       <c r="D31" t="n">
-        <v>30.9929</v>
+        <v>31.5803</v>
       </c>
       <c r="E31" t="n">
-        <v>16.5964</v>
+        <v>15.8404</v>
       </c>
       <c r="F31" t="n">
-        <v>26.8319</v>
+        <v>27.0684</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>19.5186</v>
+        <v>19.4103</v>
       </c>
       <c r="C32" t="n">
-        <v>17.0295</v>
+        <v>17.382</v>
       </c>
       <c r="D32" t="n">
-        <v>31.0509</v>
+        <v>31.7027</v>
       </c>
       <c r="E32" t="n">
-        <v>16.1345</v>
+        <v>15.5497</v>
       </c>
       <c r="F32" t="n">
-        <v>26.5971</v>
+        <v>26.752</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>18.9547</v>
+        <v>18.9413</v>
       </c>
       <c r="C33" t="n">
-        <v>16.9069</v>
+        <v>17.2624</v>
       </c>
       <c r="D33" t="n">
-        <v>31.3634</v>
+        <v>31.9002</v>
       </c>
       <c r="E33" t="n">
-        <v>16.0068</v>
+        <v>15.219</v>
       </c>
       <c r="F33" t="n">
-        <v>26.2216</v>
+        <v>26.9745</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>18.5146</v>
+        <v>18.3743</v>
       </c>
       <c r="C34" t="n">
-        <v>16.8371</v>
+        <v>17.2046</v>
       </c>
       <c r="D34" t="n">
-        <v>31.5057</v>
+        <v>32.0239</v>
       </c>
       <c r="E34" t="n">
-        <v>15.6392</v>
+        <v>14.9204</v>
       </c>
       <c r="F34" t="n">
-        <v>25.9153</v>
+        <v>26.7271</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>17.8573</v>
+        <v>17.9506</v>
       </c>
       <c r="C35" t="n">
-        <v>16.8158</v>
+        <v>17.151</v>
       </c>
       <c r="D35" t="n">
-        <v>30.938</v>
+        <v>31.167</v>
       </c>
       <c r="E35" t="n">
-        <v>21.1626</v>
+        <v>20.1207</v>
       </c>
       <c r="F35" t="n">
-        <v>30.4331</v>
+        <v>30.9752</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>17.259</v>
+        <v>17.3266</v>
       </c>
       <c r="C36" t="n">
-        <v>16.7604</v>
+        <v>17.1435</v>
       </c>
       <c r="D36" t="n">
-        <v>30.9228</v>
+        <v>31.2539</v>
       </c>
       <c r="E36" t="n">
-        <v>20.5991</v>
+        <v>19.5744</v>
       </c>
       <c r="F36" t="n">
-        <v>29.6333</v>
+        <v>30.6475</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>16.6773</v>
+        <v>16.7061</v>
       </c>
       <c r="C37" t="n">
-        <v>18.1869</v>
+        <v>18.4038</v>
       </c>
       <c r="D37" t="n">
-        <v>30.6801</v>
+        <v>31.0452</v>
       </c>
       <c r="E37" t="n">
-        <v>20.031</v>
+        <v>19.0959</v>
       </c>
       <c r="F37" t="n">
-        <v>29.3087</v>
+        <v>30.3139</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>23.0606</v>
+        <v>23.0546</v>
       </c>
       <c r="C38" t="n">
-        <v>18.0181</v>
+        <v>18.3136</v>
       </c>
       <c r="D38" t="n">
-        <v>30.7144</v>
+        <v>31.4732</v>
       </c>
       <c r="E38" t="n">
-        <v>19.5351</v>
+        <v>18.6066</v>
       </c>
       <c r="F38" t="n">
-        <v>28.8987</v>
+        <v>29.8657</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>22.7806</v>
+        <v>22.7993</v>
       </c>
       <c r="C39" t="n">
-        <v>17.8442</v>
+        <v>18.1212</v>
       </c>
       <c r="D39" t="n">
-        <v>30.6742</v>
+        <v>31.476</v>
       </c>
       <c r="E39" t="n">
-        <v>19.1341</v>
+        <v>18.1546</v>
       </c>
       <c r="F39" t="n">
-        <v>28.54</v>
+        <v>29.5491</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>22.4717</v>
+        <v>22.4174</v>
       </c>
       <c r="C40" t="n">
-        <v>17.6776</v>
+        <v>18.0474</v>
       </c>
       <c r="D40" t="n">
-        <v>30.8939</v>
+        <v>31.6924</v>
       </c>
       <c r="E40" t="n">
-        <v>18.7956</v>
+        <v>17.7887</v>
       </c>
       <c r="F40" t="n">
-        <v>28.2278</v>
+        <v>29.2691</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>22.1394</v>
+        <v>22.0506</v>
       </c>
       <c r="C41" t="n">
-        <v>17.6128</v>
+        <v>17.9061</v>
       </c>
       <c r="D41" t="n">
-        <v>30.9894</v>
+        <v>31.7565</v>
       </c>
       <c r="E41" t="n">
-        <v>18.3314</v>
+        <v>17.3756</v>
       </c>
       <c r="F41" t="n">
-        <v>27.9573</v>
+        <v>28.9874</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>21.7344</v>
+        <v>21.7233</v>
       </c>
       <c r="C42" t="n">
-        <v>17.5597</v>
+        <v>17.7085</v>
       </c>
       <c r="D42" t="n">
-        <v>30.9742</v>
+        <v>31.7744</v>
       </c>
       <c r="E42" t="n">
-        <v>17.9766</v>
+        <v>17.0409</v>
       </c>
       <c r="F42" t="n">
-        <v>27.6238</v>
+        <v>28.6447</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>21.274</v>
+        <v>21.215</v>
       </c>
       <c r="C43" t="n">
-        <v>17.4617</v>
+        <v>17.5967</v>
       </c>
       <c r="D43" t="n">
-        <v>30.971</v>
+        <v>31.8215</v>
       </c>
       <c r="E43" t="n">
-        <v>17.6026</v>
+        <v>16.7205</v>
       </c>
       <c r="F43" t="n">
-        <v>27.3061</v>
+        <v>28.3585</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>20.7816</v>
+        <v>20.719</v>
       </c>
       <c r="C44" t="n">
-        <v>17.3232</v>
+        <v>17.5344</v>
       </c>
       <c r="D44" t="n">
-        <v>31.1525</v>
+        <v>31.8912</v>
       </c>
       <c r="E44" t="n">
-        <v>17.2722</v>
+        <v>16.4166</v>
       </c>
       <c r="F44" t="n">
-        <v>26.9664</v>
+        <v>28.1155</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>20.2812</v>
+        <v>20.2379</v>
       </c>
       <c r="C45" t="n">
-        <v>17.2827</v>
+        <v>17.4229</v>
       </c>
       <c r="D45" t="n">
-        <v>31.2365</v>
+        <v>32.1412</v>
       </c>
       <c r="E45" t="n">
-        <v>16.8255</v>
+        <v>16.0885</v>
       </c>
       <c r="F45" t="n">
-        <v>26.6925</v>
+        <v>27.8186</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>19.8386</v>
+        <v>19.8501</v>
       </c>
       <c r="C46" t="n">
-        <v>17.214</v>
+        <v>17.34</v>
       </c>
       <c r="D46" t="n">
-        <v>31.2183</v>
+        <v>32.2263</v>
       </c>
       <c r="E46" t="n">
-        <v>16.4928</v>
+        <v>15.762</v>
       </c>
       <c r="F46" t="n">
-        <v>26.3244</v>
+        <v>27.5226</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>19.337</v>
+        <v>19.3574</v>
       </c>
       <c r="C47" t="n">
-        <v>17.0782</v>
+        <v>17.2392</v>
       </c>
       <c r="D47" t="n">
-        <v>31.4154</v>
+        <v>32.4397</v>
       </c>
       <c r="E47" t="n">
-        <v>16.2659</v>
+        <v>15.4745</v>
       </c>
       <c r="F47" t="n">
-        <v>25.9521</v>
+        <v>27.2026</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>18.8595</v>
+        <v>18.8238</v>
       </c>
       <c r="C48" t="n">
-        <v>17.0031</v>
+        <v>17.2481</v>
       </c>
       <c r="D48" t="n">
-        <v>31.4984</v>
+        <v>32.4786</v>
       </c>
       <c r="E48" t="n">
-        <v>15.8571</v>
+        <v>15.214</v>
       </c>
       <c r="F48" t="n">
-        <v>25.6579</v>
+        <v>26.8726</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>18.2495</v>
+        <v>18.2089</v>
       </c>
       <c r="C49" t="n">
-        <v>16.9654</v>
+        <v>17.127</v>
       </c>
       <c r="D49" t="n">
-        <v>31.4449</v>
+        <v>32.7086</v>
       </c>
       <c r="E49" t="n">
-        <v>15.3809</v>
+        <v>14.8387</v>
       </c>
       <c r="F49" t="n">
-        <v>25.6997</v>
+        <v>25.9368</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>17.6661</v>
+        <v>17.678</v>
       </c>
       <c r="C50" t="n">
-        <v>16.9139</v>
+        <v>17.0762</v>
       </c>
       <c r="D50" t="n">
-        <v>31.1869</v>
+        <v>31.9349</v>
       </c>
       <c r="E50" t="n">
-        <v>20.7514</v>
+        <v>19.787</v>
       </c>
       <c r="F50" t="n">
-        <v>29.9717</v>
+        <v>30.5705</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>16.9071</v>
+        <v>16.9836</v>
       </c>
       <c r="C51" t="n">
-        <v>18.3285</v>
+        <v>18.4829</v>
       </c>
       <c r="D51" t="n">
-        <v>31.323</v>
+        <v>32.1344</v>
       </c>
       <c r="E51" t="n">
-        <v>20.233</v>
+        <v>19.2866</v>
       </c>
       <c r="F51" t="n">
-        <v>29.2412</v>
+        <v>30.2939</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>16.1251</v>
+        <v>16.0117</v>
       </c>
       <c r="C52" t="n">
-        <v>18.2122</v>
+        <v>18.3183</v>
       </c>
       <c r="D52" t="n">
-        <v>31.4347</v>
+        <v>32.1872</v>
       </c>
       <c r="E52" t="n">
-        <v>19.7995</v>
+        <v>18.7755</v>
       </c>
       <c r="F52" t="n">
-        <v>29.0067</v>
+        <v>29.9823</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>22.9515</v>
+        <v>22.9823</v>
       </c>
       <c r="C53" t="n">
-        <v>18.0387</v>
+        <v>18.2116</v>
       </c>
       <c r="D53" t="n">
-        <v>31.4673</v>
+        <v>32.3428</v>
       </c>
       <c r="E53" t="n">
-        <v>19.2906</v>
+        <v>18.3435</v>
       </c>
       <c r="F53" t="n">
-        <v>28.9962</v>
+        <v>29.2962</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>22.6665</v>
+        <v>22.6577</v>
       </c>
       <c r="C54" t="n">
-        <v>17.896</v>
+        <v>18.0895</v>
       </c>
       <c r="D54" t="n">
-        <v>31.5152</v>
+        <v>32.379</v>
       </c>
       <c r="E54" t="n">
-        <v>18.8206</v>
+        <v>17.9579</v>
       </c>
       <c r="F54" t="n">
-        <v>28.8965</v>
+        <v>29.4989</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>22.3095</v>
+        <v>22.2479</v>
       </c>
       <c r="C55" t="n">
-        <v>17.7689</v>
+        <v>17.9718</v>
       </c>
       <c r="D55" t="n">
-        <v>31.7337</v>
+        <v>32.3829</v>
       </c>
       <c r="E55" t="n">
-        <v>18.0483</v>
+        <v>17.6374</v>
       </c>
       <c r="F55" t="n">
-        <v>28.5472</v>
+        <v>29.2537</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>21.8621</v>
+        <v>21.8302</v>
       </c>
       <c r="C56" t="n">
-        <v>17.6556</v>
+        <v>17.8269</v>
       </c>
       <c r="D56" t="n">
-        <v>31.8968</v>
+        <v>32.6803</v>
       </c>
       <c r="E56" t="n">
-        <v>18.0408</v>
+        <v>17.2154</v>
       </c>
       <c r="F56" t="n">
-        <v>28.1836</v>
+        <v>28.4537</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>21.4341</v>
+        <v>21.3954</v>
       </c>
       <c r="C57" t="n">
-        <v>17.6092</v>
+        <v>17.7173</v>
       </c>
       <c r="D57" t="n">
-        <v>32.257</v>
+        <v>32.7665</v>
       </c>
       <c r="E57" t="n">
-        <v>17.6606</v>
+        <v>16.8917</v>
       </c>
       <c r="F57" t="n">
-        <v>27.8317</v>
+        <v>28.0643</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>20.9663</v>
+        <v>20.9621</v>
       </c>
       <c r="C58" t="n">
-        <v>17.4996</v>
+        <v>17.5984</v>
       </c>
       <c r="D58" t="n">
-        <v>32.3517</v>
+        <v>33.0904</v>
       </c>
       <c r="E58" t="n">
-        <v>17.3143</v>
+        <v>16.5586</v>
       </c>
       <c r="F58" t="n">
-        <v>27.556</v>
+        <v>27.6966</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>20.511</v>
+        <v>20.4617</v>
       </c>
       <c r="C59" t="n">
-        <v>17.3789</v>
+        <v>17.5237</v>
       </c>
       <c r="D59" t="n">
-        <v>32.4721</v>
+        <v>33.2674</v>
       </c>
       <c r="E59" t="n">
-        <v>17.0397</v>
+        <v>16.2621</v>
       </c>
       <c r="F59" t="n">
-        <v>27.2907</v>
+        <v>27.4257</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>20.0662</v>
+        <v>19.9934</v>
       </c>
       <c r="C60" t="n">
-        <v>17.3194</v>
+        <v>17.4499</v>
       </c>
       <c r="D60" t="n">
-        <v>32.8432</v>
+        <v>33.583</v>
       </c>
       <c r="E60" t="n">
-        <v>16.6877</v>
+        <v>15.9441</v>
       </c>
       <c r="F60" t="n">
-        <v>26.9322</v>
+        <v>27.1241</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>19.472</v>
+        <v>19.4587</v>
       </c>
       <c r="C61" t="n">
-        <v>17.1835</v>
+        <v>17.3499</v>
       </c>
       <c r="D61" t="n">
-        <v>33.2414</v>
+        <v>34.0349</v>
       </c>
       <c r="E61" t="n">
-        <v>16.4098</v>
+        <v>15.6647</v>
       </c>
       <c r="F61" t="n">
-        <v>26.7035</v>
+        <v>27.4539</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>18.9313</v>
+        <v>18.9638</v>
       </c>
       <c r="C62" t="n">
-        <v>17.1279</v>
+        <v>17.2803</v>
       </c>
       <c r="D62" t="n">
-        <v>33.3842</v>
+        <v>34.2364</v>
       </c>
       <c r="E62" t="n">
-        <v>15.9467</v>
+        <v>15.3384</v>
       </c>
       <c r="F62" t="n">
-        <v>26.3101</v>
+        <v>26.5523</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>18.4032</v>
+        <v>18.475</v>
       </c>
       <c r="C63" t="n">
-        <v>17.1124</v>
+        <v>17.2438</v>
       </c>
       <c r="D63" t="n">
-        <v>33.751</v>
+        <v>34.5562</v>
       </c>
       <c r="E63" t="n">
-        <v>15.5548</v>
+        <v>15.0085</v>
       </c>
       <c r="F63" t="n">
-        <v>25.9722</v>
+        <v>26.2263</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>17.8217</v>
+        <v>17.8587</v>
       </c>
       <c r="C64" t="n">
-        <v>16.9838</v>
+        <v>17.1609</v>
       </c>
       <c r="D64" t="n">
-        <v>38.3786</v>
+        <v>38.4134</v>
       </c>
       <c r="E64" t="n">
-        <v>21.644</v>
+        <v>21.0745</v>
       </c>
       <c r="F64" t="n">
-        <v>29.8267</v>
+        <v>30.5774</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>17.151</v>
+        <v>17.2332</v>
       </c>
       <c r="C65" t="n">
-        <v>18.604</v>
+        <v>18.7435</v>
       </c>
       <c r="D65" t="n">
-        <v>37.9296</v>
+        <v>38.2331</v>
       </c>
       <c r="E65" t="n">
-        <v>21.3841</v>
+        <v>20.5208</v>
       </c>
       <c r="F65" t="n">
-        <v>29.4643</v>
+        <v>30.2375</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>16.3807</v>
+        <v>16.4648</v>
       </c>
       <c r="C66" t="n">
-        <v>18.3641</v>
+        <v>18.5012</v>
       </c>
       <c r="D66" t="n">
-        <v>38.0348</v>
+        <v>38.4441</v>
       </c>
       <c r="E66" t="n">
-        <v>20.786</v>
+        <v>19.7505</v>
       </c>
       <c r="F66" t="n">
-        <v>29.0659</v>
+        <v>29.8916</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>23.1663</v>
+        <v>23.1443</v>
       </c>
       <c r="C67" t="n">
-        <v>18.302</v>
+        <v>18.3616</v>
       </c>
       <c r="D67" t="n">
-        <v>38.5404</v>
+        <v>38.756</v>
       </c>
       <c r="E67" t="n">
-        <v>20.2802</v>
+        <v>19.3566</v>
       </c>
       <c r="F67" t="n">
-        <v>28.7429</v>
+        <v>29.5102</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>22.8132</v>
+        <v>22.8303</v>
       </c>
       <c r="C68" t="n">
-        <v>18.0528</v>
+        <v>18.2064</v>
       </c>
       <c r="D68" t="n">
-        <v>38.8671</v>
+        <v>39.068</v>
       </c>
       <c r="E68" t="n">
-        <v>19.5381</v>
+        <v>18.7675</v>
       </c>
       <c r="F68" t="n">
-        <v>28.4048</v>
+        <v>29.1269</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>22.4326</v>
+        <v>22.3737</v>
       </c>
       <c r="C69" t="n">
-        <v>17.908</v>
+        <v>18.0412</v>
       </c>
       <c r="D69" t="n">
-        <v>39.3651</v>
+        <v>39.2737</v>
       </c>
       <c r="E69" t="n">
-        <v>19.0199</v>
+        <v>18.1118</v>
       </c>
       <c r="F69" t="n">
-        <v>28.0628</v>
+        <v>28.8669</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>22.0008</v>
+        <v>21.9905</v>
       </c>
       <c r="C70" t="n">
-        <v>17.8604</v>
+        <v>18.0799</v>
       </c>
       <c r="D70" t="n">
-        <v>39.3116</v>
+        <v>39.2894</v>
       </c>
       <c r="E70" t="n">
-        <v>18.491</v>
+        <v>17.6038</v>
       </c>
       <c r="F70" t="n">
-        <v>27.6721</v>
+        <v>28.5098</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>21.5167</v>
+        <v>21.4823</v>
       </c>
       <c r="C71" t="n">
-        <v>17.7174</v>
+        <v>17.8475</v>
       </c>
       <c r="D71" t="n">
-        <v>39.5046</v>
+        <v>39.3416</v>
       </c>
       <c r="E71" t="n">
-        <v>18.0139</v>
+        <v>17.1577</v>
       </c>
       <c r="F71" t="n">
-        <v>27.3845</v>
+        <v>28.2073</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>21.0736</v>
+        <v>21.0741</v>
       </c>
       <c r="C72" t="n">
-        <v>17.6053</v>
+        <v>17.8395</v>
       </c>
       <c r="D72" t="n">
-        <v>39.2583</v>
+        <v>39.5216</v>
       </c>
       <c r="E72" t="n">
-        <v>17.4598</v>
+        <v>16.7672</v>
       </c>
       <c r="F72" t="n">
-        <v>27.7266</v>
+        <v>28.4928</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>20.5909</v>
+        <v>20.5764</v>
       </c>
       <c r="C73" t="n">
-        <v>17.4733</v>
+        <v>17.7577</v>
       </c>
       <c r="D73" t="n">
-        <v>39.5968</v>
+        <v>39.6554</v>
       </c>
       <c r="E73" t="n">
-        <v>17.122</v>
+        <v>16.4379</v>
       </c>
       <c r="F73" t="n">
-        <v>27.45</v>
+        <v>28.2406</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>20.1381</v>
+        <v>20.1497</v>
       </c>
       <c r="C74" t="n">
-        <v>17.3491</v>
+        <v>17.6672</v>
       </c>
       <c r="D74" t="n">
-        <v>39.5996</v>
+        <v>39.5984</v>
       </c>
       <c r="E74" t="n">
-        <v>16.7441</v>
+        <v>16.1225</v>
       </c>
       <c r="F74" t="n">
-        <v>27.1785</v>
+        <v>27.976</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>19.5981</v>
+        <v>19.6014</v>
       </c>
       <c r="C75" t="n">
-        <v>17.2667</v>
+        <v>17.5469</v>
       </c>
       <c r="D75" t="n">
-        <v>39.5394</v>
+        <v>39.7342</v>
       </c>
       <c r="E75" t="n">
-        <v>16.4348</v>
+        <v>15.791</v>
       </c>
       <c r="F75" t="n">
-        <v>26.7814</v>
+        <v>27.0151</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>19.1353</v>
+        <v>19.0552</v>
       </c>
       <c r="C76" t="n">
-        <v>17.2275</v>
+        <v>17.4766</v>
       </c>
       <c r="D76" t="n">
-        <v>39.7359</v>
+        <v>39.9114</v>
       </c>
       <c r="E76" t="n">
-        <v>16.0639</v>
+        <v>15.4849</v>
       </c>
       <c r="F76" t="n">
-        <v>26.5612</v>
+        <v>26.7229</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>18.6267</v>
+        <v>18.5739</v>
       </c>
       <c r="C77" t="n">
-        <v>17.1161</v>
+        <v>17.427</v>
       </c>
       <c r="D77" t="n">
-        <v>39.445</v>
+        <v>39.6274</v>
       </c>
       <c r="E77" t="n">
-        <v>15.704</v>
+        <v>15.1853</v>
       </c>
       <c r="F77" t="n">
-        <v>26.1471</v>
+        <v>26.3846</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>17.9847</v>
+        <v>18.0425</v>
       </c>
       <c r="C78" t="n">
-        <v>17.0441</v>
+        <v>17.1997</v>
       </c>
       <c r="D78" t="n">
-        <v>46.3449</v>
+        <v>45.4804</v>
       </c>
       <c r="E78" t="n">
-        <v>21.1882</v>
+        <v>20.4014</v>
       </c>
       <c r="F78" t="n">
-        <v>30.4529</v>
+        <v>31.0185</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>17.3689</v>
+        <v>17.3403</v>
       </c>
       <c r="C79" t="n">
-        <v>18.8606</v>
+        <v>19.103</v>
       </c>
       <c r="D79" t="n">
-        <v>46.2429</v>
+        <v>45.4808</v>
       </c>
       <c r="E79" t="n">
-        <v>20.6825</v>
+        <v>19.8354</v>
       </c>
       <c r="F79" t="n">
-        <v>30.0422</v>
+        <v>30.7154</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>16.6196</v>
+        <v>16.5562</v>
       </c>
       <c r="C80" t="n">
-        <v>18.6116</v>
+        <v>18.8837</v>
       </c>
       <c r="D80" t="n">
-        <v>45.7913</v>
+        <v>45.1041</v>
       </c>
       <c r="E80" t="n">
-        <v>19.7214</v>
+        <v>19.2786</v>
       </c>
       <c r="F80" t="n">
-        <v>29.8123</v>
+        <v>30.4101</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>23.2878</v>
+        <v>23.2631</v>
       </c>
       <c r="C81" t="n">
-        <v>18.4552</v>
+        <v>18.7036</v>
       </c>
       <c r="D81" t="n">
-        <v>45.2576</v>
+        <v>44.256</v>
       </c>
       <c r="E81" t="n">
-        <v>19.2968</v>
+        <v>18.8615</v>
       </c>
       <c r="F81" t="n">
-        <v>29.4402</v>
+        <v>30.0963</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>22.925</v>
+        <v>22.9034</v>
       </c>
       <c r="C82" t="n">
-        <v>18.2381</v>
+        <v>18.4725</v>
       </c>
       <c r="D82" t="n">
-        <v>44.6284</v>
+        <v>43.9673</v>
       </c>
       <c r="E82" t="n">
-        <v>18.8146</v>
+        <v>18.4386</v>
       </c>
       <c r="F82" t="n">
-        <v>29.0799</v>
+        <v>29.7509</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>22.551</v>
+        <v>22.5505</v>
       </c>
       <c r="C83" t="n">
-        <v>18.1004</v>
+        <v>18.3618</v>
       </c>
       <c r="D83" t="n">
-        <v>44.304</v>
+        <v>43.6701</v>
       </c>
       <c r="E83" t="n">
-        <v>18.3757</v>
+        <v>18.0254</v>
       </c>
       <c r="F83" t="n">
-        <v>28.7754</v>
+        <v>29.4378</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>22.1239</v>
+        <v>22.1297</v>
       </c>
       <c r="C84" t="n">
-        <v>17.9575</v>
+        <v>18.2088</v>
       </c>
       <c r="D84" t="n">
-        <v>44.0131</v>
+        <v>43.2302</v>
       </c>
       <c r="E84" t="n">
-        <v>18.0238</v>
+        <v>17.6126</v>
       </c>
       <c r="F84" t="n">
-        <v>28.4704</v>
+        <v>29.1438</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>21.6707</v>
+        <v>21.6691</v>
       </c>
       <c r="C85" t="n">
-        <v>17.7841</v>
+        <v>17.9822</v>
       </c>
       <c r="D85" t="n">
-        <v>42.9708</v>
+        <v>42.7954</v>
       </c>
       <c r="E85" t="n">
-        <v>17.6014</v>
+        <v>17.2684</v>
       </c>
       <c r="F85" t="n">
-        <v>28.176</v>
+        <v>28.8388</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>21.2341</v>
+        <v>21.2373</v>
       </c>
       <c r="C86" t="n">
-        <v>17.6913</v>
+        <v>17.8352</v>
       </c>
       <c r="D86" t="n">
-        <v>43.3301</v>
+        <v>42.3619</v>
       </c>
       <c r="E86" t="n">
-        <v>17.1912</v>
+        <v>16.9058</v>
       </c>
       <c r="F86" t="n">
-        <v>27.8937</v>
+        <v>28.6154</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>20.7379</v>
+        <v>20.7004</v>
       </c>
       <c r="C87" t="n">
-        <v>17.5634</v>
+        <v>17.7166</v>
       </c>
       <c r="D87" t="n">
-        <v>42.9872</v>
+        <v>42.1008</v>
       </c>
       <c r="E87" t="n">
-        <v>16.8322</v>
+        <v>16.5761</v>
       </c>
       <c r="F87" t="n">
-        <v>27.6036</v>
+        <v>28.3147</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>20.2498</v>
+        <v>20.2491</v>
       </c>
       <c r="C88" t="n">
-        <v>17.4765</v>
+        <v>17.6031</v>
       </c>
       <c r="D88" t="n">
-        <v>42.5708</v>
+        <v>41.7129</v>
       </c>
       <c r="E88" t="n">
-        <v>16.4807</v>
+        <v>16.2542</v>
       </c>
       <c r="F88" t="n">
-        <v>27.2688</v>
+        <v>28.0187</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>19.7215</v>
+        <v>19.7173</v>
       </c>
       <c r="C89" t="n">
-        <v>17.3419</v>
+        <v>17.4792</v>
       </c>
       <c r="D89" t="n">
-        <v>41.5391</v>
+        <v>41.5938</v>
       </c>
       <c r="E89" t="n">
-        <v>16.1253</v>
+        <v>15.9228</v>
       </c>
       <c r="F89" t="n">
-        <v>26.952</v>
+        <v>27.7171</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>19.2306</v>
+        <v>19.299</v>
       </c>
       <c r="C90" t="n">
-        <v>17.2338</v>
+        <v>17.3987</v>
       </c>
       <c r="D90" t="n">
-        <v>41.2561</v>
+        <v>41.5634</v>
       </c>
       <c r="E90" t="n">
-        <v>15.7084</v>
+        <v>15.6002</v>
       </c>
       <c r="F90" t="n">
-        <v>26.6794</v>
+        <v>27.4077</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>18.7216</v>
+        <v>18.7384</v>
       </c>
       <c r="C91" t="n">
-        <v>17.1301</v>
+        <v>17.2999</v>
       </c>
       <c r="D91" t="n">
-        <v>41.135</v>
+        <v>41.4486</v>
       </c>
       <c r="E91" t="n">
-        <v>15.3102</v>
+        <v>15.29</v>
       </c>
       <c r="F91" t="n">
-        <v>26.3186</v>
+        <v>27.1428</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>18.1945</v>
+        <v>18.1781</v>
       </c>
       <c r="C92" t="n">
-        <v>17.0504</v>
+        <v>17.2512</v>
       </c>
       <c r="D92" t="n">
-        <v>47.3313</v>
+        <v>46.4754</v>
       </c>
       <c r="E92" t="n">
-        <v>21.1266</v>
+        <v>20.5165</v>
       </c>
       <c r="F92" t="n">
-        <v>30.5523</v>
+        <v>31.1475</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>17.5405</v>
+        <v>17.57</v>
       </c>
       <c r="C93" t="n">
-        <v>16.9945</v>
+        <v>17.1566</v>
       </c>
       <c r="D93" t="n">
-        <v>46.6133</v>
+        <v>45.7479</v>
       </c>
       <c r="E93" t="n">
-        <v>20.5437</v>
+        <v>19.9693</v>
       </c>
       <c r="F93" t="n">
-        <v>29.7707</v>
+        <v>30.8195</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>16.8626</v>
+        <v>16.8493</v>
       </c>
       <c r="C94" t="n">
-        <v>18.6004</v>
+        <v>18.8208</v>
       </c>
       <c r="D94" t="n">
-        <v>45.5271</v>
+        <v>44.6283</v>
       </c>
       <c r="E94" t="n">
-        <v>19.9823</v>
+        <v>19.4542</v>
       </c>
       <c r="F94" t="n">
-        <v>29.4185</v>
+        <v>30.3466</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>23.3422</v>
+        <v>23.3476</v>
       </c>
       <c r="C95" t="n">
-        <v>18.398</v>
+        <v>18.6081</v>
       </c>
       <c r="D95" t="n">
-        <v>45.1164</v>
+        <v>44.1898</v>
       </c>
       <c r="E95" t="n">
-        <v>19.4786</v>
+        <v>18.952</v>
       </c>
       <c r="F95" t="n">
-        <v>29.0638</v>
+        <v>30.006</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>23.0002</v>
+        <v>23.015</v>
       </c>
       <c r="C96" t="n">
-        <v>18.2299</v>
+        <v>18.427</v>
       </c>
       <c r="D96" t="n">
-        <v>44.5656</v>
+        <v>43.8094</v>
       </c>
       <c r="E96" t="n">
-        <v>19.4947</v>
+        <v>18.502</v>
       </c>
       <c r="F96" t="n">
-        <v>28.7452</v>
+        <v>29.331</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>22.6105</v>
+        <v>22.639</v>
       </c>
       <c r="C97" t="n">
-        <v>18.0728</v>
+        <v>18.2525</v>
       </c>
       <c r="D97" t="n">
-        <v>44.3278</v>
+        <v>43.34</v>
       </c>
       <c r="E97" t="n">
-        <v>19.0278</v>
+        <v>18.0819</v>
       </c>
       <c r="F97" t="n">
-        <v>28.1936</v>
+        <v>28.8931</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>22.1731</v>
+        <v>22.2177</v>
       </c>
       <c r="C98" t="n">
-        <v>17.9193</v>
+        <v>18.1057</v>
       </c>
       <c r="D98" t="n">
-        <v>43.8596</v>
+        <v>42.9612</v>
       </c>
       <c r="E98" t="n">
-        <v>18.5448</v>
+        <v>17.6695</v>
       </c>
       <c r="F98" t="n">
-        <v>27.8685</v>
+        <v>28.4694</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>21.7379</v>
+        <v>21.7738</v>
       </c>
       <c r="C99" t="n">
-        <v>17.7904</v>
+        <v>17.9816</v>
       </c>
       <c r="D99" t="n">
-        <v>43.223</v>
+        <v>42.4586</v>
       </c>
       <c r="E99" t="n">
-        <v>18.1287</v>
+        <v>17.3035</v>
       </c>
       <c r="F99" t="n">
-        <v>27.5177</v>
+        <v>28.1414</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>21.3198</v>
+        <v>21.3353</v>
       </c>
       <c r="C100" t="n">
-        <v>17.7047</v>
+        <v>17.956</v>
       </c>
       <c r="D100" t="n">
-        <v>43.1034</v>
+        <v>42.3054</v>
       </c>
       <c r="E100" t="n">
-        <v>17.8433</v>
+        <v>16.964</v>
       </c>
       <c r="F100" t="n">
-        <v>27.2042</v>
+        <v>27.836</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>20.7806</v>
+        <v>20.8584</v>
       </c>
       <c r="C101" t="n">
-        <v>17.6203</v>
+        <v>17.8487</v>
       </c>
       <c r="D101" t="n">
-        <v>42.5903</v>
+        <v>41.9822</v>
       </c>
       <c r="E101" t="n">
-        <v>17.4757</v>
+        <v>16.6342</v>
       </c>
       <c r="F101" t="n">
-        <v>26.9155</v>
+        <v>27.5414</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>20.3397</v>
+        <v>20.3888</v>
       </c>
       <c r="C102" t="n">
-        <v>17.4826</v>
+        <v>17.735</v>
       </c>
       <c r="D102" t="n">
-        <v>42.175</v>
+        <v>41.644</v>
       </c>
       <c r="E102" t="n">
-        <v>17.1404</v>
+        <v>16.2928</v>
       </c>
       <c r="F102" t="n">
-        <v>26.6322</v>
+        <v>27.2828</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>19.8315</v>
+        <v>19.9011</v>
       </c>
       <c r="C103" t="n">
-        <v>17.3336</v>
+        <v>17.6378</v>
       </c>
       <c r="D103" t="n">
-        <v>42.1206</v>
+        <v>41.5635</v>
       </c>
       <c r="E103" t="n">
-        <v>16.6525</v>
+        <v>15.9809</v>
       </c>
       <c r="F103" t="n">
-        <v>26.3038</v>
+        <v>27.0085</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>19.362</v>
+        <v>19.3778</v>
       </c>
       <c r="C104" t="n">
-        <v>17.234</v>
+        <v>17.5853</v>
       </c>
       <c r="D104" t="n">
-        <v>41.5797</v>
+        <v>41.8344</v>
       </c>
       <c r="E104" t="n">
-        <v>16.3268</v>
+        <v>15.6857</v>
       </c>
       <c r="F104" t="n">
-        <v>26.0263</v>
+        <v>26.6911</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>18.8665</v>
+        <v>18.8012</v>
       </c>
       <c r="C105" t="n">
-        <v>17.1698</v>
+        <v>17.4556</v>
       </c>
       <c r="D105" t="n">
-        <v>41.573</v>
+        <v>41.7689</v>
       </c>
       <c r="E105" t="n">
-        <v>15.9519</v>
+        <v>15.3699</v>
       </c>
       <c r="F105" t="n">
-        <v>25.6884</v>
+        <v>26.3671</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>18.2944</v>
+        <v>18.3199</v>
       </c>
       <c r="C106" t="n">
-        <v>17.0833</v>
+        <v>17.3579</v>
       </c>
       <c r="D106" t="n">
-        <v>40.9729</v>
+        <v>41.3866</v>
       </c>
       <c r="E106" t="n">
-        <v>15.6226</v>
+        <v>15.0684</v>
       </c>
       <c r="F106" t="n">
-        <v>25.5534</v>
+        <v>26.0591</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>17.7271</v>
+        <v>17.7133</v>
       </c>
       <c r="C107" t="n">
-        <v>16.9925</v>
+        <v>17.2698</v>
       </c>
       <c r="D107" t="n">
-        <v>44.1436</v>
+        <v>44.521</v>
       </c>
       <c r="E107" t="n">
-        <v>20.9786</v>
+        <v>19.9708</v>
       </c>
       <c r="F107" t="n">
-        <v>29.5564</v>
+        <v>30.1784</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>17.0473</v>
+        <v>17.0032</v>
       </c>
       <c r="C108" t="n">
-        <v>18.7272</v>
+        <v>18.9541</v>
       </c>
       <c r="D108" t="n">
-        <v>43.9386</v>
+        <v>44.2189</v>
       </c>
       <c r="E108" t="n">
-        <v>20.4325</v>
+        <v>19.5416</v>
       </c>
       <c r="F108" t="n">
-        <v>29.2431</v>
+        <v>29.9226</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>16.143</v>
+        <v>16.1664</v>
       </c>
       <c r="C109" t="n">
-        <v>18.5527</v>
+        <v>18.8045</v>
       </c>
       <c r="D109" t="n">
-        <v>43.4686</v>
+        <v>43.8877</v>
       </c>
       <c r="E109" t="n">
-        <v>20.0068</v>
+        <v>19.0664</v>
       </c>
       <c r="F109" t="n">
-        <v>28.8963</v>
+        <v>29.5916</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>23.0693</v>
+        <v>23.0934</v>
       </c>
       <c r="C110" t="n">
-        <v>18.285</v>
+        <v>18.4759</v>
       </c>
       <c r="D110" t="n">
-        <v>42.9026</v>
+        <v>43.1769</v>
       </c>
       <c r="E110" t="n">
-        <v>19.0411</v>
+        <v>18.65</v>
       </c>
       <c r="F110" t="n">
-        <v>29.1022</v>
+        <v>29.8016</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>22.6899</v>
+        <v>22.7264</v>
       </c>
       <c r="C111" t="n">
-        <v>18.2229</v>
+        <v>18.3037</v>
       </c>
       <c r="D111" t="n">
-        <v>42.4083</v>
+        <v>42.7262</v>
       </c>
       <c r="E111" t="n">
-        <v>18.5971</v>
+        <v>18.171</v>
       </c>
       <c r="F111" t="n">
-        <v>28.7893</v>
+        <v>29.4471</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>22.2682</v>
+        <v>22.3048</v>
       </c>
       <c r="C112" t="n">
-        <v>18.0538</v>
+        <v>18.2174</v>
       </c>
       <c r="D112" t="n">
-        <v>41.8383</v>
+        <v>41.8597</v>
       </c>
       <c r="E112" t="n">
-        <v>18.1545</v>
+        <v>17.7851</v>
       </c>
       <c r="F112" t="n">
-        <v>28.4369</v>
+        <v>29.1797</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>21.8432</v>
+        <v>21.8817</v>
       </c>
       <c r="C113" t="n">
-        <v>17.9078</v>
+        <v>18.0683</v>
       </c>
       <c r="D113" t="n">
-        <v>41.6023</v>
+        <v>41.4768</v>
       </c>
       <c r="E113" t="n">
-        <v>17.7491</v>
+        <v>17.3874</v>
       </c>
       <c r="F113" t="n">
-        <v>28.1475</v>
+        <v>28.8114</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>21.4375</v>
+        <v>21.4289</v>
       </c>
       <c r="C114" t="n">
-        <v>17.7102</v>
+        <v>17.8696</v>
       </c>
       <c r="D114" t="n">
-        <v>40.8833</v>
+        <v>40.6319</v>
       </c>
       <c r="E114" t="n">
-        <v>17.3295</v>
+        <v>17.0279</v>
       </c>
       <c r="F114" t="n">
-        <v>27.8415</v>
+        <v>28.5343</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>20.9</v>
+        <v>20.9671</v>
       </c>
       <c r="C115" t="n">
-        <v>17.6691</v>
+        <v>17.7625</v>
       </c>
       <c r="D115" t="n">
-        <v>40.5114</v>
+        <v>40.2815</v>
       </c>
       <c r="E115" t="n">
-        <v>17.0189</v>
+        <v>16.6964</v>
       </c>
       <c r="F115" t="n">
-        <v>27.5443</v>
+        <v>28.2414</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>20.4308</v>
+        <v>20.4985</v>
       </c>
       <c r="C116" t="n">
-        <v>17.5424</v>
+        <v>17.6746</v>
       </c>
       <c r="D116" t="n">
-        <v>40.0544</v>
+        <v>39.8258</v>
       </c>
       <c r="E116" t="n">
-        <v>17.1822</v>
+        <v>16.3816</v>
       </c>
       <c r="F116" t="n">
-        <v>26.6842</v>
+        <v>27.388</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>19.9574</v>
+        <v>19.9719</v>
       </c>
       <c r="C117" t="n">
-        <v>17.402</v>
+        <v>17.5428</v>
       </c>
       <c r="D117" t="n">
-        <v>39.7982</v>
+        <v>39.5988</v>
       </c>
       <c r="E117" t="n">
-        <v>16.8074</v>
+        <v>16.0405</v>
       </c>
       <c r="F117" t="n">
-        <v>26.4039</v>
+        <v>27.0773</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>19.4962</v>
+        <v>19.4439</v>
       </c>
       <c r="C118" t="n">
-        <v>17.3046</v>
+        <v>17.4844</v>
       </c>
       <c r="D118" t="n">
-        <v>39.442</v>
+        <v>39.3294</v>
       </c>
       <c r="E118" t="n">
-        <v>16.5124</v>
+        <v>15.743</v>
       </c>
       <c r="F118" t="n">
-        <v>26.0748</v>
+        <v>26.8035</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>19.0077</v>
+        <v>18.9676</v>
       </c>
       <c r="C119" t="n">
-        <v>17.1878</v>
+        <v>17.4458</v>
       </c>
       <c r="D119" t="n">
-        <v>39.1788</v>
+        <v>39.1808</v>
       </c>
       <c r="E119" t="n">
-        <v>16.0508</v>
+        <v>15.425</v>
       </c>
       <c r="F119" t="n">
-        <v>25.7755</v>
+        <v>26.5086</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>18.4835</v>
+        <v>18.4178</v>
       </c>
       <c r="C120" t="n">
-        <v>17.1339</v>
+        <v>17.3017</v>
       </c>
       <c r="D120" t="n">
-        <v>38.927</v>
+        <v>38.9657</v>
       </c>
       <c r="E120" t="n">
-        <v>15.688</v>
+        <v>15.1069</v>
       </c>
       <c r="F120" t="n">
-        <v>25.5902</v>
+        <v>26.2082</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>17.8648</v>
+        <v>17.8369</v>
       </c>
       <c r="C121" t="n">
-        <v>17.0298</v>
+        <v>17.2129</v>
       </c>
       <c r="D121" t="n">
-        <v>47.4013</v>
+        <v>46.1724</v>
       </c>
       <c r="E121" t="n">
-        <v>20.607</v>
+        <v>20.1773</v>
       </c>
       <c r="F121" t="n">
-        <v>29.6879</v>
+        <v>30.6327</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>17.177</v>
+        <v>17.2212</v>
       </c>
       <c r="C122" t="n">
-        <v>18.7149</v>
+        <v>18.8793</v>
       </c>
       <c r="D122" t="n">
-        <v>46.7413</v>
+        <v>45.508</v>
       </c>
       <c r="E122" t="n">
-        <v>20.3194</v>
+        <v>19.6032</v>
       </c>
       <c r="F122" t="n">
-        <v>29.2945</v>
+        <v>29.9144</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>16.3349</v>
+        <v>16.3702</v>
       </c>
       <c r="C123" t="n">
-        <v>18.5041</v>
+        <v>18.762</v>
       </c>
       <c r="D123" t="n">
-        <v>46.5408</v>
+        <v>45.2113</v>
       </c>
       <c r="E123" t="n">
-        <v>19.5998</v>
+        <v>19.1704</v>
       </c>
       <c r="F123" t="n">
-        <v>29.12</v>
+        <v>29.5605</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>23.1802</v>
+        <v>23.1808</v>
       </c>
       <c r="C124" t="n">
-        <v>18.31</v>
+        <v>18.4723</v>
       </c>
       <c r="D124" t="n">
-        <v>45.351</v>
+        <v>44.6493</v>
       </c>
       <c r="E124" t="n">
-        <v>19.1051</v>
+        <v>18.6972</v>
       </c>
       <c r="F124" t="n">
-        <v>28.7268</v>
+        <v>29.5163</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>22.7665</v>
+        <v>22.806</v>
       </c>
       <c r="C125" t="n">
-        <v>18.1496</v>
+        <v>18.3596</v>
       </c>
       <c r="D125" t="n">
-        <v>44.7686</v>
+        <v>44.2774</v>
       </c>
       <c r="E125" t="n">
-        <v>18.6741</v>
+        <v>18.2786</v>
       </c>
       <c r="F125" t="n">
-        <v>28.3412</v>
+        <v>29.0842</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>22.3537</v>
+        <v>22.3806</v>
       </c>
       <c r="C126" t="n">
-        <v>17.9874</v>
+        <v>18.1789</v>
       </c>
       <c r="D126" t="n">
-        <v>44.4467</v>
+        <v>43.3376</v>
       </c>
       <c r="E126" t="n">
-        <v>18.2277</v>
+        <v>17.8419</v>
       </c>
       <c r="F126" t="n">
-        <v>28.0641</v>
+        <v>28.7575</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>21.9228</v>
+        <v>21.961</v>
       </c>
       <c r="C127" t="n">
-        <v>17.8465</v>
+        <v>18.0696</v>
       </c>
       <c r="D127" t="n">
-        <v>43.8967</v>
+        <v>42.7799</v>
       </c>
       <c r="E127" t="n">
-        <v>17.7579</v>
+        <v>17.4608</v>
       </c>
       <c r="F127" t="n">
-        <v>27.7717</v>
+        <v>28.4546</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>21.4963</v>
+        <v>21.5069</v>
       </c>
       <c r="C128" t="n">
-        <v>17.744</v>
+        <v>17.8939</v>
       </c>
       <c r="D128" t="n">
-        <v>43.2852</v>
+        <v>42.7503</v>
       </c>
       <c r="E128" t="n">
-        <v>17.4373</v>
+        <v>17.1097</v>
       </c>
       <c r="F128" t="n">
-        <v>27.9019</v>
+        <v>28.4743</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>20.9973</v>
+        <v>21.0516</v>
       </c>
       <c r="C129" t="n">
-        <v>17.6066</v>
+        <v>17.7854</v>
       </c>
       <c r="D129" t="n">
-        <v>42.8574</v>
+        <v>42.2257</v>
       </c>
       <c r="E129" t="n">
-        <v>17.1082</v>
+        <v>16.7689</v>
       </c>
       <c r="F129" t="n">
-        <v>27.5955</v>
+        <v>28.2858</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>20.5333</v>
+        <v>20.5584</v>
       </c>
       <c r="C130" t="n">
-        <v>17.4893</v>
+        <v>17.6557</v>
       </c>
       <c r="D130" t="n">
-        <v>42.4483</v>
+        <v>41.9231</v>
       </c>
       <c r="E130" t="n">
-        <v>17.2588</v>
+        <v>16.4228</v>
       </c>
       <c r="F130" t="n">
-        <v>26.7858</v>
+        <v>27.4148</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>20.0671</v>
+        <v>20.1095</v>
       </c>
       <c r="C131" t="n">
-        <v>17.3744</v>
+        <v>17.6196</v>
       </c>
       <c r="D131" t="n">
-        <v>42.0044</v>
+        <v>41.4026</v>
       </c>
       <c r="E131" t="n">
-        <v>16.9117</v>
+        <v>16.109</v>
       </c>
       <c r="F131" t="n">
-        <v>26.4139</v>
+        <v>27.1134</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>19.5866</v>
+        <v>19.5958</v>
       </c>
       <c r="C132" t="n">
-        <v>17.2745</v>
+        <v>17.4648</v>
       </c>
       <c r="D132" t="n">
-        <v>41.5538</v>
+        <v>41.1341</v>
       </c>
       <c r="E132" t="n">
-        <v>16.4698</v>
+        <v>15.7956</v>
       </c>
       <c r="F132" t="n">
-        <v>26.1123</v>
+        <v>26.8317</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>19.0732</v>
+        <v>19.0723</v>
       </c>
       <c r="C133" t="n">
-        <v>17.2298</v>
+        <v>17.4325</v>
       </c>
       <c r="D133" t="n">
-        <v>41.3408</v>
+        <v>40.8442</v>
       </c>
       <c r="E133" t="n">
-        <v>16.1504</v>
+        <v>15.4894</v>
       </c>
       <c r="F133" t="n">
-        <v>25.8075</v>
+        <v>26.5257</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>18.5774</v>
+        <v>18.5776</v>
       </c>
       <c r="C134" t="n">
-        <v>17.1371</v>
+        <v>17.3051</v>
       </c>
       <c r="D134" t="n">
-        <v>41.1186</v>
+        <v>40.6432</v>
       </c>
       <c r="E134" t="n">
-        <v>15.7775</v>
+        <v>15.1786</v>
       </c>
       <c r="F134" t="n">
-        <v>26.0491</v>
+        <v>26.253</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>17.9795</v>
+        <v>18.016</v>
       </c>
       <c r="C135" t="n">
-        <v>17.0296</v>
+        <v>17.2381</v>
       </c>
       <c r="D135" t="n">
-        <v>48.1407</v>
+        <v>46.7832</v>
       </c>
       <c r="E135" t="n">
-        <v>21.1629</v>
+        <v>20.1675</v>
       </c>
       <c r="F135" t="n">
-        <v>29.7465</v>
+        <v>30.3446</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>17.3422</v>
+        <v>17.3179</v>
       </c>
       <c r="C136" t="n">
-        <v>18.7672</v>
+        <v>18.9293</v>
       </c>
       <c r="D136" t="n">
-        <v>47.7784</v>
+        <v>46.2501</v>
       </c>
       <c r="E136" t="n">
-        <v>20.173</v>
+        <v>19.7256</v>
       </c>
       <c r="F136" t="n">
-        <v>29.4118</v>
+        <v>30.1901</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>16.5269</v>
+        <v>16.5607</v>
       </c>
       <c r="C137" t="n">
-        <v>18.531</v>
+        <v>18.8413</v>
       </c>
       <c r="D137" t="n">
-        <v>46.3308</v>
+        <v>45.6105</v>
       </c>
       <c r="E137" t="n">
-        <v>19.9844</v>
+        <v>19.2087</v>
       </c>
       <c r="F137" t="n">
-        <v>29.0268</v>
+        <v>29.6749</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>23.2345</v>
+        <v>23.2461</v>
       </c>
       <c r="C138" t="n">
-        <v>18.3618</v>
+        <v>18.5224</v>
       </c>
       <c r="D138" t="n">
-        <v>46.4146</v>
+        <v>45.0455</v>
       </c>
       <c r="E138" t="n">
-        <v>19.246</v>
+        <v>18.7372</v>
       </c>
       <c r="F138" t="n">
-        <v>28.6652</v>
+        <v>29.2723</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>22.8793</v>
+        <v>22.9052</v>
       </c>
       <c r="C139" t="n">
-        <v>18.173</v>
+        <v>18.483</v>
       </c>
       <c r="D139" t="n">
-        <v>45.7022</v>
+        <v>44.6947</v>
       </c>
       <c r="E139" t="n">
-        <v>18.7407</v>
+        <v>18.3073</v>
       </c>
       <c r="F139" t="n">
-        <v>28.4462</v>
+        <v>29.0183</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>22.4759</v>
+        <v>22.4965</v>
       </c>
       <c r="C140" t="n">
-        <v>18.0057</v>
+        <v>18.3234</v>
       </c>
       <c r="D140" t="n">
-        <v>45.0141</v>
+        <v>44.1072</v>
       </c>
       <c r="E140" t="n">
-        <v>18.3118</v>
+        <v>17.9145</v>
       </c>
       <c r="F140" t="n">
-        <v>28.099</v>
+        <v>28.7303</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>22.0273</v>
+        <v>22.0708</v>
       </c>
       <c r="C141" t="n">
-        <v>17.8665</v>
+        <v>18.1728</v>
       </c>
       <c r="D141" t="n">
-        <v>44.3041</v>
+        <v>43.5833</v>
       </c>
       <c r="E141" t="n">
-        <v>17.8718</v>
+        <v>17.5459</v>
       </c>
       <c r="F141" t="n">
-        <v>27.7741</v>
+        <v>28.3629</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>21.6078</v>
+        <v>21.6116</v>
       </c>
       <c r="C142" t="n">
-        <v>17.7736</v>
+        <v>17.9113</v>
       </c>
       <c r="D142" t="n">
-        <v>43.8013</v>
+        <v>42.8785</v>
       </c>
       <c r="E142" t="n">
-        <v>17.5134</v>
+        <v>17.1612</v>
       </c>
       <c r="F142" t="n">
-        <v>27.4435</v>
+        <v>28.055</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>21.1235</v>
+        <v>21.1546</v>
       </c>
       <c r="C143" t="n">
-        <v>17.6016</v>
+        <v>17.8923</v>
       </c>
       <c r="D143" t="n">
-        <v>43.4251</v>
+        <v>42.3643</v>
       </c>
       <c r="E143" t="n">
-        <v>17.6278</v>
+        <v>16.8503</v>
       </c>
       <c r="F143" t="n">
-        <v>27.1701</v>
+        <v>27.7666</v>
       </c>
     </row>
   </sheetData>

--- a/clang-x64/Running erasure.xlsx
+++ b/clang-x64/Running erasure.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>18.1873</v>
+        <v>18.226</v>
       </c>
       <c r="C2" t="n">
-        <v>13.0642</v>
+        <v>13.1125</v>
       </c>
       <c r="D2" t="n">
-        <v>30.7265</v>
+        <v>30.6679</v>
       </c>
       <c r="E2" t="n">
-        <v>12.6225</v>
+        <v>12.72</v>
       </c>
       <c r="F2" t="n">
-        <v>26.374</v>
+        <v>26.5566</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>18.2427</v>
+        <v>18.1844</v>
       </c>
       <c r="C3" t="n">
-        <v>13.2708</v>
+        <v>13.3185</v>
       </c>
       <c r="D3" t="n">
-        <v>30.8356</v>
+        <v>30.9115</v>
       </c>
       <c r="E3" t="n">
-        <v>12.6275</v>
+        <v>12.6513</v>
       </c>
       <c r="F3" t="n">
-        <v>26.4565</v>
+        <v>26.1808</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>17.5995</v>
+        <v>17.5093</v>
       </c>
       <c r="C4" t="n">
-        <v>13.4329</v>
+        <v>13.4492</v>
       </c>
       <c r="D4" t="n">
-        <v>30.9713</v>
+        <v>31.0411</v>
       </c>
       <c r="E4" t="n">
-        <v>12.3454</v>
+        <v>12.3548</v>
       </c>
       <c r="F4" t="n">
-        <v>25.9954</v>
+        <v>25.878</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>16.942</v>
+        <v>17.0869</v>
       </c>
       <c r="C5" t="n">
-        <v>13.7699</v>
+        <v>13.6164</v>
       </c>
       <c r="D5" t="n">
-        <v>31.187</v>
+        <v>31.2258</v>
       </c>
       <c r="E5" t="n">
-        <v>12.1402</v>
+        <v>12.2786</v>
       </c>
       <c r="F5" t="n">
-        <v>25.1504</v>
+        <v>25.7903</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>16.6406</v>
+        <v>16.6857</v>
       </c>
       <c r="C6" t="n">
-        <v>13.8739</v>
+        <v>13.8574</v>
       </c>
       <c r="D6" t="n">
-        <v>31.2468</v>
+        <v>31.2216</v>
       </c>
       <c r="E6" t="n">
-        <v>12.2599</v>
+        <v>12.3219</v>
       </c>
       <c r="F6" t="n">
-        <v>25.4634</v>
+        <v>25.2278</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>16.3569</v>
+        <v>16.3205</v>
       </c>
       <c r="C7" t="n">
-        <v>14.1519</v>
+        <v>14.1374</v>
       </c>
       <c r="D7" t="n">
-        <v>30.1633</v>
+        <v>30.1618</v>
       </c>
       <c r="E7" t="n">
-        <v>18.7929</v>
+        <v>18.7636</v>
       </c>
       <c r="F7" t="n">
-        <v>30.1421</v>
+        <v>30.0435</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>15.8323</v>
+        <v>15.8529</v>
       </c>
       <c r="C8" t="n">
-        <v>15.4549</v>
+        <v>15.5303</v>
       </c>
       <c r="D8" t="n">
-        <v>30.1855</v>
+        <v>30.1291</v>
       </c>
       <c r="E8" t="n">
-        <v>18.2929</v>
+        <v>18.2325</v>
       </c>
       <c r="F8" t="n">
-        <v>29.6575</v>
+        <v>29.6389</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>15.0955</v>
+        <v>15.0969</v>
       </c>
       <c r="C9" t="n">
-        <v>15.6332</v>
+        <v>15.6002</v>
       </c>
       <c r="D9" t="n">
-        <v>30.3665</v>
+        <v>30.2367</v>
       </c>
       <c r="E9" t="n">
-        <v>17.9145</v>
+        <v>17.8637</v>
       </c>
       <c r="F9" t="n">
-        <v>29.4536</v>
+        <v>29.4695</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>21.6752</v>
+        <v>21.7356</v>
       </c>
       <c r="C10" t="n">
-        <v>15.7451</v>
+        <v>15.6803</v>
       </c>
       <c r="D10" t="n">
-        <v>30.3455</v>
+        <v>30.2981</v>
       </c>
       <c r="E10" t="n">
-        <v>17.3887</v>
+        <v>17.4322</v>
       </c>
       <c r="F10" t="n">
-        <v>29.2156</v>
+        <v>29.1874</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>21.4626</v>
+        <v>21.3796</v>
       </c>
       <c r="C11" t="n">
-        <v>15.8403</v>
+        <v>15.9559</v>
       </c>
       <c r="D11" t="n">
-        <v>30.5487</v>
+        <v>30.5002</v>
       </c>
       <c r="E11" t="n">
-        <v>17.0878</v>
+        <v>17.0258</v>
       </c>
       <c r="F11" t="n">
-        <v>28.9029</v>
+        <v>28.8944</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>21.1014</v>
+        <v>21.0196</v>
       </c>
       <c r="C12" t="n">
-        <v>15.9239</v>
+        <v>16.0754</v>
       </c>
       <c r="D12" t="n">
-        <v>30.6801</v>
+        <v>30.5231</v>
       </c>
       <c r="E12" t="n">
-        <v>16.5877</v>
+        <v>16.6483</v>
       </c>
       <c r="F12" t="n">
-        <v>28.0793</v>
+        <v>28.2046</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>20.8414</v>
+        <v>20.647</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1338</v>
+        <v>16.2181</v>
       </c>
       <c r="D13" t="n">
-        <v>31.0641</v>
+        <v>30.7292</v>
       </c>
       <c r="E13" t="n">
-        <v>16.4181</v>
+        <v>16.4059</v>
       </c>
       <c r="F13" t="n">
-        <v>27.8941</v>
+        <v>27.858</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>20.3972</v>
+        <v>20.351</v>
       </c>
       <c r="C14" t="n">
-        <v>16.4019</v>
+        <v>16.4622</v>
       </c>
       <c r="D14" t="n">
-        <v>31.1088</v>
+        <v>31.0092</v>
       </c>
       <c r="E14" t="n">
-        <v>16.1298</v>
+        <v>16.1274</v>
       </c>
       <c r="F14" t="n">
-        <v>27.7083</v>
+        <v>27.6962</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>19.969</v>
+        <v>20.0362</v>
       </c>
       <c r="C15" t="n">
-        <v>16.3327</v>
+        <v>16.5455</v>
       </c>
       <c r="D15" t="n">
-        <v>31.3103</v>
+        <v>31.0009</v>
       </c>
       <c r="E15" t="n">
-        <v>15.8517</v>
+        <v>15.9672</v>
       </c>
       <c r="F15" t="n">
-        <v>27.2218</v>
+        <v>27.389</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>19.7977</v>
+        <v>19.6615</v>
       </c>
       <c r="C16" t="n">
-        <v>16.382</v>
+        <v>16.5673</v>
       </c>
       <c r="D16" t="n">
-        <v>31.5602</v>
+        <v>31.1686</v>
       </c>
       <c r="E16" t="n">
-        <v>15.5319</v>
+        <v>15.5171</v>
       </c>
       <c r="F16" t="n">
-        <v>27.0629</v>
+        <v>26.8902</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>19.2976</v>
+        <v>19.1882</v>
       </c>
       <c r="C17" t="n">
-        <v>16.4805</v>
+        <v>16.3982</v>
       </c>
       <c r="D17" t="n">
-        <v>31.6391</v>
+        <v>31.2875</v>
       </c>
       <c r="E17" t="n">
-        <v>15.2668</v>
+        <v>15.2553</v>
       </c>
       <c r="F17" t="n">
-        <v>26.6807</v>
+        <v>26.6528</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>19.0571</v>
+        <v>18.8755</v>
       </c>
       <c r="C18" t="n">
-        <v>16.4857</v>
+        <v>16.4529</v>
       </c>
       <c r="D18" t="n">
-        <v>31.935</v>
+        <v>31.5355</v>
       </c>
       <c r="E18" t="n">
-        <v>14.9616</v>
+        <v>14.9809</v>
       </c>
       <c r="F18" t="n">
-        <v>26.3869</v>
+        <v>26.4137</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>18.3642</v>
+        <v>18.3662</v>
       </c>
       <c r="C19" t="n">
-        <v>16.5577</v>
+        <v>16.5993</v>
       </c>
       <c r="D19" t="n">
-        <v>32.0637</v>
+        <v>31.7087</v>
       </c>
       <c r="E19" t="n">
-        <v>14.5992</v>
+        <v>14.6121</v>
       </c>
       <c r="F19" t="n">
-        <v>26.2361</v>
+        <v>26.0008</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>17.9687</v>
+        <v>17.947</v>
       </c>
       <c r="C20" t="n">
-        <v>16.6791</v>
+        <v>16.7527</v>
       </c>
       <c r="D20" t="n">
-        <v>32.2281</v>
+        <v>31.8708</v>
       </c>
       <c r="E20" t="n">
-        <v>14.3105</v>
+        <v>14.3062</v>
       </c>
       <c r="F20" t="n">
-        <v>25.9073</v>
+        <v>25.7959</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>17.3414</v>
+        <v>17.2388</v>
       </c>
       <c r="C21" t="n">
-        <v>16.6892</v>
+        <v>16.559</v>
       </c>
       <c r="D21" t="n">
-        <v>31.1621</v>
+        <v>31.1089</v>
       </c>
       <c r="E21" t="n">
-        <v>20.0684</v>
+        <v>19.9552</v>
       </c>
       <c r="F21" t="n">
-        <v>30.8248</v>
+        <v>30.8572</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>16.7941</v>
+        <v>16.7303</v>
       </c>
       <c r="C22" t="n">
-        <v>17.9257</v>
+        <v>18.1203</v>
       </c>
       <c r="D22" t="n">
-        <v>31.0915</v>
+        <v>31.0498</v>
       </c>
       <c r="E22" t="n">
-        <v>19.478</v>
+        <v>19.3928</v>
       </c>
       <c r="F22" t="n">
-        <v>29.8566</v>
+        <v>29.9768</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>16.0409</v>
+        <v>16.0253</v>
       </c>
       <c r="C23" t="n">
-        <v>17.9015</v>
+        <v>17.9921</v>
       </c>
       <c r="D23" t="n">
-        <v>31.1165</v>
+        <v>31.0994</v>
       </c>
       <c r="E23" t="n">
-        <v>18.8929</v>
+        <v>18.8936</v>
       </c>
       <c r="F23" t="n">
-        <v>29.6297</v>
+        <v>29.6029</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>22.5232</v>
+        <v>22.4819</v>
       </c>
       <c r="C24" t="n">
-        <v>17.8172</v>
+        <v>17.8632</v>
       </c>
       <c r="D24" t="n">
-        <v>31.0443</v>
+        <v>31.0687</v>
       </c>
       <c r="E24" t="n">
-        <v>18.4688</v>
+        <v>18.4454</v>
       </c>
       <c r="F24" t="n">
-        <v>29.2735</v>
+        <v>29.2398</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>22.228</v>
+        <v>22.2145</v>
       </c>
       <c r="C25" t="n">
-        <v>17.8205</v>
+        <v>17.811</v>
       </c>
       <c r="D25" t="n">
-        <v>31.502</v>
+        <v>31.5213</v>
       </c>
       <c r="E25" t="n">
-        <v>17.9924</v>
+        <v>18.0252</v>
       </c>
       <c r="F25" t="n">
-        <v>28.9404</v>
+        <v>29.0049</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>21.8047</v>
+        <v>21.8775</v>
       </c>
       <c r="C26" t="n">
-        <v>17.6822</v>
+        <v>17.7189</v>
       </c>
       <c r="D26" t="n">
-        <v>31.5042</v>
+        <v>31.5422</v>
       </c>
       <c r="E26" t="n">
-        <v>17.5367</v>
+        <v>17.6029</v>
       </c>
       <c r="F26" t="n">
-        <v>28.5199</v>
+        <v>28.6377</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>21.5134</v>
+        <v>21.5143</v>
       </c>
       <c r="C27" t="n">
-        <v>17.5489</v>
+        <v>17.6142</v>
       </c>
       <c r="D27" t="n">
-        <v>31.6337</v>
+        <v>31.6407</v>
       </c>
       <c r="E27" t="n">
-        <v>17.0983</v>
+        <v>17.2108</v>
       </c>
       <c r="F27" t="n">
-        <v>28.2751</v>
+        <v>28.328</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>21.2112</v>
+        <v>21.2336</v>
       </c>
       <c r="C28" t="n">
-        <v>17.5222</v>
+        <v>17.6181</v>
       </c>
       <c r="D28" t="n">
-        <v>31.6887</v>
+        <v>31.7422</v>
       </c>
       <c r="E28" t="n">
-        <v>16.8427</v>
+        <v>16.8452</v>
       </c>
       <c r="F28" t="n">
-        <v>27.8447</v>
+        <v>28.0352</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>20.8033</v>
+        <v>20.7959</v>
       </c>
       <c r="C29" t="n">
-        <v>17.3968</v>
+        <v>17.4737</v>
       </c>
       <c r="D29" t="n">
-        <v>31.7795</v>
+        <v>31.7608</v>
       </c>
       <c r="E29" t="n">
-        <v>16.462</v>
+        <v>16.4541</v>
       </c>
       <c r="F29" t="n">
-        <v>27.6815</v>
+        <v>27.6827</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>20.3748</v>
+        <v>20.3826</v>
       </c>
       <c r="C30" t="n">
-        <v>17.4377</v>
+        <v>17.495</v>
       </c>
       <c r="D30" t="n">
-        <v>31.3997</v>
+        <v>31.8278</v>
       </c>
       <c r="E30" t="n">
-        <v>16.1314</v>
+        <v>16.0962</v>
       </c>
       <c r="F30" t="n">
-        <v>27.4711</v>
+        <v>27.6499</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>19.9867</v>
+        <v>19.9134</v>
       </c>
       <c r="C31" t="n">
-        <v>17.3735</v>
+        <v>17.409</v>
       </c>
       <c r="D31" t="n">
-        <v>31.5803</v>
+        <v>31.9646</v>
       </c>
       <c r="E31" t="n">
-        <v>15.8404</v>
+        <v>15.8047</v>
       </c>
       <c r="F31" t="n">
-        <v>27.0684</v>
+        <v>27.1678</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>19.4103</v>
+        <v>19.4027</v>
       </c>
       <c r="C32" t="n">
-        <v>17.382</v>
+        <v>17.3703</v>
       </c>
       <c r="D32" t="n">
-        <v>31.7027</v>
+        <v>32.1151</v>
       </c>
       <c r="E32" t="n">
-        <v>15.5497</v>
+        <v>15.5108</v>
       </c>
       <c r="F32" t="n">
-        <v>26.752</v>
+        <v>26.7874</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>18.9413</v>
+        <v>18.9217</v>
       </c>
       <c r="C33" t="n">
-        <v>17.2624</v>
+        <v>17.316</v>
       </c>
       <c r="D33" t="n">
-        <v>31.9002</v>
+        <v>32.2876</v>
       </c>
       <c r="E33" t="n">
-        <v>15.219</v>
+        <v>15.2166</v>
       </c>
       <c r="F33" t="n">
-        <v>26.9745</v>
+        <v>26.9574</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>18.3743</v>
+        <v>18.3861</v>
       </c>
       <c r="C34" t="n">
-        <v>17.2046</v>
+        <v>17.2585</v>
       </c>
       <c r="D34" t="n">
-        <v>32.0239</v>
+        <v>32.4392</v>
       </c>
       <c r="E34" t="n">
-        <v>14.9204</v>
+        <v>14.8868</v>
       </c>
       <c r="F34" t="n">
-        <v>26.7271</v>
+        <v>26.6942</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>17.9506</v>
+        <v>17.8429</v>
       </c>
       <c r="C35" t="n">
-        <v>17.151</v>
+        <v>17.2079</v>
       </c>
       <c r="D35" t="n">
-        <v>31.167</v>
+        <v>31.6983</v>
       </c>
       <c r="E35" t="n">
-        <v>20.1207</v>
+        <v>20.1034</v>
       </c>
       <c r="F35" t="n">
-        <v>30.9752</v>
+        <v>31.0002</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>17.3266</v>
+        <v>17.2692</v>
       </c>
       <c r="C36" t="n">
-        <v>17.1435</v>
+        <v>17.1477</v>
       </c>
       <c r="D36" t="n">
-        <v>31.2539</v>
+        <v>31.6338</v>
       </c>
       <c r="E36" t="n">
-        <v>19.5744</v>
+        <v>19.5109</v>
       </c>
       <c r="F36" t="n">
-        <v>30.6475</v>
+        <v>30.6492</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>16.7061</v>
+        <v>16.7174</v>
       </c>
       <c r="C37" t="n">
-        <v>18.4038</v>
+        <v>18.4097</v>
       </c>
       <c r="D37" t="n">
-        <v>31.0452</v>
+        <v>31.5414</v>
       </c>
       <c r="E37" t="n">
-        <v>19.0959</v>
+        <v>19.0714</v>
       </c>
       <c r="F37" t="n">
-        <v>30.3139</v>
+        <v>30.3495</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>23.0546</v>
+        <v>23.0934</v>
       </c>
       <c r="C38" t="n">
-        <v>18.3136</v>
+        <v>18.2178</v>
       </c>
       <c r="D38" t="n">
-        <v>31.4732</v>
+        <v>31.5376</v>
       </c>
       <c r="E38" t="n">
-        <v>18.6066</v>
+        <v>18.6178</v>
       </c>
       <c r="F38" t="n">
-        <v>29.8657</v>
+        <v>29.9341</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>22.7993</v>
+        <v>22.8397</v>
       </c>
       <c r="C39" t="n">
-        <v>18.1212</v>
+        <v>18.1716</v>
       </c>
       <c r="D39" t="n">
-        <v>31.476</v>
+        <v>31.6017</v>
       </c>
       <c r="E39" t="n">
-        <v>18.1546</v>
+        <v>18.1677</v>
       </c>
       <c r="F39" t="n">
-        <v>29.5491</v>
+        <v>29.5958</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>22.4174</v>
+        <v>22.4851</v>
       </c>
       <c r="C40" t="n">
-        <v>18.0474</v>
+        <v>18.035</v>
       </c>
       <c r="D40" t="n">
-        <v>31.6924</v>
+        <v>31.7983</v>
       </c>
       <c r="E40" t="n">
-        <v>17.7887</v>
+        <v>17.8271</v>
       </c>
       <c r="F40" t="n">
-        <v>29.2691</v>
+        <v>29.2522</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>22.0506</v>
+        <v>22.0771</v>
       </c>
       <c r="C41" t="n">
-        <v>17.9061</v>
+        <v>17.9226</v>
       </c>
       <c r="D41" t="n">
-        <v>31.7565</v>
+        <v>31.9653</v>
       </c>
       <c r="E41" t="n">
-        <v>17.3756</v>
+        <v>17.4101</v>
       </c>
       <c r="F41" t="n">
-        <v>28.9874</v>
+        <v>29.0244</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>21.7233</v>
+        <v>21.6706</v>
       </c>
       <c r="C42" t="n">
-        <v>17.7085</v>
+        <v>17.7271</v>
       </c>
       <c r="D42" t="n">
-        <v>31.7744</v>
+        <v>31.8172</v>
       </c>
       <c r="E42" t="n">
-        <v>17.0409</v>
+        <v>17.0867</v>
       </c>
       <c r="F42" t="n">
-        <v>28.6447</v>
+        <v>28.633</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>21.215</v>
+        <v>21.1495</v>
       </c>
       <c r="C43" t="n">
-        <v>17.5967</v>
+        <v>17.5743</v>
       </c>
       <c r="D43" t="n">
-        <v>31.8215</v>
+        <v>31.9322</v>
       </c>
       <c r="E43" t="n">
-        <v>16.7205</v>
+        <v>16.6917</v>
       </c>
       <c r="F43" t="n">
-        <v>28.3585</v>
+        <v>28.3351</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>20.719</v>
+        <v>20.7014</v>
       </c>
       <c r="C44" t="n">
-        <v>17.5344</v>
+        <v>17.5225</v>
       </c>
       <c r="D44" t="n">
-        <v>31.8912</v>
+        <v>31.9893</v>
       </c>
       <c r="E44" t="n">
-        <v>16.4166</v>
+        <v>16.4172</v>
       </c>
       <c r="F44" t="n">
-        <v>28.1155</v>
+        <v>28.1406</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>20.2379</v>
+        <v>20.254</v>
       </c>
       <c r="C45" t="n">
-        <v>17.4229</v>
+        <v>17.4272</v>
       </c>
       <c r="D45" t="n">
-        <v>32.1412</v>
+        <v>32.1674</v>
       </c>
       <c r="E45" t="n">
-        <v>16.0885</v>
+        <v>16.0848</v>
       </c>
       <c r="F45" t="n">
-        <v>27.8186</v>
+        <v>27.8398</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>19.8501</v>
+        <v>19.8379</v>
       </c>
       <c r="C46" t="n">
-        <v>17.34</v>
+        <v>17.3427</v>
       </c>
       <c r="D46" t="n">
-        <v>32.2263</v>
+        <v>31.8228</v>
       </c>
       <c r="E46" t="n">
-        <v>15.762</v>
+        <v>15.7804</v>
       </c>
       <c r="F46" t="n">
-        <v>27.5226</v>
+        <v>27.5417</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>19.3574</v>
+        <v>19.3555</v>
       </c>
       <c r="C47" t="n">
-        <v>17.2392</v>
+        <v>17.2554</v>
       </c>
       <c r="D47" t="n">
-        <v>32.4397</v>
+        <v>32.0873</v>
       </c>
       <c r="E47" t="n">
-        <v>15.4745</v>
+        <v>15.4647</v>
       </c>
       <c r="F47" t="n">
-        <v>27.2026</v>
+        <v>27.2836</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>18.8238</v>
+        <v>18.7797</v>
       </c>
       <c r="C48" t="n">
-        <v>17.2481</v>
+        <v>17.2229</v>
       </c>
       <c r="D48" t="n">
-        <v>32.4786</v>
+        <v>32.1452</v>
       </c>
       <c r="E48" t="n">
-        <v>15.214</v>
+        <v>15.1915</v>
       </c>
       <c r="F48" t="n">
-        <v>26.8726</v>
+        <v>26.9112</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>18.2089</v>
+        <v>18.2825</v>
       </c>
       <c r="C49" t="n">
-        <v>17.127</v>
+        <v>17.1643</v>
       </c>
       <c r="D49" t="n">
-        <v>32.7086</v>
+        <v>32.6099</v>
       </c>
       <c r="E49" t="n">
-        <v>14.8387</v>
+        <v>14.8303</v>
       </c>
       <c r="F49" t="n">
-        <v>25.9368</v>
+        <v>25.97</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>17.678</v>
+        <v>17.7287</v>
       </c>
       <c r="C50" t="n">
-        <v>17.0762</v>
+        <v>17.111</v>
       </c>
       <c r="D50" t="n">
-        <v>31.9349</v>
+        <v>31.6089</v>
       </c>
       <c r="E50" t="n">
-        <v>19.787</v>
+        <v>19.7792</v>
       </c>
       <c r="F50" t="n">
-        <v>30.5705</v>
+        <v>30.6325</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>16.9836</v>
+        <v>16.9469</v>
       </c>
       <c r="C51" t="n">
-        <v>18.4829</v>
+        <v>18.523</v>
       </c>
       <c r="D51" t="n">
-        <v>32.1344</v>
+        <v>31.8563</v>
       </c>
       <c r="E51" t="n">
-        <v>19.2866</v>
+        <v>19.3043</v>
       </c>
       <c r="F51" t="n">
-        <v>30.2939</v>
+        <v>30.3047</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>16.0117</v>
+        <v>15.9815</v>
       </c>
       <c r="C52" t="n">
-        <v>18.3183</v>
+        <v>18.3703</v>
       </c>
       <c r="D52" t="n">
-        <v>32.1872</v>
+        <v>32.4059</v>
       </c>
       <c r="E52" t="n">
-        <v>18.7755</v>
+        <v>18.8315</v>
       </c>
       <c r="F52" t="n">
-        <v>29.9823</v>
+        <v>30.0122</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>22.9823</v>
+        <v>23.0266</v>
       </c>
       <c r="C53" t="n">
-        <v>18.2116</v>
+        <v>18.2358</v>
       </c>
       <c r="D53" t="n">
-        <v>32.3428</v>
+        <v>32.421</v>
       </c>
       <c r="E53" t="n">
-        <v>18.3435</v>
+        <v>18.4106</v>
       </c>
       <c r="F53" t="n">
-        <v>29.2962</v>
+        <v>29.2124</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>22.6577</v>
+        <v>22.6461</v>
       </c>
       <c r="C54" t="n">
-        <v>18.0895</v>
+        <v>18.1088</v>
       </c>
       <c r="D54" t="n">
-        <v>32.379</v>
+        <v>32.402</v>
       </c>
       <c r="E54" t="n">
-        <v>17.9579</v>
+        <v>17.9717</v>
       </c>
       <c r="F54" t="n">
-        <v>29.4989</v>
+        <v>29.3825</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>22.2479</v>
+        <v>22.2854</v>
       </c>
       <c r="C55" t="n">
-        <v>17.9718</v>
+        <v>17.9705</v>
       </c>
       <c r="D55" t="n">
-        <v>32.3829</v>
+        <v>32.4786</v>
       </c>
       <c r="E55" t="n">
-        <v>17.6374</v>
+        <v>17.6524</v>
       </c>
       <c r="F55" t="n">
-        <v>29.2537</v>
+        <v>29.1074</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>21.8302</v>
+        <v>21.839</v>
       </c>
       <c r="C56" t="n">
-        <v>17.8269</v>
+        <v>17.8174</v>
       </c>
       <c r="D56" t="n">
-        <v>32.6803</v>
+        <v>32.5956</v>
       </c>
       <c r="E56" t="n">
-        <v>17.2154</v>
+        <v>17.2592</v>
       </c>
       <c r="F56" t="n">
-        <v>28.4537</v>
+        <v>28.2716</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>21.3954</v>
+        <v>21.3772</v>
       </c>
       <c r="C57" t="n">
-        <v>17.7173</v>
+        <v>17.7542</v>
       </c>
       <c r="D57" t="n">
-        <v>32.7665</v>
+        <v>32.8561</v>
       </c>
       <c r="E57" t="n">
-        <v>16.8917</v>
+        <v>16.9128</v>
       </c>
       <c r="F57" t="n">
-        <v>28.0643</v>
+        <v>27.9353</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>20.9621</v>
+        <v>20.9151</v>
       </c>
       <c r="C58" t="n">
-        <v>17.5984</v>
+        <v>17.6701</v>
       </c>
       <c r="D58" t="n">
-        <v>33.0904</v>
+        <v>33.0401</v>
       </c>
       <c r="E58" t="n">
-        <v>16.5586</v>
+        <v>16.5846</v>
       </c>
       <c r="F58" t="n">
-        <v>27.6966</v>
+        <v>27.6555</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>20.4617</v>
+        <v>20.4841</v>
       </c>
       <c r="C59" t="n">
-        <v>17.5237</v>
+        <v>17.5288</v>
       </c>
       <c r="D59" t="n">
-        <v>33.2674</v>
+        <v>33.0962</v>
       </c>
       <c r="E59" t="n">
-        <v>16.2621</v>
+        <v>16.2597</v>
       </c>
       <c r="F59" t="n">
-        <v>27.4257</v>
+        <v>27.3265</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>19.9934</v>
+        <v>19.9279</v>
       </c>
       <c r="C60" t="n">
-        <v>17.4499</v>
+        <v>17.4633</v>
       </c>
       <c r="D60" t="n">
-        <v>33.583</v>
+        <v>33.5297</v>
       </c>
       <c r="E60" t="n">
-        <v>15.9441</v>
+        <v>15.9704</v>
       </c>
       <c r="F60" t="n">
-        <v>27.1241</v>
+        <v>27.0263</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>19.4587</v>
+        <v>19.4849</v>
       </c>
       <c r="C61" t="n">
-        <v>17.3499</v>
+        <v>17.3651</v>
       </c>
       <c r="D61" t="n">
-        <v>34.0349</v>
+        <v>33.493</v>
       </c>
       <c r="E61" t="n">
-        <v>15.6647</v>
+        <v>15.6648</v>
       </c>
       <c r="F61" t="n">
-        <v>27.4539</v>
+        <v>27.3463</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>18.9638</v>
+        <v>18.9859</v>
       </c>
       <c r="C62" t="n">
-        <v>17.2803</v>
+        <v>17.2939</v>
       </c>
       <c r="D62" t="n">
-        <v>34.2364</v>
+        <v>33.7216</v>
       </c>
       <c r="E62" t="n">
-        <v>15.3384</v>
+        <v>15.3304</v>
       </c>
       <c r="F62" t="n">
-        <v>26.5523</v>
+        <v>26.4507</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>18.475</v>
+        <v>18.4183</v>
       </c>
       <c r="C63" t="n">
-        <v>17.2438</v>
+        <v>17.2543</v>
       </c>
       <c r="D63" t="n">
-        <v>34.5562</v>
+        <v>34.15</v>
       </c>
       <c r="E63" t="n">
-        <v>15.0085</v>
+        <v>15.0393</v>
       </c>
       <c r="F63" t="n">
-        <v>26.2263</v>
+        <v>26.1336</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>17.8587</v>
+        <v>17.7846</v>
       </c>
       <c r="C64" t="n">
-        <v>17.1609</v>
+        <v>17.1801</v>
       </c>
       <c r="D64" t="n">
-        <v>38.4134</v>
+        <v>38.3608</v>
       </c>
       <c r="E64" t="n">
-        <v>21.0745</v>
+        <v>20.6265</v>
       </c>
       <c r="F64" t="n">
-        <v>30.5774</v>
+        <v>30.4073</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>17.2332</v>
+        <v>17.1702</v>
       </c>
       <c r="C65" t="n">
-        <v>18.7435</v>
+        <v>18.7881</v>
       </c>
       <c r="D65" t="n">
-        <v>38.2331</v>
+        <v>38.2475</v>
       </c>
       <c r="E65" t="n">
-        <v>20.5208</v>
+        <v>20.4219</v>
       </c>
       <c r="F65" t="n">
-        <v>30.2375</v>
+        <v>30.123</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>16.4648</v>
+        <v>16.4551</v>
       </c>
       <c r="C66" t="n">
-        <v>18.5012</v>
+        <v>18.5357</v>
       </c>
       <c r="D66" t="n">
-        <v>38.4441</v>
+        <v>38.4751</v>
       </c>
       <c r="E66" t="n">
-        <v>19.7505</v>
+        <v>19.8165</v>
       </c>
       <c r="F66" t="n">
-        <v>29.8916</v>
+        <v>29.7162</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>23.1443</v>
+        <v>23.1757</v>
       </c>
       <c r="C67" t="n">
-        <v>18.3616</v>
+        <v>18.3543</v>
       </c>
       <c r="D67" t="n">
-        <v>38.756</v>
+        <v>38.8643</v>
       </c>
       <c r="E67" t="n">
-        <v>19.3566</v>
+        <v>19.4055</v>
       </c>
       <c r="F67" t="n">
-        <v>29.5102</v>
+        <v>29.4401</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>22.8303</v>
+        <v>22.7884</v>
       </c>
       <c r="C68" t="n">
-        <v>18.2064</v>
+        <v>18.2076</v>
       </c>
       <c r="D68" t="n">
-        <v>39.068</v>
+        <v>39.2408</v>
       </c>
       <c r="E68" t="n">
-        <v>18.7675</v>
+        <v>18.6935</v>
       </c>
       <c r="F68" t="n">
-        <v>29.1269</v>
+        <v>28.997</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>22.3737</v>
+        <v>22.4006</v>
       </c>
       <c r="C69" t="n">
-        <v>18.0412</v>
+        <v>18.0566</v>
       </c>
       <c r="D69" t="n">
-        <v>39.2737</v>
+        <v>39.5778</v>
       </c>
       <c r="E69" t="n">
-        <v>18.1118</v>
+        <v>18.1367</v>
       </c>
       <c r="F69" t="n">
-        <v>28.8669</v>
+        <v>28.7187</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>21.9905</v>
+        <v>21.9992</v>
       </c>
       <c r="C70" t="n">
-        <v>18.0799</v>
+        <v>18.0653</v>
       </c>
       <c r="D70" t="n">
-        <v>39.2894</v>
+        <v>39.6123</v>
       </c>
       <c r="E70" t="n">
-        <v>17.6038</v>
+        <v>17.6277</v>
       </c>
       <c r="F70" t="n">
-        <v>28.5098</v>
+        <v>28.3463</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>21.4823</v>
+        <v>21.4775</v>
       </c>
       <c r="C71" t="n">
-        <v>17.8475</v>
+        <v>17.9477</v>
       </c>
       <c r="D71" t="n">
-        <v>39.3416</v>
+        <v>39.8148</v>
       </c>
       <c r="E71" t="n">
-        <v>17.1577</v>
+        <v>17.1842</v>
       </c>
       <c r="F71" t="n">
-        <v>28.2073</v>
+        <v>28.0614</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>21.0741</v>
+        <v>21.0447</v>
       </c>
       <c r="C72" t="n">
-        <v>17.8395</v>
+        <v>17.824</v>
       </c>
       <c r="D72" t="n">
-        <v>39.5216</v>
+        <v>39.9166</v>
       </c>
       <c r="E72" t="n">
-        <v>16.7672</v>
+        <v>16.749</v>
       </c>
       <c r="F72" t="n">
-        <v>28.4928</v>
+        <v>28.3649</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>20.5764</v>
+        <v>20.5446</v>
       </c>
       <c r="C73" t="n">
-        <v>17.7577</v>
+        <v>17.752</v>
       </c>
       <c r="D73" t="n">
-        <v>39.6554</v>
+        <v>39.8293</v>
       </c>
       <c r="E73" t="n">
-        <v>16.4379</v>
+        <v>16.4169</v>
       </c>
       <c r="F73" t="n">
-        <v>28.2406</v>
+        <v>28.1078</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>20.1497</v>
+        <v>20.1095</v>
       </c>
       <c r="C74" t="n">
-        <v>17.6672</v>
+        <v>17.6431</v>
       </c>
       <c r="D74" t="n">
-        <v>39.5984</v>
+        <v>39.9477</v>
       </c>
       <c r="E74" t="n">
-        <v>16.1225</v>
+        <v>16.0919</v>
       </c>
       <c r="F74" t="n">
-        <v>27.976</v>
+        <v>27.8291</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>19.6014</v>
+        <v>19.6071</v>
       </c>
       <c r="C75" t="n">
-        <v>17.5469</v>
+        <v>17.5582</v>
       </c>
       <c r="D75" t="n">
-        <v>39.7342</v>
+        <v>40.0096</v>
       </c>
       <c r="E75" t="n">
-        <v>15.791</v>
+        <v>15.7897</v>
       </c>
       <c r="F75" t="n">
-        <v>27.0151</v>
+        <v>26.8919</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>19.0552</v>
+        <v>19.0727</v>
       </c>
       <c r="C76" t="n">
-        <v>17.4766</v>
+        <v>17.492</v>
       </c>
       <c r="D76" t="n">
-        <v>39.9114</v>
+        <v>40.0891</v>
       </c>
       <c r="E76" t="n">
-        <v>15.4849</v>
+        <v>15.4708</v>
       </c>
       <c r="F76" t="n">
-        <v>26.7229</v>
+        <v>26.6029</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>18.5739</v>
+        <v>18.5986</v>
       </c>
       <c r="C77" t="n">
-        <v>17.427</v>
+        <v>17.428</v>
       </c>
       <c r="D77" t="n">
-        <v>39.6274</v>
+        <v>39.7617</v>
       </c>
       <c r="E77" t="n">
-        <v>15.1853</v>
+        <v>15.1607</v>
       </c>
       <c r="F77" t="n">
-        <v>26.3846</v>
+        <v>26.2627</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>18.0425</v>
+        <v>18.0032</v>
       </c>
       <c r="C78" t="n">
-        <v>17.1997</v>
+        <v>17.2209</v>
       </c>
       <c r="D78" t="n">
-        <v>45.4804</v>
+        <v>46.5327</v>
       </c>
       <c r="E78" t="n">
-        <v>20.4014</v>
+        <v>20.3916</v>
       </c>
       <c r="F78" t="n">
-        <v>31.0185</v>
+        <v>30.8479</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>17.3403</v>
+        <v>17.3547</v>
       </c>
       <c r="C79" t="n">
-        <v>19.103</v>
+        <v>19.106</v>
       </c>
       <c r="D79" t="n">
-        <v>45.4808</v>
+        <v>46.4093</v>
       </c>
       <c r="E79" t="n">
-        <v>19.8354</v>
+        <v>19.8298</v>
       </c>
       <c r="F79" t="n">
-        <v>30.7154</v>
+        <v>30.5359</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>16.5562</v>
+        <v>16.5498</v>
       </c>
       <c r="C80" t="n">
-        <v>18.8837</v>
+        <v>18.8804</v>
       </c>
       <c r="D80" t="n">
-        <v>45.1041</v>
+        <v>46.0321</v>
       </c>
       <c r="E80" t="n">
-        <v>19.2786</v>
+        <v>19.3197</v>
       </c>
       <c r="F80" t="n">
-        <v>30.4101</v>
+        <v>30.3494</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>23.2631</v>
+        <v>23.2784</v>
       </c>
       <c r="C81" t="n">
-        <v>18.7036</v>
+        <v>18.7401</v>
       </c>
       <c r="D81" t="n">
-        <v>44.256</v>
+        <v>45.4079</v>
       </c>
       <c r="E81" t="n">
-        <v>18.8615</v>
+        <v>18.8525</v>
       </c>
       <c r="F81" t="n">
-        <v>30.0963</v>
+        <v>29.991</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>22.9034</v>
+        <v>22.9152</v>
       </c>
       <c r="C82" t="n">
-        <v>18.4725</v>
+        <v>18.5158</v>
       </c>
       <c r="D82" t="n">
-        <v>43.9673</v>
+        <v>44.9968</v>
       </c>
       <c r="E82" t="n">
-        <v>18.4386</v>
+        <v>18.4304</v>
       </c>
       <c r="F82" t="n">
-        <v>29.7509</v>
+        <v>29.6057</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>22.5505</v>
+        <v>22.5408</v>
       </c>
       <c r="C83" t="n">
-        <v>18.3618</v>
+        <v>18.3974</v>
       </c>
       <c r="D83" t="n">
-        <v>43.6701</v>
+        <v>44.7307</v>
       </c>
       <c r="E83" t="n">
-        <v>18.0254</v>
+        <v>18.0439</v>
       </c>
       <c r="F83" t="n">
-        <v>29.4378</v>
+        <v>29.3167</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>22.1297</v>
+        <v>22.107</v>
       </c>
       <c r="C84" t="n">
-        <v>18.2088</v>
+        <v>18.2427</v>
       </c>
       <c r="D84" t="n">
-        <v>43.2302</v>
+        <v>44.3269</v>
       </c>
       <c r="E84" t="n">
-        <v>17.6126</v>
+        <v>17.622</v>
       </c>
       <c r="F84" t="n">
-        <v>29.1438</v>
+        <v>29.0422</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>21.6691</v>
+        <v>21.6615</v>
       </c>
       <c r="C85" t="n">
-        <v>17.9822</v>
+        <v>17.9403</v>
       </c>
       <c r="D85" t="n">
-        <v>42.7954</v>
+        <v>44.3132</v>
       </c>
       <c r="E85" t="n">
-        <v>17.2684</v>
+        <v>17.2557</v>
       </c>
       <c r="F85" t="n">
-        <v>28.8388</v>
+        <v>28.6872</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>21.2373</v>
+        <v>21.1903</v>
       </c>
       <c r="C86" t="n">
-        <v>17.8352</v>
+        <v>17.8329</v>
       </c>
       <c r="D86" t="n">
-        <v>42.3619</v>
+        <v>42.8807</v>
       </c>
       <c r="E86" t="n">
-        <v>16.9058</v>
+        <v>16.9285</v>
       </c>
       <c r="F86" t="n">
-        <v>28.6154</v>
+        <v>28.4545</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>20.7004</v>
+        <v>20.7018</v>
       </c>
       <c r="C87" t="n">
-        <v>17.7166</v>
+        <v>17.7013</v>
       </c>
       <c r="D87" t="n">
-        <v>42.1008</v>
+        <v>42.6553</v>
       </c>
       <c r="E87" t="n">
-        <v>16.5761</v>
+        <v>16.552</v>
       </c>
       <c r="F87" t="n">
-        <v>28.3147</v>
+        <v>28.1561</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>20.2491</v>
+        <v>20.2376</v>
       </c>
       <c r="C88" t="n">
-        <v>17.6031</v>
+        <v>17.6009</v>
       </c>
       <c r="D88" t="n">
-        <v>41.7129</v>
+        <v>42.3276</v>
       </c>
       <c r="E88" t="n">
-        <v>16.2542</v>
+        <v>16.2571</v>
       </c>
       <c r="F88" t="n">
-        <v>28.0187</v>
+        <v>27.8554</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>19.7173</v>
+        <v>19.71</v>
       </c>
       <c r="C89" t="n">
-        <v>17.4792</v>
+        <v>17.5232</v>
       </c>
       <c r="D89" t="n">
-        <v>41.5938</v>
+        <v>42.7969</v>
       </c>
       <c r="E89" t="n">
-        <v>15.9228</v>
+        <v>15.9624</v>
       </c>
       <c r="F89" t="n">
-        <v>27.7171</v>
+        <v>27.5627</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>19.299</v>
+        <v>19.2437</v>
       </c>
       <c r="C90" t="n">
-        <v>17.3987</v>
+        <v>17.3851</v>
       </c>
       <c r="D90" t="n">
-        <v>41.5634</v>
+        <v>41.7454</v>
       </c>
       <c r="E90" t="n">
-        <v>15.6002</v>
+        <v>15.6</v>
       </c>
       <c r="F90" t="n">
-        <v>27.4077</v>
+        <v>27.2355</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>18.7384</v>
+        <v>18.7661</v>
       </c>
       <c r="C91" t="n">
-        <v>17.2999</v>
+        <v>17.3034</v>
       </c>
       <c r="D91" t="n">
-        <v>41.4486</v>
+        <v>41.5824</v>
       </c>
       <c r="E91" t="n">
-        <v>15.29</v>
+        <v>15.2924</v>
       </c>
       <c r="F91" t="n">
-        <v>27.1428</v>
+        <v>26.9524</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>18.1781</v>
+        <v>18.1722</v>
       </c>
       <c r="C92" t="n">
-        <v>17.2512</v>
+        <v>17.2328</v>
       </c>
       <c r="D92" t="n">
-        <v>46.4754</v>
+        <v>47.3941</v>
       </c>
       <c r="E92" t="n">
-        <v>20.5165</v>
+        <v>20.5417</v>
       </c>
       <c r="F92" t="n">
-        <v>31.1475</v>
+        <v>31.0472</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>17.57</v>
+        <v>17.5107</v>
       </c>
       <c r="C93" t="n">
-        <v>17.1566</v>
+        <v>17.1589</v>
       </c>
       <c r="D93" t="n">
-        <v>45.7479</v>
+        <v>46.6118</v>
       </c>
       <c r="E93" t="n">
-        <v>19.9693</v>
+        <v>20.0059</v>
       </c>
       <c r="F93" t="n">
-        <v>30.8195</v>
+        <v>30.6973</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>16.8493</v>
+        <v>16.815</v>
       </c>
       <c r="C94" t="n">
-        <v>18.8208</v>
+        <v>18.8231</v>
       </c>
       <c r="D94" t="n">
-        <v>44.6283</v>
+        <v>45.8229</v>
       </c>
       <c r="E94" t="n">
-        <v>19.4542</v>
+        <v>19.4887</v>
       </c>
       <c r="F94" t="n">
-        <v>30.3466</v>
+        <v>30.386</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>23.3476</v>
+        <v>23.3411</v>
       </c>
       <c r="C95" t="n">
-        <v>18.6081</v>
+        <v>18.6276</v>
       </c>
       <c r="D95" t="n">
-        <v>44.1898</v>
+        <v>45.3001</v>
       </c>
       <c r="E95" t="n">
-        <v>18.952</v>
+        <v>18.9998</v>
       </c>
       <c r="F95" t="n">
-        <v>30.006</v>
+        <v>30.0372</v>
       </c>
     </row>
     <row r="96">
@@ -6962,16 +6962,16 @@
         <v>23.015</v>
       </c>
       <c r="C96" t="n">
-        <v>18.427</v>
+        <v>18.4712</v>
       </c>
       <c r="D96" t="n">
-        <v>43.8094</v>
+        <v>44.8301</v>
       </c>
       <c r="E96" t="n">
-        <v>18.502</v>
+        <v>18.525</v>
       </c>
       <c r="F96" t="n">
-        <v>29.331</v>
+        <v>29.3135</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>22.639</v>
+        <v>22.6315</v>
       </c>
       <c r="C97" t="n">
-        <v>18.2525</v>
+        <v>18.2835</v>
       </c>
       <c r="D97" t="n">
-        <v>43.34</v>
+        <v>44.5044</v>
       </c>
       <c r="E97" t="n">
-        <v>18.0819</v>
+        <v>18.0785</v>
       </c>
       <c r="F97" t="n">
-        <v>28.8931</v>
+        <v>28.8439</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>22.2177</v>
+        <v>22.1969</v>
       </c>
       <c r="C98" t="n">
-        <v>18.1057</v>
+        <v>18.1339</v>
       </c>
       <c r="D98" t="n">
-        <v>42.9612</v>
+        <v>43.9711</v>
       </c>
       <c r="E98" t="n">
-        <v>17.6695</v>
+        <v>17.6788</v>
       </c>
       <c r="F98" t="n">
-        <v>28.4694</v>
+        <v>28.4766</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>21.7738</v>
+        <v>21.7541</v>
       </c>
       <c r="C99" t="n">
-        <v>17.9816</v>
+        <v>17.992</v>
       </c>
       <c r="D99" t="n">
-        <v>42.4586</v>
+        <v>43.5689</v>
       </c>
       <c r="E99" t="n">
-        <v>17.3035</v>
+        <v>17.3022</v>
       </c>
       <c r="F99" t="n">
-        <v>28.1414</v>
+        <v>28.166</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>21.3353</v>
+        <v>21.3132</v>
       </c>
       <c r="C100" t="n">
-        <v>17.956</v>
+        <v>17.9752</v>
       </c>
       <c r="D100" t="n">
-        <v>42.3054</v>
+        <v>43.2648</v>
       </c>
       <c r="E100" t="n">
-        <v>16.964</v>
+        <v>16.9629</v>
       </c>
       <c r="F100" t="n">
-        <v>27.836</v>
+        <v>27.8685</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>20.8584</v>
+        <v>20.8315</v>
       </c>
       <c r="C101" t="n">
-        <v>17.8487</v>
+        <v>17.8472</v>
       </c>
       <c r="D101" t="n">
-        <v>41.9822</v>
+        <v>42.8706</v>
       </c>
       <c r="E101" t="n">
-        <v>16.6342</v>
+        <v>16.6102</v>
       </c>
       <c r="F101" t="n">
-        <v>27.5414</v>
+        <v>27.5359</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>20.3888</v>
+        <v>20.3616</v>
       </c>
       <c r="C102" t="n">
-        <v>17.735</v>
+        <v>17.7313</v>
       </c>
       <c r="D102" t="n">
-        <v>41.644</v>
+        <v>42.4136</v>
       </c>
       <c r="E102" t="n">
-        <v>16.2928</v>
+        <v>16.296</v>
       </c>
       <c r="F102" t="n">
-        <v>27.2828</v>
+        <v>27.2919</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>19.9011</v>
+        <v>19.8855</v>
       </c>
       <c r="C103" t="n">
-        <v>17.6378</v>
+        <v>17.6385</v>
       </c>
       <c r="D103" t="n">
-        <v>41.5635</v>
+        <v>42.2848</v>
       </c>
       <c r="E103" t="n">
-        <v>15.9809</v>
+        <v>15.9743</v>
       </c>
       <c r="F103" t="n">
-        <v>27.0085</v>
+        <v>27.0206</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>19.3778</v>
+        <v>19.3564</v>
       </c>
       <c r="C104" t="n">
-        <v>17.5853</v>
+        <v>17.5457</v>
       </c>
       <c r="D104" t="n">
-        <v>41.8344</v>
+        <v>41.9124</v>
       </c>
       <c r="E104" t="n">
-        <v>15.6857</v>
+        <v>15.6622</v>
       </c>
       <c r="F104" t="n">
-        <v>26.6911</v>
+        <v>26.6889</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>18.8012</v>
+        <v>18.819</v>
       </c>
       <c r="C105" t="n">
-        <v>17.4556</v>
+        <v>17.4285</v>
       </c>
       <c r="D105" t="n">
-        <v>41.7689</v>
+        <v>41.6885</v>
       </c>
       <c r="E105" t="n">
-        <v>15.3699</v>
+        <v>15.3697</v>
       </c>
       <c r="F105" t="n">
-        <v>26.3671</v>
+        <v>26.3712</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>18.3199</v>
+        <v>18.2833</v>
       </c>
       <c r="C106" t="n">
-        <v>17.3579</v>
+        <v>17.3642</v>
       </c>
       <c r="D106" t="n">
-        <v>41.3866</v>
+        <v>41.3337</v>
       </c>
       <c r="E106" t="n">
-        <v>15.0684</v>
+        <v>15.0617</v>
       </c>
       <c r="F106" t="n">
-        <v>26.0591</v>
+        <v>26.0496</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>17.7133</v>
+        <v>17.7031</v>
       </c>
       <c r="C107" t="n">
-        <v>17.2698</v>
+        <v>17.2755</v>
       </c>
       <c r="D107" t="n">
-        <v>44.521</v>
+        <v>44.4428</v>
       </c>
       <c r="E107" t="n">
-        <v>19.9708</v>
+        <v>19.9797</v>
       </c>
       <c r="F107" t="n">
-        <v>30.1784</v>
+        <v>30.1845</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>17.0032</v>
+        <v>16.9956</v>
       </c>
       <c r="C108" t="n">
-        <v>18.9541</v>
+        <v>18.9636</v>
       </c>
       <c r="D108" t="n">
-        <v>44.2189</v>
+        <v>44.1385</v>
       </c>
       <c r="E108" t="n">
-        <v>19.5416</v>
+        <v>19.5188</v>
       </c>
       <c r="F108" t="n">
-        <v>29.9226</v>
+        <v>29.9015</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>16.1664</v>
+        <v>16.1593</v>
       </c>
       <c r="C109" t="n">
-        <v>18.8045</v>
+        <v>18.7859</v>
       </c>
       <c r="D109" t="n">
-        <v>43.8877</v>
+        <v>43.6343</v>
       </c>
       <c r="E109" t="n">
-        <v>19.0664</v>
+        <v>19.0507</v>
       </c>
       <c r="F109" t="n">
-        <v>29.5916</v>
+        <v>29.5321</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>23.0934</v>
+        <v>23.1064</v>
       </c>
       <c r="C110" t="n">
-        <v>18.4759</v>
+        <v>18.476</v>
       </c>
       <c r="D110" t="n">
-        <v>43.1769</v>
+        <v>43.0901</v>
       </c>
       <c r="E110" t="n">
-        <v>18.65</v>
+        <v>18.5978</v>
       </c>
       <c r="F110" t="n">
-        <v>29.8016</v>
+        <v>29.7746</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>22.7264</v>
+        <v>22.7055</v>
       </c>
       <c r="C111" t="n">
-        <v>18.3037</v>
+        <v>18.3525</v>
       </c>
       <c r="D111" t="n">
-        <v>42.7262</v>
+        <v>42.6835</v>
       </c>
       <c r="E111" t="n">
-        <v>18.171</v>
+        <v>18.154</v>
       </c>
       <c r="F111" t="n">
-        <v>29.4471</v>
+        <v>29.399</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>22.3048</v>
+        <v>22.2758</v>
       </c>
       <c r="C112" t="n">
-        <v>18.2174</v>
+        <v>18.1348</v>
       </c>
       <c r="D112" t="n">
-        <v>41.8597</v>
+        <v>41.874</v>
       </c>
       <c r="E112" t="n">
-        <v>17.7851</v>
+        <v>17.7317</v>
       </c>
       <c r="F112" t="n">
-        <v>29.1797</v>
+        <v>29.0563</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>21.8817</v>
+        <v>21.849</v>
       </c>
       <c r="C113" t="n">
-        <v>18.0683</v>
+        <v>18.0396</v>
       </c>
       <c r="D113" t="n">
-        <v>41.4768</v>
+        <v>41.539</v>
       </c>
       <c r="E113" t="n">
-        <v>17.3874</v>
+        <v>17.356</v>
       </c>
       <c r="F113" t="n">
-        <v>28.8114</v>
+        <v>28.7811</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>21.4289</v>
+        <v>21.3985</v>
       </c>
       <c r="C114" t="n">
-        <v>17.8696</v>
+        <v>17.8518</v>
       </c>
       <c r="D114" t="n">
-        <v>40.6319</v>
+        <v>40.6688</v>
       </c>
       <c r="E114" t="n">
-        <v>17.0279</v>
+        <v>17.0172</v>
       </c>
       <c r="F114" t="n">
-        <v>28.5343</v>
+        <v>28.4876</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>20.9671</v>
+        <v>20.9288</v>
       </c>
       <c r="C115" t="n">
-        <v>17.7625</v>
+        <v>17.7413</v>
       </c>
       <c r="D115" t="n">
-        <v>40.2815</v>
+        <v>40.3501</v>
       </c>
       <c r="E115" t="n">
-        <v>16.6964</v>
+        <v>16.6883</v>
       </c>
       <c r="F115" t="n">
-        <v>28.2414</v>
+        <v>28.2212</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>20.4985</v>
+        <v>20.4661</v>
       </c>
       <c r="C116" t="n">
-        <v>17.6746</v>
+        <v>17.6532</v>
       </c>
       <c r="D116" t="n">
-        <v>39.8258</v>
+        <v>39.9067</v>
       </c>
       <c r="E116" t="n">
-        <v>16.3816</v>
+        <v>16.3584</v>
       </c>
       <c r="F116" t="n">
-        <v>27.388</v>
+        <v>27.3362</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>19.9719</v>
+        <v>19.9436</v>
       </c>
       <c r="C117" t="n">
-        <v>17.5428</v>
+        <v>17.6064</v>
       </c>
       <c r="D117" t="n">
-        <v>39.5988</v>
+        <v>39.7037</v>
       </c>
       <c r="E117" t="n">
-        <v>16.0405</v>
+        <v>16.0263</v>
       </c>
       <c r="F117" t="n">
-        <v>27.0773</v>
+        <v>27.0659</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>19.4439</v>
+        <v>19.4527</v>
       </c>
       <c r="C118" t="n">
-        <v>17.4844</v>
+        <v>17.4498</v>
       </c>
       <c r="D118" t="n">
-        <v>39.3294</v>
+        <v>39.4029</v>
       </c>
       <c r="E118" t="n">
-        <v>15.743</v>
+        <v>15.7171</v>
       </c>
       <c r="F118" t="n">
-        <v>26.8035</v>
+        <v>26.7819</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>18.9676</v>
+        <v>18.9422</v>
       </c>
       <c r="C119" t="n">
-        <v>17.4458</v>
+        <v>17.3589</v>
       </c>
       <c r="D119" t="n">
-        <v>39.1808</v>
+        <v>39.2046</v>
       </c>
       <c r="E119" t="n">
-        <v>15.425</v>
+        <v>15.4095</v>
       </c>
       <c r="F119" t="n">
-        <v>26.5086</v>
+        <v>26.4688</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>18.4178</v>
+        <v>18.4243</v>
       </c>
       <c r="C120" t="n">
-        <v>17.3017</v>
+        <v>17.2662</v>
       </c>
       <c r="D120" t="n">
-        <v>38.9657</v>
+        <v>39.0415</v>
       </c>
       <c r="E120" t="n">
-        <v>15.1069</v>
+        <v>15.0865</v>
       </c>
       <c r="F120" t="n">
-        <v>26.2082</v>
+        <v>26.159</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>17.8369</v>
+        <v>17.8924</v>
       </c>
       <c r="C121" t="n">
-        <v>17.2129</v>
+        <v>17.1821</v>
       </c>
       <c r="D121" t="n">
-        <v>46.1724</v>
+        <v>47.4628</v>
       </c>
       <c r="E121" t="n">
-        <v>20.1773</v>
+        <v>20.1436</v>
       </c>
       <c r="F121" t="n">
-        <v>30.6327</v>
+        <v>30.7635</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>17.2212</v>
+        <v>17.2156</v>
       </c>
       <c r="C122" t="n">
-        <v>18.8793</v>
+        <v>18.8686</v>
       </c>
       <c r="D122" t="n">
-        <v>45.508</v>
+        <v>46.7908</v>
       </c>
       <c r="E122" t="n">
-        <v>19.6032</v>
+        <v>19.6388</v>
       </c>
       <c r="F122" t="n">
-        <v>29.9144</v>
+        <v>29.9271</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>16.3702</v>
+        <v>16.3982</v>
       </c>
       <c r="C123" t="n">
-        <v>18.762</v>
+        <v>18.7104</v>
       </c>
       <c r="D123" t="n">
-        <v>45.2113</v>
+        <v>46.7003</v>
       </c>
       <c r="E123" t="n">
-        <v>19.1704</v>
+        <v>19.125</v>
       </c>
       <c r="F123" t="n">
-        <v>29.5605</v>
+        <v>29.8268</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>23.1808</v>
+        <v>23.1585</v>
       </c>
       <c r="C124" t="n">
-        <v>18.4723</v>
+        <v>18.4782</v>
       </c>
       <c r="D124" t="n">
-        <v>44.6493</v>
+        <v>45.5566</v>
       </c>
       <c r="E124" t="n">
-        <v>18.6972</v>
+        <v>18.6615</v>
       </c>
       <c r="F124" t="n">
-        <v>29.5163</v>
+        <v>29.7074</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>22.806</v>
+        <v>22.7972</v>
       </c>
       <c r="C125" t="n">
-        <v>18.3596</v>
+        <v>18.3671</v>
       </c>
       <c r="D125" t="n">
-        <v>44.2774</v>
+        <v>45.1501</v>
       </c>
       <c r="E125" t="n">
-        <v>18.2786</v>
+        <v>18.2475</v>
       </c>
       <c r="F125" t="n">
-        <v>29.0842</v>
+        <v>29.0615</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>22.3806</v>
+        <v>22.3872</v>
       </c>
       <c r="C126" t="n">
-        <v>18.1789</v>
+        <v>18.2045</v>
       </c>
       <c r="D126" t="n">
-        <v>43.3376</v>
+        <v>44.879</v>
       </c>
       <c r="E126" t="n">
-        <v>17.8419</v>
+        <v>17.8182</v>
       </c>
       <c r="F126" t="n">
-        <v>28.7575</v>
+        <v>28.7626</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>21.961</v>
+        <v>21.9491</v>
       </c>
       <c r="C127" t="n">
-        <v>18.0696</v>
+        <v>18.0403</v>
       </c>
       <c r="D127" t="n">
-        <v>42.7799</v>
+        <v>44.3384</v>
       </c>
       <c r="E127" t="n">
-        <v>17.4608</v>
+        <v>17.4397</v>
       </c>
       <c r="F127" t="n">
-        <v>28.4546</v>
+        <v>28.6052</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>21.5069</v>
+        <v>21.4985</v>
       </c>
       <c r="C128" t="n">
-        <v>17.8939</v>
+        <v>17.8963</v>
       </c>
       <c r="D128" t="n">
-        <v>42.7503</v>
+        <v>43.7273</v>
       </c>
       <c r="E128" t="n">
-        <v>17.1097</v>
+        <v>17.0891</v>
       </c>
       <c r="F128" t="n">
-        <v>28.4743</v>
+        <v>28.7725</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>21.0516</v>
+        <v>21.0367</v>
       </c>
       <c r="C129" t="n">
-        <v>17.7854</v>
+        <v>17.8027</v>
       </c>
       <c r="D129" t="n">
-        <v>42.2257</v>
+        <v>43.2943</v>
       </c>
       <c r="E129" t="n">
-        <v>16.7689</v>
+        <v>16.7568</v>
       </c>
       <c r="F129" t="n">
-        <v>28.2858</v>
+        <v>28.4673</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>20.5584</v>
+        <v>20.5798</v>
       </c>
       <c r="C130" t="n">
-        <v>17.6557</v>
+        <v>17.6755</v>
       </c>
       <c r="D130" t="n">
-        <v>41.9231</v>
+        <v>42.8724</v>
       </c>
       <c r="E130" t="n">
-        <v>16.4228</v>
+        <v>16.4261</v>
       </c>
       <c r="F130" t="n">
-        <v>27.4148</v>
+        <v>27.5611</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>20.1095</v>
+        <v>20.1379</v>
       </c>
       <c r="C131" t="n">
-        <v>17.6196</v>
+        <v>17.5595</v>
       </c>
       <c r="D131" t="n">
-        <v>41.4026</v>
+        <v>42.4668</v>
       </c>
       <c r="E131" t="n">
-        <v>16.109</v>
+        <v>16.1038</v>
       </c>
       <c r="F131" t="n">
-        <v>27.1134</v>
+        <v>27.2666</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>19.5958</v>
+        <v>19.5725</v>
       </c>
       <c r="C132" t="n">
-        <v>17.4648</v>
+        <v>17.435</v>
       </c>
       <c r="D132" t="n">
-        <v>41.1341</v>
+        <v>42.0287</v>
       </c>
       <c r="E132" t="n">
-        <v>15.7956</v>
+        <v>15.7905</v>
       </c>
       <c r="F132" t="n">
-        <v>26.8317</v>
+        <v>26.8401</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>19.0723</v>
+        <v>19.0618</v>
       </c>
       <c r="C133" t="n">
-        <v>17.4325</v>
+        <v>17.3904</v>
       </c>
       <c r="D133" t="n">
-        <v>40.8442</v>
+        <v>41.7585</v>
       </c>
       <c r="E133" t="n">
-        <v>15.4894</v>
+        <v>15.4821</v>
       </c>
       <c r="F133" t="n">
-        <v>26.5257</v>
+        <v>26.9954</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>18.5776</v>
+        <v>18.5316</v>
       </c>
       <c r="C134" t="n">
-        <v>17.3051</v>
+        <v>17.291</v>
       </c>
       <c r="D134" t="n">
-        <v>40.6432</v>
+        <v>41.5745</v>
       </c>
       <c r="E134" t="n">
-        <v>15.1786</v>
+        <v>15.1663</v>
       </c>
       <c r="F134" t="n">
-        <v>26.253</v>
+        <v>26.2317</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>18.016</v>
+        <v>17.9423</v>
       </c>
       <c r="C135" t="n">
-        <v>17.2381</v>
+        <v>17.2243</v>
       </c>
       <c r="D135" t="n">
-        <v>46.7832</v>
+        <v>48.3717</v>
       </c>
       <c r="E135" t="n">
-        <v>20.1675</v>
+        <v>20.1919</v>
       </c>
       <c r="F135" t="n">
-        <v>30.3446</v>
+        <v>30.3675</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>17.3179</v>
+        <v>17.3936</v>
       </c>
       <c r="C136" t="n">
-        <v>18.9293</v>
+        <v>18.9756</v>
       </c>
       <c r="D136" t="n">
-        <v>46.2501</v>
+        <v>46.3101</v>
       </c>
       <c r="E136" t="n">
-        <v>19.7256</v>
+        <v>19.7175</v>
       </c>
       <c r="F136" t="n">
-        <v>30.1901</v>
+        <v>30.115</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>16.5607</v>
+        <v>16.5481</v>
       </c>
       <c r="C137" t="n">
-        <v>18.8413</v>
+        <v>18.8593</v>
       </c>
       <c r="D137" t="n">
-        <v>45.6105</v>
+        <v>45.6776</v>
       </c>
       <c r="E137" t="n">
-        <v>19.2087</v>
+        <v>19.2004</v>
       </c>
       <c r="F137" t="n">
-        <v>29.6749</v>
+        <v>29.6537</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>23.2461</v>
+        <v>23.2493</v>
       </c>
       <c r="C138" t="n">
-        <v>18.5224</v>
+        <v>18.5429</v>
       </c>
       <c r="D138" t="n">
-        <v>45.0455</v>
+        <v>45.0672</v>
       </c>
       <c r="E138" t="n">
-        <v>18.7372</v>
+        <v>18.7391</v>
       </c>
       <c r="F138" t="n">
-        <v>29.2723</v>
+        <v>29.2611</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>22.9052</v>
+        <v>22.8965</v>
       </c>
       <c r="C139" t="n">
-        <v>18.483</v>
+        <v>18.4904</v>
       </c>
       <c r="D139" t="n">
-        <v>44.6947</v>
+        <v>44.675</v>
       </c>
       <c r="E139" t="n">
-        <v>18.3073</v>
+        <v>18.3347</v>
       </c>
       <c r="F139" t="n">
-        <v>29.0183</v>
+        <v>29.0953</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>22.4965</v>
+        <v>22.4946</v>
       </c>
       <c r="C140" t="n">
-        <v>18.3234</v>
+        <v>18.3283</v>
       </c>
       <c r="D140" t="n">
-        <v>44.1072</v>
+        <v>44.1297</v>
       </c>
       <c r="E140" t="n">
-        <v>17.9145</v>
+        <v>17.9105</v>
       </c>
       <c r="F140" t="n">
-        <v>28.7303</v>
+        <v>28.8227</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>22.0708</v>
+        <v>22.0732</v>
       </c>
       <c r="C141" t="n">
-        <v>18.1728</v>
+        <v>18.1907</v>
       </c>
       <c r="D141" t="n">
-        <v>43.5833</v>
+        <v>43.567</v>
       </c>
       <c r="E141" t="n">
-        <v>17.5459</v>
+        <v>17.5425</v>
       </c>
       <c r="F141" t="n">
-        <v>28.3629</v>
+        <v>28.3733</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>21.6116</v>
+        <v>21.6209</v>
       </c>
       <c r="C142" t="n">
-        <v>17.9113</v>
+        <v>17.917</v>
       </c>
       <c r="D142" t="n">
-        <v>42.8785</v>
+        <v>42.8981</v>
       </c>
       <c r="E142" t="n">
-        <v>17.1612</v>
+        <v>17.1565</v>
       </c>
       <c r="F142" t="n">
-        <v>28.055</v>
+        <v>28.0543</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>21.1546</v>
+        <v>21.1583</v>
       </c>
       <c r="C143" t="n">
-        <v>17.8923</v>
+        <v>17.9074</v>
       </c>
       <c r="D143" t="n">
-        <v>42.3643</v>
+        <v>42.3446</v>
       </c>
       <c r="E143" t="n">
-        <v>16.8503</v>
+        <v>16.8419</v>
       </c>
       <c r="F143" t="n">
-        <v>27.7666</v>
+        <v>27.7784</v>
       </c>
     </row>
   </sheetData>

--- a/clang-x64/Running erasure.xlsx
+++ b/clang-x64/Running erasure.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>18.226</v>
+        <v>18.1973</v>
       </c>
       <c r="C2" t="n">
-        <v>13.1125</v>
+        <v>13.1224</v>
       </c>
       <c r="D2" t="n">
-        <v>30.6679</v>
+        <v>30.6769</v>
       </c>
       <c r="E2" t="n">
-        <v>12.72</v>
+        <v>12.6967</v>
       </c>
       <c r="F2" t="n">
-        <v>26.5566</v>
+        <v>26.4006</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>18.1844</v>
+        <v>18.1562</v>
       </c>
       <c r="C3" t="n">
-        <v>13.3185</v>
+        <v>13.3414</v>
       </c>
       <c r="D3" t="n">
-        <v>30.9115</v>
+        <v>30.9002</v>
       </c>
       <c r="E3" t="n">
-        <v>12.6513</v>
+        <v>12.6568</v>
       </c>
       <c r="F3" t="n">
-        <v>26.1808</v>
+        <v>26.3232</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>17.5093</v>
+        <v>17.5354</v>
       </c>
       <c r="C4" t="n">
-        <v>13.4492</v>
+        <v>13.7231</v>
       </c>
       <c r="D4" t="n">
-        <v>31.0411</v>
+        <v>30.9897</v>
       </c>
       <c r="E4" t="n">
-        <v>12.3548</v>
+        <v>12.4155</v>
       </c>
       <c r="F4" t="n">
-        <v>25.878</v>
+        <v>26.0863</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>17.0869</v>
+        <v>17.1779</v>
       </c>
       <c r="C5" t="n">
-        <v>13.6164</v>
+        <v>13.8058</v>
       </c>
       <c r="D5" t="n">
-        <v>31.2258</v>
+        <v>31.2362</v>
       </c>
       <c r="E5" t="n">
-        <v>12.2786</v>
+        <v>12.2613</v>
       </c>
       <c r="F5" t="n">
-        <v>25.7903</v>
+        <v>25.2908</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>16.6857</v>
+        <v>16.5482</v>
       </c>
       <c r="C6" t="n">
-        <v>13.8574</v>
+        <v>14.1375</v>
       </c>
       <c r="D6" t="n">
-        <v>31.2216</v>
+        <v>31.2835</v>
       </c>
       <c r="E6" t="n">
-        <v>12.3219</v>
+        <v>12.3689</v>
       </c>
       <c r="F6" t="n">
-        <v>25.2278</v>
+        <v>25.1268</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>16.3205</v>
+        <v>16.282</v>
       </c>
       <c r="C7" t="n">
-        <v>14.1374</v>
+        <v>14.3212</v>
       </c>
       <c r="D7" t="n">
-        <v>30.1618</v>
+        <v>30.2085</v>
       </c>
       <c r="E7" t="n">
-        <v>18.7636</v>
+        <v>18.8147</v>
       </c>
       <c r="F7" t="n">
-        <v>30.0435</v>
+        <v>30.446</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>15.8529</v>
+        <v>15.8395</v>
       </c>
       <c r="C8" t="n">
-        <v>15.5303</v>
+        <v>15.5827</v>
       </c>
       <c r="D8" t="n">
-        <v>30.1291</v>
+        <v>30.2294</v>
       </c>
       <c r="E8" t="n">
-        <v>18.2325</v>
+        <v>18.3353</v>
       </c>
       <c r="F8" t="n">
-        <v>29.6389</v>
+        <v>29.902</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>15.0969</v>
+        <v>15.0721</v>
       </c>
       <c r="C9" t="n">
-        <v>15.6002</v>
+        <v>15.5704</v>
       </c>
       <c r="D9" t="n">
-        <v>30.2367</v>
+        <v>30.347</v>
       </c>
       <c r="E9" t="n">
-        <v>17.8637</v>
+        <v>17.7949</v>
       </c>
       <c r="F9" t="n">
-        <v>29.4695</v>
+        <v>29.5464</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>21.7356</v>
+        <v>21.7068</v>
       </c>
       <c r="C10" t="n">
-        <v>15.6803</v>
+        <v>15.7898</v>
       </c>
       <c r="D10" t="n">
-        <v>30.2981</v>
+        <v>30.4484</v>
       </c>
       <c r="E10" t="n">
-        <v>17.4322</v>
+        <v>17.4833</v>
       </c>
       <c r="F10" t="n">
-        <v>29.1874</v>
+        <v>28.8196</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>21.3796</v>
+        <v>21.4139</v>
       </c>
       <c r="C11" t="n">
-        <v>15.9559</v>
+        <v>15.9035</v>
       </c>
       <c r="D11" t="n">
-        <v>30.5002</v>
+        <v>30.5966</v>
       </c>
       <c r="E11" t="n">
-        <v>17.0258</v>
+        <v>17.1656</v>
       </c>
       <c r="F11" t="n">
-        <v>28.8944</v>
+        <v>28.985</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>21.0196</v>
+        <v>21.0861</v>
       </c>
       <c r="C12" t="n">
-        <v>16.0754</v>
+        <v>16.0411</v>
       </c>
       <c r="D12" t="n">
-        <v>30.5231</v>
+        <v>30.6833</v>
       </c>
       <c r="E12" t="n">
-        <v>16.6483</v>
+        <v>16.7298</v>
       </c>
       <c r="F12" t="n">
-        <v>28.2046</v>
+        <v>28.2783</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>20.647</v>
+        <v>20.6585</v>
       </c>
       <c r="C13" t="n">
-        <v>16.2181</v>
+        <v>16.3036</v>
       </c>
       <c r="D13" t="n">
-        <v>30.7292</v>
+        <v>30.879</v>
       </c>
       <c r="E13" t="n">
-        <v>16.4059</v>
+        <v>16.4973</v>
       </c>
       <c r="F13" t="n">
-        <v>27.858</v>
+        <v>28.0877</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>20.351</v>
+        <v>20.4456</v>
       </c>
       <c r="C14" t="n">
-        <v>16.4622</v>
+        <v>16.2531</v>
       </c>
       <c r="D14" t="n">
-        <v>31.0092</v>
+        <v>31.069</v>
       </c>
       <c r="E14" t="n">
-        <v>16.1274</v>
+        <v>16.2445</v>
       </c>
       <c r="F14" t="n">
-        <v>27.6962</v>
+        <v>27.696</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>20.0362</v>
+        <v>20.0315</v>
       </c>
       <c r="C15" t="n">
-        <v>16.5455</v>
+        <v>16.3783</v>
       </c>
       <c r="D15" t="n">
-        <v>31.0009</v>
+        <v>31.1139</v>
       </c>
       <c r="E15" t="n">
-        <v>15.9672</v>
+        <v>15.87</v>
       </c>
       <c r="F15" t="n">
-        <v>27.389</v>
+        <v>27.4129</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>19.6615</v>
+        <v>19.6848</v>
       </c>
       <c r="C16" t="n">
-        <v>16.5673</v>
+        <v>16.468</v>
       </c>
       <c r="D16" t="n">
-        <v>31.1686</v>
+        <v>31.5888</v>
       </c>
       <c r="E16" t="n">
-        <v>15.5171</v>
+        <v>15.6191</v>
       </c>
       <c r="F16" t="n">
-        <v>26.8902</v>
+        <v>27.0265</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>19.1882</v>
+        <v>19.2393</v>
       </c>
       <c r="C17" t="n">
-        <v>16.3982</v>
+        <v>16.4466</v>
       </c>
       <c r="D17" t="n">
-        <v>31.2875</v>
+        <v>31.8543</v>
       </c>
       <c r="E17" t="n">
-        <v>15.2553</v>
+        <v>15.268</v>
       </c>
       <c r="F17" t="n">
-        <v>26.6528</v>
+        <v>26.6056</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>18.8755</v>
+        <v>18.9317</v>
       </c>
       <c r="C18" t="n">
-        <v>16.4529</v>
+        <v>16.4619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.5355</v>
+        <v>32.0249</v>
       </c>
       <c r="E18" t="n">
-        <v>14.9809</v>
+        <v>15.0156</v>
       </c>
       <c r="F18" t="n">
-        <v>26.4137</v>
+        <v>26.3793</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>18.3662</v>
+        <v>18.376</v>
       </c>
       <c r="C19" t="n">
-        <v>16.5993</v>
+        <v>16.5457</v>
       </c>
       <c r="D19" t="n">
-        <v>31.7087</v>
+        <v>32.1463</v>
       </c>
       <c r="E19" t="n">
-        <v>14.6121</v>
+        <v>14.6226</v>
       </c>
       <c r="F19" t="n">
-        <v>26.0008</v>
+        <v>26.029</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>17.947</v>
+        <v>17.8673</v>
       </c>
       <c r="C20" t="n">
-        <v>16.7527</v>
+        <v>16.7084</v>
       </c>
       <c r="D20" t="n">
-        <v>31.8708</v>
+        <v>32.1952</v>
       </c>
       <c r="E20" t="n">
-        <v>14.3062</v>
+        <v>14.3172</v>
       </c>
       <c r="F20" t="n">
-        <v>25.7959</v>
+        <v>26.3955</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>17.2388</v>
+        <v>17.258</v>
       </c>
       <c r="C21" t="n">
-        <v>16.559</v>
+        <v>16.6168</v>
       </c>
       <c r="D21" t="n">
-        <v>31.1089</v>
+        <v>31.5243</v>
       </c>
       <c r="E21" t="n">
-        <v>19.9552</v>
+        <v>19.9063</v>
       </c>
       <c r="F21" t="n">
-        <v>30.8572</v>
+        <v>30.9315</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>16.7303</v>
+        <v>16.7772</v>
       </c>
       <c r="C22" t="n">
-        <v>18.1203</v>
+        <v>18.0092</v>
       </c>
       <c r="D22" t="n">
-        <v>31.0498</v>
+        <v>31.4482</v>
       </c>
       <c r="E22" t="n">
-        <v>19.3928</v>
+        <v>19.3587</v>
       </c>
       <c r="F22" t="n">
-        <v>29.9768</v>
+        <v>30.3452</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>16.0253</v>
+        <v>16.0963</v>
       </c>
       <c r="C23" t="n">
-        <v>17.9921</v>
+        <v>17.995</v>
       </c>
       <c r="D23" t="n">
-        <v>31.0994</v>
+        <v>31.2935</v>
       </c>
       <c r="E23" t="n">
-        <v>18.8936</v>
+        <v>18.9106</v>
       </c>
       <c r="F23" t="n">
-        <v>29.6029</v>
+        <v>29.5718</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>22.4819</v>
+        <v>22.4451</v>
       </c>
       <c r="C24" t="n">
-        <v>17.8632</v>
+        <v>17.8143</v>
       </c>
       <c r="D24" t="n">
-        <v>31.0687</v>
+        <v>31.173</v>
       </c>
       <c r="E24" t="n">
-        <v>18.4454</v>
+        <v>18.4491</v>
       </c>
       <c r="F24" t="n">
-        <v>29.2398</v>
+        <v>29.2842</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>22.2145</v>
+        <v>22.1709</v>
       </c>
       <c r="C25" t="n">
-        <v>17.811</v>
+        <v>17.7602</v>
       </c>
       <c r="D25" t="n">
-        <v>31.5213</v>
+        <v>31.5852</v>
       </c>
       <c r="E25" t="n">
-        <v>18.0252</v>
+        <v>17.9992</v>
       </c>
       <c r="F25" t="n">
-        <v>29.0049</v>
+        <v>28.8749</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>21.8775</v>
+        <v>21.8023</v>
       </c>
       <c r="C26" t="n">
-        <v>17.7189</v>
+        <v>17.7143</v>
       </c>
       <c r="D26" t="n">
-        <v>31.5422</v>
+        <v>31.7907</v>
       </c>
       <c r="E26" t="n">
-        <v>17.6029</v>
+        <v>17.6007</v>
       </c>
       <c r="F26" t="n">
-        <v>28.6377</v>
+        <v>28.6307</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>21.5143</v>
+        <v>21.5134</v>
       </c>
       <c r="C27" t="n">
-        <v>17.6142</v>
+        <v>17.5791</v>
       </c>
       <c r="D27" t="n">
-        <v>31.6407</v>
+        <v>31.9219</v>
       </c>
       <c r="E27" t="n">
-        <v>17.2108</v>
+        <v>17.2019</v>
       </c>
       <c r="F27" t="n">
-        <v>28.328</v>
+        <v>28.2889</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>21.2336</v>
+        <v>21.2167</v>
       </c>
       <c r="C28" t="n">
-        <v>17.6181</v>
+        <v>17.6292</v>
       </c>
       <c r="D28" t="n">
-        <v>31.7422</v>
+        <v>31.7378</v>
       </c>
       <c r="E28" t="n">
-        <v>16.8452</v>
+        <v>16.8383</v>
       </c>
       <c r="F28" t="n">
-        <v>28.0352</v>
+        <v>27.9677</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>20.7959</v>
+        <v>20.7982</v>
       </c>
       <c r="C29" t="n">
-        <v>17.4737</v>
+        <v>17.4855</v>
       </c>
       <c r="D29" t="n">
-        <v>31.7608</v>
+        <v>32.0767</v>
       </c>
       <c r="E29" t="n">
-        <v>16.4541</v>
+        <v>16.4286</v>
       </c>
       <c r="F29" t="n">
-        <v>27.6827</v>
+        <v>27.6752</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>20.3826</v>
+        <v>20.3693</v>
       </c>
       <c r="C30" t="n">
-        <v>17.495</v>
+        <v>17.5571</v>
       </c>
       <c r="D30" t="n">
-        <v>31.8278</v>
+        <v>32.0182</v>
       </c>
       <c r="E30" t="n">
-        <v>16.0962</v>
+        <v>16.113</v>
       </c>
       <c r="F30" t="n">
-        <v>27.6499</v>
+        <v>27.4847</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>19.9134</v>
+        <v>20.0081</v>
       </c>
       <c r="C31" t="n">
-        <v>17.409</v>
+        <v>17.424</v>
       </c>
       <c r="D31" t="n">
-        <v>31.9646</v>
+        <v>32.0602</v>
       </c>
       <c r="E31" t="n">
-        <v>15.8047</v>
+        <v>15.8332</v>
       </c>
       <c r="F31" t="n">
-        <v>27.1678</v>
+        <v>27.0614</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>19.4027</v>
+        <v>19.5291</v>
       </c>
       <c r="C32" t="n">
-        <v>17.3703</v>
+        <v>17.4065</v>
       </c>
       <c r="D32" t="n">
-        <v>32.1151</v>
+        <v>32.2376</v>
       </c>
       <c r="E32" t="n">
-        <v>15.5108</v>
+        <v>15.4494</v>
       </c>
       <c r="F32" t="n">
-        <v>26.7874</v>
+        <v>26.7707</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>18.9217</v>
+        <v>19.0179</v>
       </c>
       <c r="C33" t="n">
-        <v>17.316</v>
+        <v>17.3197</v>
       </c>
       <c r="D33" t="n">
-        <v>32.2876</v>
+        <v>32.4815</v>
       </c>
       <c r="E33" t="n">
-        <v>15.2166</v>
+        <v>15.2327</v>
       </c>
       <c r="F33" t="n">
-        <v>26.9574</v>
+        <v>26.9632</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>18.3861</v>
+        <v>18.4187</v>
       </c>
       <c r="C34" t="n">
-        <v>17.2585</v>
+        <v>17.2792</v>
       </c>
       <c r="D34" t="n">
-        <v>32.4392</v>
+        <v>32.5141</v>
       </c>
       <c r="E34" t="n">
-        <v>14.8868</v>
+        <v>14.8981</v>
       </c>
       <c r="F34" t="n">
-        <v>26.6942</v>
+        <v>26.7152</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>17.8429</v>
+        <v>17.9146</v>
       </c>
       <c r="C35" t="n">
-        <v>17.2079</v>
+        <v>17.1953</v>
       </c>
       <c r="D35" t="n">
-        <v>31.6983</v>
+        <v>31.7177</v>
       </c>
       <c r="E35" t="n">
-        <v>20.1034</v>
+        <v>20.1125</v>
       </c>
       <c r="F35" t="n">
-        <v>31.0002</v>
+        <v>31.0045</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>17.2692</v>
+        <v>17.3476</v>
       </c>
       <c r="C36" t="n">
-        <v>17.1477</v>
+        <v>17.144</v>
       </c>
       <c r="D36" t="n">
-        <v>31.6338</v>
+        <v>31.6224</v>
       </c>
       <c r="E36" t="n">
-        <v>19.5109</v>
+        <v>19.6312</v>
       </c>
       <c r="F36" t="n">
-        <v>30.6492</v>
+        <v>30.6269</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>16.7174</v>
+        <v>16.6522</v>
       </c>
       <c r="C37" t="n">
-        <v>18.4097</v>
+        <v>18.4232</v>
       </c>
       <c r="D37" t="n">
-        <v>31.5414</v>
+        <v>31.7898</v>
       </c>
       <c r="E37" t="n">
-        <v>19.0714</v>
+        <v>19.0261</v>
       </c>
       <c r="F37" t="n">
-        <v>30.3495</v>
+        <v>30.2881</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>23.0934</v>
+        <v>23.0223</v>
       </c>
       <c r="C38" t="n">
-        <v>18.2178</v>
+        <v>18.2335</v>
       </c>
       <c r="D38" t="n">
-        <v>31.5376</v>
+        <v>31.6379</v>
       </c>
       <c r="E38" t="n">
-        <v>18.6178</v>
+        <v>18.7028</v>
       </c>
       <c r="F38" t="n">
-        <v>29.9341</v>
+        <v>29.8481</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>22.8397</v>
+        <v>22.8177</v>
       </c>
       <c r="C39" t="n">
-        <v>18.1716</v>
+        <v>18.1746</v>
       </c>
       <c r="D39" t="n">
-        <v>31.6017</v>
+        <v>31.4786</v>
       </c>
       <c r="E39" t="n">
-        <v>18.1677</v>
+        <v>18.1686</v>
       </c>
       <c r="F39" t="n">
-        <v>29.5958</v>
+        <v>29.6266</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>22.4851</v>
+        <v>22.4424</v>
       </c>
       <c r="C40" t="n">
-        <v>18.035</v>
+        <v>18.1126</v>
       </c>
       <c r="D40" t="n">
-        <v>31.7983</v>
+        <v>31.725</v>
       </c>
       <c r="E40" t="n">
-        <v>17.8271</v>
+        <v>17.8297</v>
       </c>
       <c r="F40" t="n">
-        <v>29.2522</v>
+        <v>29.3023</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>22.0771</v>
+        <v>22.0962</v>
       </c>
       <c r="C41" t="n">
-        <v>17.9226</v>
+        <v>17.8897</v>
       </c>
       <c r="D41" t="n">
-        <v>31.9653</v>
+        <v>31.9773</v>
       </c>
       <c r="E41" t="n">
-        <v>17.4101</v>
+        <v>17.462</v>
       </c>
       <c r="F41" t="n">
-        <v>29.0244</v>
+        <v>28.9797</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>21.6706</v>
+        <v>21.6554</v>
       </c>
       <c r="C42" t="n">
-        <v>17.7271</v>
+        <v>17.7375</v>
       </c>
       <c r="D42" t="n">
-        <v>31.8172</v>
+        <v>31.8105</v>
       </c>
       <c r="E42" t="n">
-        <v>17.0867</v>
+        <v>17.0506</v>
       </c>
       <c r="F42" t="n">
-        <v>28.633</v>
+        <v>28.6324</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>21.1495</v>
+        <v>21.1576</v>
       </c>
       <c r="C43" t="n">
-        <v>17.5743</v>
+        <v>17.5798</v>
       </c>
       <c r="D43" t="n">
-        <v>31.9322</v>
+        <v>32.0438</v>
       </c>
       <c r="E43" t="n">
-        <v>16.6917</v>
+        <v>16.7442</v>
       </c>
       <c r="F43" t="n">
-        <v>28.3351</v>
+        <v>28.3382</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>20.7014</v>
+        <v>20.7011</v>
       </c>
       <c r="C44" t="n">
-        <v>17.5225</v>
+        <v>17.5007</v>
       </c>
       <c r="D44" t="n">
-        <v>31.9893</v>
+        <v>32.0217</v>
       </c>
       <c r="E44" t="n">
-        <v>16.4172</v>
+        <v>16.4092</v>
       </c>
       <c r="F44" t="n">
-        <v>28.1406</v>
+        <v>28.1051</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>20.254</v>
+        <v>20.274</v>
       </c>
       <c r="C45" t="n">
-        <v>17.4272</v>
+        <v>17.4299</v>
       </c>
       <c r="D45" t="n">
-        <v>32.1674</v>
+        <v>32.1862</v>
       </c>
       <c r="E45" t="n">
-        <v>16.0848</v>
+        <v>16.0828</v>
       </c>
       <c r="F45" t="n">
-        <v>27.8398</v>
+        <v>27.8754</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>19.8379</v>
+        <v>19.8296</v>
       </c>
       <c r="C46" t="n">
-        <v>17.3427</v>
+        <v>17.3533</v>
       </c>
       <c r="D46" t="n">
-        <v>31.8228</v>
+        <v>32.2173</v>
       </c>
       <c r="E46" t="n">
-        <v>15.7804</v>
+        <v>15.7543</v>
       </c>
       <c r="F46" t="n">
-        <v>27.5417</v>
+        <v>27.5319</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>19.3555</v>
+        <v>19.3179</v>
       </c>
       <c r="C47" t="n">
-        <v>17.2554</v>
+        <v>17.3041</v>
       </c>
       <c r="D47" t="n">
-        <v>32.0873</v>
+        <v>32.4653</v>
       </c>
       <c r="E47" t="n">
-        <v>15.4647</v>
+        <v>15.4969</v>
       </c>
       <c r="F47" t="n">
-        <v>27.2836</v>
+        <v>27.2257</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>18.7797</v>
+        <v>18.8713</v>
       </c>
       <c r="C48" t="n">
-        <v>17.2229</v>
+        <v>17.215</v>
       </c>
       <c r="D48" t="n">
-        <v>32.1452</v>
+        <v>32.5349</v>
       </c>
       <c r="E48" t="n">
-        <v>15.1915</v>
+        <v>15.2074</v>
       </c>
       <c r="F48" t="n">
-        <v>26.9112</v>
+        <v>26.8485</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>18.2825</v>
+        <v>18.2599</v>
       </c>
       <c r="C49" t="n">
-        <v>17.1643</v>
+        <v>17.1351</v>
       </c>
       <c r="D49" t="n">
-        <v>32.6099</v>
+        <v>32.7167</v>
       </c>
       <c r="E49" t="n">
-        <v>14.8303</v>
+        <v>14.817</v>
       </c>
       <c r="F49" t="n">
-        <v>25.97</v>
+        <v>26.577</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>17.7287</v>
+        <v>17.7394</v>
       </c>
       <c r="C50" t="n">
-        <v>17.111</v>
+        <v>17.0996</v>
       </c>
       <c r="D50" t="n">
-        <v>31.6089</v>
+        <v>31.8033</v>
       </c>
       <c r="E50" t="n">
-        <v>19.7792</v>
+        <v>19.7639</v>
       </c>
       <c r="F50" t="n">
-        <v>30.6325</v>
+        <v>30.6224</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>16.9469</v>
+        <v>16.9576</v>
       </c>
       <c r="C51" t="n">
-        <v>18.523</v>
+        <v>18.4638</v>
       </c>
       <c r="D51" t="n">
-        <v>31.8563</v>
+        <v>32.0555</v>
       </c>
       <c r="E51" t="n">
-        <v>19.3043</v>
+        <v>19.2808</v>
       </c>
       <c r="F51" t="n">
-        <v>30.3047</v>
+        <v>30.305</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>15.9815</v>
+        <v>16.0561</v>
       </c>
       <c r="C52" t="n">
-        <v>18.3703</v>
+        <v>18.3398</v>
       </c>
       <c r="D52" t="n">
-        <v>32.4059</v>
+        <v>31.6503</v>
       </c>
       <c r="E52" t="n">
-        <v>18.8315</v>
+        <v>18.7568</v>
       </c>
       <c r="F52" t="n">
-        <v>30.0122</v>
+        <v>29.9487</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>23.0266</v>
+        <v>23.0144</v>
       </c>
       <c r="C53" t="n">
-        <v>18.2358</v>
+        <v>18.1772</v>
       </c>
       <c r="D53" t="n">
-        <v>32.421</v>
+        <v>31.7485</v>
       </c>
       <c r="E53" t="n">
-        <v>18.4106</v>
+        <v>18.367</v>
       </c>
       <c r="F53" t="n">
-        <v>29.2124</v>
+        <v>29.2138</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>22.6461</v>
+        <v>22.7085</v>
       </c>
       <c r="C54" t="n">
-        <v>18.1088</v>
+        <v>18.0622</v>
       </c>
       <c r="D54" t="n">
-        <v>32.402</v>
+        <v>32.2927</v>
       </c>
       <c r="E54" t="n">
-        <v>17.9717</v>
+        <v>17.9716</v>
       </c>
       <c r="F54" t="n">
-        <v>29.3825</v>
+        <v>29.3346</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>22.2854</v>
+        <v>22.288</v>
       </c>
       <c r="C55" t="n">
-        <v>17.9705</v>
+        <v>17.9558</v>
       </c>
       <c r="D55" t="n">
-        <v>32.4786</v>
+        <v>32.4652</v>
       </c>
       <c r="E55" t="n">
-        <v>17.6524</v>
+        <v>17.6285</v>
       </c>
       <c r="F55" t="n">
-        <v>29.1074</v>
+        <v>29.0669</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>21.839</v>
+        <v>21.8279</v>
       </c>
       <c r="C56" t="n">
-        <v>17.8174</v>
+        <v>17.8141</v>
       </c>
       <c r="D56" t="n">
-        <v>32.5956</v>
+        <v>32.3551</v>
       </c>
       <c r="E56" t="n">
-        <v>17.2592</v>
+        <v>17.2468</v>
       </c>
       <c r="F56" t="n">
-        <v>28.2716</v>
+        <v>28.3198</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>21.3772</v>
+        <v>21.3769</v>
       </c>
       <c r="C57" t="n">
-        <v>17.7542</v>
+        <v>17.7081</v>
       </c>
       <c r="D57" t="n">
-        <v>32.8561</v>
+        <v>32.4327</v>
       </c>
       <c r="E57" t="n">
-        <v>16.9128</v>
+        <v>16.9049</v>
       </c>
       <c r="F57" t="n">
-        <v>27.9353</v>
+        <v>27.8952</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>20.9151</v>
+        <v>20.9495</v>
       </c>
       <c r="C58" t="n">
-        <v>17.6701</v>
+        <v>17.6028</v>
       </c>
       <c r="D58" t="n">
-        <v>33.0401</v>
+        <v>33.045</v>
       </c>
       <c r="E58" t="n">
-        <v>16.5846</v>
+        <v>16.6029</v>
       </c>
       <c r="F58" t="n">
-        <v>27.6555</v>
+        <v>27.6867</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>20.4841</v>
+        <v>20.4658</v>
       </c>
       <c r="C59" t="n">
-        <v>17.5288</v>
+        <v>17.5229</v>
       </c>
       <c r="D59" t="n">
-        <v>33.0962</v>
+        <v>33.1341</v>
       </c>
       <c r="E59" t="n">
-        <v>16.2597</v>
+        <v>16.2901</v>
       </c>
       <c r="F59" t="n">
-        <v>27.3265</v>
+        <v>27.3332</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>19.9279</v>
+        <v>19.9278</v>
       </c>
       <c r="C60" t="n">
-        <v>17.4633</v>
+        <v>17.4511</v>
       </c>
       <c r="D60" t="n">
-        <v>33.5297</v>
+        <v>33.5165</v>
       </c>
       <c r="E60" t="n">
-        <v>15.9704</v>
+        <v>15.9691</v>
       </c>
       <c r="F60" t="n">
-        <v>27.0263</v>
+        <v>26.9743</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>19.4849</v>
+        <v>19.4944</v>
       </c>
       <c r="C61" t="n">
-        <v>17.3651</v>
+        <v>17.3362</v>
       </c>
       <c r="D61" t="n">
-        <v>33.493</v>
+        <v>33.7815</v>
       </c>
       <c r="E61" t="n">
-        <v>15.6648</v>
+        <v>15.672</v>
       </c>
       <c r="F61" t="n">
-        <v>27.3463</v>
+        <v>27.2905</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>18.9859</v>
+        <v>18.9749</v>
       </c>
       <c r="C62" t="n">
-        <v>17.2939</v>
+        <v>17.2723</v>
       </c>
       <c r="D62" t="n">
-        <v>33.7216</v>
+        <v>33.9951</v>
       </c>
       <c r="E62" t="n">
-        <v>15.3304</v>
+        <v>15.3635</v>
       </c>
       <c r="F62" t="n">
-        <v>26.4507</v>
+        <v>26.4159</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>18.4183</v>
+        <v>18.4436</v>
       </c>
       <c r="C63" t="n">
-        <v>17.2543</v>
+        <v>17.2312</v>
       </c>
       <c r="D63" t="n">
-        <v>34.15</v>
+        <v>34.3974</v>
       </c>
       <c r="E63" t="n">
-        <v>15.0393</v>
+        <v>15.01</v>
       </c>
       <c r="F63" t="n">
-        <v>26.1336</v>
+        <v>26.0838</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>17.7846</v>
+        <v>17.7679</v>
       </c>
       <c r="C64" t="n">
-        <v>17.1801</v>
+        <v>17.1452</v>
       </c>
       <c r="D64" t="n">
-        <v>38.3608</v>
+        <v>38.3569</v>
       </c>
       <c r="E64" t="n">
-        <v>20.6265</v>
+        <v>20.879</v>
       </c>
       <c r="F64" t="n">
-        <v>30.4073</v>
+        <v>30.3837</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>17.1702</v>
+        <v>17.1412</v>
       </c>
       <c r="C65" t="n">
-        <v>18.7881</v>
+        <v>18.743</v>
       </c>
       <c r="D65" t="n">
-        <v>38.2475</v>
+        <v>38.3356</v>
       </c>
       <c r="E65" t="n">
-        <v>20.4219</v>
+        <v>20.4047</v>
       </c>
       <c r="F65" t="n">
-        <v>30.123</v>
+        <v>30.0757</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>16.4551</v>
+        <v>16.391</v>
       </c>
       <c r="C66" t="n">
-        <v>18.5357</v>
+        <v>18.5206</v>
       </c>
       <c r="D66" t="n">
-        <v>38.4751</v>
+        <v>38.6104</v>
       </c>
       <c r="E66" t="n">
-        <v>19.8165</v>
+        <v>19.8478</v>
       </c>
       <c r="F66" t="n">
-        <v>29.7162</v>
+        <v>29.6888</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>23.1757</v>
+        <v>23.1633</v>
       </c>
       <c r="C67" t="n">
-        <v>18.3543</v>
+        <v>18.3311</v>
       </c>
       <c r="D67" t="n">
-        <v>38.8643</v>
+        <v>38.837</v>
       </c>
       <c r="E67" t="n">
-        <v>19.4055</v>
+        <v>19.3616</v>
       </c>
       <c r="F67" t="n">
-        <v>29.4401</v>
+        <v>29.3536</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>22.7884</v>
+        <v>22.8248</v>
       </c>
       <c r="C68" t="n">
-        <v>18.2076</v>
+        <v>18.2096</v>
       </c>
       <c r="D68" t="n">
-        <v>39.2408</v>
+        <v>39.1429</v>
       </c>
       <c r="E68" t="n">
-        <v>18.6935</v>
+        <v>18.6875</v>
       </c>
       <c r="F68" t="n">
-        <v>28.997</v>
+        <v>29.0528</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>22.4006</v>
+        <v>22.371</v>
       </c>
       <c r="C69" t="n">
-        <v>18.0566</v>
+        <v>18.0658</v>
       </c>
       <c r="D69" t="n">
-        <v>39.5778</v>
+        <v>39.2098</v>
       </c>
       <c r="E69" t="n">
-        <v>18.1367</v>
+        <v>18.1651</v>
       </c>
       <c r="F69" t="n">
-        <v>28.7187</v>
+        <v>28.7456</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>21.9992</v>
+        <v>21.9846</v>
       </c>
       <c r="C70" t="n">
-        <v>18.0653</v>
+        <v>18.0795</v>
       </c>
       <c r="D70" t="n">
-        <v>39.6123</v>
+        <v>39.321</v>
       </c>
       <c r="E70" t="n">
-        <v>17.6277</v>
+        <v>17.5884</v>
       </c>
       <c r="F70" t="n">
-        <v>28.3463</v>
+        <v>28.3261</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>21.4775</v>
+        <v>21.4906</v>
       </c>
       <c r="C71" t="n">
-        <v>17.9477</v>
+        <v>17.93</v>
       </c>
       <c r="D71" t="n">
-        <v>39.8148</v>
+        <v>39.5896</v>
       </c>
       <c r="E71" t="n">
-        <v>17.1842</v>
+        <v>17.1337</v>
       </c>
       <c r="F71" t="n">
-        <v>28.0614</v>
+        <v>28.2135</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>21.0447</v>
+        <v>21.0523</v>
       </c>
       <c r="C72" t="n">
-        <v>17.824</v>
+        <v>17.8257</v>
       </c>
       <c r="D72" t="n">
-        <v>39.9166</v>
+        <v>39.6532</v>
       </c>
       <c r="E72" t="n">
-        <v>16.749</v>
+        <v>16.7765</v>
       </c>
       <c r="F72" t="n">
-        <v>28.3649</v>
+        <v>28.5006</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>20.5446</v>
+        <v>20.5503</v>
       </c>
       <c r="C73" t="n">
-        <v>17.752</v>
+        <v>17.7583</v>
       </c>
       <c r="D73" t="n">
-        <v>39.8293</v>
+        <v>39.7772</v>
       </c>
       <c r="E73" t="n">
-        <v>16.4169</v>
+        <v>16.4466</v>
       </c>
       <c r="F73" t="n">
-        <v>28.1078</v>
+        <v>28.2053</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>20.1095</v>
+        <v>20.121</v>
       </c>
       <c r="C74" t="n">
-        <v>17.6431</v>
+        <v>17.6571</v>
       </c>
       <c r="D74" t="n">
-        <v>39.9477</v>
+        <v>39.654</v>
       </c>
       <c r="E74" t="n">
-        <v>16.0919</v>
+        <v>16.1064</v>
       </c>
       <c r="F74" t="n">
-        <v>27.8291</v>
+        <v>27.9324</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>19.6071</v>
+        <v>19.6084</v>
       </c>
       <c r="C75" t="n">
-        <v>17.5582</v>
+        <v>17.5554</v>
       </c>
       <c r="D75" t="n">
-        <v>40.0096</v>
+        <v>39.8045</v>
       </c>
       <c r="E75" t="n">
-        <v>15.7897</v>
+        <v>15.7877</v>
       </c>
       <c r="F75" t="n">
-        <v>26.8919</v>
+        <v>27.6323</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>19.0727</v>
+        <v>19.0889</v>
       </c>
       <c r="C76" t="n">
-        <v>17.492</v>
+        <v>17.4774</v>
       </c>
       <c r="D76" t="n">
-        <v>40.0891</v>
+        <v>39.6689</v>
       </c>
       <c r="E76" t="n">
-        <v>15.4708</v>
+        <v>15.4868</v>
       </c>
       <c r="F76" t="n">
-        <v>26.6029</v>
+        <v>27.3339</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>18.5986</v>
+        <v>18.5767</v>
       </c>
       <c r="C77" t="n">
-        <v>17.428</v>
+        <v>17.4098</v>
       </c>
       <c r="D77" t="n">
-        <v>39.7617</v>
+        <v>39.6987</v>
       </c>
       <c r="E77" t="n">
-        <v>15.1607</v>
+        <v>15.1595</v>
       </c>
       <c r="F77" t="n">
-        <v>26.2627</v>
+        <v>26.3591</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>18.0032</v>
+        <v>18.0044</v>
       </c>
       <c r="C78" t="n">
-        <v>17.2209</v>
+        <v>17.2158</v>
       </c>
       <c r="D78" t="n">
-        <v>46.5327</v>
+        <v>45.5036</v>
       </c>
       <c r="E78" t="n">
-        <v>20.3916</v>
+        <v>20.4135</v>
       </c>
       <c r="F78" t="n">
-        <v>30.8479</v>
+        <v>30.9679</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>17.3547</v>
+        <v>17.3288</v>
       </c>
       <c r="C79" t="n">
-        <v>19.106</v>
+        <v>19.0924</v>
       </c>
       <c r="D79" t="n">
-        <v>46.4093</v>
+        <v>45.4108</v>
       </c>
       <c r="E79" t="n">
-        <v>19.8298</v>
+        <v>19.8603</v>
       </c>
       <c r="F79" t="n">
-        <v>30.5359</v>
+        <v>30.6669</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>16.5498</v>
+        <v>16.5946</v>
       </c>
       <c r="C80" t="n">
-        <v>18.8804</v>
+        <v>18.8591</v>
       </c>
       <c r="D80" t="n">
-        <v>46.0321</v>
+        <v>45.1062</v>
       </c>
       <c r="E80" t="n">
-        <v>19.3197</v>
+        <v>19.3249</v>
       </c>
       <c r="F80" t="n">
-        <v>30.3494</v>
+        <v>30.3674</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>23.2784</v>
+        <v>23.2915</v>
       </c>
       <c r="C81" t="n">
-        <v>18.7401</v>
+        <v>18.7452</v>
       </c>
       <c r="D81" t="n">
-        <v>45.4079</v>
+        <v>44.6299</v>
       </c>
       <c r="E81" t="n">
-        <v>18.8525</v>
+        <v>18.8827</v>
       </c>
       <c r="F81" t="n">
-        <v>29.991</v>
+        <v>30.0913</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>22.9152</v>
+        <v>22.9487</v>
       </c>
       <c r="C82" t="n">
-        <v>18.5158</v>
+        <v>18.514</v>
       </c>
       <c r="D82" t="n">
-        <v>44.9968</v>
+        <v>44.3388</v>
       </c>
       <c r="E82" t="n">
-        <v>18.4304</v>
+        <v>18.4706</v>
       </c>
       <c r="F82" t="n">
-        <v>29.6057</v>
+        <v>29.7451</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>22.5408</v>
+        <v>22.565</v>
       </c>
       <c r="C83" t="n">
-        <v>18.3974</v>
+        <v>18.3828</v>
       </c>
       <c r="D83" t="n">
-        <v>44.7307</v>
+        <v>44.0769</v>
       </c>
       <c r="E83" t="n">
-        <v>18.0439</v>
+        <v>18.0581</v>
       </c>
       <c r="F83" t="n">
-        <v>29.3167</v>
+        <v>29.4542</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>22.107</v>
+        <v>22.111</v>
       </c>
       <c r="C84" t="n">
-        <v>18.2427</v>
+        <v>18.2313</v>
       </c>
       <c r="D84" t="n">
-        <v>44.3269</v>
+        <v>43.6363</v>
       </c>
       <c r="E84" t="n">
-        <v>17.622</v>
+        <v>17.6065</v>
       </c>
       <c r="F84" t="n">
-        <v>29.0422</v>
+        <v>29.1564</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>21.6615</v>
+        <v>21.6448</v>
       </c>
       <c r="C85" t="n">
-        <v>17.9403</v>
+        <v>18.0024</v>
       </c>
       <c r="D85" t="n">
-        <v>44.3132</v>
+        <v>43.2298</v>
       </c>
       <c r="E85" t="n">
-        <v>17.2557</v>
+        <v>17.3002</v>
       </c>
       <c r="F85" t="n">
-        <v>28.6872</v>
+        <v>28.853</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>21.1903</v>
+        <v>21.2013</v>
       </c>
       <c r="C86" t="n">
-        <v>17.8329</v>
+        <v>17.846</v>
       </c>
       <c r="D86" t="n">
-        <v>42.8807</v>
+        <v>42.6921</v>
       </c>
       <c r="E86" t="n">
-        <v>16.9285</v>
+        <v>16.9387</v>
       </c>
       <c r="F86" t="n">
-        <v>28.4545</v>
+        <v>28.5937</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>20.7018</v>
+        <v>20.7009</v>
       </c>
       <c r="C87" t="n">
-        <v>17.7013</v>
+        <v>17.7116</v>
       </c>
       <c r="D87" t="n">
-        <v>42.6553</v>
+        <v>42.4711</v>
       </c>
       <c r="E87" t="n">
-        <v>16.552</v>
+        <v>16.5925</v>
       </c>
       <c r="F87" t="n">
-        <v>28.1561</v>
+        <v>28.3178</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>20.2376</v>
+        <v>20.22</v>
       </c>
       <c r="C88" t="n">
-        <v>17.6009</v>
+        <v>17.614</v>
       </c>
       <c r="D88" t="n">
-        <v>42.3276</v>
+        <v>42.1819</v>
       </c>
       <c r="E88" t="n">
-        <v>16.2571</v>
+        <v>16.2861</v>
       </c>
       <c r="F88" t="n">
-        <v>27.8554</v>
+        <v>28.0315</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>19.71</v>
+        <v>19.7328</v>
       </c>
       <c r="C89" t="n">
-        <v>17.5232</v>
+        <v>17.5097</v>
       </c>
       <c r="D89" t="n">
-        <v>42.7969</v>
+        <v>42.0165</v>
       </c>
       <c r="E89" t="n">
-        <v>15.9624</v>
+        <v>15.9654</v>
       </c>
       <c r="F89" t="n">
-        <v>27.5627</v>
+        <v>27.7087</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>19.2437</v>
+        <v>19.2426</v>
       </c>
       <c r="C90" t="n">
-        <v>17.3851</v>
+        <v>17.4035</v>
       </c>
       <c r="D90" t="n">
-        <v>41.7454</v>
+        <v>41.5871</v>
       </c>
       <c r="E90" t="n">
-        <v>15.6</v>
+        <v>15.6272</v>
       </c>
       <c r="F90" t="n">
-        <v>27.2355</v>
+        <v>27.3985</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>18.7661</v>
+        <v>18.7323</v>
       </c>
       <c r="C91" t="n">
-        <v>17.3034</v>
+        <v>17.3026</v>
       </c>
       <c r="D91" t="n">
-        <v>41.5824</v>
+        <v>41.4894</v>
       </c>
       <c r="E91" t="n">
-        <v>15.2924</v>
+        <v>15.3082</v>
       </c>
       <c r="F91" t="n">
-        <v>26.9524</v>
+        <v>27.1114</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>18.1722</v>
+        <v>18.203</v>
       </c>
       <c r="C92" t="n">
-        <v>17.2328</v>
+        <v>17.2365</v>
       </c>
       <c r="D92" t="n">
-        <v>47.3941</v>
+        <v>46.4165</v>
       </c>
       <c r="E92" t="n">
-        <v>20.5417</v>
+        <v>20.4905</v>
       </c>
       <c r="F92" t="n">
-        <v>31.0472</v>
+        <v>31.144</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>17.5107</v>
+        <v>17.4598</v>
       </c>
       <c r="C93" t="n">
-        <v>17.1589</v>
+        <v>17.1615</v>
       </c>
       <c r="D93" t="n">
-        <v>46.6118</v>
+        <v>45.975</v>
       </c>
       <c r="E93" t="n">
-        <v>20.0059</v>
+        <v>19.9787</v>
       </c>
       <c r="F93" t="n">
-        <v>30.6973</v>
+        <v>30.7521</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>16.815</v>
+        <v>16.7968</v>
       </c>
       <c r="C94" t="n">
-        <v>18.8231</v>
+        <v>18.8815</v>
       </c>
       <c r="D94" t="n">
-        <v>45.8229</v>
+        <v>45.3401</v>
       </c>
       <c r="E94" t="n">
-        <v>19.4887</v>
+        <v>19.4524</v>
       </c>
       <c r="F94" t="n">
-        <v>30.386</v>
+        <v>30.4489</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>23.3411</v>
+        <v>23.3416</v>
       </c>
       <c r="C95" t="n">
-        <v>18.6276</v>
+        <v>18.5684</v>
       </c>
       <c r="D95" t="n">
-        <v>45.3001</v>
+        <v>44.8624</v>
       </c>
       <c r="E95" t="n">
-        <v>18.9998</v>
+        <v>18.9605</v>
       </c>
       <c r="F95" t="n">
-        <v>30.0372</v>
+        <v>30.2382</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>23.015</v>
+        <v>22.9961</v>
       </c>
       <c r="C96" t="n">
-        <v>18.4712</v>
+        <v>18.3941</v>
       </c>
       <c r="D96" t="n">
-        <v>44.8301</v>
+        <v>44.404</v>
       </c>
       <c r="E96" t="n">
-        <v>18.525</v>
+        <v>18.4982</v>
       </c>
       <c r="F96" t="n">
-        <v>29.3135</v>
+        <v>29.3548</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>22.6315</v>
+        <v>22.5939</v>
       </c>
       <c r="C97" t="n">
-        <v>18.2835</v>
+        <v>18.2218</v>
       </c>
       <c r="D97" t="n">
-        <v>44.5044</v>
+        <v>44.0006</v>
       </c>
       <c r="E97" t="n">
-        <v>18.0785</v>
+        <v>18.0789</v>
       </c>
       <c r="F97" t="n">
-        <v>28.8439</v>
+        <v>28.8212</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>22.1969</v>
+        <v>22.2002</v>
       </c>
       <c r="C98" t="n">
-        <v>18.1339</v>
+        <v>18.0982</v>
       </c>
       <c r="D98" t="n">
-        <v>43.9711</v>
+        <v>43.0782</v>
       </c>
       <c r="E98" t="n">
-        <v>17.6788</v>
+        <v>17.6671</v>
       </c>
       <c r="F98" t="n">
-        <v>28.4766</v>
+        <v>28.4525</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>21.7541</v>
+        <v>21.7448</v>
       </c>
       <c r="C99" t="n">
-        <v>17.992</v>
+        <v>17.9703</v>
       </c>
       <c r="D99" t="n">
-        <v>43.5689</v>
+        <v>42.6621</v>
       </c>
       <c r="E99" t="n">
-        <v>17.3022</v>
+        <v>17.2937</v>
       </c>
       <c r="F99" t="n">
-        <v>28.166</v>
+        <v>28.1483</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>21.3132</v>
+        <v>21.3094</v>
       </c>
       <c r="C100" t="n">
-        <v>17.9752</v>
+        <v>17.9632</v>
       </c>
       <c r="D100" t="n">
-        <v>43.2648</v>
+        <v>42.6388</v>
       </c>
       <c r="E100" t="n">
-        <v>16.9629</v>
+        <v>16.9742</v>
       </c>
       <c r="F100" t="n">
-        <v>27.8685</v>
+        <v>27.8094</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>20.8315</v>
+        <v>20.8405</v>
       </c>
       <c r="C101" t="n">
-        <v>17.8472</v>
+        <v>17.8296</v>
       </c>
       <c r="D101" t="n">
-        <v>42.8706</v>
+        <v>42.574</v>
       </c>
       <c r="E101" t="n">
-        <v>16.6102</v>
+        <v>16.6497</v>
       </c>
       <c r="F101" t="n">
-        <v>27.5359</v>
+        <v>27.5513</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>20.3616</v>
+        <v>20.3812</v>
       </c>
       <c r="C102" t="n">
-        <v>17.7313</v>
+        <v>17.7238</v>
       </c>
       <c r="D102" t="n">
-        <v>42.4136</v>
+        <v>41.7816</v>
       </c>
       <c r="E102" t="n">
-        <v>16.296</v>
+        <v>16.3007</v>
       </c>
       <c r="F102" t="n">
-        <v>27.2919</v>
+        <v>27.2357</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>19.8855</v>
+        <v>19.8926</v>
       </c>
       <c r="C103" t="n">
-        <v>17.6385</v>
+        <v>17.6226</v>
       </c>
       <c r="D103" t="n">
-        <v>42.2848</v>
+        <v>41.5243</v>
       </c>
       <c r="E103" t="n">
-        <v>15.9743</v>
+        <v>15.9944</v>
       </c>
       <c r="F103" t="n">
-        <v>27.0206</v>
+        <v>26.9799</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>19.3564</v>
+        <v>19.3752</v>
       </c>
       <c r="C104" t="n">
-        <v>17.5457</v>
+        <v>17.5402</v>
       </c>
       <c r="D104" t="n">
-        <v>41.9124</v>
+        <v>41.1448</v>
       </c>
       <c r="E104" t="n">
-        <v>15.6622</v>
+        <v>15.6793</v>
       </c>
       <c r="F104" t="n">
-        <v>26.6889</v>
+        <v>26.6376</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>18.819</v>
+        <v>18.8204</v>
       </c>
       <c r="C105" t="n">
-        <v>17.4285</v>
+        <v>17.4293</v>
       </c>
       <c r="D105" t="n">
-        <v>41.6885</v>
+        <v>40.9442</v>
       </c>
       <c r="E105" t="n">
-        <v>15.3697</v>
+        <v>15.3652</v>
       </c>
       <c r="F105" t="n">
-        <v>26.3712</v>
+        <v>26.3534</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>18.2833</v>
+        <v>18.3049</v>
       </c>
       <c r="C106" t="n">
-        <v>17.3642</v>
+        <v>17.3632</v>
       </c>
       <c r="D106" t="n">
-        <v>41.3337</v>
+        <v>40.702</v>
       </c>
       <c r="E106" t="n">
-        <v>15.0617</v>
+        <v>15.0675</v>
       </c>
       <c r="F106" t="n">
-        <v>26.0496</v>
+        <v>26.0617</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>17.7031</v>
+        <v>17.7425</v>
       </c>
       <c r="C107" t="n">
-        <v>17.2755</v>
+        <v>17.2771</v>
       </c>
       <c r="D107" t="n">
-        <v>44.4428</v>
+        <v>43.9336</v>
       </c>
       <c r="E107" t="n">
-        <v>19.9797</v>
+        <v>19.9537</v>
       </c>
       <c r="F107" t="n">
-        <v>30.1845</v>
+        <v>30.1072</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>16.9956</v>
+        <v>16.9949</v>
       </c>
       <c r="C108" t="n">
-        <v>18.9636</v>
+        <v>18.9458</v>
       </c>
       <c r="D108" t="n">
-        <v>44.1385</v>
+        <v>43.6476</v>
       </c>
       <c r="E108" t="n">
-        <v>19.5188</v>
+        <v>19.5301</v>
       </c>
       <c r="F108" t="n">
-        <v>29.9015</v>
+        <v>29.8802</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>16.1593</v>
+        <v>16.2116</v>
       </c>
       <c r="C109" t="n">
-        <v>18.7859</v>
+        <v>18.7508</v>
       </c>
       <c r="D109" t="n">
-        <v>43.6343</v>
+        <v>43.2262</v>
       </c>
       <c r="E109" t="n">
-        <v>19.0507</v>
+        <v>19.0492</v>
       </c>
       <c r="F109" t="n">
-        <v>29.5321</v>
+        <v>29.4989</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>23.1064</v>
+        <v>23.1169</v>
       </c>
       <c r="C110" t="n">
-        <v>18.476</v>
+        <v>18.4543</v>
       </c>
       <c r="D110" t="n">
-        <v>43.0901</v>
+        <v>42.6946</v>
       </c>
       <c r="E110" t="n">
-        <v>18.5978</v>
+        <v>18.6212</v>
       </c>
       <c r="F110" t="n">
-        <v>29.7746</v>
+        <v>29.7241</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>22.7055</v>
+        <v>22.7152</v>
       </c>
       <c r="C111" t="n">
-        <v>18.3525</v>
+        <v>18.2942</v>
       </c>
       <c r="D111" t="n">
-        <v>42.6835</v>
+        <v>42.2729</v>
       </c>
       <c r="E111" t="n">
-        <v>18.154</v>
+        <v>18.1832</v>
       </c>
       <c r="F111" t="n">
-        <v>29.399</v>
+        <v>29.3939</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>22.2758</v>
+        <v>22.3048</v>
       </c>
       <c r="C112" t="n">
-        <v>18.1348</v>
+        <v>18.1652</v>
       </c>
       <c r="D112" t="n">
-        <v>41.874</v>
+        <v>42.0079</v>
       </c>
       <c r="E112" t="n">
-        <v>17.7317</v>
+        <v>17.7705</v>
       </c>
       <c r="F112" t="n">
-        <v>29.0563</v>
+        <v>29.0946</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>21.849</v>
+        <v>21.8574</v>
       </c>
       <c r="C113" t="n">
-        <v>18.0396</v>
+        <v>18.0137</v>
       </c>
       <c r="D113" t="n">
-        <v>41.539</v>
+        <v>41.6564</v>
       </c>
       <c r="E113" t="n">
-        <v>17.356</v>
+        <v>17.3966</v>
       </c>
       <c r="F113" t="n">
-        <v>28.7811</v>
+        <v>28.7858</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>21.3985</v>
+        <v>21.4151</v>
       </c>
       <c r="C114" t="n">
-        <v>17.8518</v>
+        <v>17.8597</v>
       </c>
       <c r="D114" t="n">
-        <v>40.6688</v>
+        <v>40.9123</v>
       </c>
       <c r="E114" t="n">
-        <v>17.0172</v>
+        <v>17.0601</v>
       </c>
       <c r="F114" t="n">
-        <v>28.4876</v>
+        <v>28.5132</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>20.9288</v>
+        <v>20.9629</v>
       </c>
       <c r="C115" t="n">
-        <v>17.7413</v>
+        <v>17.7593</v>
       </c>
       <c r="D115" t="n">
-        <v>40.3501</v>
+        <v>40.5374</v>
       </c>
       <c r="E115" t="n">
-        <v>16.6883</v>
+        <v>16.7211</v>
       </c>
       <c r="F115" t="n">
-        <v>28.2212</v>
+        <v>28.233</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>20.4661</v>
+        <v>20.4989</v>
       </c>
       <c r="C116" t="n">
-        <v>17.6532</v>
+        <v>17.6632</v>
       </c>
       <c r="D116" t="n">
-        <v>39.9067</v>
+        <v>40.1344</v>
       </c>
       <c r="E116" t="n">
-        <v>16.3584</v>
+        <v>16.3732</v>
       </c>
       <c r="F116" t="n">
-        <v>27.3362</v>
+        <v>27.318</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>19.9436</v>
+        <v>19.9636</v>
       </c>
       <c r="C117" t="n">
-        <v>17.6064</v>
+        <v>17.5521</v>
       </c>
       <c r="D117" t="n">
-        <v>39.7037</v>
+        <v>39.8978</v>
       </c>
       <c r="E117" t="n">
-        <v>16.0263</v>
+        <v>16.0659</v>
       </c>
       <c r="F117" t="n">
-        <v>27.0659</v>
+        <v>27.0731</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>19.4527</v>
+        <v>19.4411</v>
       </c>
       <c r="C118" t="n">
-        <v>17.4498</v>
+        <v>17.4668</v>
       </c>
       <c r="D118" t="n">
-        <v>39.4029</v>
+        <v>39.6067</v>
       </c>
       <c r="E118" t="n">
-        <v>15.7171</v>
+        <v>15.7623</v>
       </c>
       <c r="F118" t="n">
-        <v>26.7819</v>
+        <v>26.7463</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>18.9422</v>
+        <v>18.9535</v>
       </c>
       <c r="C119" t="n">
-        <v>17.3589</v>
+        <v>17.3673</v>
       </c>
       <c r="D119" t="n">
-        <v>39.2046</v>
+        <v>39.3875</v>
       </c>
       <c r="E119" t="n">
-        <v>15.4095</v>
+        <v>15.461</v>
       </c>
       <c r="F119" t="n">
-        <v>26.4688</v>
+        <v>26.4537</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>18.4243</v>
+        <v>18.4311</v>
       </c>
       <c r="C120" t="n">
-        <v>17.2662</v>
+        <v>17.2717</v>
       </c>
       <c r="D120" t="n">
-        <v>39.0415</v>
+        <v>39.1267</v>
       </c>
       <c r="E120" t="n">
-        <v>15.0865</v>
+        <v>15.1145</v>
       </c>
       <c r="F120" t="n">
-        <v>26.159</v>
+        <v>26.1493</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>17.8924</v>
+        <v>17.8037</v>
       </c>
       <c r="C121" t="n">
-        <v>17.1821</v>
+        <v>17.1806</v>
       </c>
       <c r="D121" t="n">
-        <v>47.4628</v>
+        <v>46.8755</v>
       </c>
       <c r="E121" t="n">
-        <v>20.1436</v>
+        <v>20.1476</v>
       </c>
       <c r="F121" t="n">
-        <v>30.7635</v>
+        <v>30.7602</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>17.2156</v>
+        <v>17.1931</v>
       </c>
       <c r="C122" t="n">
-        <v>18.8686</v>
+        <v>18.8917</v>
       </c>
       <c r="D122" t="n">
-        <v>46.7908</v>
+        <v>46.0189</v>
       </c>
       <c r="E122" t="n">
-        <v>19.6388</v>
+        <v>19.6206</v>
       </c>
       <c r="F122" t="n">
-        <v>29.9271</v>
+        <v>29.8577</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>16.3982</v>
+        <v>16.3409</v>
       </c>
       <c r="C123" t="n">
-        <v>18.7104</v>
+        <v>18.6969</v>
       </c>
       <c r="D123" t="n">
-        <v>46.7003</v>
+        <v>45.4478</v>
       </c>
       <c r="E123" t="n">
-        <v>19.125</v>
+        <v>19.1448</v>
       </c>
       <c r="F123" t="n">
-        <v>29.8268</v>
+        <v>29.6758</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>23.1585</v>
+        <v>23.1723</v>
       </c>
       <c r="C124" t="n">
-        <v>18.4782</v>
+        <v>18.4788</v>
       </c>
       <c r="D124" t="n">
-        <v>45.5566</v>
+        <v>44.8497</v>
       </c>
       <c r="E124" t="n">
-        <v>18.6615</v>
+        <v>18.6625</v>
       </c>
       <c r="F124" t="n">
-        <v>29.7074</v>
+        <v>29.6858</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>22.7972</v>
+        <v>22.778</v>
       </c>
       <c r="C125" t="n">
-        <v>18.3671</v>
+        <v>18.3389</v>
       </c>
       <c r="D125" t="n">
-        <v>45.1501</v>
+        <v>44.5496</v>
       </c>
       <c r="E125" t="n">
-        <v>18.2475</v>
+        <v>18.2504</v>
       </c>
       <c r="F125" t="n">
-        <v>29.0615</v>
+        <v>29.0401</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>22.3872</v>
+        <v>22.3597</v>
       </c>
       <c r="C126" t="n">
-        <v>18.2045</v>
+        <v>18.1684</v>
       </c>
       <c r="D126" t="n">
-        <v>44.879</v>
+        <v>43.5204</v>
       </c>
       <c r="E126" t="n">
-        <v>17.8182</v>
+        <v>17.8457</v>
       </c>
       <c r="F126" t="n">
-        <v>28.7626</v>
+        <v>28.6941</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>21.9491</v>
+        <v>21.9352</v>
       </c>
       <c r="C127" t="n">
-        <v>18.0403</v>
+        <v>18.0526</v>
       </c>
       <c r="D127" t="n">
-        <v>44.3384</v>
+        <v>42.9135</v>
       </c>
       <c r="E127" t="n">
-        <v>17.4397</v>
+        <v>17.4454</v>
       </c>
       <c r="F127" t="n">
-        <v>28.6052</v>
+        <v>28.3849</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>21.4985</v>
+        <v>21.489</v>
       </c>
       <c r="C128" t="n">
-        <v>17.8963</v>
+        <v>17.9061</v>
       </c>
       <c r="D128" t="n">
-        <v>43.7273</v>
+        <v>42.8889</v>
       </c>
       <c r="E128" t="n">
-        <v>17.0891</v>
+        <v>17.102</v>
       </c>
       <c r="F128" t="n">
-        <v>28.7725</v>
+        <v>28.5649</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>21.0367</v>
+        <v>21.0392</v>
       </c>
       <c r="C129" t="n">
-        <v>17.8027</v>
+        <v>17.7581</v>
       </c>
       <c r="D129" t="n">
-        <v>43.2943</v>
+        <v>42.3755</v>
       </c>
       <c r="E129" t="n">
-        <v>16.7568</v>
+        <v>16.7832</v>
       </c>
       <c r="F129" t="n">
-        <v>28.4673</v>
+        <v>28.2819</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>20.5798</v>
+        <v>20.5667</v>
       </c>
       <c r="C130" t="n">
-        <v>17.6755</v>
+        <v>17.6723</v>
       </c>
       <c r="D130" t="n">
-        <v>42.8724</v>
+        <v>42.0554</v>
       </c>
       <c r="E130" t="n">
-        <v>16.4261</v>
+        <v>16.4337</v>
       </c>
       <c r="F130" t="n">
-        <v>27.5611</v>
+        <v>27.3671</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>20.1379</v>
+        <v>20.0884</v>
       </c>
       <c r="C131" t="n">
-        <v>17.5595</v>
+        <v>17.5426</v>
       </c>
       <c r="D131" t="n">
-        <v>42.4668</v>
+        <v>41.6161</v>
       </c>
       <c r="E131" t="n">
-        <v>16.1038</v>
+        <v>16.1086</v>
       </c>
       <c r="F131" t="n">
-        <v>27.2666</v>
+        <v>27.0741</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>19.5725</v>
+        <v>19.611</v>
       </c>
       <c r="C132" t="n">
-        <v>17.435</v>
+        <v>17.4393</v>
       </c>
       <c r="D132" t="n">
-        <v>42.0287</v>
+        <v>41.3025</v>
       </c>
       <c r="E132" t="n">
-        <v>15.7905</v>
+        <v>15.7976</v>
       </c>
       <c r="F132" t="n">
-        <v>26.8401</v>
+        <v>26.788</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>19.0618</v>
+        <v>19.0936</v>
       </c>
       <c r="C133" t="n">
-        <v>17.3904</v>
+        <v>17.367</v>
       </c>
       <c r="D133" t="n">
-        <v>41.7585</v>
+        <v>41.018</v>
       </c>
       <c r="E133" t="n">
-        <v>15.4821</v>
+        <v>15.4997</v>
       </c>
       <c r="F133" t="n">
-        <v>26.9954</v>
+        <v>26.4914</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>18.5316</v>
+        <v>18.5556</v>
       </c>
       <c r="C134" t="n">
-        <v>17.291</v>
+        <v>17.2726</v>
       </c>
       <c r="D134" t="n">
-        <v>41.5745</v>
+        <v>40.8678</v>
       </c>
       <c r="E134" t="n">
-        <v>15.1663</v>
+        <v>15.1734</v>
       </c>
       <c r="F134" t="n">
-        <v>26.2317</v>
+        <v>26.1997</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>17.9423</v>
+        <v>17.9923</v>
       </c>
       <c r="C135" t="n">
-        <v>17.2243</v>
+        <v>17.2082</v>
       </c>
       <c r="D135" t="n">
-        <v>48.3717</v>
+        <v>47.4387</v>
       </c>
       <c r="E135" t="n">
-        <v>20.1919</v>
+        <v>20.1607</v>
       </c>
       <c r="F135" t="n">
-        <v>30.3675</v>
+        <v>30.2099</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>17.3936</v>
+        <v>17.3805</v>
       </c>
       <c r="C136" t="n">
-        <v>18.9756</v>
+        <v>18.916</v>
       </c>
       <c r="D136" t="n">
-        <v>46.3101</v>
+        <v>46.9382</v>
       </c>
       <c r="E136" t="n">
-        <v>19.7175</v>
+        <v>19.7238</v>
       </c>
       <c r="F136" t="n">
-        <v>30.115</v>
+        <v>30.1834</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>16.5481</v>
+        <v>16.5164</v>
       </c>
       <c r="C137" t="n">
-        <v>18.8593</v>
+        <v>18.8444</v>
       </c>
       <c r="D137" t="n">
-        <v>45.6776</v>
+        <v>46.2137</v>
       </c>
       <c r="E137" t="n">
-        <v>19.2004</v>
+        <v>19.2275</v>
       </c>
       <c r="F137" t="n">
-        <v>29.6537</v>
+        <v>29.5828</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>23.2493</v>
+        <v>23.2501</v>
       </c>
       <c r="C138" t="n">
-        <v>18.5429</v>
+        <v>18.5219</v>
       </c>
       <c r="D138" t="n">
-        <v>45.0672</v>
+        <v>46.0168</v>
       </c>
       <c r="E138" t="n">
-        <v>18.7391</v>
+        <v>18.7438</v>
       </c>
       <c r="F138" t="n">
-        <v>29.2611</v>
+        <v>29.2039</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>22.8965</v>
+        <v>22.8794</v>
       </c>
       <c r="C139" t="n">
-        <v>18.4904</v>
+        <v>18.4866</v>
       </c>
       <c r="D139" t="n">
-        <v>44.675</v>
+        <v>45.7559</v>
       </c>
       <c r="E139" t="n">
-        <v>18.3347</v>
+        <v>18.3066</v>
       </c>
       <c r="F139" t="n">
-        <v>29.0953</v>
+        <v>28.9287</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>22.4946</v>
+        <v>22.4944</v>
       </c>
       <c r="C140" t="n">
-        <v>18.3283</v>
+        <v>18.3133</v>
       </c>
       <c r="D140" t="n">
-        <v>44.1297</v>
+        <v>44.9456</v>
       </c>
       <c r="E140" t="n">
-        <v>17.9105</v>
+        <v>17.9077</v>
       </c>
       <c r="F140" t="n">
-        <v>28.8227</v>
+        <v>28.6296</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>22.0732</v>
+        <v>22.0657</v>
       </c>
       <c r="C141" t="n">
-        <v>18.1907</v>
+        <v>18.1762</v>
       </c>
       <c r="D141" t="n">
-        <v>43.567</v>
+        <v>44.0778</v>
       </c>
       <c r="E141" t="n">
-        <v>17.5425</v>
+        <v>17.5215</v>
       </c>
       <c r="F141" t="n">
-        <v>28.3733</v>
+        <v>28.3296</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>21.6209</v>
+        <v>21.6222</v>
       </c>
       <c r="C142" t="n">
-        <v>17.917</v>
+        <v>17.9214</v>
       </c>
       <c r="D142" t="n">
-        <v>42.8981</v>
+        <v>43.3401</v>
       </c>
       <c r="E142" t="n">
-        <v>17.1565</v>
+        <v>17.1601</v>
       </c>
       <c r="F142" t="n">
-        <v>28.0543</v>
+        <v>28.1157</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>21.1583</v>
+        <v>21.1381</v>
       </c>
       <c r="C143" t="n">
-        <v>17.9074</v>
+        <v>17.8694</v>
       </c>
       <c r="D143" t="n">
-        <v>42.3446</v>
+        <v>42.7044</v>
       </c>
       <c r="E143" t="n">
-        <v>16.8419</v>
+        <v>16.8231</v>
       </c>
       <c r="F143" t="n">
-        <v>27.7784</v>
+        <v>27.8675</v>
       </c>
     </row>
   </sheetData>

--- a/clang-x64/Running erasure.xlsx
+++ b/clang-x64/Running erasure.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>18.1973</v>
+        <v>18.0815</v>
       </c>
       <c r="C2" t="n">
-        <v>13.1224</v>
+        <v>13.1828</v>
       </c>
       <c r="D2" t="n">
-        <v>30.6769</v>
+        <v>30.5528</v>
       </c>
       <c r="E2" t="n">
-        <v>12.6967</v>
+        <v>12.5875</v>
       </c>
       <c r="F2" t="n">
-        <v>26.4006</v>
+        <v>26.4511</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>18.1562</v>
+        <v>17.9983</v>
       </c>
       <c r="C3" t="n">
-        <v>13.3414</v>
+        <v>13.4973</v>
       </c>
       <c r="D3" t="n">
-        <v>30.9002</v>
+        <v>30.8458</v>
       </c>
       <c r="E3" t="n">
-        <v>12.6568</v>
+        <v>12.6753</v>
       </c>
       <c r="F3" t="n">
-        <v>26.3232</v>
+        <v>26.1548</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>17.5354</v>
+        <v>17.666</v>
       </c>
       <c r="C4" t="n">
-        <v>13.7231</v>
+        <v>13.7908</v>
       </c>
       <c r="D4" t="n">
-        <v>30.9897</v>
+        <v>31.0324</v>
       </c>
       <c r="E4" t="n">
-        <v>12.4155</v>
+        <v>12.4033</v>
       </c>
       <c r="F4" t="n">
-        <v>26.0863</v>
+        <v>25.9896</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>17.1779</v>
+        <v>17.129</v>
       </c>
       <c r="C5" t="n">
-        <v>13.8058</v>
+        <v>13.8225</v>
       </c>
       <c r="D5" t="n">
-        <v>31.2362</v>
+        <v>31.2364</v>
       </c>
       <c r="E5" t="n">
-        <v>12.2613</v>
+        <v>19.8777</v>
       </c>
       <c r="F5" t="n">
-        <v>25.2908</v>
+        <v>30.6088</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>16.5482</v>
+        <v>16.6968</v>
       </c>
       <c r="C6" t="n">
-        <v>14.1375</v>
+        <v>14.0734</v>
       </c>
       <c r="D6" t="n">
-        <v>31.2835</v>
+        <v>31.2815</v>
       </c>
       <c r="E6" t="n">
-        <v>12.3689</v>
+        <v>19.151</v>
       </c>
       <c r="F6" t="n">
-        <v>25.1268</v>
+        <v>30.1665</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>16.282</v>
+        <v>16.0907</v>
       </c>
       <c r="C7" t="n">
-        <v>14.3212</v>
+        <v>14.358</v>
       </c>
       <c r="D7" t="n">
-        <v>30.2085</v>
+        <v>30.2059</v>
       </c>
       <c r="E7" t="n">
-        <v>18.8147</v>
+        <v>18.754</v>
       </c>
       <c r="F7" t="n">
-        <v>30.446</v>
+        <v>30.2272</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>15.8395</v>
+        <v>15.6611</v>
       </c>
       <c r="C8" t="n">
-        <v>15.5827</v>
+        <v>15.5905</v>
       </c>
       <c r="D8" t="n">
-        <v>30.2294</v>
+        <v>30.0918</v>
       </c>
       <c r="E8" t="n">
-        <v>18.3353</v>
+        <v>18.338</v>
       </c>
       <c r="F8" t="n">
-        <v>29.902</v>
+        <v>29.7643</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>15.0721</v>
+        <v>14.8882</v>
       </c>
       <c r="C9" t="n">
-        <v>15.5704</v>
+        <v>15.6978</v>
       </c>
       <c r="D9" t="n">
-        <v>30.347</v>
+        <v>30.2357</v>
       </c>
       <c r="E9" t="n">
-        <v>17.7949</v>
+        <v>17.9596</v>
       </c>
       <c r="F9" t="n">
-        <v>29.5464</v>
+        <v>29.4959</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>21.7068</v>
+        <v>21.6509</v>
       </c>
       <c r="C10" t="n">
-        <v>15.7898</v>
+        <v>15.8818</v>
       </c>
       <c r="D10" t="n">
-        <v>30.4484</v>
+        <v>30.4822</v>
       </c>
       <c r="E10" t="n">
-        <v>17.4833</v>
+        <v>17.4686</v>
       </c>
       <c r="F10" t="n">
-        <v>28.8196</v>
+        <v>29.1652</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>21.4139</v>
+        <v>21.4021</v>
       </c>
       <c r="C11" t="n">
-        <v>15.9035</v>
+        <v>15.9616</v>
       </c>
       <c r="D11" t="n">
-        <v>30.5966</v>
+        <v>30.6006</v>
       </c>
       <c r="E11" t="n">
-        <v>17.1656</v>
+        <v>17.0854</v>
       </c>
       <c r="F11" t="n">
-        <v>28.985</v>
+        <v>29.1222</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>21.0861</v>
+        <v>21.0041</v>
       </c>
       <c r="C12" t="n">
-        <v>16.0411</v>
+        <v>16.0586</v>
       </c>
       <c r="D12" t="n">
-        <v>30.6833</v>
+        <v>31.0775</v>
       </c>
       <c r="E12" t="n">
-        <v>16.7298</v>
+        <v>16.6109</v>
       </c>
       <c r="F12" t="n">
-        <v>28.2783</v>
+        <v>28.246</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>20.6585</v>
+        <v>20.6571</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3036</v>
+        <v>16.1347</v>
       </c>
       <c r="D13" t="n">
-        <v>30.879</v>
+        <v>31.1994</v>
       </c>
       <c r="E13" t="n">
-        <v>16.4973</v>
+        <v>16.413</v>
       </c>
       <c r="F13" t="n">
-        <v>28.0877</v>
+        <v>28.0496</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>20.4456</v>
+        <v>20.4914</v>
       </c>
       <c r="C14" t="n">
-        <v>16.2531</v>
+        <v>16.3571</v>
       </c>
       <c r="D14" t="n">
-        <v>31.069</v>
+        <v>31.4612</v>
       </c>
       <c r="E14" t="n">
-        <v>16.2445</v>
+        <v>16.1903</v>
       </c>
       <c r="F14" t="n">
-        <v>27.696</v>
+        <v>27.5591</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>20.0315</v>
+        <v>20.1682</v>
       </c>
       <c r="C15" t="n">
-        <v>16.3783</v>
+        <v>16.4861</v>
       </c>
       <c r="D15" t="n">
-        <v>31.1139</v>
+        <v>31.5003</v>
       </c>
       <c r="E15" t="n">
-        <v>15.87</v>
+        <v>15.917</v>
       </c>
       <c r="F15" t="n">
-        <v>27.4129</v>
+        <v>27.3936</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>19.6848</v>
+        <v>19.8086</v>
       </c>
       <c r="C16" t="n">
-        <v>16.468</v>
+        <v>16.5214</v>
       </c>
       <c r="D16" t="n">
-        <v>31.5888</v>
+        <v>31.5884</v>
       </c>
       <c r="E16" t="n">
-        <v>15.6191</v>
+        <v>15.5837</v>
       </c>
       <c r="F16" t="n">
-        <v>27.0265</v>
+        <v>26.9499</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>19.2393</v>
+        <v>19.2943</v>
       </c>
       <c r="C17" t="n">
-        <v>16.4466</v>
+        <v>16.3403</v>
       </c>
       <c r="D17" t="n">
-        <v>31.8543</v>
+        <v>31.7362</v>
       </c>
       <c r="E17" t="n">
-        <v>15.268</v>
+        <v>15.273</v>
       </c>
       <c r="F17" t="n">
-        <v>26.6056</v>
+        <v>26.6041</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>18.9317</v>
+        <v>18.9016</v>
       </c>
       <c r="C18" t="n">
-        <v>16.4619</v>
+        <v>16.4878</v>
       </c>
       <c r="D18" t="n">
-        <v>32.0249</v>
+        <v>31.9521</v>
       </c>
       <c r="E18" t="n">
-        <v>15.0156</v>
+        <v>14.9881</v>
       </c>
       <c r="F18" t="n">
-        <v>26.3793</v>
+        <v>26.3919</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>18.376</v>
+        <v>18.4529</v>
       </c>
       <c r="C19" t="n">
-        <v>16.5457</v>
+        <v>16.5017</v>
       </c>
       <c r="D19" t="n">
-        <v>32.1463</v>
+        <v>32.1302</v>
       </c>
       <c r="E19" t="n">
-        <v>14.6226</v>
+        <v>14.6222</v>
       </c>
       <c r="F19" t="n">
-        <v>26.029</v>
+        <v>26.0207</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>17.8673</v>
+        <v>17.8311</v>
       </c>
       <c r="C20" t="n">
-        <v>16.7084</v>
+        <v>16.7201</v>
       </c>
       <c r="D20" t="n">
-        <v>32.1952</v>
+        <v>32.2854</v>
       </c>
       <c r="E20" t="n">
-        <v>14.3172</v>
+        <v>20.3655</v>
       </c>
       <c r="F20" t="n">
-        <v>26.3955</v>
+        <v>31.0536</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>17.258</v>
+        <v>17.365</v>
       </c>
       <c r="C21" t="n">
-        <v>16.6168</v>
+        <v>16.5318</v>
       </c>
       <c r="D21" t="n">
-        <v>31.5243</v>
+        <v>31.3398</v>
       </c>
       <c r="E21" t="n">
-        <v>19.9063</v>
+        <v>19.9496</v>
       </c>
       <c r="F21" t="n">
-        <v>30.9315</v>
+        <v>30.9289</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>16.7772</v>
+        <v>16.626</v>
       </c>
       <c r="C22" t="n">
-        <v>18.0092</v>
+        <v>17.9928</v>
       </c>
       <c r="D22" t="n">
-        <v>31.4482</v>
+        <v>31.5335</v>
       </c>
       <c r="E22" t="n">
-        <v>19.3587</v>
+        <v>19.3912</v>
       </c>
       <c r="F22" t="n">
-        <v>30.3452</v>
+        <v>30.5919</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>16.0963</v>
+        <v>16.0053</v>
       </c>
       <c r="C23" t="n">
-        <v>17.995</v>
+        <v>17.9231</v>
       </c>
       <c r="D23" t="n">
-        <v>31.2935</v>
+        <v>31.47</v>
       </c>
       <c r="E23" t="n">
-        <v>18.9106</v>
+        <v>18.9175</v>
       </c>
       <c r="F23" t="n">
-        <v>29.5718</v>
+        <v>30.1706</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>22.4451</v>
+        <v>22.5098</v>
       </c>
       <c r="C24" t="n">
-        <v>17.8143</v>
+        <v>17.8219</v>
       </c>
       <c r="D24" t="n">
-        <v>31.173</v>
+        <v>31.3218</v>
       </c>
       <c r="E24" t="n">
-        <v>18.4491</v>
+        <v>18.5126</v>
       </c>
       <c r="F24" t="n">
-        <v>29.2842</v>
+        <v>29.6709</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>22.1709</v>
+        <v>22.1768</v>
       </c>
       <c r="C25" t="n">
-        <v>17.7602</v>
+        <v>17.8118</v>
       </c>
       <c r="D25" t="n">
-        <v>31.5852</v>
+        <v>31.625</v>
       </c>
       <c r="E25" t="n">
-        <v>17.9992</v>
+        <v>17.9574</v>
       </c>
       <c r="F25" t="n">
-        <v>28.8749</v>
+        <v>28.8972</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>21.8023</v>
+        <v>21.8184</v>
       </c>
       <c r="C26" t="n">
-        <v>17.7143</v>
+        <v>17.671</v>
       </c>
       <c r="D26" t="n">
-        <v>31.7907</v>
+        <v>31.6559</v>
       </c>
       <c r="E26" t="n">
-        <v>17.6007</v>
+        <v>17.6111</v>
       </c>
       <c r="F26" t="n">
-        <v>28.6307</v>
+        <v>28.5307</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>21.5134</v>
+        <v>21.6685</v>
       </c>
       <c r="C27" t="n">
-        <v>17.5791</v>
+        <v>17.6865</v>
       </c>
       <c r="D27" t="n">
-        <v>31.9219</v>
+        <v>31.8361</v>
       </c>
       <c r="E27" t="n">
-        <v>17.2019</v>
+        <v>17.1405</v>
       </c>
       <c r="F27" t="n">
-        <v>28.2889</v>
+        <v>28.2569</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>21.2167</v>
+        <v>21.2615</v>
       </c>
       <c r="C28" t="n">
-        <v>17.6292</v>
+        <v>17.6376</v>
       </c>
       <c r="D28" t="n">
-        <v>31.7378</v>
+        <v>31.8391</v>
       </c>
       <c r="E28" t="n">
-        <v>16.8383</v>
+        <v>16.9641</v>
       </c>
       <c r="F28" t="n">
-        <v>27.9677</v>
+        <v>27.9271</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>20.7982</v>
+        <v>20.862</v>
       </c>
       <c r="C29" t="n">
-        <v>17.4855</v>
+        <v>17.4766</v>
       </c>
       <c r="D29" t="n">
-        <v>32.0767</v>
+        <v>31.8896</v>
       </c>
       <c r="E29" t="n">
-        <v>16.4286</v>
+        <v>16.46</v>
       </c>
       <c r="F29" t="n">
-        <v>27.6752</v>
+        <v>27.6547</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>20.3693</v>
+        <v>20.449</v>
       </c>
       <c r="C30" t="n">
-        <v>17.5571</v>
+        <v>17.502</v>
       </c>
       <c r="D30" t="n">
-        <v>32.0182</v>
+        <v>32.1074</v>
       </c>
       <c r="E30" t="n">
-        <v>16.113</v>
+        <v>16.106</v>
       </c>
       <c r="F30" t="n">
-        <v>27.4847</v>
+        <v>27.4511</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>20.0081</v>
+        <v>19.9411</v>
       </c>
       <c r="C31" t="n">
-        <v>17.424</v>
+        <v>17.4056</v>
       </c>
       <c r="D31" t="n">
-        <v>32.0602</v>
+        <v>32.2489</v>
       </c>
       <c r="E31" t="n">
-        <v>15.8332</v>
+        <v>15.8043</v>
       </c>
       <c r="F31" t="n">
-        <v>27.0614</v>
+        <v>27.0618</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>19.5291</v>
+        <v>19.5287</v>
       </c>
       <c r="C32" t="n">
-        <v>17.4065</v>
+        <v>17.4052</v>
       </c>
       <c r="D32" t="n">
-        <v>32.2376</v>
+        <v>32.2763</v>
       </c>
       <c r="E32" t="n">
-        <v>15.4494</v>
+        <v>15.5367</v>
       </c>
       <c r="F32" t="n">
-        <v>26.7707</v>
+        <v>26.7854</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>19.0179</v>
+        <v>18.9673</v>
       </c>
       <c r="C33" t="n">
-        <v>17.3197</v>
+        <v>17.345</v>
       </c>
       <c r="D33" t="n">
-        <v>32.4815</v>
+        <v>32.495</v>
       </c>
       <c r="E33" t="n">
-        <v>15.2327</v>
+        <v>15.2271</v>
       </c>
       <c r="F33" t="n">
-        <v>26.9632</v>
+        <v>26.9966</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>18.4187</v>
+        <v>18.3922</v>
       </c>
       <c r="C34" t="n">
-        <v>17.2792</v>
+        <v>17.2161</v>
       </c>
       <c r="D34" t="n">
-        <v>32.5141</v>
+        <v>32.6076</v>
       </c>
       <c r="E34" t="n">
-        <v>14.8981</v>
+        <v>20.6758</v>
       </c>
       <c r="F34" t="n">
-        <v>26.7152</v>
+        <v>31.3393</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>17.9146</v>
+        <v>17.9676</v>
       </c>
       <c r="C35" t="n">
-        <v>17.1953</v>
+        <v>17.1421</v>
       </c>
       <c r="D35" t="n">
-        <v>31.7177</v>
+        <v>31.5501</v>
       </c>
       <c r="E35" t="n">
-        <v>20.1125</v>
+        <v>19.9935</v>
       </c>
       <c r="F35" t="n">
-        <v>31.0045</v>
+        <v>30.9388</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>17.3476</v>
+        <v>17.2976</v>
       </c>
       <c r="C36" t="n">
-        <v>17.144</v>
+        <v>17.1135</v>
       </c>
       <c r="D36" t="n">
-        <v>31.6224</v>
+        <v>31.8104</v>
       </c>
       <c r="E36" t="n">
-        <v>19.6312</v>
+        <v>19.6268</v>
       </c>
       <c r="F36" t="n">
-        <v>30.6269</v>
+        <v>30.7151</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>16.6522</v>
+        <v>16.6135</v>
       </c>
       <c r="C37" t="n">
-        <v>18.4232</v>
+        <v>18.3835</v>
       </c>
       <c r="D37" t="n">
-        <v>31.7898</v>
+        <v>31.7398</v>
       </c>
       <c r="E37" t="n">
-        <v>19.0261</v>
+        <v>19.0553</v>
       </c>
       <c r="F37" t="n">
-        <v>30.2881</v>
+        <v>30.3244</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>23.0223</v>
+        <v>23.0869</v>
       </c>
       <c r="C38" t="n">
-        <v>18.2335</v>
+        <v>18.2402</v>
       </c>
       <c r="D38" t="n">
-        <v>31.6379</v>
+        <v>31.6608</v>
       </c>
       <c r="E38" t="n">
-        <v>18.7028</v>
+        <v>18.649</v>
       </c>
       <c r="F38" t="n">
-        <v>29.8481</v>
+        <v>29.986</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>22.8177</v>
+        <v>22.7855</v>
       </c>
       <c r="C39" t="n">
-        <v>18.1746</v>
+        <v>18.1448</v>
       </c>
       <c r="D39" t="n">
-        <v>31.4786</v>
+        <v>31.5755</v>
       </c>
       <c r="E39" t="n">
-        <v>18.1686</v>
+        <v>18.1969</v>
       </c>
       <c r="F39" t="n">
-        <v>29.6266</v>
+        <v>29.5986</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>22.4424</v>
+        <v>22.4629</v>
       </c>
       <c r="C40" t="n">
-        <v>18.1126</v>
+        <v>18.0032</v>
       </c>
       <c r="D40" t="n">
-        <v>31.725</v>
+        <v>31.77</v>
       </c>
       <c r="E40" t="n">
-        <v>17.8297</v>
+        <v>17.8221</v>
       </c>
       <c r="F40" t="n">
-        <v>29.3023</v>
+        <v>29.2626</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>22.0962</v>
+        <v>22.0486</v>
       </c>
       <c r="C41" t="n">
-        <v>17.8897</v>
+        <v>17.87</v>
       </c>
       <c r="D41" t="n">
-        <v>31.9773</v>
+        <v>31.8179</v>
       </c>
       <c r="E41" t="n">
-        <v>17.462</v>
+        <v>17.4226</v>
       </c>
       <c r="F41" t="n">
-        <v>28.9797</v>
+        <v>29.0031</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>21.6554</v>
+        <v>21.5733</v>
       </c>
       <c r="C42" t="n">
-        <v>17.7375</v>
+        <v>17.7254</v>
       </c>
       <c r="D42" t="n">
-        <v>31.8105</v>
+        <v>31.7541</v>
       </c>
       <c r="E42" t="n">
-        <v>17.0506</v>
+        <v>17.0699</v>
       </c>
       <c r="F42" t="n">
-        <v>28.6324</v>
+        <v>28.6796</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>21.1576</v>
+        <v>21.1774</v>
       </c>
       <c r="C43" t="n">
-        <v>17.5798</v>
+        <v>17.5883</v>
       </c>
       <c r="D43" t="n">
-        <v>32.0438</v>
+        <v>31.8556</v>
       </c>
       <c r="E43" t="n">
-        <v>16.7442</v>
+        <v>16.7255</v>
       </c>
       <c r="F43" t="n">
-        <v>28.3382</v>
+        <v>28.329</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>20.7011</v>
+        <v>20.7001</v>
       </c>
       <c r="C44" t="n">
-        <v>17.5007</v>
+        <v>17.5413</v>
       </c>
       <c r="D44" t="n">
-        <v>32.0217</v>
+        <v>32.0521</v>
       </c>
       <c r="E44" t="n">
-        <v>16.4092</v>
+        <v>16.4041</v>
       </c>
       <c r="F44" t="n">
-        <v>28.1051</v>
+        <v>28.0765</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>20.274</v>
+        <v>20.232</v>
       </c>
       <c r="C45" t="n">
-        <v>17.4299</v>
+        <v>17.4761</v>
       </c>
       <c r="D45" t="n">
-        <v>32.1862</v>
+        <v>32.1063</v>
       </c>
       <c r="E45" t="n">
-        <v>16.0828</v>
+        <v>16.1033</v>
       </c>
       <c r="F45" t="n">
-        <v>27.8754</v>
+        <v>27.8034</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>19.8296</v>
+        <v>19.9023</v>
       </c>
       <c r="C46" t="n">
-        <v>17.3533</v>
+        <v>17.3682</v>
       </c>
       <c r="D46" t="n">
-        <v>32.2173</v>
+        <v>32.241</v>
       </c>
       <c r="E46" t="n">
-        <v>15.7543</v>
+        <v>15.7708</v>
       </c>
       <c r="F46" t="n">
-        <v>27.5319</v>
+        <v>27.5459</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>19.3179</v>
+        <v>19.3312</v>
       </c>
       <c r="C47" t="n">
-        <v>17.3041</v>
+        <v>17.2684</v>
       </c>
       <c r="D47" t="n">
-        <v>32.4653</v>
+        <v>32.4719</v>
       </c>
       <c r="E47" t="n">
-        <v>15.4969</v>
+        <v>15.485</v>
       </c>
       <c r="F47" t="n">
-        <v>27.2257</v>
+        <v>27.193</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>18.8713</v>
+        <v>18.8381</v>
       </c>
       <c r="C48" t="n">
-        <v>17.215</v>
+        <v>17.2136</v>
       </c>
       <c r="D48" t="n">
-        <v>32.5349</v>
+        <v>32.4853</v>
       </c>
       <c r="E48" t="n">
-        <v>15.2074</v>
+        <v>20.6561</v>
       </c>
       <c r="F48" t="n">
-        <v>26.8485</v>
+        <v>31.27</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>18.2599</v>
+        <v>18.2989</v>
       </c>
       <c r="C49" t="n">
-        <v>17.1351</v>
+        <v>17.158</v>
       </c>
       <c r="D49" t="n">
-        <v>32.7167</v>
+        <v>32.3882</v>
       </c>
       <c r="E49" t="n">
-        <v>14.817</v>
+        <v>20.1855</v>
       </c>
       <c r="F49" t="n">
-        <v>26.577</v>
+        <v>30.9235</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>17.7394</v>
+        <v>17.8005</v>
       </c>
       <c r="C50" t="n">
-        <v>17.0996</v>
+        <v>17.0817</v>
       </c>
       <c r="D50" t="n">
-        <v>31.8033</v>
+        <v>31.3669</v>
       </c>
       <c r="E50" t="n">
-        <v>19.7639</v>
+        <v>19.7578</v>
       </c>
       <c r="F50" t="n">
-        <v>30.6224</v>
+        <v>30.6715</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>16.9576</v>
+        <v>16.9456</v>
       </c>
       <c r="C51" t="n">
-        <v>18.4638</v>
+        <v>18.4636</v>
       </c>
       <c r="D51" t="n">
-        <v>32.0555</v>
+        <v>31.8231</v>
       </c>
       <c r="E51" t="n">
-        <v>19.2808</v>
+        <v>19.3098</v>
       </c>
       <c r="F51" t="n">
-        <v>30.305</v>
+        <v>30.217</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>16.0561</v>
+        <v>16.1966</v>
       </c>
       <c r="C52" t="n">
-        <v>18.3398</v>
+        <v>18.3144</v>
       </c>
       <c r="D52" t="n">
-        <v>31.6503</v>
+        <v>31.9753</v>
       </c>
       <c r="E52" t="n">
-        <v>18.7568</v>
+        <v>18.7986</v>
       </c>
       <c r="F52" t="n">
-        <v>29.9487</v>
+        <v>29.9842</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>23.0144</v>
+        <v>22.9801</v>
       </c>
       <c r="C53" t="n">
-        <v>18.1772</v>
+        <v>18.1738</v>
       </c>
       <c r="D53" t="n">
-        <v>31.7485</v>
+        <v>32.0478</v>
       </c>
       <c r="E53" t="n">
-        <v>18.367</v>
+        <v>18.3495</v>
       </c>
       <c r="F53" t="n">
-        <v>29.2138</v>
+        <v>29.6444</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>22.7085</v>
+        <v>22.6064</v>
       </c>
       <c r="C54" t="n">
-        <v>18.0622</v>
+        <v>18.0276</v>
       </c>
       <c r="D54" t="n">
-        <v>32.2927</v>
+        <v>32.1192</v>
       </c>
       <c r="E54" t="n">
-        <v>17.9716</v>
+        <v>17.9561</v>
       </c>
       <c r="F54" t="n">
-        <v>29.3346</v>
+        <v>29.4099</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>22.288</v>
+        <v>22.2305</v>
       </c>
       <c r="C55" t="n">
-        <v>17.9558</v>
+        <v>17.9545</v>
       </c>
       <c r="D55" t="n">
-        <v>32.4652</v>
+        <v>32.2068</v>
       </c>
       <c r="E55" t="n">
-        <v>17.6285</v>
+        <v>17.637</v>
       </c>
       <c r="F55" t="n">
-        <v>29.0669</v>
+        <v>29.1112</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>21.8279</v>
+        <v>21.8284</v>
       </c>
       <c r="C56" t="n">
-        <v>17.8141</v>
+        <v>17.7926</v>
       </c>
       <c r="D56" t="n">
-        <v>32.3551</v>
+        <v>32.5334</v>
       </c>
       <c r="E56" t="n">
-        <v>17.2468</v>
+        <v>17.2843</v>
       </c>
       <c r="F56" t="n">
-        <v>28.3198</v>
+        <v>28.7588</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>21.3769</v>
+        <v>21.3749</v>
       </c>
       <c r="C57" t="n">
-        <v>17.7081</v>
+        <v>17.7272</v>
       </c>
       <c r="D57" t="n">
-        <v>32.4327</v>
+        <v>32.7146</v>
       </c>
       <c r="E57" t="n">
-        <v>16.9049</v>
+        <v>16.9295</v>
       </c>
       <c r="F57" t="n">
-        <v>27.8952</v>
+        <v>28.4682</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>20.9495</v>
+        <v>20.9202</v>
       </c>
       <c r="C58" t="n">
-        <v>17.6028</v>
+        <v>17.5852</v>
       </c>
       <c r="D58" t="n">
-        <v>33.045</v>
+        <v>32.5668</v>
       </c>
       <c r="E58" t="n">
-        <v>16.6029</v>
+        <v>16.5874</v>
       </c>
       <c r="F58" t="n">
-        <v>27.6867</v>
+        <v>27.6627</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>20.4658</v>
+        <v>20.4836</v>
       </c>
       <c r="C59" t="n">
-        <v>17.5229</v>
+        <v>17.5151</v>
       </c>
       <c r="D59" t="n">
-        <v>33.1341</v>
+        <v>32.7751</v>
       </c>
       <c r="E59" t="n">
-        <v>16.2901</v>
+        <v>16.2635</v>
       </c>
       <c r="F59" t="n">
-        <v>27.3332</v>
+        <v>27.2942</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>19.9278</v>
+        <v>19.9365</v>
       </c>
       <c r="C60" t="n">
-        <v>17.4511</v>
+        <v>17.4474</v>
       </c>
       <c r="D60" t="n">
-        <v>33.5165</v>
+        <v>33.1077</v>
       </c>
       <c r="E60" t="n">
-        <v>15.9691</v>
+        <v>15.9812</v>
       </c>
       <c r="F60" t="n">
-        <v>26.9743</v>
+        <v>27.028</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>19.4944</v>
+        <v>19.4983</v>
       </c>
       <c r="C61" t="n">
-        <v>17.3362</v>
+        <v>17.3606</v>
       </c>
       <c r="D61" t="n">
-        <v>33.7815</v>
+        <v>33.7275</v>
       </c>
       <c r="E61" t="n">
-        <v>15.672</v>
+        <v>15.6751</v>
       </c>
       <c r="F61" t="n">
-        <v>27.2905</v>
+        <v>27.2872</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>18.9749</v>
+        <v>18.9572</v>
       </c>
       <c r="C62" t="n">
-        <v>17.2723</v>
+        <v>17.2642</v>
       </c>
       <c r="D62" t="n">
-        <v>33.9951</v>
+        <v>34.114</v>
       </c>
       <c r="E62" t="n">
-        <v>15.3635</v>
+        <v>15.3522</v>
       </c>
       <c r="F62" t="n">
-        <v>26.4159</v>
+        <v>27.0581</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>18.4436</v>
+        <v>18.4479</v>
       </c>
       <c r="C63" t="n">
-        <v>17.2312</v>
+        <v>17.2564</v>
       </c>
       <c r="D63" t="n">
-        <v>34.3974</v>
+        <v>34.4234</v>
       </c>
       <c r="E63" t="n">
-        <v>15.01</v>
+        <v>21.2019</v>
       </c>
       <c r="F63" t="n">
-        <v>26.0838</v>
+        <v>30.8087</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>17.7679</v>
+        <v>17.8419</v>
       </c>
       <c r="C64" t="n">
-        <v>17.1452</v>
+        <v>17.1849</v>
       </c>
       <c r="D64" t="n">
-        <v>38.3569</v>
+        <v>37.9381</v>
       </c>
       <c r="E64" t="n">
-        <v>20.879</v>
+        <v>20.8226</v>
       </c>
       <c r="F64" t="n">
-        <v>30.3837</v>
+        <v>30.4152</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>17.1412</v>
+        <v>17.1636</v>
       </c>
       <c r="C65" t="n">
-        <v>18.743</v>
+        <v>18.7501</v>
       </c>
       <c r="D65" t="n">
-        <v>38.3356</v>
+        <v>38.1899</v>
       </c>
       <c r="E65" t="n">
         <v>20.4047</v>
       </c>
       <c r="F65" t="n">
-        <v>30.0757</v>
+        <v>30.093</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>16.391</v>
+        <v>16.3547</v>
       </c>
       <c r="C66" t="n">
-        <v>18.5206</v>
+        <v>18.5194</v>
       </c>
       <c r="D66" t="n">
-        <v>38.6104</v>
+        <v>38.4956</v>
       </c>
       <c r="E66" t="n">
-        <v>19.8478</v>
+        <v>19.8474</v>
       </c>
       <c r="F66" t="n">
-        <v>29.6888</v>
+        <v>29.7786</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>23.1633</v>
+        <v>23.1161</v>
       </c>
       <c r="C67" t="n">
-        <v>18.3311</v>
+        <v>18.3436</v>
       </c>
       <c r="D67" t="n">
-        <v>38.837</v>
+        <v>38.6811</v>
       </c>
       <c r="E67" t="n">
-        <v>19.3616</v>
+        <v>19.3295</v>
       </c>
       <c r="F67" t="n">
-        <v>29.3536</v>
+        <v>29.384</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>22.8248</v>
+        <v>22.7879</v>
       </c>
       <c r="C68" t="n">
-        <v>18.2096</v>
+        <v>18.1894</v>
       </c>
       <c r="D68" t="n">
-        <v>39.1429</v>
+        <v>38.9282</v>
       </c>
       <c r="E68" t="n">
-        <v>18.6875</v>
+        <v>18.6141</v>
       </c>
       <c r="F68" t="n">
-        <v>29.0528</v>
+        <v>29.1153</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>22.371</v>
+        <v>22.3801</v>
       </c>
       <c r="C69" t="n">
-        <v>18.0658</v>
+        <v>18.0694</v>
       </c>
       <c r="D69" t="n">
-        <v>39.2098</v>
+        <v>38.9957</v>
       </c>
       <c r="E69" t="n">
-        <v>18.1651</v>
+        <v>18.1103</v>
       </c>
       <c r="F69" t="n">
-        <v>28.7456</v>
+        <v>28.8108</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>21.9846</v>
+        <v>21.9558</v>
       </c>
       <c r="C70" t="n">
-        <v>18.0795</v>
+        <v>18.0632</v>
       </c>
       <c r="D70" t="n">
-        <v>39.321</v>
+        <v>39.2521</v>
       </c>
       <c r="E70" t="n">
-        <v>17.5884</v>
+        <v>17.6572</v>
       </c>
       <c r="F70" t="n">
-        <v>28.3261</v>
+        <v>28.3169</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>21.4906</v>
+        <v>21.5131</v>
       </c>
       <c r="C71" t="n">
-        <v>17.93</v>
+        <v>17.9451</v>
       </c>
       <c r="D71" t="n">
-        <v>39.5896</v>
+        <v>39.4744</v>
       </c>
       <c r="E71" t="n">
-        <v>17.1337</v>
+        <v>17.1672</v>
       </c>
       <c r="F71" t="n">
-        <v>28.2135</v>
+        <v>28.094</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>21.0523</v>
+        <v>21.0743</v>
       </c>
       <c r="C72" t="n">
-        <v>17.8257</v>
+        <v>17.8268</v>
       </c>
       <c r="D72" t="n">
-        <v>39.6532</v>
+        <v>39.7263</v>
       </c>
       <c r="E72" t="n">
-        <v>16.7765</v>
+        <v>16.7463</v>
       </c>
       <c r="F72" t="n">
-        <v>28.5006</v>
+        <v>28.3749</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>20.5503</v>
+        <v>20.581</v>
       </c>
       <c r="C73" t="n">
-        <v>17.7583</v>
+        <v>17.7304</v>
       </c>
       <c r="D73" t="n">
-        <v>39.7772</v>
+        <v>39.6295</v>
       </c>
       <c r="E73" t="n">
-        <v>16.4466</v>
+        <v>16.4385</v>
       </c>
       <c r="F73" t="n">
-        <v>28.2053</v>
+        <v>28.1034</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>20.121</v>
+        <v>20.0595</v>
       </c>
       <c r="C74" t="n">
-        <v>17.6571</v>
+        <v>17.6526</v>
       </c>
       <c r="D74" t="n">
-        <v>39.654</v>
+        <v>39.7279</v>
       </c>
       <c r="E74" t="n">
-        <v>16.1064</v>
+        <v>16.1052</v>
       </c>
       <c r="F74" t="n">
-        <v>27.9324</v>
+        <v>27.8386</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>19.6084</v>
+        <v>19.5809</v>
       </c>
       <c r="C75" t="n">
-        <v>17.5554</v>
+        <v>17.5511</v>
       </c>
       <c r="D75" t="n">
-        <v>39.8045</v>
+        <v>39.6626</v>
       </c>
       <c r="E75" t="n">
-        <v>15.7877</v>
+        <v>15.803</v>
       </c>
       <c r="F75" t="n">
-        <v>27.6323</v>
+        <v>27.5073</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>19.0889</v>
+        <v>19.0617</v>
       </c>
       <c r="C76" t="n">
-        <v>17.4774</v>
+        <v>17.471</v>
       </c>
       <c r="D76" t="n">
-        <v>39.6689</v>
+        <v>39.9246</v>
       </c>
       <c r="E76" t="n">
-        <v>15.4868</v>
+        <v>15.4917</v>
       </c>
       <c r="F76" t="n">
-        <v>27.3339</v>
+        <v>27.2068</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>18.5767</v>
+        <v>18.5908</v>
       </c>
       <c r="C77" t="n">
-        <v>17.4098</v>
+        <v>17.3911</v>
       </c>
       <c r="D77" t="n">
-        <v>39.6987</v>
+        <v>39.8497</v>
       </c>
       <c r="E77" t="n">
-        <v>15.1595</v>
+        <v>20.8607</v>
       </c>
       <c r="F77" t="n">
-        <v>26.3591</v>
+        <v>31.2252</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>18.0044</v>
+        <v>18.0208</v>
       </c>
       <c r="C78" t="n">
-        <v>17.2158</v>
+        <v>17.1937</v>
       </c>
       <c r="D78" t="n">
-        <v>45.5036</v>
+        <v>46.2046</v>
       </c>
       <c r="E78" t="n">
-        <v>20.4135</v>
+        <v>20.4003</v>
       </c>
       <c r="F78" t="n">
-        <v>30.9679</v>
+        <v>30.8395</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>17.3288</v>
+        <v>17.293</v>
       </c>
       <c r="C79" t="n">
-        <v>19.0924</v>
+        <v>19.0466</v>
       </c>
       <c r="D79" t="n">
-        <v>45.4108</v>
+        <v>45.8592</v>
       </c>
       <c r="E79" t="n">
-        <v>19.8603</v>
+        <v>19.8507</v>
       </c>
       <c r="F79" t="n">
-        <v>30.6669</v>
+        <v>30.5337</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>16.5946</v>
+        <v>16.5819</v>
       </c>
       <c r="C80" t="n">
-        <v>18.8591</v>
+        <v>18.8398</v>
       </c>
       <c r="D80" t="n">
-        <v>45.1062</v>
+        <v>45.5053</v>
       </c>
       <c r="E80" t="n">
-        <v>19.3249</v>
+        <v>19.3083</v>
       </c>
       <c r="F80" t="n">
-        <v>30.3674</v>
+        <v>30.2786</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>23.2915</v>
+        <v>23.2431</v>
       </c>
       <c r="C81" t="n">
-        <v>18.7452</v>
+        <v>18.6858</v>
       </c>
       <c r="D81" t="n">
-        <v>44.6299</v>
+        <v>45.0721</v>
       </c>
       <c r="E81" t="n">
-        <v>18.8827</v>
+        <v>18.8745</v>
       </c>
       <c r="F81" t="n">
-        <v>30.0913</v>
+        <v>29.9454</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>22.9487</v>
+        <v>22.9051</v>
       </c>
       <c r="C82" t="n">
-        <v>18.514</v>
+        <v>18.4629</v>
       </c>
       <c r="D82" t="n">
-        <v>44.3388</v>
+        <v>44.322</v>
       </c>
       <c r="E82" t="n">
-        <v>18.4706</v>
+        <v>18.4707</v>
       </c>
       <c r="F82" t="n">
-        <v>29.7451</v>
+        <v>29.6139</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>22.565</v>
+        <v>22.5426</v>
       </c>
       <c r="C83" t="n">
-        <v>18.3828</v>
+        <v>18.3635</v>
       </c>
       <c r="D83" t="n">
-        <v>44.0769</v>
+        <v>44.5343</v>
       </c>
       <c r="E83" t="n">
-        <v>18.0581</v>
+        <v>18.0319</v>
       </c>
       <c r="F83" t="n">
-        <v>29.4542</v>
+        <v>29.3</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>22.111</v>
+        <v>22.1247</v>
       </c>
       <c r="C84" t="n">
-        <v>18.2313</v>
+        <v>18.1899</v>
       </c>
       <c r="D84" t="n">
-        <v>43.6363</v>
+        <v>43.6457</v>
       </c>
       <c r="E84" t="n">
-        <v>17.6065</v>
+        <v>17.6215</v>
       </c>
       <c r="F84" t="n">
-        <v>29.1564</v>
+        <v>29.014</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>21.6448</v>
+        <v>21.6797</v>
       </c>
       <c r="C85" t="n">
-        <v>18.0024</v>
+        <v>17.9579</v>
       </c>
       <c r="D85" t="n">
-        <v>43.2298</v>
+        <v>43.2714</v>
       </c>
       <c r="E85" t="n">
-        <v>17.3002</v>
+        <v>17.2916</v>
       </c>
       <c r="F85" t="n">
-        <v>28.853</v>
+        <v>28.6967</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>21.2013</v>
+        <v>21.2083</v>
       </c>
       <c r="C86" t="n">
-        <v>17.846</v>
+        <v>17.8171</v>
       </c>
       <c r="D86" t="n">
-        <v>42.6921</v>
+        <v>42.7913</v>
       </c>
       <c r="E86" t="n">
-        <v>16.9387</v>
+        <v>16.9425</v>
       </c>
       <c r="F86" t="n">
-        <v>28.5937</v>
+        <v>28.4257</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>20.7009</v>
+        <v>20.7068</v>
       </c>
       <c r="C87" t="n">
-        <v>17.7116</v>
+        <v>17.7093</v>
       </c>
       <c r="D87" t="n">
-        <v>42.4711</v>
+        <v>42.6924</v>
       </c>
       <c r="E87" t="n">
-        <v>16.5925</v>
+        <v>16.6012</v>
       </c>
       <c r="F87" t="n">
-        <v>28.3178</v>
+        <v>28.1636</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>20.22</v>
+        <v>20.2506</v>
       </c>
       <c r="C88" t="n">
-        <v>17.614</v>
+        <v>17.6169</v>
       </c>
       <c r="D88" t="n">
-        <v>42.1819</v>
+        <v>42.4387</v>
       </c>
       <c r="E88" t="n">
-        <v>16.2861</v>
+        <v>16.3011</v>
       </c>
       <c r="F88" t="n">
-        <v>28.0315</v>
+        <v>27.8316</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>19.7328</v>
+        <v>19.736</v>
       </c>
       <c r="C89" t="n">
-        <v>17.5097</v>
+        <v>17.5337</v>
       </c>
       <c r="D89" t="n">
-        <v>42.0165</v>
+        <v>42.0162</v>
       </c>
       <c r="E89" t="n">
-        <v>15.9654</v>
+        <v>16.0087</v>
       </c>
       <c r="F89" t="n">
-        <v>27.7087</v>
+        <v>27.5848</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>19.2426</v>
+        <v>19.2775</v>
       </c>
       <c r="C90" t="n">
-        <v>17.4035</v>
+        <v>17.4517</v>
       </c>
       <c r="D90" t="n">
-        <v>41.5871</v>
+        <v>41.9475</v>
       </c>
       <c r="E90" t="n">
-        <v>15.6272</v>
+        <v>15.6589</v>
       </c>
       <c r="F90" t="n">
-        <v>27.3985</v>
+        <v>27.2494</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>18.7323</v>
+        <v>18.7703</v>
       </c>
       <c r="C91" t="n">
-        <v>17.3026</v>
+        <v>17.3359</v>
       </c>
       <c r="D91" t="n">
-        <v>41.4894</v>
+        <v>41.7798</v>
       </c>
       <c r="E91" t="n">
-        <v>15.3082</v>
+        <v>20.9676</v>
       </c>
       <c r="F91" t="n">
-        <v>27.1114</v>
+        <v>31.2912</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>18.203</v>
+        <v>18.1685</v>
       </c>
       <c r="C92" t="n">
-        <v>17.2365</v>
+        <v>17.2815</v>
       </c>
       <c r="D92" t="n">
-        <v>46.4165</v>
+        <v>46.1242</v>
       </c>
       <c r="E92" t="n">
-        <v>20.4905</v>
+        <v>20.5157</v>
       </c>
       <c r="F92" t="n">
-        <v>31.144</v>
+        <v>31.0111</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>17.4598</v>
+        <v>17.5491</v>
       </c>
       <c r="C93" t="n">
-        <v>17.1615</v>
+        <v>17.1548</v>
       </c>
       <c r="D93" t="n">
-        <v>45.975</v>
+        <v>45.7833</v>
       </c>
       <c r="E93" t="n">
-        <v>19.9787</v>
+        <v>19.9608</v>
       </c>
       <c r="F93" t="n">
-        <v>30.7521</v>
+        <v>30.6779</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>16.7968</v>
+        <v>16.8793</v>
       </c>
       <c r="C94" t="n">
-        <v>18.8815</v>
+        <v>18.7839</v>
       </c>
       <c r="D94" t="n">
-        <v>45.3401</v>
+        <v>45.2982</v>
       </c>
       <c r="E94" t="n">
-        <v>19.4524</v>
+        <v>19.4377</v>
       </c>
       <c r="F94" t="n">
-        <v>30.4489</v>
+        <v>30.3347</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>23.3416</v>
+        <v>23.3411</v>
       </c>
       <c r="C95" t="n">
-        <v>18.5684</v>
+        <v>18.6048</v>
       </c>
       <c r="D95" t="n">
-        <v>44.8624</v>
+        <v>44.4985</v>
       </c>
       <c r="E95" t="n">
-        <v>18.9605</v>
+        <v>18.9576</v>
       </c>
       <c r="F95" t="n">
-        <v>30.2382</v>
+        <v>30.249</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>22.9961</v>
+        <v>23.0099</v>
       </c>
       <c r="C96" t="n">
-        <v>18.3941</v>
+        <v>18.4384</v>
       </c>
       <c r="D96" t="n">
-        <v>44.404</v>
+        <v>44.107</v>
       </c>
       <c r="E96" t="n">
-        <v>18.4982</v>
+        <v>18.5024</v>
       </c>
       <c r="F96" t="n">
-        <v>29.3548</v>
+        <v>29.4034</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>22.5939</v>
+        <v>22.6134</v>
       </c>
       <c r="C97" t="n">
-        <v>18.2218</v>
+        <v>18.2477</v>
       </c>
       <c r="D97" t="n">
-        <v>44.0006</v>
+        <v>43.7488</v>
       </c>
       <c r="E97" t="n">
-        <v>18.0789</v>
+        <v>18.079</v>
       </c>
       <c r="F97" t="n">
-        <v>28.8212</v>
+        <v>28.9125</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>22.2002</v>
+        <v>22.2057</v>
       </c>
       <c r="C98" t="n">
-        <v>18.0982</v>
+        <v>18.1202</v>
       </c>
       <c r="D98" t="n">
-        <v>43.0782</v>
+        <v>43.1232</v>
       </c>
       <c r="E98" t="n">
-        <v>17.6671</v>
+        <v>17.6726</v>
       </c>
       <c r="F98" t="n">
-        <v>28.4525</v>
+        <v>28.4573</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>21.7448</v>
+        <v>21.8015</v>
       </c>
       <c r="C99" t="n">
-        <v>17.9703</v>
+        <v>17.9698</v>
       </c>
       <c r="D99" t="n">
-        <v>42.6621</v>
+        <v>42.9338</v>
       </c>
       <c r="E99" t="n">
-        <v>17.2937</v>
+        <v>17.2982</v>
       </c>
       <c r="F99" t="n">
-        <v>28.1483</v>
+        <v>28.1379</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>21.3094</v>
+        <v>21.3091</v>
       </c>
       <c r="C100" t="n">
-        <v>17.9632</v>
+        <v>17.9596</v>
       </c>
       <c r="D100" t="n">
-        <v>42.6388</v>
+        <v>42.7167</v>
       </c>
       <c r="E100" t="n">
-        <v>16.9742</v>
+        <v>16.9861</v>
       </c>
       <c r="F100" t="n">
-        <v>27.8094</v>
+        <v>27.8499</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>20.8405</v>
+        <v>20.8244</v>
       </c>
       <c r="C101" t="n">
-        <v>17.8296</v>
+        <v>17.8414</v>
       </c>
       <c r="D101" t="n">
-        <v>42.574</v>
+        <v>42.3614</v>
       </c>
       <c r="E101" t="n">
-        <v>16.6497</v>
+        <v>16.6517</v>
       </c>
       <c r="F101" t="n">
-        <v>27.5513</v>
+        <v>27.5443</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>20.3812</v>
+        <v>20.3827</v>
       </c>
       <c r="C102" t="n">
-        <v>17.7238</v>
+        <v>17.7309</v>
       </c>
       <c r="D102" t="n">
-        <v>41.7816</v>
+        <v>41.8468</v>
       </c>
       <c r="E102" t="n">
-        <v>16.3007</v>
+        <v>16.3136</v>
       </c>
       <c r="F102" t="n">
-        <v>27.2357</v>
+        <v>27.2692</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>19.8926</v>
+        <v>19.8659</v>
       </c>
       <c r="C103" t="n">
-        <v>17.6226</v>
+        <v>17.6395</v>
       </c>
       <c r="D103" t="n">
-        <v>41.5243</v>
+        <v>41.5223</v>
       </c>
       <c r="E103" t="n">
-        <v>15.9944</v>
+        <v>15.9741</v>
       </c>
       <c r="F103" t="n">
-        <v>26.9799</v>
+        <v>27.0026</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>19.3752</v>
+        <v>19.3716</v>
       </c>
       <c r="C104" t="n">
-        <v>17.5402</v>
+        <v>17.54</v>
       </c>
       <c r="D104" t="n">
-        <v>41.1448</v>
+        <v>41.3139</v>
       </c>
       <c r="E104" t="n">
-        <v>15.6793</v>
+        <v>15.6801</v>
       </c>
       <c r="F104" t="n">
-        <v>26.6376</v>
+        <v>26.664</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>18.8204</v>
+        <v>18.8196</v>
       </c>
       <c r="C105" t="n">
-        <v>17.4293</v>
+        <v>17.438</v>
       </c>
       <c r="D105" t="n">
-        <v>40.9442</v>
+        <v>40.9544</v>
       </c>
       <c r="E105" t="n">
-        <v>15.3652</v>
+        <v>20.9772</v>
       </c>
       <c r="F105" t="n">
-        <v>26.3534</v>
+        <v>30.8074</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>18.3049</v>
+        <v>18.2904</v>
       </c>
       <c r="C106" t="n">
-        <v>17.3632</v>
+        <v>17.3455</v>
       </c>
       <c r="D106" t="n">
-        <v>40.702</v>
+        <v>40.1959</v>
       </c>
       <c r="E106" t="n">
-        <v>15.0675</v>
+        <v>20.4593</v>
       </c>
       <c r="F106" t="n">
-        <v>26.0617</v>
+        <v>30.4278</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>17.7425</v>
+        <v>17.6648</v>
       </c>
       <c r="C107" t="n">
-        <v>17.2771</v>
+        <v>17.2709</v>
       </c>
       <c r="D107" t="n">
-        <v>43.9336</v>
+        <v>43.6993</v>
       </c>
       <c r="E107" t="n">
-        <v>19.9537</v>
+        <v>19.9804</v>
       </c>
       <c r="F107" t="n">
-        <v>30.1072</v>
+        <v>30.1449</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>16.9949</v>
+        <v>16.9683</v>
       </c>
       <c r="C108" t="n">
-        <v>18.9458</v>
+        <v>18.9478</v>
       </c>
       <c r="D108" t="n">
-        <v>43.6476</v>
+        <v>43.835</v>
       </c>
       <c r="E108" t="n">
-        <v>19.5301</v>
+        <v>19.5252</v>
       </c>
       <c r="F108" t="n">
-        <v>29.8802</v>
+        <v>29.8032</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>16.2116</v>
+        <v>16.1718</v>
       </c>
       <c r="C109" t="n">
-        <v>18.7508</v>
+        <v>18.7642</v>
       </c>
       <c r="D109" t="n">
-        <v>43.2262</v>
+        <v>43.2641</v>
       </c>
       <c r="E109" t="n">
-        <v>19.0492</v>
+        <v>19.0375</v>
       </c>
       <c r="F109" t="n">
-        <v>29.4989</v>
+        <v>29.5467</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>23.1169</v>
+        <v>23.0808</v>
       </c>
       <c r="C110" t="n">
-        <v>18.4543</v>
+        <v>18.4376</v>
       </c>
       <c r="D110" t="n">
-        <v>42.6946</v>
+        <v>42.7849</v>
       </c>
       <c r="E110" t="n">
-        <v>18.6212</v>
+        <v>18.6059</v>
       </c>
       <c r="F110" t="n">
-        <v>29.7241</v>
+        <v>29.8982</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>22.7152</v>
+        <v>22.6978</v>
       </c>
       <c r="C111" t="n">
-        <v>18.2942</v>
+        <v>18.2891</v>
       </c>
       <c r="D111" t="n">
-        <v>42.2729</v>
+        <v>42.4636</v>
       </c>
       <c r="E111" t="n">
-        <v>18.1832</v>
+        <v>18.1732</v>
       </c>
       <c r="F111" t="n">
-        <v>29.3939</v>
+        <v>29.5388</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>22.3048</v>
+        <v>22.2984</v>
       </c>
       <c r="C112" t="n">
-        <v>18.1652</v>
+        <v>18.1476</v>
       </c>
       <c r="D112" t="n">
-        <v>42.0079</v>
+        <v>42.0859</v>
       </c>
       <c r="E112" t="n">
-        <v>17.7705</v>
+        <v>17.768</v>
       </c>
       <c r="F112" t="n">
-        <v>29.0946</v>
+        <v>29.2542</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>21.8574</v>
+        <v>21.8693</v>
       </c>
       <c r="C113" t="n">
-        <v>18.0137</v>
+        <v>17.9916</v>
       </c>
       <c r="D113" t="n">
-        <v>41.6564</v>
+        <v>41.357</v>
       </c>
       <c r="E113" t="n">
-        <v>17.3966</v>
+        <v>17.3859</v>
       </c>
       <c r="F113" t="n">
-        <v>28.7858</v>
+        <v>28.9677</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>21.4151</v>
+        <v>21.426</v>
       </c>
       <c r="C114" t="n">
-        <v>17.8597</v>
+        <v>17.8432</v>
       </c>
       <c r="D114" t="n">
-        <v>40.9123</v>
+        <v>40.9935</v>
       </c>
       <c r="E114" t="n">
-        <v>17.0601</v>
+        <v>17.0492</v>
       </c>
       <c r="F114" t="n">
-        <v>28.5132</v>
+        <v>28.6609</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>20.9629</v>
+        <v>20.9658</v>
       </c>
       <c r="C115" t="n">
-        <v>17.7593</v>
+        <v>17.7482</v>
       </c>
       <c r="D115" t="n">
-        <v>40.5374</v>
+        <v>40.5329</v>
       </c>
       <c r="E115" t="n">
-        <v>16.7211</v>
+        <v>16.7113</v>
       </c>
       <c r="F115" t="n">
-        <v>28.233</v>
+        <v>28.3949</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>20.4989</v>
+        <v>20.4986</v>
       </c>
       <c r="C116" t="n">
-        <v>17.6632</v>
+        <v>17.6311</v>
       </c>
       <c r="D116" t="n">
-        <v>40.1344</v>
+        <v>40.2482</v>
       </c>
       <c r="E116" t="n">
-        <v>16.3732</v>
+        <v>16.403</v>
       </c>
       <c r="F116" t="n">
-        <v>27.318</v>
+        <v>27.4691</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>19.9636</v>
+        <v>19.9785</v>
       </c>
       <c r="C117" t="n">
-        <v>17.5521</v>
+        <v>17.5477</v>
       </c>
       <c r="D117" t="n">
-        <v>39.8978</v>
+        <v>39.9084</v>
       </c>
       <c r="E117" t="n">
-        <v>16.0659</v>
+        <v>16.0786</v>
       </c>
       <c r="F117" t="n">
-        <v>27.0731</v>
+        <v>27.1847</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>19.4411</v>
+        <v>19.4328</v>
       </c>
       <c r="C118" t="n">
-        <v>17.4668</v>
+        <v>17.4309</v>
       </c>
       <c r="D118" t="n">
-        <v>39.6067</v>
+        <v>39.5915</v>
       </c>
       <c r="E118" t="n">
-        <v>15.7623</v>
+        <v>15.7692</v>
       </c>
       <c r="F118" t="n">
-        <v>26.7463</v>
+        <v>26.891</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>18.9535</v>
+        <v>18.9347</v>
       </c>
       <c r="C119" t="n">
-        <v>17.3673</v>
+        <v>17.373</v>
       </c>
       <c r="D119" t="n">
-        <v>39.3875</v>
+        <v>39.3372</v>
       </c>
       <c r="E119" t="n">
-        <v>15.461</v>
+        <v>21.2206</v>
       </c>
       <c r="F119" t="n">
-        <v>26.4537</v>
+        <v>31.5908</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>18.4311</v>
+        <v>18.3649</v>
       </c>
       <c r="C120" t="n">
         <v>17.2717</v>
       </c>
       <c r="D120" t="n">
-        <v>39.1267</v>
+        <v>39.9928</v>
       </c>
       <c r="E120" t="n">
-        <v>15.1145</v>
+        <v>20.6886</v>
       </c>
       <c r="F120" t="n">
-        <v>26.1493</v>
+        <v>31.1344</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>17.8037</v>
+        <v>17.8163</v>
       </c>
       <c r="C121" t="n">
-        <v>17.1806</v>
+        <v>17.1929</v>
       </c>
       <c r="D121" t="n">
-        <v>46.8755</v>
+        <v>47.1088</v>
       </c>
       <c r="E121" t="n">
-        <v>20.1476</v>
+        <v>20.1518</v>
       </c>
       <c r="F121" t="n">
-        <v>30.7602</v>
+        <v>30.8619</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>17.1931</v>
+        <v>17.1354</v>
       </c>
       <c r="C122" t="n">
-        <v>18.8917</v>
+        <v>18.8502</v>
       </c>
       <c r="D122" t="n">
-        <v>46.0189</v>
+        <v>46.5281</v>
       </c>
       <c r="E122" t="n">
-        <v>19.6206</v>
+        <v>19.6445</v>
       </c>
       <c r="F122" t="n">
-        <v>29.8577</v>
+        <v>30.0251</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>16.3409</v>
+        <v>16.3404</v>
       </c>
       <c r="C123" t="n">
-        <v>18.6969</v>
+        <v>18.6614</v>
       </c>
       <c r="D123" t="n">
-        <v>45.4478</v>
+        <v>45.5803</v>
       </c>
       <c r="E123" t="n">
-        <v>19.1448</v>
+        <v>19.1403</v>
       </c>
       <c r="F123" t="n">
-        <v>29.6758</v>
+        <v>30.179</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>23.1723</v>
+        <v>23.1567</v>
       </c>
       <c r="C124" t="n">
-        <v>18.4788</v>
+        <v>18.4934</v>
       </c>
       <c r="D124" t="n">
-        <v>44.8497</v>
+        <v>44.8936</v>
       </c>
       <c r="E124" t="n">
-        <v>18.6625</v>
+        <v>18.6717</v>
       </c>
       <c r="F124" t="n">
-        <v>29.6858</v>
+        <v>29.5311</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>22.778</v>
+        <v>22.786</v>
       </c>
       <c r="C125" t="n">
-        <v>18.3389</v>
+        <v>18.3018</v>
       </c>
       <c r="D125" t="n">
-        <v>44.5496</v>
+        <v>44.2541</v>
       </c>
       <c r="E125" t="n">
-        <v>18.2504</v>
+        <v>18.2765</v>
       </c>
       <c r="F125" t="n">
-        <v>29.0401</v>
+        <v>29.1769</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>22.3597</v>
+        <v>22.38</v>
       </c>
       <c r="C126" t="n">
-        <v>18.1684</v>
+        <v>18.1524</v>
       </c>
       <c r="D126" t="n">
-        <v>43.5204</v>
+        <v>43.6925</v>
       </c>
       <c r="E126" t="n">
-        <v>17.8457</v>
+        <v>17.8429</v>
       </c>
       <c r="F126" t="n">
-        <v>28.6941</v>
+        <v>28.8556</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>21.9352</v>
+        <v>21.9882</v>
       </c>
       <c r="C127" t="n">
-        <v>18.0526</v>
+        <v>18.0257</v>
       </c>
       <c r="D127" t="n">
-        <v>42.9135</v>
+        <v>43.4383</v>
       </c>
       <c r="E127" t="n">
-        <v>17.4454</v>
+        <v>17.4344</v>
       </c>
       <c r="F127" t="n">
-        <v>28.3849</v>
+        <v>29.0243</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>21.489</v>
+        <v>21.5152</v>
       </c>
       <c r="C128" t="n">
-        <v>17.9061</v>
+        <v>17.8992</v>
       </c>
       <c r="D128" t="n">
-        <v>42.8889</v>
+        <v>43.006</v>
       </c>
       <c r="E128" t="n">
-        <v>17.102</v>
+        <v>17.1064</v>
       </c>
       <c r="F128" t="n">
-        <v>28.5649</v>
+        <v>28.7174</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>21.0392</v>
+        <v>21.0368</v>
       </c>
       <c r="C129" t="n">
-        <v>17.7581</v>
+        <v>17.7479</v>
       </c>
       <c r="D129" t="n">
-        <v>42.3755</v>
+        <v>42.616</v>
       </c>
       <c r="E129" t="n">
-        <v>16.7832</v>
+        <v>16.779</v>
       </c>
       <c r="F129" t="n">
-        <v>28.2819</v>
+        <v>28.4155</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>20.5667</v>
+        <v>20.5545</v>
       </c>
       <c r="C130" t="n">
-        <v>17.6723</v>
+        <v>17.6464</v>
       </c>
       <c r="D130" t="n">
-        <v>42.0554</v>
+        <v>42.2202</v>
       </c>
       <c r="E130" t="n">
-        <v>16.4337</v>
+        <v>16.4432</v>
       </c>
       <c r="F130" t="n">
-        <v>27.3671</v>
+        <v>27.4992</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>20.0884</v>
+        <v>20.0742</v>
       </c>
       <c r="C131" t="n">
-        <v>17.5426</v>
+        <v>17.5421</v>
       </c>
       <c r="D131" t="n">
-        <v>41.6161</v>
+        <v>41.7795</v>
       </c>
       <c r="E131" t="n">
-        <v>16.1086</v>
+        <v>16.1038</v>
       </c>
       <c r="F131" t="n">
-        <v>27.0741</v>
+        <v>27.2061</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>19.611</v>
+        <v>19.5702</v>
       </c>
       <c r="C132" t="n">
-        <v>17.4393</v>
+        <v>17.4421</v>
       </c>
       <c r="D132" t="n">
-        <v>41.3025</v>
+        <v>41.4279</v>
       </c>
       <c r="E132" t="n">
-        <v>15.7976</v>
+        <v>15.8135</v>
       </c>
       <c r="F132" t="n">
-        <v>26.788</v>
+        <v>26.919</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>19.0936</v>
+        <v>19.0587</v>
       </c>
       <c r="C133" t="n">
-        <v>17.367</v>
+        <v>17.364</v>
       </c>
       <c r="D133" t="n">
-        <v>41.018</v>
+        <v>41.0622</v>
       </c>
       <c r="E133" t="n">
-        <v>15.4997</v>
+        <v>15.5185</v>
       </c>
       <c r="F133" t="n">
-        <v>26.4914</v>
+        <v>27.2786</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>18.5556</v>
+        <v>18.5225</v>
       </c>
       <c r="C134" t="n">
-        <v>17.2726</v>
+        <v>17.3</v>
       </c>
       <c r="D134" t="n">
-        <v>40.8678</v>
+        <v>40.8136</v>
       </c>
       <c r="E134" t="n">
-        <v>15.1734</v>
+        <v>20.7617</v>
       </c>
       <c r="F134" t="n">
-        <v>26.1997</v>
+        <v>30.7458</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>17.9923</v>
+        <v>17.9378</v>
       </c>
       <c r="C135" t="n">
-        <v>17.2082</v>
+        <v>17.2107</v>
       </c>
       <c r="D135" t="n">
-        <v>47.4387</v>
+        <v>47.1544</v>
       </c>
       <c r="E135" t="n">
-        <v>20.1607</v>
+        <v>20.2496</v>
       </c>
       <c r="F135" t="n">
-        <v>30.2099</v>
+        <v>30.3832</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>17.3805</v>
+        <v>17.3434</v>
       </c>
       <c r="C136" t="n">
-        <v>18.916</v>
+        <v>19.038</v>
       </c>
       <c r="D136" t="n">
-        <v>46.9382</v>
+        <v>47.0605</v>
       </c>
       <c r="E136" t="n">
-        <v>19.7238</v>
+        <v>19.71</v>
       </c>
       <c r="F136" t="n">
-        <v>30.1834</v>
+        <v>30.0515</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>16.5164</v>
+        <v>16.5102</v>
       </c>
       <c r="C137" t="n">
-        <v>18.8444</v>
+        <v>18.7118</v>
       </c>
       <c r="D137" t="n">
-        <v>46.2137</v>
+        <v>46.5268</v>
       </c>
       <c r="E137" t="n">
-        <v>19.2275</v>
+        <v>19.2307</v>
       </c>
       <c r="F137" t="n">
-        <v>29.5828</v>
+        <v>29.7157</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>23.2501</v>
+        <v>23.2438</v>
       </c>
       <c r="C138" t="n">
-        <v>18.5219</v>
+        <v>18.6602</v>
       </c>
       <c r="D138" t="n">
-        <v>46.0168</v>
+        <v>45.8214</v>
       </c>
       <c r="E138" t="n">
-        <v>18.7438</v>
+        <v>18.761</v>
       </c>
       <c r="F138" t="n">
-        <v>29.2039</v>
+        <v>29.265</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>22.8794</v>
+        <v>22.8771</v>
       </c>
       <c r="C139" t="n">
-        <v>18.4866</v>
+        <v>18.4762</v>
       </c>
       <c r="D139" t="n">
-        <v>45.7559</v>
+        <v>44.6501</v>
       </c>
       <c r="E139" t="n">
-        <v>18.3066</v>
+        <v>18.3225</v>
       </c>
       <c r="F139" t="n">
-        <v>28.9287</v>
+        <v>28.9265</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>22.4944</v>
+        <v>22.4793</v>
       </c>
       <c r="C140" t="n">
-        <v>18.3133</v>
+        <v>18.3081</v>
       </c>
       <c r="D140" t="n">
-        <v>44.9456</v>
+        <v>44.6549</v>
       </c>
       <c r="E140" t="n">
-        <v>17.9077</v>
+        <v>17.8937</v>
       </c>
       <c r="F140" t="n">
-        <v>28.6296</v>
+        <v>28.5997</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>22.0657</v>
+        <v>22.049</v>
       </c>
       <c r="C141" t="n">
-        <v>18.1762</v>
+        <v>18.0602</v>
       </c>
       <c r="D141" t="n">
-        <v>44.0778</v>
+        <v>43.7542</v>
       </c>
       <c r="E141" t="n">
-        <v>17.5215</v>
+        <v>17.5297</v>
       </c>
       <c r="F141" t="n">
-        <v>28.3296</v>
+        <v>28.5406</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>21.6222</v>
+        <v>21.5859</v>
       </c>
       <c r="C142" t="n">
-        <v>17.9214</v>
+        <v>17.9211</v>
       </c>
       <c r="D142" t="n">
-        <v>43.3401</v>
+        <v>43.0495</v>
       </c>
       <c r="E142" t="n">
-        <v>17.1601</v>
+        <v>17.1674</v>
       </c>
       <c r="F142" t="n">
-        <v>28.1157</v>
+        <v>28.0316</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>21.1381</v>
+        <v>21.1143</v>
       </c>
       <c r="C143" t="n">
-        <v>17.8694</v>
+        <v>17.8832</v>
       </c>
       <c r="D143" t="n">
-        <v>42.7044</v>
+        <v>42.6387</v>
       </c>
       <c r="E143" t="n">
-        <v>16.8231</v>
+        <v>16.8439</v>
       </c>
       <c r="F143" t="n">
-        <v>27.8675</v>
+        <v>27.7254</v>
       </c>
     </row>
   </sheetData>

--- a/clang-x64/Running erasure.xlsx
+++ b/clang-x64/Running erasure.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>18.0815</v>
+        <v>18.2788</v>
       </c>
       <c r="C2" t="n">
-        <v>13.1828</v>
+        <v>13.1657</v>
       </c>
       <c r="D2" t="n">
-        <v>30.5528</v>
+        <v>30.6175</v>
       </c>
       <c r="E2" t="n">
-        <v>12.5875</v>
+        <v>12.6816</v>
       </c>
       <c r="F2" t="n">
-        <v>26.4511</v>
+        <v>26.4323</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>17.9983</v>
+        <v>18.1776</v>
       </c>
       <c r="C3" t="n">
-        <v>13.4973</v>
+        <v>13.2887</v>
       </c>
       <c r="D3" t="n">
-        <v>30.8458</v>
+        <v>30.8565</v>
       </c>
       <c r="E3" t="n">
-        <v>12.6753</v>
+        <v>12.5147</v>
       </c>
       <c r="F3" t="n">
-        <v>26.1548</v>
+        <v>26.1762</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>17.666</v>
+        <v>17.7147</v>
       </c>
       <c r="C4" t="n">
-        <v>13.7908</v>
+        <v>13.5186</v>
       </c>
       <c r="D4" t="n">
-        <v>31.0324</v>
+        <v>30.9712</v>
       </c>
       <c r="E4" t="n">
-        <v>12.4033</v>
+        <v>12.3907</v>
       </c>
       <c r="F4" t="n">
-        <v>25.9896</v>
+        <v>25.9752</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>17.129</v>
+        <v>17.2232</v>
       </c>
       <c r="C5" t="n">
-        <v>13.8225</v>
+        <v>13.5718</v>
       </c>
       <c r="D5" t="n">
-        <v>31.2364</v>
+        <v>31.1076</v>
       </c>
       <c r="E5" t="n">
-        <v>19.8777</v>
+        <v>19.8717</v>
       </c>
       <c r="F5" t="n">
-        <v>30.6088</v>
+        <v>30.7422</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>16.6968</v>
+        <v>16.8798</v>
       </c>
       <c r="C6" t="n">
-        <v>14.0734</v>
+        <v>13.8138</v>
       </c>
       <c r="D6" t="n">
-        <v>31.2815</v>
+        <v>31.3255</v>
       </c>
       <c r="E6" t="n">
-        <v>19.151</v>
+        <v>19.0566</v>
       </c>
       <c r="F6" t="n">
-        <v>30.1665</v>
+        <v>30.1772</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>16.0907</v>
+        <v>16.1381</v>
       </c>
       <c r="C7" t="n">
-        <v>14.358</v>
+        <v>14.1568</v>
       </c>
       <c r="D7" t="n">
-        <v>30.2059</v>
+        <v>30.0364</v>
       </c>
       <c r="E7" t="n">
-        <v>18.754</v>
+        <v>18.7096</v>
       </c>
       <c r="F7" t="n">
-        <v>30.2272</v>
+        <v>29.912</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>15.6611</v>
+        <v>15.5463</v>
       </c>
       <c r="C8" t="n">
-        <v>15.5905</v>
+        <v>15.6436</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0918</v>
+        <v>30.078</v>
       </c>
       <c r="E8" t="n">
-        <v>18.338</v>
+        <v>18.3835</v>
       </c>
       <c r="F8" t="n">
-        <v>29.7643</v>
+        <v>29.72</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>14.8882</v>
+        <v>14.9348</v>
       </c>
       <c r="C9" t="n">
-        <v>15.6978</v>
+        <v>15.723</v>
       </c>
       <c r="D9" t="n">
-        <v>30.2357</v>
+        <v>30.1762</v>
       </c>
       <c r="E9" t="n">
-        <v>17.9596</v>
+        <v>17.956</v>
       </c>
       <c r="F9" t="n">
-        <v>29.4959</v>
+        <v>28.9882</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>21.6509</v>
+        <v>21.8444</v>
       </c>
       <c r="C10" t="n">
-        <v>15.8818</v>
+        <v>15.8338</v>
       </c>
       <c r="D10" t="n">
-        <v>30.4822</v>
+        <v>30.4141</v>
       </c>
       <c r="E10" t="n">
-        <v>17.4686</v>
+        <v>17.3266</v>
       </c>
       <c r="F10" t="n">
-        <v>29.1652</v>
+        <v>29.085</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>21.4021</v>
+        <v>21.6419</v>
       </c>
       <c r="C11" t="n">
-        <v>15.9616</v>
+        <v>15.897</v>
       </c>
       <c r="D11" t="n">
-        <v>30.6006</v>
+        <v>30.5142</v>
       </c>
       <c r="E11" t="n">
-        <v>17.0854</v>
+        <v>17.194</v>
       </c>
       <c r="F11" t="n">
-        <v>29.1222</v>
+        <v>28.8553</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>21.0041</v>
+        <v>21.3124</v>
       </c>
       <c r="C12" t="n">
-        <v>16.0586</v>
+        <v>15.9277</v>
       </c>
       <c r="D12" t="n">
-        <v>31.0775</v>
+        <v>30.5165</v>
       </c>
       <c r="E12" t="n">
-        <v>16.6109</v>
+        <v>16.6826</v>
       </c>
       <c r="F12" t="n">
-        <v>28.246</v>
+        <v>28.1582</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>20.6571</v>
+        <v>20.932</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1347</v>
+        <v>16.316</v>
       </c>
       <c r="D13" t="n">
-        <v>31.1994</v>
+        <v>30.8331</v>
       </c>
       <c r="E13" t="n">
-        <v>16.413</v>
+        <v>16.4654</v>
       </c>
       <c r="F13" t="n">
-        <v>28.0496</v>
+        <v>27.9986</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>20.4914</v>
+        <v>20.6059</v>
       </c>
       <c r="C14" t="n">
-        <v>16.3571</v>
+        <v>16.3301</v>
       </c>
       <c r="D14" t="n">
-        <v>31.4612</v>
+        <v>30.9024</v>
       </c>
       <c r="E14" t="n">
-        <v>16.1903</v>
+        <v>16.2582</v>
       </c>
       <c r="F14" t="n">
-        <v>27.5591</v>
+        <v>27.6028</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>20.1682</v>
+        <v>20.2545</v>
       </c>
       <c r="C15" t="n">
-        <v>16.4861</v>
+        <v>16.5668</v>
       </c>
       <c r="D15" t="n">
-        <v>31.5003</v>
+        <v>31.4812</v>
       </c>
       <c r="E15" t="n">
-        <v>15.917</v>
+        <v>15.9517</v>
       </c>
       <c r="F15" t="n">
-        <v>27.3936</v>
+        <v>27.3188</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>19.8086</v>
+        <v>19.8516</v>
       </c>
       <c r="C16" t="n">
-        <v>16.5214</v>
+        <v>16.3155</v>
       </c>
       <c r="D16" t="n">
-        <v>31.5884</v>
+        <v>31.1942</v>
       </c>
       <c r="E16" t="n">
-        <v>15.5837</v>
+        <v>15.56</v>
       </c>
       <c r="F16" t="n">
-        <v>26.9499</v>
+        <v>26.8551</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>19.2943</v>
+        <v>19.4205</v>
       </c>
       <c r="C17" t="n">
-        <v>16.3403</v>
+        <v>16.3371</v>
       </c>
       <c r="D17" t="n">
-        <v>31.7362</v>
+        <v>31.3454</v>
       </c>
       <c r="E17" t="n">
-        <v>15.273</v>
+        <v>15.2884</v>
       </c>
       <c r="F17" t="n">
-        <v>26.6041</v>
+        <v>26.6103</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>18.9016</v>
+        <v>18.9846</v>
       </c>
       <c r="C18" t="n">
-        <v>16.4878</v>
+        <v>16.3738</v>
       </c>
       <c r="D18" t="n">
-        <v>31.9521</v>
+        <v>31.4727</v>
       </c>
       <c r="E18" t="n">
-        <v>14.9881</v>
+        <v>14.9801</v>
       </c>
       <c r="F18" t="n">
-        <v>26.3919</v>
+        <v>26.454</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>18.4529</v>
+        <v>18.5422</v>
       </c>
       <c r="C19" t="n">
-        <v>16.5017</v>
+        <v>16.4285</v>
       </c>
       <c r="D19" t="n">
-        <v>32.1302</v>
+        <v>32.1602</v>
       </c>
       <c r="E19" t="n">
-        <v>14.6222</v>
+        <v>14.6338</v>
       </c>
       <c r="F19" t="n">
-        <v>26.0207</v>
+        <v>26.1663</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>17.8311</v>
+        <v>17.9324</v>
       </c>
       <c r="C20" t="n">
-        <v>16.7201</v>
+        <v>16.6487</v>
       </c>
       <c r="D20" t="n">
-        <v>32.2854</v>
+        <v>32.2993</v>
       </c>
       <c r="E20" t="n">
-        <v>20.3655</v>
+        <v>20.3636</v>
       </c>
       <c r="F20" t="n">
-        <v>31.0536</v>
+        <v>30.9052</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>17.365</v>
+        <v>17.5091</v>
       </c>
       <c r="C21" t="n">
-        <v>16.5318</v>
+        <v>16.5238</v>
       </c>
       <c r="D21" t="n">
-        <v>31.3398</v>
+        <v>31.1693</v>
       </c>
       <c r="E21" t="n">
-        <v>19.9496</v>
+        <v>19.9356</v>
       </c>
       <c r="F21" t="n">
-        <v>30.9289</v>
+        <v>30.7517</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>16.626</v>
+        <v>16.7806</v>
       </c>
       <c r="C22" t="n">
-        <v>17.9928</v>
+        <v>18.0706</v>
       </c>
       <c r="D22" t="n">
-        <v>31.5335</v>
+        <v>31.1755</v>
       </c>
       <c r="E22" t="n">
-        <v>19.3912</v>
+        <v>19.3699</v>
       </c>
       <c r="F22" t="n">
-        <v>30.5919</v>
+        <v>29.8888</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>16.0053</v>
+        <v>16.0459</v>
       </c>
       <c r="C23" t="n">
-        <v>17.9231</v>
+        <v>17.9661</v>
       </c>
       <c r="D23" t="n">
-        <v>31.47</v>
+        <v>31.2589</v>
       </c>
       <c r="E23" t="n">
-        <v>18.9175</v>
+        <v>18.9151</v>
       </c>
       <c r="F23" t="n">
-        <v>30.1706</v>
+        <v>29.5658</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>22.5098</v>
+        <v>22.4562</v>
       </c>
       <c r="C24" t="n">
-        <v>17.8219</v>
+        <v>17.8275</v>
       </c>
       <c r="D24" t="n">
-        <v>31.3218</v>
+        <v>31.2462</v>
       </c>
       <c r="E24" t="n">
-        <v>18.5126</v>
+        <v>18.4868</v>
       </c>
       <c r="F24" t="n">
-        <v>29.6709</v>
+        <v>29.031</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>22.1768</v>
+        <v>22.2035</v>
       </c>
       <c r="C25" t="n">
-        <v>17.8118</v>
+        <v>17.8045</v>
       </c>
       <c r="D25" t="n">
-        <v>31.625</v>
+        <v>31.4353</v>
       </c>
       <c r="E25" t="n">
-        <v>17.9574</v>
+        <v>18.0832</v>
       </c>
       <c r="F25" t="n">
-        <v>28.8972</v>
+        <v>28.7419</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>21.8184</v>
+        <v>21.8163</v>
       </c>
       <c r="C26" t="n">
-        <v>17.671</v>
+        <v>17.6595</v>
       </c>
       <c r="D26" t="n">
-        <v>31.6559</v>
+        <v>31.4328</v>
       </c>
       <c r="E26" t="n">
-        <v>17.6111</v>
+        <v>17.5643</v>
       </c>
       <c r="F26" t="n">
-        <v>28.5307</v>
+        <v>28.4869</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>21.6685</v>
+        <v>21.5958</v>
       </c>
       <c r="C27" t="n">
-        <v>17.6865</v>
+        <v>17.5671</v>
       </c>
       <c r="D27" t="n">
-        <v>31.8361</v>
+        <v>31.4865</v>
       </c>
       <c r="E27" t="n">
-        <v>17.1405</v>
+        <v>17.181</v>
       </c>
       <c r="F27" t="n">
-        <v>28.2569</v>
+        <v>28.2326</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>21.2615</v>
+        <v>21.239</v>
       </c>
       <c r="C28" t="n">
-        <v>17.6376</v>
+        <v>17.6111</v>
       </c>
       <c r="D28" t="n">
-        <v>31.8391</v>
+        <v>31.6283</v>
       </c>
       <c r="E28" t="n">
-        <v>16.9641</v>
+        <v>16.8323</v>
       </c>
       <c r="F28" t="n">
-        <v>27.9271</v>
+        <v>27.9395</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>20.862</v>
+        <v>20.8695</v>
       </c>
       <c r="C29" t="n">
-        <v>17.4766</v>
+        <v>17.4577</v>
       </c>
       <c r="D29" t="n">
-        <v>31.8896</v>
+        <v>31.8226</v>
       </c>
       <c r="E29" t="n">
-        <v>16.46</v>
+        <v>16.4267</v>
       </c>
       <c r="F29" t="n">
-        <v>27.6547</v>
+        <v>27.623</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>20.449</v>
+        <v>20.4861</v>
       </c>
       <c r="C30" t="n">
-        <v>17.502</v>
+        <v>17.496</v>
       </c>
       <c r="D30" t="n">
-        <v>32.1074</v>
+        <v>31.8044</v>
       </c>
       <c r="E30" t="n">
-        <v>16.106</v>
+        <v>16.1672</v>
       </c>
       <c r="F30" t="n">
-        <v>27.4511</v>
+        <v>27.4662</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>19.9411</v>
+        <v>19.8997</v>
       </c>
       <c r="C31" t="n">
-        <v>17.4056</v>
+        <v>17.4111</v>
       </c>
       <c r="D31" t="n">
-        <v>32.2489</v>
+        <v>31.9351</v>
       </c>
       <c r="E31" t="n">
-        <v>15.8043</v>
+        <v>15.8072</v>
       </c>
       <c r="F31" t="n">
-        <v>27.0618</v>
+        <v>26.9935</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>19.5287</v>
+        <v>19.4208</v>
       </c>
       <c r="C32" t="n">
-        <v>17.4052</v>
+        <v>17.3531</v>
       </c>
       <c r="D32" t="n">
-        <v>32.2763</v>
+        <v>32.162</v>
       </c>
       <c r="E32" t="n">
-        <v>15.5367</v>
+        <v>15.5013</v>
       </c>
       <c r="F32" t="n">
-        <v>26.7854</v>
+        <v>26.6713</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>18.9673</v>
+        <v>18.9438</v>
       </c>
       <c r="C33" t="n">
-        <v>17.345</v>
+        <v>17.3574</v>
       </c>
       <c r="D33" t="n">
-        <v>32.495</v>
+        <v>32.0662</v>
       </c>
       <c r="E33" t="n">
-        <v>15.2271</v>
+        <v>15.2248</v>
       </c>
       <c r="F33" t="n">
-        <v>26.9966</v>
+        <v>26.9465</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>18.3922</v>
+        <v>18.9456</v>
       </c>
       <c r="C34" t="n">
-        <v>17.2161</v>
+        <v>17.2832</v>
       </c>
       <c r="D34" t="n">
-        <v>32.6076</v>
+        <v>32.0491</v>
       </c>
       <c r="E34" t="n">
-        <v>20.6758</v>
+        <v>20.6884</v>
       </c>
       <c r="F34" t="n">
-        <v>31.3393</v>
+        <v>31.3377</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>17.9676</v>
+        <v>18.1223</v>
       </c>
       <c r="C35" t="n">
-        <v>17.1421</v>
+        <v>17.2121</v>
       </c>
       <c r="D35" t="n">
-        <v>31.5501</v>
+        <v>31.1801</v>
       </c>
       <c r="E35" t="n">
-        <v>19.9935</v>
+        <v>19.9897</v>
       </c>
       <c r="F35" t="n">
-        <v>30.9388</v>
+        <v>30.8907</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>17.2976</v>
+        <v>17.3477</v>
       </c>
       <c r="C36" t="n">
-        <v>17.1135</v>
+        <v>17.1381</v>
       </c>
       <c r="D36" t="n">
-        <v>31.8104</v>
+        <v>31.1888</v>
       </c>
       <c r="E36" t="n">
-        <v>19.6268</v>
+        <v>19.6022</v>
       </c>
       <c r="F36" t="n">
-        <v>30.7151</v>
+        <v>30.5348</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>16.6135</v>
+        <v>16.6713</v>
       </c>
       <c r="C37" t="n">
-        <v>18.3835</v>
+        <v>18.5602</v>
       </c>
       <c r="D37" t="n">
-        <v>31.7398</v>
+        <v>31.1684</v>
       </c>
       <c r="E37" t="n">
-        <v>19.0553</v>
+        <v>19.0779</v>
       </c>
       <c r="F37" t="n">
-        <v>30.3244</v>
+        <v>30.2806</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>23.0869</v>
+        <v>23.1569</v>
       </c>
       <c r="C38" t="n">
-        <v>18.2402</v>
+        <v>18.3702</v>
       </c>
       <c r="D38" t="n">
-        <v>31.6608</v>
+        <v>31.2255</v>
       </c>
       <c r="E38" t="n">
-        <v>18.649</v>
+        <v>18.6308</v>
       </c>
       <c r="F38" t="n">
-        <v>29.986</v>
+        <v>29.8818</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>22.7855</v>
+        <v>22.8156</v>
       </c>
       <c r="C39" t="n">
-        <v>18.1448</v>
+        <v>18.2059</v>
       </c>
       <c r="D39" t="n">
-        <v>31.5755</v>
+        <v>31.159</v>
       </c>
       <c r="E39" t="n">
-        <v>18.1969</v>
+        <v>18.2022</v>
       </c>
       <c r="F39" t="n">
-        <v>29.5986</v>
+        <v>29.5809</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>22.4629</v>
+        <v>22.49</v>
       </c>
       <c r="C40" t="n">
-        <v>18.0032</v>
+        <v>18.0992</v>
       </c>
       <c r="D40" t="n">
-        <v>31.77</v>
+        <v>31.4026</v>
       </c>
       <c r="E40" t="n">
-        <v>17.8221</v>
+        <v>17.8389</v>
       </c>
       <c r="F40" t="n">
-        <v>29.2626</v>
+        <v>29.2418</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>22.0486</v>
+        <v>22.1104</v>
       </c>
       <c r="C41" t="n">
-        <v>17.87</v>
+        <v>17.9798</v>
       </c>
       <c r="D41" t="n">
-        <v>31.8179</v>
+        <v>31.485</v>
       </c>
       <c r="E41" t="n">
-        <v>17.4226</v>
+        <v>17.4543</v>
       </c>
       <c r="F41" t="n">
-        <v>29.0031</v>
+        <v>29.0037</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>21.5733</v>
+        <v>21.6436</v>
       </c>
       <c r="C42" t="n">
-        <v>17.7254</v>
+        <v>17.7851</v>
       </c>
       <c r="D42" t="n">
-        <v>31.7541</v>
+        <v>31.3834</v>
       </c>
       <c r="E42" t="n">
-        <v>17.0699</v>
+        <v>17.1043</v>
       </c>
       <c r="F42" t="n">
-        <v>28.6796</v>
+        <v>28.6343</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>21.1774</v>
+        <v>21.2114</v>
       </c>
       <c r="C43" t="n">
-        <v>17.5883</v>
+        <v>17.706</v>
       </c>
       <c r="D43" t="n">
-        <v>31.8556</v>
+        <v>31.6416</v>
       </c>
       <c r="E43" t="n">
-        <v>16.7255</v>
+        <v>16.7515</v>
       </c>
       <c r="F43" t="n">
-        <v>28.329</v>
+        <v>28.3389</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>20.7001</v>
+        <v>20.7084</v>
       </c>
       <c r="C44" t="n">
-        <v>17.5413</v>
+        <v>17.5578</v>
       </c>
       <c r="D44" t="n">
-        <v>32.0521</v>
+        <v>31.7071</v>
       </c>
       <c r="E44" t="n">
-        <v>16.4041</v>
+        <v>16.4374</v>
       </c>
       <c r="F44" t="n">
-        <v>28.0765</v>
+        <v>28.0927</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>20.232</v>
+        <v>20.2621</v>
       </c>
       <c r="C45" t="n">
-        <v>17.4761</v>
+        <v>17.4223</v>
       </c>
       <c r="D45" t="n">
-        <v>32.1063</v>
+        <v>31.8299</v>
       </c>
       <c r="E45" t="n">
-        <v>16.1033</v>
+        <v>16.1154</v>
       </c>
       <c r="F45" t="n">
-        <v>27.8034</v>
+        <v>27.851</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>19.9023</v>
+        <v>19.8509</v>
       </c>
       <c r="C46" t="n">
-        <v>17.3682</v>
+        <v>17.3784</v>
       </c>
       <c r="D46" t="n">
-        <v>32.241</v>
+        <v>31.9195</v>
       </c>
       <c r="E46" t="n">
-        <v>15.7708</v>
+        <v>15.7761</v>
       </c>
       <c r="F46" t="n">
-        <v>27.5459</v>
+        <v>27.5612</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>19.3312</v>
+        <v>19.3505</v>
       </c>
       <c r="C47" t="n">
-        <v>17.2684</v>
+        <v>17.2686</v>
       </c>
       <c r="D47" t="n">
-        <v>32.4719</v>
+        <v>32.3943</v>
       </c>
       <c r="E47" t="n">
-        <v>15.485</v>
+        <v>15.5088</v>
       </c>
       <c r="F47" t="n">
-        <v>27.193</v>
+        <v>27.2286</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>18.8381</v>
+        <v>18.909</v>
       </c>
       <c r="C48" t="n">
-        <v>17.2136</v>
+        <v>17.2204</v>
       </c>
       <c r="D48" t="n">
-        <v>32.4853</v>
+        <v>32.5228</v>
       </c>
       <c r="E48" t="n">
-        <v>20.6561</v>
+        <v>20.7877</v>
       </c>
       <c r="F48" t="n">
-        <v>31.27</v>
+        <v>31.3697</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>18.2989</v>
+        <v>18.3013</v>
       </c>
       <c r="C49" t="n">
-        <v>17.158</v>
+        <v>17.1666</v>
       </c>
       <c r="D49" t="n">
-        <v>32.3882</v>
+        <v>32.7859</v>
       </c>
       <c r="E49" t="n">
-        <v>20.1855</v>
+        <v>20.1736</v>
       </c>
       <c r="F49" t="n">
-        <v>30.9235</v>
+        <v>30.9284</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>17.8005</v>
+        <v>17.7575</v>
       </c>
       <c r="C50" t="n">
-        <v>17.0817</v>
+        <v>17.1153</v>
       </c>
       <c r="D50" t="n">
-        <v>31.3669</v>
+        <v>31.9056</v>
       </c>
       <c r="E50" t="n">
-        <v>19.7578</v>
+        <v>19.7638</v>
       </c>
       <c r="F50" t="n">
-        <v>30.6715</v>
+        <v>30.544</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>16.9456</v>
+        <v>16.9014</v>
       </c>
       <c r="C51" t="n">
-        <v>18.4636</v>
+        <v>18.552</v>
       </c>
       <c r="D51" t="n">
-        <v>31.8231</v>
+        <v>31.9596</v>
       </c>
       <c r="E51" t="n">
-        <v>19.3098</v>
+        <v>19.3152</v>
       </c>
       <c r="F51" t="n">
-        <v>30.217</v>
+        <v>30.238</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>16.1966</v>
+        <v>16.229</v>
       </c>
       <c r="C52" t="n">
-        <v>18.3144</v>
+        <v>18.3942</v>
       </c>
       <c r="D52" t="n">
-        <v>31.9753</v>
+        <v>32.0289</v>
       </c>
       <c r="E52" t="n">
-        <v>18.7986</v>
+        <v>18.8276</v>
       </c>
       <c r="F52" t="n">
-        <v>29.9842</v>
+        <v>29.9111</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>22.9801</v>
+        <v>23.0055</v>
       </c>
       <c r="C53" t="n">
-        <v>18.1738</v>
+        <v>18.2065</v>
       </c>
       <c r="D53" t="n">
-        <v>32.0478</v>
+        <v>32.0337</v>
       </c>
       <c r="E53" t="n">
-        <v>18.3495</v>
+        <v>18.3774</v>
       </c>
       <c r="F53" t="n">
-        <v>29.6444</v>
+        <v>29.2166</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>22.6064</v>
+        <v>22.6458</v>
       </c>
       <c r="C54" t="n">
-        <v>18.0276</v>
+        <v>18.0747</v>
       </c>
       <c r="D54" t="n">
-        <v>32.1192</v>
+        <v>32.0241</v>
       </c>
       <c r="E54" t="n">
-        <v>17.9561</v>
+        <v>17.9823</v>
       </c>
       <c r="F54" t="n">
-        <v>29.4099</v>
+        <v>29.3835</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>22.2305</v>
+        <v>22.2864</v>
       </c>
       <c r="C55" t="n">
-        <v>17.9545</v>
+        <v>17.9483</v>
       </c>
       <c r="D55" t="n">
-        <v>32.2068</v>
+        <v>32.2039</v>
       </c>
       <c r="E55" t="n">
-        <v>17.637</v>
+        <v>17.6475</v>
       </c>
       <c r="F55" t="n">
-        <v>29.1112</v>
+        <v>29.0449</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>21.8284</v>
+        <v>21.8126</v>
       </c>
       <c r="C56" t="n">
-        <v>17.7926</v>
+        <v>17.8304</v>
       </c>
       <c r="D56" t="n">
-        <v>32.5334</v>
+        <v>32.5936</v>
       </c>
       <c r="E56" t="n">
-        <v>17.2843</v>
+        <v>17.2323</v>
       </c>
       <c r="F56" t="n">
-        <v>28.7588</v>
+        <v>28.2185</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>21.3749</v>
+        <v>21.3622</v>
       </c>
       <c r="C57" t="n">
-        <v>17.7272</v>
+        <v>17.7475</v>
       </c>
       <c r="D57" t="n">
-        <v>32.7146</v>
+        <v>32.6918</v>
       </c>
       <c r="E57" t="n">
-        <v>16.9295</v>
+        <v>16.9172</v>
       </c>
       <c r="F57" t="n">
-        <v>28.4682</v>
+        <v>27.8715</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>20.9202</v>
+        <v>20.9718</v>
       </c>
       <c r="C58" t="n">
-        <v>17.5852</v>
+        <v>17.6253</v>
       </c>
       <c r="D58" t="n">
-        <v>32.5668</v>
+        <v>33.0338</v>
       </c>
       <c r="E58" t="n">
-        <v>16.5874</v>
+        <v>16.6267</v>
       </c>
       <c r="F58" t="n">
-        <v>27.6627</v>
+        <v>27.675</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>20.4836</v>
+        <v>20.4799</v>
       </c>
       <c r="C59" t="n">
-        <v>17.5151</v>
+        <v>17.5386</v>
       </c>
       <c r="D59" t="n">
-        <v>32.7751</v>
+        <v>33.1564</v>
       </c>
       <c r="E59" t="n">
-        <v>16.2635</v>
+        <v>16.286</v>
       </c>
       <c r="F59" t="n">
-        <v>27.2942</v>
+        <v>27.3397</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>19.9365</v>
+        <v>19.9519</v>
       </c>
       <c r="C60" t="n">
-        <v>17.4474</v>
+        <v>17.4779</v>
       </c>
       <c r="D60" t="n">
-        <v>33.1077</v>
+        <v>33.3709</v>
       </c>
       <c r="E60" t="n">
-        <v>15.9812</v>
+        <v>15.9713</v>
       </c>
       <c r="F60" t="n">
-        <v>27.028</v>
+        <v>27.0343</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>19.4983</v>
+        <v>19.486</v>
       </c>
       <c r="C61" t="n">
-        <v>17.3606</v>
+        <v>17.3634</v>
       </c>
       <c r="D61" t="n">
-        <v>33.7275</v>
+        <v>33.7188</v>
       </c>
       <c r="E61" t="n">
-        <v>15.6751</v>
+        <v>15.6712</v>
       </c>
       <c r="F61" t="n">
-        <v>27.2872</v>
+        <v>27.3158</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>18.9572</v>
+        <v>18.9538</v>
       </c>
       <c r="C62" t="n">
-        <v>17.2642</v>
+        <v>17.2927</v>
       </c>
       <c r="D62" t="n">
-        <v>34.114</v>
+        <v>34.159</v>
       </c>
       <c r="E62" t="n">
-        <v>15.3522</v>
+        <v>15.3872</v>
       </c>
       <c r="F62" t="n">
-        <v>27.0581</v>
+        <v>26.4331</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>18.4479</v>
+        <v>18.415</v>
       </c>
       <c r="C63" t="n">
-        <v>17.2564</v>
+        <v>17.244</v>
       </c>
       <c r="D63" t="n">
-        <v>34.4234</v>
+        <v>34.4726</v>
       </c>
       <c r="E63" t="n">
-        <v>21.2019</v>
+        <v>21.4545</v>
       </c>
       <c r="F63" t="n">
-        <v>30.8087</v>
+        <v>30.7459</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>17.8419</v>
+        <v>17.8823</v>
       </c>
       <c r="C64" t="n">
-        <v>17.1849</v>
+        <v>17.1565</v>
       </c>
       <c r="D64" t="n">
-        <v>37.9381</v>
+        <v>38.3302</v>
       </c>
       <c r="E64" t="n">
-        <v>20.8226</v>
+        <v>20.9182</v>
       </c>
       <c r="F64" t="n">
-        <v>30.4152</v>
+        <v>30.4228</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>17.1636</v>
+        <v>17.1682</v>
       </c>
       <c r="C65" t="n">
-        <v>18.7501</v>
+        <v>18.7622</v>
       </c>
       <c r="D65" t="n">
-        <v>38.1899</v>
+        <v>38.4351</v>
       </c>
       <c r="E65" t="n">
-        <v>20.4047</v>
+        <v>20.513</v>
       </c>
       <c r="F65" t="n">
-        <v>30.093</v>
+        <v>30.0527</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>16.3547</v>
+        <v>16.3304</v>
       </c>
       <c r="C66" t="n">
-        <v>18.5194</v>
+        <v>18.5165</v>
       </c>
       <c r="D66" t="n">
-        <v>38.4956</v>
+        <v>38.9534</v>
       </c>
       <c r="E66" t="n">
-        <v>19.8474</v>
+        <v>19.9924</v>
       </c>
       <c r="F66" t="n">
-        <v>29.7786</v>
+        <v>29.6809</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>23.1161</v>
+        <v>23.142</v>
       </c>
       <c r="C67" t="n">
-        <v>18.3436</v>
+        <v>18.3555</v>
       </c>
       <c r="D67" t="n">
-        <v>38.6811</v>
+        <v>39.1398</v>
       </c>
       <c r="E67" t="n">
-        <v>19.3295</v>
+        <v>19.4004</v>
       </c>
       <c r="F67" t="n">
-        <v>29.384</v>
+        <v>29.3169</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>22.7879</v>
+        <v>22.831</v>
       </c>
       <c r="C68" t="n">
-        <v>18.1894</v>
+        <v>18.2261</v>
       </c>
       <c r="D68" t="n">
-        <v>38.9282</v>
+        <v>39.5547</v>
       </c>
       <c r="E68" t="n">
-        <v>18.6141</v>
+        <v>18.6785</v>
       </c>
       <c r="F68" t="n">
-        <v>29.1153</v>
+        <v>29.0637</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>22.3801</v>
+        <v>22.3837</v>
       </c>
       <c r="C69" t="n">
-        <v>18.0694</v>
+        <v>18.0784</v>
       </c>
       <c r="D69" t="n">
-        <v>38.9957</v>
+        <v>39.4486</v>
       </c>
       <c r="E69" t="n">
-        <v>18.1103</v>
+        <v>18.1387</v>
       </c>
       <c r="F69" t="n">
-        <v>28.8108</v>
+        <v>28.797</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>21.9558</v>
+        <v>21.9825</v>
       </c>
       <c r="C70" t="n">
-        <v>18.0632</v>
+        <v>18.0911</v>
       </c>
       <c r="D70" t="n">
-        <v>39.2521</v>
+        <v>39.7536</v>
       </c>
       <c r="E70" t="n">
-        <v>17.6572</v>
+        <v>17.6532</v>
       </c>
       <c r="F70" t="n">
-        <v>28.3169</v>
+        <v>28.3865</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>21.5131</v>
+        <v>21.5345</v>
       </c>
       <c r="C71" t="n">
-        <v>17.9451</v>
+        <v>17.9498</v>
       </c>
       <c r="D71" t="n">
-        <v>39.4744</v>
+        <v>40.0523</v>
       </c>
       <c r="E71" t="n">
-        <v>17.1672</v>
+        <v>17.159</v>
       </c>
       <c r="F71" t="n">
-        <v>28.094</v>
+        <v>28.0983</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>21.0743</v>
+        <v>21.0519</v>
       </c>
       <c r="C72" t="n">
-        <v>17.8268</v>
+        <v>17.8459</v>
       </c>
       <c r="D72" t="n">
-        <v>39.7263</v>
+        <v>40.2284</v>
       </c>
       <c r="E72" t="n">
-        <v>16.7463</v>
+        <v>16.7601</v>
       </c>
       <c r="F72" t="n">
-        <v>28.3749</v>
+        <v>28.3436</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>20.581</v>
+        <v>20.5775</v>
       </c>
       <c r="C73" t="n">
-        <v>17.7304</v>
+        <v>17.7768</v>
       </c>
       <c r="D73" t="n">
-        <v>39.6295</v>
+        <v>40.149</v>
       </c>
       <c r="E73" t="n">
-        <v>16.4385</v>
+        <v>16.4424</v>
       </c>
       <c r="F73" t="n">
-        <v>28.1034</v>
+        <v>28.0916</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>20.0595</v>
+        <v>20.0873</v>
       </c>
       <c r="C74" t="n">
-        <v>17.6526</v>
+        <v>17.6704</v>
       </c>
       <c r="D74" t="n">
-        <v>39.7279</v>
+        <v>40.14</v>
       </c>
       <c r="E74" t="n">
-        <v>16.1052</v>
+        <v>16.1004</v>
       </c>
       <c r="F74" t="n">
-        <v>27.8386</v>
+        <v>27.8307</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>19.5809</v>
+        <v>19.6422</v>
       </c>
       <c r="C75" t="n">
-        <v>17.5511</v>
+        <v>17.5726</v>
       </c>
       <c r="D75" t="n">
-        <v>39.6626</v>
+        <v>40.1826</v>
       </c>
       <c r="E75" t="n">
-        <v>15.803</v>
+        <v>15.8222</v>
       </c>
       <c r="F75" t="n">
-        <v>27.5073</v>
+        <v>26.8913</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>19.0617</v>
+        <v>19.089</v>
       </c>
       <c r="C76" t="n">
-        <v>17.471</v>
+        <v>17.4795</v>
       </c>
       <c r="D76" t="n">
-        <v>39.9246</v>
+        <v>40.2224</v>
       </c>
       <c r="E76" t="n">
-        <v>15.4917</v>
+        <v>15.4863</v>
       </c>
       <c r="F76" t="n">
-        <v>27.2068</v>
+        <v>26.5872</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>18.5908</v>
+        <v>18.6046</v>
       </c>
       <c r="C77" t="n">
-        <v>17.3911</v>
+        <v>17.4005</v>
       </c>
       <c r="D77" t="n">
-        <v>39.8497</v>
+        <v>40.1444</v>
       </c>
       <c r="E77" t="n">
-        <v>20.8607</v>
+        <v>20.8679</v>
       </c>
       <c r="F77" t="n">
-        <v>31.2252</v>
+        <v>31.2433</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>18.0208</v>
+        <v>17.985</v>
       </c>
       <c r="C78" t="n">
-        <v>17.1937</v>
+        <v>17.2007</v>
       </c>
       <c r="D78" t="n">
-        <v>46.2046</v>
+        <v>47.3931</v>
       </c>
       <c r="E78" t="n">
-        <v>20.4003</v>
+        <v>20.3519</v>
       </c>
       <c r="F78" t="n">
-        <v>30.8395</v>
+        <v>30.8985</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>17.293</v>
+        <v>17.3621</v>
       </c>
       <c r="C79" t="n">
-        <v>19.0466</v>
+        <v>18.9338</v>
       </c>
       <c r="D79" t="n">
-        <v>45.8592</v>
+        <v>47.0991</v>
       </c>
       <c r="E79" t="n">
-        <v>19.8507</v>
+        <v>19.7942</v>
       </c>
       <c r="F79" t="n">
-        <v>30.5337</v>
+        <v>30.5951</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>16.5819</v>
+        <v>16.547</v>
       </c>
       <c r="C80" t="n">
-        <v>18.8398</v>
+        <v>18.8348</v>
       </c>
       <c r="D80" t="n">
-        <v>45.5053</v>
+        <v>46.4342</v>
       </c>
       <c r="E80" t="n">
-        <v>19.3083</v>
+        <v>19.3033</v>
       </c>
       <c r="F80" t="n">
-        <v>30.2786</v>
+        <v>30.3266</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>23.2431</v>
+        <v>23.2845</v>
       </c>
       <c r="C81" t="n">
-        <v>18.6858</v>
+        <v>18.6683</v>
       </c>
       <c r="D81" t="n">
-        <v>45.0721</v>
+        <v>46.1974</v>
       </c>
       <c r="E81" t="n">
-        <v>18.8745</v>
+        <v>18.8205</v>
       </c>
       <c r="F81" t="n">
-        <v>29.9454</v>
+        <v>30.0123</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>22.9051</v>
+        <v>22.925</v>
       </c>
       <c r="C82" t="n">
-        <v>18.4629</v>
+        <v>18.4638</v>
       </c>
       <c r="D82" t="n">
-        <v>44.322</v>
+        <v>44.1731</v>
       </c>
       <c r="E82" t="n">
-        <v>18.4707</v>
+        <v>18.3988</v>
       </c>
       <c r="F82" t="n">
-        <v>29.6139</v>
+        <v>29.6196</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>22.5426</v>
+        <v>22.5578</v>
       </c>
       <c r="C83" t="n">
-        <v>18.3635</v>
+        <v>18.3383</v>
       </c>
       <c r="D83" t="n">
-        <v>44.5343</v>
+        <v>44.3918</v>
       </c>
       <c r="E83" t="n">
-        <v>18.0319</v>
+        <v>18.0047</v>
       </c>
       <c r="F83" t="n">
-        <v>29.3</v>
+        <v>29.3283</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>22.1247</v>
+        <v>22.1187</v>
       </c>
       <c r="C84" t="n">
-        <v>18.1899</v>
+        <v>18.1929</v>
       </c>
       <c r="D84" t="n">
-        <v>43.6457</v>
+        <v>43.5408</v>
       </c>
       <c r="E84" t="n">
-        <v>17.6215</v>
+        <v>17.6431</v>
       </c>
       <c r="F84" t="n">
-        <v>29.014</v>
+        <v>29.0134</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>21.6797</v>
+        <v>21.6596</v>
       </c>
       <c r="C85" t="n">
-        <v>17.9579</v>
+        <v>17.9331</v>
       </c>
       <c r="D85" t="n">
-        <v>43.2714</v>
+        <v>43.2274</v>
       </c>
       <c r="E85" t="n">
-        <v>17.2916</v>
+        <v>17.2611</v>
       </c>
       <c r="F85" t="n">
-        <v>28.6967</v>
+        <v>28.6827</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>21.2083</v>
+        <v>21.2056</v>
       </c>
       <c r="C86" t="n">
-        <v>17.8171</v>
+        <v>17.8274</v>
       </c>
       <c r="D86" t="n">
-        <v>42.7913</v>
+        <v>42.7139</v>
       </c>
       <c r="E86" t="n">
-        <v>16.9425</v>
+        <v>16.9148</v>
       </c>
       <c r="F86" t="n">
-        <v>28.4257</v>
+        <v>28.433</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>20.7068</v>
+        <v>20.7055</v>
       </c>
       <c r="C87" t="n">
-        <v>17.7093</v>
+        <v>17.7003</v>
       </c>
       <c r="D87" t="n">
-        <v>42.6924</v>
+        <v>42.4732</v>
       </c>
       <c r="E87" t="n">
-        <v>16.6012</v>
+        <v>16.5703</v>
       </c>
       <c r="F87" t="n">
-        <v>28.1636</v>
+        <v>28.1625</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>20.2506</v>
+        <v>20.2456</v>
       </c>
       <c r="C88" t="n">
-        <v>17.6169</v>
+        <v>17.6109</v>
       </c>
       <c r="D88" t="n">
-        <v>42.4387</v>
+        <v>42.3632</v>
       </c>
       <c r="E88" t="n">
-        <v>16.3011</v>
+        <v>16.2737</v>
       </c>
       <c r="F88" t="n">
-        <v>27.8316</v>
+        <v>27.8594</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>19.736</v>
+        <v>19.703</v>
       </c>
       <c r="C89" t="n">
-        <v>17.5337</v>
+        <v>17.5123</v>
       </c>
       <c r="D89" t="n">
-        <v>42.0162</v>
+        <v>41.8915</v>
       </c>
       <c r="E89" t="n">
-        <v>16.0087</v>
+        <v>15.9804</v>
       </c>
       <c r="F89" t="n">
-        <v>27.5848</v>
+        <v>27.5837</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>19.2775</v>
+        <v>19.2496</v>
       </c>
       <c r="C90" t="n">
-        <v>17.4517</v>
+        <v>17.4372</v>
       </c>
       <c r="D90" t="n">
-        <v>41.9475</v>
+        <v>41.7469</v>
       </c>
       <c r="E90" t="n">
-        <v>15.6589</v>
+        <v>15.6528</v>
       </c>
       <c r="F90" t="n">
-        <v>27.2494</v>
+        <v>27.2424</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>18.7703</v>
+        <v>18.7449</v>
       </c>
       <c r="C91" t="n">
-        <v>17.3359</v>
+        <v>17.3576</v>
       </c>
       <c r="D91" t="n">
-        <v>41.7798</v>
+        <v>41.781</v>
       </c>
       <c r="E91" t="n">
-        <v>20.9676</v>
+        <v>20.9141</v>
       </c>
       <c r="F91" t="n">
-        <v>31.2912</v>
+        <v>31.3226</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>18.1685</v>
+        <v>18.1428</v>
       </c>
       <c r="C92" t="n">
-        <v>17.2815</v>
+        <v>17.2767</v>
       </c>
       <c r="D92" t="n">
-        <v>46.1242</v>
+        <v>45.8814</v>
       </c>
       <c r="E92" t="n">
-        <v>20.5157</v>
+        <v>20.5131</v>
       </c>
       <c r="F92" t="n">
-        <v>31.0111</v>
+        <v>31.0856</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>17.5491</v>
+        <v>17.5125</v>
       </c>
       <c r="C93" t="n">
-        <v>17.1548</v>
+        <v>17.1802</v>
       </c>
       <c r="D93" t="n">
-        <v>45.7833</v>
+        <v>45.3659</v>
       </c>
       <c r="E93" t="n">
-        <v>19.9608</v>
+        <v>19.941</v>
       </c>
       <c r="F93" t="n">
-        <v>30.6779</v>
+        <v>30.7232</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>16.8793</v>
+        <v>16.8722</v>
       </c>
       <c r="C94" t="n">
-        <v>18.7839</v>
+        <v>18.7743</v>
       </c>
       <c r="D94" t="n">
-        <v>45.2982</v>
+        <v>44.8239</v>
       </c>
       <c r="E94" t="n">
-        <v>19.4377</v>
+        <v>19.4279</v>
       </c>
       <c r="F94" t="n">
-        <v>30.3347</v>
+        <v>30.3597</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>23.3411</v>
+        <v>23.3281</v>
       </c>
       <c r="C95" t="n">
-        <v>18.6048</v>
+        <v>18.6122</v>
       </c>
       <c r="D95" t="n">
-        <v>44.4985</v>
+        <v>44.2053</v>
       </c>
       <c r="E95" t="n">
-        <v>18.9576</v>
+        <v>18.9456</v>
       </c>
       <c r="F95" t="n">
-        <v>30.249</v>
+        <v>30.2899</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>23.0099</v>
+        <v>23.0001</v>
       </c>
       <c r="C96" t="n">
-        <v>18.4384</v>
+        <v>18.463</v>
       </c>
       <c r="D96" t="n">
-        <v>44.107</v>
+        <v>43.8738</v>
       </c>
       <c r="E96" t="n">
-        <v>18.5024</v>
+        <v>18.4799</v>
       </c>
       <c r="F96" t="n">
-        <v>29.4034</v>
+        <v>29.3917</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>22.6134</v>
+        <v>22.6078</v>
       </c>
       <c r="C97" t="n">
-        <v>18.2477</v>
+        <v>18.3132</v>
       </c>
       <c r="D97" t="n">
-        <v>43.7488</v>
+        <v>43.3578</v>
       </c>
       <c r="E97" t="n">
-        <v>18.079</v>
+        <v>18.0531</v>
       </c>
       <c r="F97" t="n">
-        <v>28.9125</v>
+        <v>28.9234</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>22.2057</v>
+        <v>22.1879</v>
       </c>
       <c r="C98" t="n">
-        <v>18.1202</v>
+        <v>18.1217</v>
       </c>
       <c r="D98" t="n">
-        <v>43.1232</v>
+        <v>42.7883</v>
       </c>
       <c r="E98" t="n">
-        <v>17.6726</v>
+        <v>17.6568</v>
       </c>
       <c r="F98" t="n">
-        <v>28.4573</v>
+        <v>28.4966</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>21.8015</v>
+        <v>21.7824</v>
       </c>
       <c r="C99" t="n">
-        <v>17.9698</v>
+        <v>17.9508</v>
       </c>
       <c r="D99" t="n">
-        <v>42.9338</v>
+        <v>42.7223</v>
       </c>
       <c r="E99" t="n">
-        <v>17.2982</v>
+        <v>17.2992</v>
       </c>
       <c r="F99" t="n">
-        <v>28.1379</v>
+        <v>28.1831</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>21.3091</v>
+        <v>21.3257</v>
       </c>
       <c r="C100" t="n">
-        <v>17.9596</v>
+        <v>17.9746</v>
       </c>
       <c r="D100" t="n">
-        <v>42.7167</v>
+        <v>42.5726</v>
       </c>
       <c r="E100" t="n">
-        <v>16.9861</v>
+        <v>16.9613</v>
       </c>
       <c r="F100" t="n">
-        <v>27.8499</v>
+        <v>27.8701</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>20.8244</v>
+        <v>20.8688</v>
       </c>
       <c r="C101" t="n">
-        <v>17.8414</v>
+        <v>17.8601</v>
       </c>
       <c r="D101" t="n">
-        <v>42.3614</v>
+        <v>42.1748</v>
       </c>
       <c r="E101" t="n">
-        <v>16.6517</v>
+        <v>16.6174</v>
       </c>
       <c r="F101" t="n">
-        <v>27.5443</v>
+        <v>27.5722</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>20.3827</v>
+        <v>20.3887</v>
       </c>
       <c r="C102" t="n">
-        <v>17.7309</v>
+        <v>17.7417</v>
       </c>
       <c r="D102" t="n">
-        <v>41.8468</v>
+        <v>41.7458</v>
       </c>
       <c r="E102" t="n">
-        <v>16.3136</v>
+        <v>16.3034</v>
       </c>
       <c r="F102" t="n">
-        <v>27.2692</v>
+        <v>27.2817</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>19.8659</v>
+        <v>19.9248</v>
       </c>
       <c r="C103" t="n">
-        <v>17.6395</v>
+        <v>17.6446</v>
       </c>
       <c r="D103" t="n">
-        <v>41.5223</v>
+        <v>41.5297</v>
       </c>
       <c r="E103" t="n">
-        <v>15.9741</v>
+        <v>15.9763</v>
       </c>
       <c r="F103" t="n">
-        <v>27.0026</v>
+        <v>26.9985</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>19.3716</v>
+        <v>19.3814</v>
       </c>
       <c r="C104" t="n">
-        <v>17.54</v>
+        <v>17.5407</v>
       </c>
       <c r="D104" t="n">
-        <v>41.3139</v>
+        <v>41.3084</v>
       </c>
       <c r="E104" t="n">
-        <v>15.6801</v>
+        <v>15.6789</v>
       </c>
       <c r="F104" t="n">
-        <v>26.664</v>
+        <v>26.7007</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>18.8196</v>
+        <v>18.8155</v>
       </c>
       <c r="C105" t="n">
-        <v>17.438</v>
+        <v>17.4321</v>
       </c>
       <c r="D105" t="n">
-        <v>40.9544</v>
+        <v>41.0231</v>
       </c>
       <c r="E105" t="n">
-        <v>20.9772</v>
+        <v>20.9688</v>
       </c>
       <c r="F105" t="n">
-        <v>30.8074</v>
+        <v>30.9173</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>18.2904</v>
+        <v>18.3416</v>
       </c>
       <c r="C106" t="n">
-        <v>17.3455</v>
+        <v>17.3486</v>
       </c>
       <c r="D106" t="n">
-        <v>40.1959</v>
+        <v>40.0882</v>
       </c>
       <c r="E106" t="n">
-        <v>20.4593</v>
+        <v>20.4484</v>
       </c>
       <c r="F106" t="n">
-        <v>30.4278</v>
+        <v>30.5492</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>17.6648</v>
+        <v>17.7113</v>
       </c>
       <c r="C107" t="n">
-        <v>17.2709</v>
+        <v>17.2721</v>
       </c>
       <c r="D107" t="n">
-        <v>43.6993</v>
+        <v>43.9038</v>
       </c>
       <c r="E107" t="n">
-        <v>19.9804</v>
+        <v>19.951</v>
       </c>
       <c r="F107" t="n">
-        <v>30.1449</v>
+        <v>30.237</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>16.9683</v>
+        <v>16.9734</v>
       </c>
       <c r="C108" t="n">
-        <v>18.9478</v>
+        <v>18.9322</v>
       </c>
       <c r="D108" t="n">
-        <v>43.835</v>
+        <v>43.8539</v>
       </c>
       <c r="E108" t="n">
-        <v>19.5252</v>
+        <v>19.536</v>
       </c>
       <c r="F108" t="n">
-        <v>29.8032</v>
+        <v>29.8738</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>16.1718</v>
+        <v>16.2044</v>
       </c>
       <c r="C109" t="n">
-        <v>18.7642</v>
+        <v>18.7366</v>
       </c>
       <c r="D109" t="n">
-        <v>43.2641</v>
+        <v>43.293</v>
       </c>
       <c r="E109" t="n">
-        <v>19.0375</v>
+        <v>19.048</v>
       </c>
       <c r="F109" t="n">
-        <v>29.5467</v>
+        <v>29.5604</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>23.0808</v>
+        <v>23.0906</v>
       </c>
       <c r="C110" t="n">
-        <v>18.4376</v>
+        <v>18.4953</v>
       </c>
       <c r="D110" t="n">
-        <v>42.7849</v>
+        <v>42.9188</v>
       </c>
       <c r="E110" t="n">
-        <v>18.6059</v>
+        <v>18.6321</v>
       </c>
       <c r="F110" t="n">
-        <v>29.8982</v>
+        <v>29.7775</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>22.6978</v>
+        <v>22.7188</v>
       </c>
       <c r="C111" t="n">
-        <v>18.2891</v>
+        <v>18.3631</v>
       </c>
       <c r="D111" t="n">
-        <v>42.4636</v>
+        <v>42.5661</v>
       </c>
       <c r="E111" t="n">
-        <v>18.1732</v>
+        <v>18.1934</v>
       </c>
       <c r="F111" t="n">
-        <v>29.5388</v>
+        <v>29.4771</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>22.2984</v>
+        <v>22.3069</v>
       </c>
       <c r="C112" t="n">
-        <v>18.1476</v>
+        <v>18.1837</v>
       </c>
       <c r="D112" t="n">
-        <v>42.0859</v>
+        <v>42.1072</v>
       </c>
       <c r="E112" t="n">
-        <v>17.768</v>
+        <v>17.7752</v>
       </c>
       <c r="F112" t="n">
-        <v>29.2542</v>
+        <v>29.1273</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>21.8693</v>
+        <v>21.898</v>
       </c>
       <c r="C113" t="n">
-        <v>17.9916</v>
+        <v>18.0131</v>
       </c>
       <c r="D113" t="n">
-        <v>41.357</v>
+        <v>41.5069</v>
       </c>
       <c r="E113" t="n">
-        <v>17.3859</v>
+        <v>17.3916</v>
       </c>
       <c r="F113" t="n">
-        <v>28.9677</v>
+        <v>28.8531</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>21.426</v>
+        <v>21.4257</v>
       </c>
       <c r="C114" t="n">
-        <v>17.8432</v>
+        <v>17.8696</v>
       </c>
       <c r="D114" t="n">
-        <v>40.9935</v>
+        <v>41.1489</v>
       </c>
       <c r="E114" t="n">
-        <v>17.0492</v>
+        <v>17.0389</v>
       </c>
       <c r="F114" t="n">
-        <v>28.6609</v>
+        <v>28.5556</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>20.9658</v>
+        <v>20.9646</v>
       </c>
       <c r="C115" t="n">
-        <v>17.7482</v>
+        <v>17.7641</v>
       </c>
       <c r="D115" t="n">
-        <v>40.5329</v>
+        <v>40.689</v>
       </c>
       <c r="E115" t="n">
-        <v>16.7113</v>
+        <v>16.7172</v>
       </c>
       <c r="F115" t="n">
-        <v>28.3949</v>
+        <v>28.2704</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>20.4986</v>
+        <v>20.494</v>
       </c>
       <c r="C116" t="n">
-        <v>17.6311</v>
+        <v>17.6738</v>
       </c>
       <c r="D116" t="n">
-        <v>40.2482</v>
+        <v>40.478</v>
       </c>
       <c r="E116" t="n">
-        <v>16.403</v>
+        <v>16.3902</v>
       </c>
       <c r="F116" t="n">
-        <v>27.4691</v>
+        <v>27.367</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>19.9785</v>
+        <v>19.9762</v>
       </c>
       <c r="C117" t="n">
-        <v>17.5477</v>
+        <v>17.5626</v>
       </c>
       <c r="D117" t="n">
-        <v>39.9084</v>
+        <v>40.1539</v>
       </c>
       <c r="E117" t="n">
-        <v>16.0786</v>
+        <v>16.0609</v>
       </c>
       <c r="F117" t="n">
-        <v>27.1847</v>
+        <v>27.1041</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>19.4328</v>
+        <v>19.4571</v>
       </c>
       <c r="C118" t="n">
-        <v>17.4309</v>
+        <v>17.4548</v>
       </c>
       <c r="D118" t="n">
-        <v>39.5915</v>
+        <v>39.8752</v>
       </c>
       <c r="E118" t="n">
-        <v>15.7692</v>
+        <v>15.7628</v>
       </c>
       <c r="F118" t="n">
-        <v>26.891</v>
+        <v>26.801</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>18.9347</v>
+        <v>18.9619</v>
       </c>
       <c r="C119" t="n">
-        <v>17.373</v>
+        <v>17.3762</v>
       </c>
       <c r="D119" t="n">
-        <v>39.3372</v>
+        <v>39.6066</v>
       </c>
       <c r="E119" t="n">
-        <v>21.2206</v>
+        <v>21.1935</v>
       </c>
       <c r="F119" t="n">
-        <v>31.5908</v>
+        <v>31.5454</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>18.3649</v>
+        <v>18.3867</v>
       </c>
       <c r="C120" t="n">
-        <v>17.2717</v>
+        <v>17.3091</v>
       </c>
       <c r="D120" t="n">
-        <v>39.9928</v>
+        <v>40.2175</v>
       </c>
       <c r="E120" t="n">
-        <v>20.6886</v>
+        <v>20.6734</v>
       </c>
       <c r="F120" t="n">
-        <v>31.1344</v>
+        <v>31.1292</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>17.8163</v>
+        <v>17.8409</v>
       </c>
       <c r="C121" t="n">
-        <v>17.1929</v>
+        <v>17.2083</v>
       </c>
       <c r="D121" t="n">
-        <v>47.1088</v>
+        <v>47.8172</v>
       </c>
       <c r="E121" t="n">
-        <v>20.1518</v>
+        <v>20.1451</v>
       </c>
       <c r="F121" t="n">
-        <v>30.8619</v>
+        <v>30.8458</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>17.1354</v>
+        <v>17.1619</v>
       </c>
       <c r="C122" t="n">
-        <v>18.8502</v>
+        <v>18.9122</v>
       </c>
       <c r="D122" t="n">
-        <v>46.5281</v>
+        <v>47.1282</v>
       </c>
       <c r="E122" t="n">
-        <v>19.6445</v>
+        <v>19.6733</v>
       </c>
       <c r="F122" t="n">
-        <v>30.0251</v>
+        <v>29.9885</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>16.3404</v>
+        <v>16.3414</v>
       </c>
       <c r="C123" t="n">
-        <v>18.6614</v>
+        <v>18.6676</v>
       </c>
       <c r="D123" t="n">
-        <v>45.5803</v>
+        <v>46.0651</v>
       </c>
       <c r="E123" t="n">
-        <v>19.1403</v>
+        <v>19.1616</v>
       </c>
       <c r="F123" t="n">
-        <v>30.179</v>
+        <v>30.2761</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>23.1567</v>
+        <v>23.1619</v>
       </c>
       <c r="C124" t="n">
-        <v>18.4934</v>
+        <v>18.5435</v>
       </c>
       <c r="D124" t="n">
-        <v>44.8936</v>
+        <v>45.8962</v>
       </c>
       <c r="E124" t="n">
-        <v>18.6717</v>
+        <v>18.7257</v>
       </c>
       <c r="F124" t="n">
-        <v>29.5311</v>
+        <v>29.6709</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>22.786</v>
+        <v>22.7639</v>
       </c>
       <c r="C125" t="n">
-        <v>18.3018</v>
+        <v>18.3759</v>
       </c>
       <c r="D125" t="n">
-        <v>44.2541</v>
+        <v>45.3863</v>
       </c>
       <c r="E125" t="n">
-        <v>18.2765</v>
+        <v>18.2917</v>
       </c>
       <c r="F125" t="n">
-        <v>29.1769</v>
+        <v>29.2415</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>22.38</v>
+        <v>22.3794</v>
       </c>
       <c r="C126" t="n">
-        <v>18.1524</v>
+        <v>18.1787</v>
       </c>
       <c r="D126" t="n">
-        <v>43.6925</v>
+        <v>44.5767</v>
       </c>
       <c r="E126" t="n">
-        <v>17.8429</v>
+        <v>17.86</v>
       </c>
       <c r="F126" t="n">
-        <v>28.8556</v>
+        <v>29.0064</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>21.9882</v>
+        <v>22.0026</v>
       </c>
       <c r="C127" t="n">
-        <v>18.0257</v>
+        <v>18.0199</v>
       </c>
       <c r="D127" t="n">
-        <v>43.4383</v>
+        <v>44.1417</v>
       </c>
       <c r="E127" t="n">
-        <v>17.4344</v>
+        <v>17.4618</v>
       </c>
       <c r="F127" t="n">
-        <v>29.0243</v>
+        <v>29.0748</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>21.5152</v>
+        <v>21.5401</v>
       </c>
       <c r="C128" t="n">
-        <v>17.8992</v>
+        <v>17.9063</v>
       </c>
       <c r="D128" t="n">
-        <v>43.006</v>
+        <v>43.6373</v>
       </c>
       <c r="E128" t="n">
-        <v>17.1064</v>
+        <v>17.1163</v>
       </c>
       <c r="F128" t="n">
-        <v>28.7174</v>
+        <v>28.7611</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>21.0368</v>
+        <v>21.0555</v>
       </c>
       <c r="C129" t="n">
-        <v>17.7479</v>
+        <v>17.8058</v>
       </c>
       <c r="D129" t="n">
-        <v>42.616</v>
+        <v>43.3017</v>
       </c>
       <c r="E129" t="n">
-        <v>16.779</v>
+        <v>16.7901</v>
       </c>
       <c r="F129" t="n">
-        <v>28.4155</v>
+        <v>28.5022</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>20.5545</v>
+        <v>20.5743</v>
       </c>
       <c r="C130" t="n">
-        <v>17.6464</v>
+        <v>17.6762</v>
       </c>
       <c r="D130" t="n">
-        <v>42.2202</v>
+        <v>42.842</v>
       </c>
       <c r="E130" t="n">
-        <v>16.4432</v>
+        <v>16.4413</v>
       </c>
       <c r="F130" t="n">
-        <v>27.4992</v>
+        <v>27.5462</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>20.0742</v>
+        <v>20.1414</v>
       </c>
       <c r="C131" t="n">
-        <v>17.5421</v>
+        <v>17.6226</v>
       </c>
       <c r="D131" t="n">
-        <v>41.7795</v>
+        <v>42.3847</v>
       </c>
       <c r="E131" t="n">
-        <v>16.1038</v>
+        <v>16.1284</v>
       </c>
       <c r="F131" t="n">
-        <v>27.2061</v>
+        <v>27.2771</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>19.5702</v>
+        <v>19.5961</v>
       </c>
       <c r="C132" t="n">
-        <v>17.4421</v>
+        <v>17.4684</v>
       </c>
       <c r="D132" t="n">
-        <v>41.4279</v>
+        <v>42.1399</v>
       </c>
       <c r="E132" t="n">
-        <v>15.8135</v>
+        <v>15.8328</v>
       </c>
       <c r="F132" t="n">
-        <v>26.919</v>
+        <v>26.9853</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>19.0587</v>
+        <v>19.0958</v>
       </c>
       <c r="C133" t="n">
-        <v>17.364</v>
+        <v>17.4021</v>
       </c>
       <c r="D133" t="n">
-        <v>41.0622</v>
+        <v>41.8418</v>
       </c>
       <c r="E133" t="n">
-        <v>15.5185</v>
+        <v>15.5213</v>
       </c>
       <c r="F133" t="n">
-        <v>27.2786</v>
+        <v>26.7017</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>18.5225</v>
+        <v>18.557</v>
       </c>
       <c r="C134" t="n">
-        <v>17.3</v>
+        <v>17.3055</v>
       </c>
       <c r="D134" t="n">
-        <v>40.8136</v>
+        <v>41.4996</v>
       </c>
       <c r="E134" t="n">
-        <v>20.7617</v>
+        <v>20.7988</v>
       </c>
       <c r="F134" t="n">
-        <v>30.7458</v>
+        <v>30.8528</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>17.9378</v>
+        <v>17.9989</v>
       </c>
       <c r="C135" t="n">
-        <v>17.2107</v>
+        <v>17.2778</v>
       </c>
       <c r="D135" t="n">
-        <v>47.1544</v>
+        <v>47.95</v>
       </c>
       <c r="E135" t="n">
-        <v>20.2496</v>
+        <v>20.2764</v>
       </c>
       <c r="F135" t="n">
-        <v>30.3832</v>
+        <v>30.4873</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>17.3434</v>
+        <v>17.3272</v>
       </c>
       <c r="C136" t="n">
-        <v>19.038</v>
+        <v>19.0665</v>
       </c>
       <c r="D136" t="n">
-        <v>47.0605</v>
+        <v>47.4707</v>
       </c>
       <c r="E136" t="n">
-        <v>19.71</v>
+        <v>19.7594</v>
       </c>
       <c r="F136" t="n">
-        <v>30.0515</v>
+        <v>30.0357</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>16.5102</v>
+        <v>16.5418</v>
       </c>
       <c r="C137" t="n">
-        <v>18.7118</v>
+        <v>18.7235</v>
       </c>
       <c r="D137" t="n">
-        <v>46.5268</v>
+        <v>47.4342</v>
       </c>
       <c r="E137" t="n">
-        <v>19.2307</v>
+        <v>19.2531</v>
       </c>
       <c r="F137" t="n">
-        <v>29.7157</v>
+        <v>29.6695</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>23.2438</v>
+        <v>23.261</v>
       </c>
       <c r="C138" t="n">
-        <v>18.6602</v>
+        <v>18.6726</v>
       </c>
       <c r="D138" t="n">
-        <v>45.8214</v>
+        <v>46.725</v>
       </c>
       <c r="E138" t="n">
-        <v>18.761</v>
+        <v>18.7479</v>
       </c>
       <c r="F138" t="n">
-        <v>29.265</v>
+        <v>29.3715</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>22.8771</v>
+        <v>22.9007</v>
       </c>
       <c r="C139" t="n">
-        <v>18.4762</v>
+        <v>18.4999</v>
       </c>
       <c r="D139" t="n">
-        <v>44.6501</v>
+        <v>45.7288</v>
       </c>
       <c r="E139" t="n">
-        <v>18.3225</v>
+        <v>18.3438</v>
       </c>
       <c r="F139" t="n">
-        <v>28.9265</v>
+        <v>29.0535</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>22.4793</v>
+        <v>22.4979</v>
       </c>
       <c r="C140" t="n">
-        <v>18.3081</v>
+        <v>18.3261</v>
       </c>
       <c r="D140" t="n">
-        <v>44.6549</v>
+        <v>45.1429</v>
       </c>
       <c r="E140" t="n">
-        <v>17.8937</v>
+        <v>17.9277</v>
       </c>
       <c r="F140" t="n">
-        <v>28.5997</v>
+        <v>28.6948</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>22.049</v>
+        <v>22.093</v>
       </c>
       <c r="C141" t="n">
-        <v>18.0602</v>
+        <v>18.0714</v>
       </c>
       <c r="D141" t="n">
-        <v>43.7542</v>
+        <v>44.7414</v>
       </c>
       <c r="E141" t="n">
-        <v>17.5297</v>
+        <v>17.5465</v>
       </c>
       <c r="F141" t="n">
-        <v>28.5406</v>
+        <v>28.4722</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>21.5859</v>
+        <v>21.6215</v>
       </c>
       <c r="C142" t="n">
-        <v>17.9211</v>
+        <v>17.9308</v>
       </c>
       <c r="D142" t="n">
-        <v>43.0495</v>
+        <v>44.0843</v>
       </c>
       <c r="E142" t="n">
-        <v>17.1674</v>
+        <v>17.1925</v>
       </c>
       <c r="F142" t="n">
-        <v>28.0316</v>
+        <v>28.1569</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>21.1143</v>
+        <v>21.1674</v>
       </c>
       <c r="C143" t="n">
-        <v>17.8832</v>
+        <v>17.9049</v>
       </c>
       <c r="D143" t="n">
-        <v>42.6387</v>
+        <v>43.6551</v>
       </c>
       <c r="E143" t="n">
-        <v>16.8439</v>
+        <v>16.8646</v>
       </c>
       <c r="F143" t="n">
-        <v>27.7254</v>
+        <v>27.9392</v>
       </c>
     </row>
   </sheetData>

--- a/clang-x64/Running erasure.xlsx
+++ b/clang-x64/Running erasure.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>19.5712</v>
+        <v>86.4451</v>
       </c>
       <c r="C2" t="n">
-        <v>32.4169</v>
+        <v>124.729</v>
       </c>
       <c r="D2" t="n">
-        <v>32.3548</v>
+        <v>49.5287</v>
       </c>
       <c r="E2" t="n">
-        <v>13.7134</v>
+        <v>22.8676</v>
       </c>
       <c r="F2" t="n">
-        <v>26.1729</v>
+        <v>39.4053</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>19.5468</v>
+        <v>86.59310000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>31.8743</v>
+        <v>123.296</v>
       </c>
       <c r="D3" t="n">
-        <v>32.3259</v>
+        <v>50.2526</v>
       </c>
       <c r="E3" t="n">
-        <v>13.2515</v>
+        <v>22.2117</v>
       </c>
       <c r="F3" t="n">
-        <v>25.8568</v>
+        <v>39.2941</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>18.8916</v>
+        <v>85.2226</v>
       </c>
       <c r="C4" t="n">
-        <v>31.8579</v>
+        <v>123.148</v>
       </c>
       <c r="D4" t="n">
-        <v>32.351</v>
+        <v>49.8111</v>
       </c>
       <c r="E4" t="n">
-        <v>13.2091</v>
+        <v>21.7162</v>
       </c>
       <c r="F4" t="n">
-        <v>25.8044</v>
+        <v>38.5165</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>18.3889</v>
+        <v>84.1682</v>
       </c>
       <c r="C5" t="n">
-        <v>31.0955</v>
+        <v>121.823</v>
       </c>
       <c r="D5" t="n">
-        <v>32.4596</v>
+        <v>50.1189</v>
       </c>
       <c r="E5" t="n">
-        <v>13.2821</v>
+        <v>21.4631</v>
       </c>
       <c r="F5" t="n">
-        <v>25.988</v>
+        <v>38.6517</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>17.7598</v>
+        <v>84.3837</v>
       </c>
       <c r="C6" t="n">
-        <v>31.1922</v>
+        <v>121.741</v>
       </c>
       <c r="D6" t="n">
-        <v>32.5839</v>
+        <v>49.9484</v>
       </c>
       <c r="E6" t="n">
-        <v>12.9202</v>
+        <v>21.1492</v>
       </c>
       <c r="F6" t="n">
-        <v>25.7892</v>
+        <v>38.0793</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>17.0245</v>
+        <v>83.9453</v>
       </c>
       <c r="C7" t="n">
-        <v>29.3642</v>
+        <v>120.537</v>
       </c>
       <c r="D7" t="n">
-        <v>31.8394</v>
+        <v>51.0683</v>
       </c>
       <c r="E7" t="n">
-        <v>12.7819</v>
+        <v>20.6549</v>
       </c>
       <c r="F7" t="n">
-        <v>25.3473</v>
+        <v>37.432</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>16.1128</v>
+        <v>83.1002</v>
       </c>
       <c r="C8" t="n">
-        <v>29.2507</v>
+        <v>119.921</v>
       </c>
       <c r="D8" t="n">
-        <v>31.7849</v>
+        <v>51.0465</v>
       </c>
       <c r="E8" t="n">
-        <v>12.7526</v>
+        <v>20.2229</v>
       </c>
       <c r="F8" t="n">
-        <v>24.9575</v>
+        <v>36.9766</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>15.1663</v>
+        <v>82.1091</v>
       </c>
       <c r="C9" t="n">
-        <v>28.0698</v>
+        <v>118.649</v>
       </c>
       <c r="D9" t="n">
-        <v>31.972</v>
+        <v>51.9071</v>
       </c>
       <c r="E9" t="n">
-        <v>18.8149</v>
+        <v>27.0053</v>
       </c>
       <c r="F9" t="n">
-        <v>29.4978</v>
+        <v>44.4026</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>23.1245</v>
+        <v>89.8073</v>
       </c>
       <c r="C10" t="n">
-        <v>35.6823</v>
+        <v>127.014</v>
       </c>
       <c r="D10" t="n">
-        <v>31.9343</v>
+        <v>51.1075</v>
       </c>
       <c r="E10" t="n">
-        <v>18.2956</v>
+        <v>26.3377</v>
       </c>
       <c r="F10" t="n">
-        <v>29.2042</v>
+        <v>43.8081</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>22.7276</v>
+        <v>89.9851</v>
       </c>
       <c r="C11" t="n">
-        <v>35.4801</v>
+        <v>126.999</v>
       </c>
       <c r="D11" t="n">
-        <v>32.1228</v>
+        <v>51.5923</v>
       </c>
       <c r="E11" t="n">
-        <v>17.9469</v>
+        <v>26.1386</v>
       </c>
       <c r="F11" t="n">
-        <v>29.0085</v>
+        <v>43.59</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>22.4395</v>
+        <v>89.5376</v>
       </c>
       <c r="C12" t="n">
-        <v>35.1832</v>
+        <v>125.019</v>
       </c>
       <c r="D12" t="n">
-        <v>32.079</v>
+        <v>52.767</v>
       </c>
       <c r="E12" t="n">
-        <v>17.5639</v>
+        <v>25.2945</v>
       </c>
       <c r="F12" t="n">
-        <v>28.5731</v>
+        <v>43.0519</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>22.1276</v>
+        <v>88.6392</v>
       </c>
       <c r="C13" t="n">
-        <v>34.5253</v>
+        <v>125.802</v>
       </c>
       <c r="D13" t="n">
-        <v>32.1647</v>
+        <v>51.0993</v>
       </c>
       <c r="E13" t="n">
-        <v>17.0586</v>
+        <v>25.06</v>
       </c>
       <c r="F13" t="n">
-        <v>28.4366</v>
+        <v>42.2326</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>21.8952</v>
+        <v>88.18389999999999</v>
       </c>
       <c r="C14" t="n">
-        <v>34.1336</v>
+        <v>126.088</v>
       </c>
       <c r="D14" t="n">
-        <v>32.2961</v>
+        <v>51.023</v>
       </c>
       <c r="E14" t="n">
-        <v>16.8871</v>
+        <v>24.7036</v>
       </c>
       <c r="F14" t="n">
-        <v>28.1186</v>
+        <v>41.6305</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>21.4727</v>
+        <v>87.8976</v>
       </c>
       <c r="C15" t="n">
-        <v>33.8685</v>
+        <v>122.413</v>
       </c>
       <c r="D15" t="n">
-        <v>32.387</v>
+        <v>52.3791</v>
       </c>
       <c r="E15" t="n">
-        <v>16.6152</v>
+        <v>24.2014</v>
       </c>
       <c r="F15" t="n">
-        <v>27.5503</v>
+        <v>41.3296</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>21.1944</v>
+        <v>87.1769</v>
       </c>
       <c r="C16" t="n">
-        <v>33.2539</v>
+        <v>122.828</v>
       </c>
       <c r="D16" t="n">
-        <v>32.5546</v>
+        <v>52.4619</v>
       </c>
       <c r="E16" t="n">
-        <v>16.1838</v>
+        <v>24.0877</v>
       </c>
       <c r="F16" t="n">
-        <v>27.209</v>
+        <v>41.5404</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>20.8012</v>
+        <v>86.6583</v>
       </c>
       <c r="C17" t="n">
-        <v>32.68</v>
+        <v>123.999</v>
       </c>
       <c r="D17" t="n">
-        <v>32.7433</v>
+        <v>52.0389</v>
       </c>
       <c r="E17" t="n">
-        <v>15.9017</v>
+        <v>23.5856</v>
       </c>
       <c r="F17" t="n">
-        <v>27.1776</v>
+        <v>40.9023</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>20.207</v>
+        <v>85.6354</v>
       </c>
       <c r="C18" t="n">
-        <v>32.3858</v>
+        <v>123.246</v>
       </c>
       <c r="D18" t="n">
-        <v>32.6731</v>
+        <v>52.4958</v>
       </c>
       <c r="E18" t="n">
-        <v>15.5843</v>
+        <v>22.9833</v>
       </c>
       <c r="F18" t="n">
-        <v>26.7096</v>
+        <v>39.8422</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>19.6907</v>
+        <v>85.5213</v>
       </c>
       <c r="C19" t="n">
-        <v>31.6282</v>
+        <v>121.119</v>
       </c>
       <c r="D19" t="n">
-        <v>32.9088</v>
+        <v>52.5238</v>
       </c>
       <c r="E19" t="n">
-        <v>15.188</v>
+        <v>22.382</v>
       </c>
       <c r="F19" t="n">
-        <v>26.9191</v>
+        <v>39.9739</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>19.1122</v>
+        <v>84.6418</v>
       </c>
       <c r="C20" t="n">
-        <v>30.9681</v>
+        <v>121.539</v>
       </c>
       <c r="D20" t="n">
-        <v>32.9973</v>
+        <v>52.492</v>
       </c>
       <c r="E20" t="n">
-        <v>14.9034</v>
+        <v>22.3749</v>
       </c>
       <c r="F20" t="n">
-        <v>26.1324</v>
+        <v>39.6057</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>18.4477</v>
+        <v>84.0839</v>
       </c>
       <c r="C21" t="n">
-        <v>30.9473</v>
+        <v>121.726</v>
       </c>
       <c r="D21" t="n">
-        <v>32.5488</v>
+        <v>55.007</v>
       </c>
       <c r="E21" t="n">
-        <v>14.5431</v>
+        <v>21.5406</v>
       </c>
       <c r="F21" t="n">
-        <v>25.7132</v>
+        <v>38.4342</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>17.4643</v>
+        <v>83.3141</v>
       </c>
       <c r="C22" t="n">
-        <v>29.5201</v>
+        <v>120.767</v>
       </c>
       <c r="D22" t="n">
-        <v>32.6324</v>
+        <v>55.5838</v>
       </c>
       <c r="E22" t="n">
-        <v>14.1624</v>
+        <v>20.9763</v>
       </c>
       <c r="F22" t="n">
-        <v>25.279</v>
+        <v>38.1593</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>16.5627</v>
+        <v>82.4893</v>
       </c>
       <c r="C23" t="n">
-        <v>28.4764</v>
+        <v>118.784</v>
       </c>
       <c r="D23" t="n">
-        <v>32.4175</v>
+        <v>53.3908</v>
       </c>
       <c r="E23" t="n">
-        <v>19.476</v>
+        <v>27.371</v>
       </c>
       <c r="F23" t="n">
-        <v>30.1618</v>
+        <v>45.0289</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>24.2479</v>
+        <v>90.3867</v>
       </c>
       <c r="C24" t="n">
-        <v>35.6339</v>
+        <v>127.442</v>
       </c>
       <c r="D24" t="n">
-        <v>32.3946</v>
+        <v>54.8671</v>
       </c>
       <c r="E24" t="n">
-        <v>18.9346</v>
+        <v>26.759</v>
       </c>
       <c r="F24" t="n">
-        <v>29.6991</v>
+        <v>43.7196</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>23.832</v>
+        <v>90.029</v>
       </c>
       <c r="C25" t="n">
-        <v>35.182</v>
+        <v>128.149</v>
       </c>
       <c r="D25" t="n">
-        <v>32.5553</v>
+        <v>55.1534</v>
       </c>
       <c r="E25" t="n">
-        <v>18.6036</v>
+        <v>26.419</v>
       </c>
       <c r="F25" t="n">
-        <v>29.3291</v>
+        <v>44.8894</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>23.4682</v>
+        <v>89.2808</v>
       </c>
       <c r="C26" t="n">
-        <v>34.7727</v>
+        <v>126.873</v>
       </c>
       <c r="D26" t="n">
-        <v>32.5087</v>
+        <v>55.1371</v>
       </c>
       <c r="E26" t="n">
-        <v>18.1545</v>
+        <v>25.8948</v>
       </c>
       <c r="F26" t="n">
-        <v>29.1399</v>
+        <v>43.9947</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>23.1299</v>
+        <v>89.0492</v>
       </c>
       <c r="C27" t="n">
-        <v>34.3529</v>
+        <v>126.608</v>
       </c>
       <c r="D27" t="n">
-        <v>32.5235</v>
+        <v>56.3471</v>
       </c>
       <c r="E27" t="n">
-        <v>17.8374</v>
+        <v>25.4809</v>
       </c>
       <c r="F27" t="n">
-        <v>29.2104</v>
+        <v>43.6189</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>22.8336</v>
+        <v>88.4023</v>
       </c>
       <c r="C28" t="n">
-        <v>33.9868</v>
+        <v>126.188</v>
       </c>
       <c r="D28" t="n">
-        <v>32.527</v>
+        <v>52.2337</v>
       </c>
       <c r="E28" t="n">
-        <v>17.4272</v>
+        <v>24.9122</v>
       </c>
       <c r="F28" t="n">
-        <v>28.8166</v>
+        <v>41.7953</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>22.2167</v>
+        <v>87.9542</v>
       </c>
       <c r="C29" t="n">
-        <v>33.5239</v>
+        <v>125.146</v>
       </c>
       <c r="D29" t="n">
-        <v>32.7323</v>
+        <v>55.3393</v>
       </c>
       <c r="E29" t="n">
-        <v>17.1515</v>
+        <v>24.5177</v>
       </c>
       <c r="F29" t="n">
-        <v>28.5845</v>
+        <v>43.4117</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>21.754</v>
+        <v>87.0408</v>
       </c>
       <c r="C30" t="n">
-        <v>32.7259</v>
+        <v>124.48</v>
       </c>
       <c r="D30" t="n">
-        <v>32.9192</v>
+        <v>57.3512</v>
       </c>
       <c r="E30" t="n">
-        <v>16.8113</v>
+        <v>24.0098</v>
       </c>
       <c r="F30" t="n">
-        <v>28.2802</v>
+        <v>41.0724</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>21.3296</v>
+        <v>86.33799999999999</v>
       </c>
       <c r="C31" t="n">
-        <v>32.6791</v>
+        <v>124.044</v>
       </c>
       <c r="D31" t="n">
-        <v>32.7623</v>
+        <v>55.7383</v>
       </c>
       <c r="E31" t="n">
-        <v>16.494</v>
+        <v>23.5424</v>
       </c>
       <c r="F31" t="n">
-        <v>27.4813</v>
+        <v>42.1275</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>20.9157</v>
+        <v>86.1536</v>
       </c>
       <c r="C32" t="n">
-        <v>32.5328</v>
+        <v>123.544</v>
       </c>
       <c r="D32" t="n">
-        <v>32.9132</v>
+        <v>56.5413</v>
       </c>
       <c r="E32" t="n">
-        <v>16.0821</v>
+        <v>23.2356</v>
       </c>
       <c r="F32" t="n">
-        <v>27.1039</v>
+        <v>40.1568</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>20.316</v>
+        <v>85.66030000000001</v>
       </c>
       <c r="C33" t="n">
-        <v>31.3534</v>
+        <v>125.642</v>
       </c>
       <c r="D33" t="n">
-        <v>33.2063</v>
+        <v>55.4948</v>
       </c>
       <c r="E33" t="n">
-        <v>15.7456</v>
+        <v>22.6798</v>
       </c>
       <c r="F33" t="n">
-        <v>26.7529</v>
+        <v>40.3544</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>19.7228</v>
+        <v>84.94459999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>31.1103</v>
+        <v>123.72</v>
       </c>
       <c r="D34" t="n">
-        <v>33.2326</v>
+        <v>57.5559</v>
       </c>
       <c r="E34" t="n">
-        <v>15.4802</v>
+        <v>22.2421</v>
       </c>
       <c r="F34" t="n">
-        <v>26.9235</v>
+        <v>41.4854</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>18.8534</v>
+        <v>84.2794</v>
       </c>
       <c r="C35" t="n">
-        <v>30.6415</v>
+        <v>125.124</v>
       </c>
       <c r="D35" t="n">
-        <v>32.7393</v>
+        <v>61.9436</v>
       </c>
       <c r="E35" t="n">
-        <v>15.0878</v>
+        <v>21.7705</v>
       </c>
       <c r="F35" t="n">
-        <v>26.0212</v>
+        <v>41.4389</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>18.1225</v>
+        <v>83.5732</v>
       </c>
       <c r="C36" t="n">
-        <v>29.8632</v>
+        <v>122.84</v>
       </c>
       <c r="D36" t="n">
-        <v>32.8623</v>
+        <v>61.4872</v>
       </c>
       <c r="E36" t="n">
-        <v>14.7045</v>
+        <v>21.3076</v>
       </c>
       <c r="F36" t="n">
-        <v>25.7651</v>
+        <v>39.1588</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>17.2218</v>
+        <v>82.7957</v>
       </c>
       <c r="C37" t="n">
-        <v>28.3407</v>
+        <v>118.88</v>
       </c>
       <c r="D37" t="n">
-        <v>32.7656</v>
+        <v>61.4097</v>
       </c>
       <c r="E37" t="n">
-        <v>19.716</v>
+        <v>27.4852</v>
       </c>
       <c r="F37" t="n">
-        <v>30.7043</v>
+        <v>49.4803</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>24.9509</v>
+        <v>90.1216</v>
       </c>
       <c r="C38" t="n">
-        <v>35.7345</v>
+        <v>128.395</v>
       </c>
       <c r="D38" t="n">
-        <v>32.6992</v>
+        <v>62.3781</v>
       </c>
       <c r="E38" t="n">
-        <v>19.3737</v>
+        <v>27.0055</v>
       </c>
       <c r="F38" t="n">
-        <v>30.3253</v>
+        <v>44.7948</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>24.3047</v>
+        <v>89.9639</v>
       </c>
       <c r="C39" t="n">
-        <v>35.3776</v>
+        <v>128.928</v>
       </c>
       <c r="D39" t="n">
-        <v>32.6813</v>
+        <v>60.0624</v>
       </c>
       <c r="E39" t="n">
-        <v>18.8359</v>
+        <v>26.4479</v>
       </c>
       <c r="F39" t="n">
-        <v>29.6419</v>
+        <v>44.3881</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>23.8396</v>
+        <v>89.5074</v>
       </c>
       <c r="C40" t="n">
-        <v>35.0695</v>
+        <v>134.951</v>
       </c>
       <c r="D40" t="n">
-        <v>32.7753</v>
+        <v>61.0518</v>
       </c>
       <c r="E40" t="n">
-        <v>18.4569</v>
+        <v>25.9293</v>
       </c>
       <c r="F40" t="n">
-        <v>29.2622</v>
+        <v>43.3978</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>23.558</v>
+        <v>88.78579999999999</v>
       </c>
       <c r="C41" t="n">
-        <v>34.5741</v>
+        <v>127.747</v>
       </c>
       <c r="D41" t="n">
-        <v>32.8035</v>
+        <v>61.9046</v>
       </c>
       <c r="E41" t="n">
-        <v>17.9301</v>
+        <v>25.371</v>
       </c>
       <c r="F41" t="n">
-        <v>28.9127</v>
+        <v>43.0058</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>23.1962</v>
+        <v>88.54949999999999</v>
       </c>
       <c r="C42" t="n">
-        <v>34.206</v>
+        <v>126.947</v>
       </c>
       <c r="D42" t="n">
-        <v>32.7936</v>
+        <v>59.8995</v>
       </c>
       <c r="E42" t="n">
-        <v>17.5664</v>
+        <v>25.1034</v>
       </c>
       <c r="F42" t="n">
-        <v>28.6283</v>
+        <v>42.2677</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>22.6496</v>
+        <v>87.9547</v>
       </c>
       <c r="C43" t="n">
-        <v>33.6492</v>
+        <v>127.416</v>
       </c>
       <c r="D43" t="n">
-        <v>32.8061</v>
+        <v>65.3437</v>
       </c>
       <c r="E43" t="n">
-        <v>17.1585</v>
+        <v>24.6774</v>
       </c>
       <c r="F43" t="n">
-        <v>28.3096</v>
+        <v>43.0406</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>22.1581</v>
+        <v>87.069</v>
       </c>
       <c r="C44" t="n">
-        <v>33.6725</v>
+        <v>127.622</v>
       </c>
       <c r="D44" t="n">
-        <v>32.8267</v>
+        <v>61.29</v>
       </c>
       <c r="E44" t="n">
-        <v>16.8763</v>
+        <v>24.2534</v>
       </c>
       <c r="F44" t="n">
-        <v>27.9949</v>
+        <v>42.6011</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>21.6812</v>
+        <v>86.7441</v>
       </c>
       <c r="C45" t="n">
-        <v>33.4763</v>
+        <v>130.324</v>
       </c>
       <c r="D45" t="n">
-        <v>33.1476</v>
+        <v>60.5607</v>
       </c>
       <c r="E45" t="n">
-        <v>16.5358</v>
+        <v>23.788</v>
       </c>
       <c r="F45" t="n">
-        <v>27.5976</v>
+        <v>40.7226</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>21.1514</v>
+        <v>86.21769999999999</v>
       </c>
       <c r="C46" t="n">
-        <v>32.5623</v>
+        <v>129.238</v>
       </c>
       <c r="D46" t="n">
-        <v>33.0779</v>
+        <v>65.30289999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>16.1624</v>
+        <v>23.2617</v>
       </c>
       <c r="F46" t="n">
-        <v>27.2651</v>
+        <v>41.5883</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>20.7</v>
+        <v>85.5774</v>
       </c>
       <c r="C47" t="n">
-        <v>32.5888</v>
+        <v>125.56</v>
       </c>
       <c r="D47" t="n">
-        <v>33.2753</v>
+        <v>63.0092</v>
       </c>
       <c r="E47" t="n">
-        <v>16.0495</v>
+        <v>22.8591</v>
       </c>
       <c r="F47" t="n">
-        <v>27.512</v>
+        <v>41.1374</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>20.0144</v>
+        <v>84.5215</v>
       </c>
       <c r="C48" t="n">
-        <v>30.9826</v>
+        <v>131.665</v>
       </c>
       <c r="D48" t="n">
-        <v>33.3254</v>
+        <v>60.4321</v>
       </c>
       <c r="E48" t="n">
-        <v>15.6986</v>
+        <v>22.3182</v>
       </c>
       <c r="F48" t="n">
-        <v>27.1207</v>
+        <v>42.8778</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>19.3033</v>
+        <v>84.181</v>
       </c>
       <c r="C49" t="n">
-        <v>30.7402</v>
+        <v>128.462</v>
       </c>
       <c r="D49" t="n">
-        <v>33.7205</v>
+        <v>65.2179</v>
       </c>
       <c r="E49" t="n">
-        <v>15.353</v>
+        <v>21.842</v>
       </c>
       <c r="F49" t="n">
-        <v>26.7924</v>
+        <v>40.2234</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>18.5182</v>
+        <v>83.4158</v>
       </c>
       <c r="C50" t="n">
-        <v>30.0531</v>
+        <v>125.748</v>
       </c>
       <c r="D50" t="n">
-        <v>33.0372</v>
+        <v>79.13039999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>14.9978</v>
+        <v>21.4537</v>
       </c>
       <c r="F50" t="n">
-        <v>25.8824</v>
+        <v>38.5529</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>17.6294</v>
+        <v>82.5016</v>
       </c>
       <c r="C51" t="n">
-        <v>29.5188</v>
+        <v>127.73</v>
       </c>
       <c r="D51" t="n">
-        <v>33.1005</v>
+        <v>75.5827</v>
       </c>
       <c r="E51" t="n">
-        <v>19.8417</v>
+        <v>27.0398</v>
       </c>
       <c r="F51" t="n">
-        <v>30.3999</v>
+        <v>47.799</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>16.6311</v>
+        <v>81.9683</v>
       </c>
       <c r="C52" t="n">
-        <v>28.4781</v>
+        <v>123.676</v>
       </c>
       <c r="D52" t="n">
-        <v>33.2693</v>
+        <v>75.9521</v>
       </c>
       <c r="E52" t="n">
-        <v>19.4498</v>
+        <v>26.5398</v>
       </c>
       <c r="F52" t="n">
-        <v>30.0282</v>
+        <v>45.2577</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>24.5514</v>
+        <v>90.12569999999999</v>
       </c>
       <c r="C53" t="n">
-        <v>35.6754</v>
+        <v>135.573</v>
       </c>
       <c r="D53" t="n">
-        <v>33.4358</v>
+        <v>68.2719</v>
       </c>
       <c r="E53" t="n">
-        <v>18.9822</v>
+        <v>26.213</v>
       </c>
       <c r="F53" t="n">
-        <v>29.7171</v>
+        <v>44.8686</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>24.1786</v>
+        <v>89.40900000000001</v>
       </c>
       <c r="C54" t="n">
-        <v>34.7604</v>
+        <v>135.836</v>
       </c>
       <c r="D54" t="n">
-        <v>33.3312</v>
+        <v>76.6217</v>
       </c>
       <c r="E54" t="n">
-        <v>18.6404</v>
+        <v>25.5564</v>
       </c>
       <c r="F54" t="n">
-        <v>29.3512</v>
+        <v>43.4777</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>23.9842</v>
+        <v>89.07340000000001</v>
       </c>
       <c r="C55" t="n">
-        <v>35.0489</v>
+        <v>126.341</v>
       </c>
       <c r="D55" t="n">
-        <v>33.6221</v>
+        <v>80.62649999999999</v>
       </c>
       <c r="E55" t="n">
-        <v>18.171</v>
+        <v>25.1806</v>
       </c>
       <c r="F55" t="n">
-        <v>28.9388</v>
+        <v>42.9038</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>23.4567</v>
+        <v>88.499</v>
       </c>
       <c r="C56" t="n">
-        <v>34.6781</v>
+        <v>125.893</v>
       </c>
       <c r="D56" t="n">
-        <v>33.7555</v>
+        <v>78.9586</v>
       </c>
       <c r="E56" t="n">
-        <v>17.6863</v>
+        <v>24.7153</v>
       </c>
       <c r="F56" t="n">
-        <v>28.7557</v>
+        <v>44.0015</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>22.9974</v>
+        <v>87.8434</v>
       </c>
       <c r="C57" t="n">
-        <v>34.2725</v>
+        <v>137.784</v>
       </c>
       <c r="D57" t="n">
-        <v>33.9131</v>
+        <v>74.8477</v>
       </c>
       <c r="E57" t="n">
-        <v>17.4118</v>
+        <v>24.3584</v>
       </c>
       <c r="F57" t="n">
-        <v>28.4453</v>
+        <v>44.2817</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>22.3513</v>
+        <v>87.3009</v>
       </c>
       <c r="C58" t="n">
-        <v>35.8665</v>
+        <v>136.953</v>
       </c>
       <c r="D58" t="n">
-        <v>33.9714</v>
+        <v>72.30719999999999</v>
       </c>
       <c r="E58" t="n">
-        <v>17.0327</v>
+        <v>23.9072</v>
       </c>
       <c r="F58" t="n">
-        <v>28.113</v>
+        <v>42.1978</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>21.9546</v>
+        <v>87.0031</v>
       </c>
       <c r="C59" t="n">
-        <v>33.4465</v>
+        <v>136.358</v>
       </c>
       <c r="D59" t="n">
-        <v>34.0639</v>
+        <v>65.2599</v>
       </c>
       <c r="E59" t="n">
-        <v>16.6929</v>
+        <v>23.5829</v>
       </c>
       <c r="F59" t="n">
-        <v>27.7821</v>
+        <v>41.2424</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>21.3973</v>
+        <v>86.12</v>
       </c>
       <c r="C60" t="n">
-        <v>33.806</v>
+        <v>136.478</v>
       </c>
       <c r="D60" t="n">
-        <v>34.3362</v>
+        <v>80.2997</v>
       </c>
       <c r="E60" t="n">
-        <v>16.3676</v>
+        <v>23.1611</v>
       </c>
       <c r="F60" t="n">
-        <v>27.4355</v>
+        <v>40.7334</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>20.7814</v>
+        <v>85.3437</v>
       </c>
       <c r="C61" t="n">
-        <v>35.2562</v>
+        <v>136.536</v>
       </c>
       <c r="D61" t="n">
-        <v>34.984</v>
+        <v>76.07089999999999</v>
       </c>
       <c r="E61" t="n">
-        <v>16.196</v>
+        <v>22.7539</v>
       </c>
       <c r="F61" t="n">
-        <v>27.1314</v>
+        <v>40.4844</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>20.1692</v>
+        <v>85.0873</v>
       </c>
       <c r="C62" t="n">
-        <v>32.1153</v>
+        <v>137.295</v>
       </c>
       <c r="D62" t="n">
-        <v>35.3885</v>
+        <v>68.91889999999999</v>
       </c>
       <c r="E62" t="n">
-        <v>15.7177</v>
+        <v>22.3707</v>
       </c>
       <c r="F62" t="n">
-        <v>26.7996</v>
+        <v>43.791</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>19.5521</v>
+        <v>84.11020000000001</v>
       </c>
       <c r="C63" t="n">
-        <v>34.8917</v>
+        <v>122.255</v>
       </c>
       <c r="D63" t="n">
-        <v>35.6502</v>
+        <v>74.9157</v>
       </c>
       <c r="E63" t="n">
-        <v>15.3981</v>
+        <v>21.9636</v>
       </c>
       <c r="F63" t="n">
-        <v>26.4801</v>
+        <v>40.9145</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>18.7407</v>
+        <v>83.6498</v>
       </c>
       <c r="C64" t="n">
-        <v>32.3849</v>
+        <v>136.3</v>
       </c>
       <c r="D64" t="n">
-        <v>39.9336</v>
+        <v>97.29430000000001</v>
       </c>
       <c r="E64" t="n">
-        <v>15.1033</v>
+        <v>21.5138</v>
       </c>
       <c r="F64" t="n">
-        <v>26.1012</v>
+        <v>38.9271</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>17.8233</v>
+        <v>82.86490000000001</v>
       </c>
       <c r="C65" t="n">
-        <v>31.8501</v>
+        <v>136.879</v>
       </c>
       <c r="D65" t="n">
-        <v>39.8078</v>
+        <v>90.8321</v>
       </c>
       <c r="E65" t="n">
-        <v>14.8033</v>
+        <v>21.137</v>
       </c>
       <c r="F65" t="n">
-        <v>25.7464</v>
+        <v>38.3948</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>16.9602</v>
+        <v>81.7594</v>
       </c>
       <c r="C66" t="n">
-        <v>31.4454</v>
+        <v>135.663</v>
       </c>
       <c r="D66" t="n">
-        <v>40.0481</v>
+        <v>91.54389999999999</v>
       </c>
       <c r="E66" t="n">
-        <v>20.144</v>
+        <v>27.1752</v>
       </c>
       <c r="F66" t="n">
-        <v>30.2031</v>
+        <v>44.8036</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>24.7985</v>
+        <v>90.1575</v>
       </c>
       <c r="C67" t="n">
-        <v>39.5392</v>
+        <v>142.292</v>
       </c>
       <c r="D67" t="n">
-        <v>40.1726</v>
+        <v>82.28319999999999</v>
       </c>
       <c r="E67" t="n">
-        <v>19.4835</v>
+        <v>26.5259</v>
       </c>
       <c r="F67" t="n">
-        <v>29.8278</v>
+        <v>44.9217</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>24.3981</v>
+        <v>89.7667</v>
       </c>
       <c r="C68" t="n">
-        <v>38.8802</v>
+        <v>138.345</v>
       </c>
       <c r="D68" t="n">
-        <v>40.1715</v>
+        <v>88.2938</v>
       </c>
       <c r="E68" t="n">
-        <v>18.9949</v>
+        <v>26.1123</v>
       </c>
       <c r="F68" t="n">
-        <v>29.5116</v>
+        <v>43.8468</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>23.9581</v>
+        <v>89.0951</v>
       </c>
       <c r="C69" t="n">
-        <v>38.5758</v>
+        <v>144.678</v>
       </c>
       <c r="D69" t="n">
-        <v>40.475</v>
+        <v>89.8746</v>
       </c>
       <c r="E69" t="n">
-        <v>18.5598</v>
+        <v>25.5324</v>
       </c>
       <c r="F69" t="n">
-        <v>29.1397</v>
+        <v>43.3335</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>23.537</v>
+        <v>88.8523</v>
       </c>
       <c r="C70" t="n">
-        <v>38.2454</v>
+        <v>144.303</v>
       </c>
       <c r="D70" t="n">
-        <v>40.4642</v>
+        <v>87.1807</v>
       </c>
       <c r="E70" t="n">
-        <v>17.9604</v>
+        <v>25.1612</v>
       </c>
       <c r="F70" t="n">
-        <v>28.8427</v>
+        <v>46.8068</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>23.0793</v>
+        <v>88.26260000000001</v>
       </c>
       <c r="C71" t="n">
-        <v>37.9353</v>
+        <v>141.905</v>
       </c>
       <c r="D71" t="n">
-        <v>40.5336</v>
+        <v>72.735</v>
       </c>
       <c r="E71" t="n">
-        <v>17.796</v>
+        <v>24.5568</v>
       </c>
       <c r="F71" t="n">
-        <v>28.9924</v>
+        <v>43.5162</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>22.5449</v>
+        <v>87.9438</v>
       </c>
       <c r="C72" t="n">
-        <v>36.3626</v>
+        <v>125.174</v>
       </c>
       <c r="D72" t="n">
-        <v>40.5347</v>
+        <v>71.8034</v>
       </c>
       <c r="E72" t="n">
-        <v>17.4378</v>
+        <v>24.0501</v>
       </c>
       <c r="F72" t="n">
-        <v>28.7218</v>
+        <v>42.6208</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>21.9661</v>
+        <v>86.8326</v>
       </c>
       <c r="C73" t="n">
-        <v>46.5634</v>
+        <v>130.685</v>
       </c>
       <c r="D73" t="n">
-        <v>40.7337</v>
+        <v>88.5489</v>
       </c>
       <c r="E73" t="n">
-        <v>16.9797</v>
+        <v>23.6565</v>
       </c>
       <c r="F73" t="n">
-        <v>28.3568</v>
+        <v>41.6165</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>21.5434</v>
+        <v>86.3566</v>
       </c>
       <c r="C74" t="n">
-        <v>45.0506</v>
+        <v>148.232</v>
       </c>
       <c r="D74" t="n">
-        <v>40.9405</v>
+        <v>92.7149</v>
       </c>
       <c r="E74" t="n">
-        <v>16.6379</v>
+        <v>23.2895</v>
       </c>
       <c r="F74" t="n">
-        <v>27.5474</v>
+        <v>41.0084</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>21.018</v>
+        <v>85.6683</v>
       </c>
       <c r="C75" t="n">
-        <v>49.341</v>
+        <v>146.184</v>
       </c>
       <c r="D75" t="n">
-        <v>40.6678</v>
+        <v>90.066</v>
       </c>
       <c r="E75" t="n">
-        <v>16.3104</v>
+        <v>22.8484</v>
       </c>
       <c r="F75" t="n">
-        <v>27.7196</v>
+        <v>40.4308</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>20.3884</v>
+        <v>85.122</v>
       </c>
       <c r="C76" t="n">
-        <v>49.24</v>
+        <v>143.606</v>
       </c>
       <c r="D76" t="n">
-        <v>40.7984</v>
+        <v>81.3954</v>
       </c>
       <c r="E76" t="n">
-        <v>16.0069</v>
+        <v>22.4521</v>
       </c>
       <c r="F76" t="n">
-        <v>26.8326</v>
+        <v>41.2877</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>19.6827</v>
+        <v>84.45959999999999</v>
       </c>
       <c r="C77" t="n">
-        <v>44.1783</v>
+        <v>150.21</v>
       </c>
       <c r="D77" t="n">
-        <v>40.7573</v>
+        <v>77.7308</v>
       </c>
       <c r="E77" t="n">
-        <v>15.6441</v>
+        <v>22.0833</v>
       </c>
       <c r="F77" t="n">
-        <v>26.5199</v>
+        <v>39.662</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>19.0707</v>
+        <v>84.0441</v>
       </c>
       <c r="C78" t="n">
-        <v>40.2342</v>
+        <v>139.42</v>
       </c>
       <c r="D78" t="n">
-        <v>47.7113</v>
+        <v>102.62</v>
       </c>
       <c r="E78" t="n">
-        <v>15.2637</v>
+        <v>21.6399</v>
       </c>
       <c r="F78" t="n">
-        <v>26.1832</v>
+        <v>39.1258</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>18.0947</v>
+        <v>82.8419</v>
       </c>
       <c r="C79" t="n">
-        <v>41.1563</v>
+        <v>141.493</v>
       </c>
       <c r="D79" t="n">
-        <v>46.637</v>
+        <v>95.7379</v>
       </c>
       <c r="E79" t="n">
-        <v>14.9546</v>
+        <v>21.2405</v>
       </c>
       <c r="F79" t="n">
-        <v>26.3568</v>
+        <v>38.4773</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>17.1725</v>
+        <v>82.00449999999999</v>
       </c>
       <c r="C80" t="n">
-        <v>43.5658</v>
+        <v>144.52</v>
       </c>
       <c r="D80" t="n">
-        <v>46.7636</v>
+        <v>97.4161</v>
       </c>
       <c r="E80" t="n">
-        <v>19.8751</v>
+        <v>26.914</v>
       </c>
       <c r="F80" t="n">
-        <v>30.678</v>
+        <v>44.8397</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>24.7729</v>
+        <v>90.3556</v>
       </c>
       <c r="C81" t="n">
-        <v>38.0679</v>
+        <v>150.398</v>
       </c>
       <c r="D81" t="n">
-        <v>46.1846</v>
+        <v>97.0324</v>
       </c>
       <c r="E81" t="n">
-        <v>19.3938</v>
+        <v>26.3139</v>
       </c>
       <c r="F81" t="n">
-        <v>30.2356</v>
+        <v>44.1629</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>24.498</v>
+        <v>90.2427</v>
       </c>
       <c r="C82" t="n">
-        <v>37.8147</v>
+        <v>146.638</v>
       </c>
       <c r="D82" t="n">
-        <v>45.8033</v>
+        <v>95.5917</v>
       </c>
       <c r="E82" t="n">
-        <v>18.9958</v>
+        <v>25.8865</v>
       </c>
       <c r="F82" t="n">
-        <v>29.5245</v>
+        <v>43.7278</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>24.1218</v>
+        <v>89.7773</v>
       </c>
       <c r="C83" t="n">
-        <v>37.378</v>
+        <v>149.57</v>
       </c>
       <c r="D83" t="n">
-        <v>45.0658</v>
+        <v>82.8475</v>
       </c>
       <c r="E83" t="n">
-        <v>18.564</v>
+        <v>25.4566</v>
       </c>
       <c r="F83" t="n">
-        <v>29.1573</v>
+        <v>43.7031</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>23.6631</v>
+        <v>89.6623</v>
       </c>
       <c r="C84" t="n">
-        <v>36.7839</v>
+        <v>150.571</v>
       </c>
       <c r="D84" t="n">
-        <v>44.8205</v>
+        <v>81.4049</v>
       </c>
       <c r="E84" t="n">
-        <v>18.235</v>
+        <v>24.9149</v>
       </c>
       <c r="F84" t="n">
-        <v>29.268</v>
+        <v>42.6893</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>23.2387</v>
+        <v>88.5539</v>
       </c>
       <c r="C85" t="n">
-        <v>36.2141</v>
+        <v>149.282</v>
       </c>
       <c r="D85" t="n">
-        <v>44.2662</v>
+        <v>79.8419</v>
       </c>
       <c r="E85" t="n">
-        <v>17.8392</v>
+        <v>24.5379</v>
       </c>
       <c r="F85" t="n">
-        <v>28.9824</v>
+        <v>42.3054</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>22.7905</v>
+        <v>87.6892</v>
       </c>
       <c r="C86" t="n">
-        <v>35.6414</v>
+        <v>150.104</v>
       </c>
       <c r="D86" t="n">
-        <v>44.5199</v>
+        <v>99.50530000000001</v>
       </c>
       <c r="E86" t="n">
-        <v>17.4852</v>
+        <v>24.2673</v>
       </c>
       <c r="F86" t="n">
-        <v>28.6771</v>
+        <v>42.3965</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>22.2938</v>
+        <v>87.10250000000001</v>
       </c>
       <c r="C87" t="n">
-        <v>41.0958</v>
+        <v>149.921</v>
       </c>
       <c r="D87" t="n">
-        <v>43.884</v>
+        <v>105.674</v>
       </c>
       <c r="E87" t="n">
-        <v>17.155</v>
+        <v>23.8039</v>
       </c>
       <c r="F87" t="n">
-        <v>28.4066</v>
+        <v>41.5768</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>21.6964</v>
+        <v>86.6151</v>
       </c>
       <c r="C88" t="n">
-        <v>38.4834</v>
+        <v>154.983</v>
       </c>
       <c r="D88" t="n">
-        <v>43.285</v>
+        <v>101.447</v>
       </c>
       <c r="E88" t="n">
-        <v>16.8245</v>
+        <v>23.4246</v>
       </c>
       <c r="F88" t="n">
-        <v>28.0772</v>
+        <v>40.7935</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>21.0801</v>
+        <v>85.8805</v>
       </c>
       <c r="C89" t="n">
-        <v>43.992</v>
+        <v>148.565</v>
       </c>
       <c r="D89" t="n">
-        <v>43.0234</v>
+        <v>92.2749</v>
       </c>
       <c r="E89" t="n">
-        <v>16.5184</v>
+        <v>22.9928</v>
       </c>
       <c r="F89" t="n">
-        <v>27.7644</v>
+        <v>40.427</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>20.5829</v>
+        <v>85.2269</v>
       </c>
       <c r="C90" t="n">
-        <v>42.4696</v>
+        <v>121.599</v>
       </c>
       <c r="D90" t="n">
-        <v>42.8962</v>
+        <v>86.13330000000001</v>
       </c>
       <c r="E90" t="n">
-        <v>16.1357</v>
+        <v>22.6016</v>
       </c>
       <c r="F90" t="n">
-        <v>27.4611</v>
+        <v>40.1272</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>19.9441</v>
+        <v>84.76990000000001</v>
       </c>
       <c r="C91" t="n">
-        <v>43.2677</v>
+        <v>123.737</v>
       </c>
       <c r="D91" t="n">
-        <v>42.6316</v>
+        <v>86.99469999999999</v>
       </c>
       <c r="E91" t="n">
-        <v>15.802</v>
+        <v>22.2475</v>
       </c>
       <c r="F91" t="n">
-        <v>27.1273</v>
+        <v>39.8855</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>19.2061</v>
+        <v>84.0133</v>
       </c>
       <c r="C92" t="n">
-        <v>35.4075</v>
+        <v>119.732</v>
       </c>
       <c r="D92" t="n">
-        <v>48.4803</v>
+        <v>95.7773</v>
       </c>
       <c r="E92" t="n">
-        <v>15.3993</v>
+        <v>21.8485</v>
       </c>
       <c r="F92" t="n">
-        <v>26.2933</v>
+        <v>39.1291</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>18.3427</v>
+        <v>83.21639999999999</v>
       </c>
       <c r="C93" t="n">
-        <v>42.3115</v>
+        <v>118.624</v>
       </c>
       <c r="D93" t="n">
-        <v>48.1255</v>
+        <v>90.40949999999999</v>
       </c>
       <c r="E93" t="n">
-        <v>15.0396</v>
+        <v>21.4256</v>
       </c>
       <c r="F93" t="n">
-        <v>25.9528</v>
+        <v>38.6287</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>17.4327</v>
+        <v>82.3335</v>
       </c>
       <c r="C94" t="n">
-        <v>36.4795</v>
+        <v>149.531</v>
       </c>
       <c r="D94" t="n">
-        <v>47.6274</v>
+        <v>92.12649999999999</v>
       </c>
       <c r="E94" t="n">
-        <v>19.7809</v>
+        <v>27.0803</v>
       </c>
       <c r="F94" t="n">
-        <v>30.1657</v>
+        <v>44.6572</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>24.9666</v>
+        <v>90.80419999999999</v>
       </c>
       <c r="C95" t="n">
-        <v>43.4046</v>
+        <v>173.968</v>
       </c>
       <c r="D95" t="n">
-        <v>46.9377</v>
+        <v>88.40940000000001</v>
       </c>
       <c r="E95" t="n">
-        <v>19.2969</v>
+        <v>26.6066</v>
       </c>
       <c r="F95" t="n">
-        <v>29.8223</v>
+        <v>44.2164</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>24.5728</v>
+        <v>90.1097</v>
       </c>
       <c r="C96" t="n">
-        <v>45.9442</v>
+        <v>141.379</v>
       </c>
       <c r="D96" t="n">
-        <v>45.9897</v>
+        <v>88.7017</v>
       </c>
       <c r="E96" t="n">
-        <v>18.8623</v>
+        <v>26.029</v>
       </c>
       <c r="F96" t="n">
-        <v>29.48</v>
+        <v>43.8045</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>24.1939</v>
+        <v>89.616</v>
       </c>
       <c r="C97" t="n">
-        <v>36.2093</v>
+        <v>159.13</v>
       </c>
       <c r="D97" t="n">
-        <v>45.4968</v>
+        <v>81.4717</v>
       </c>
       <c r="E97" t="n">
-        <v>18.4648</v>
+        <v>25.4879</v>
       </c>
       <c r="F97" t="n">
-        <v>29.134</v>
+        <v>43.1965</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>23.7915</v>
+        <v>88.9842</v>
       </c>
       <c r="C98" t="n">
-        <v>35.7504</v>
+        <v>157.796</v>
       </c>
       <c r="D98" t="n">
-        <v>44.8651</v>
+        <v>80.5185</v>
       </c>
       <c r="E98" t="n">
-        <v>18.0868</v>
+        <v>25.0889</v>
       </c>
       <c r="F98" t="n">
-        <v>29.1044</v>
+        <v>42.6532</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>23.3405</v>
+        <v>88.2175</v>
       </c>
       <c r="C99" t="n">
-        <v>35.2682</v>
+        <v>152.964</v>
       </c>
       <c r="D99" t="n">
-        <v>44.8137</v>
+        <v>83.7385</v>
       </c>
       <c r="E99" t="n">
-        <v>17.7023</v>
+        <v>24.6615</v>
       </c>
       <c r="F99" t="n">
-        <v>28.7723</v>
+        <v>42.2509</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>22.8547</v>
+        <v>87.74169999999999</v>
       </c>
       <c r="C100" t="n">
-        <v>34.7828</v>
+        <v>158.112</v>
       </c>
       <c r="D100" t="n">
-        <v>43.8497</v>
+        <v>77.7394</v>
       </c>
       <c r="E100" t="n">
-        <v>17.3846</v>
+        <v>24.3721</v>
       </c>
       <c r="F100" t="n">
-        <v>28.2088</v>
+        <v>41.7406</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>22.3505</v>
+        <v>86.6797</v>
       </c>
       <c r="C101" t="n">
-        <v>41.2985</v>
+        <v>165.894</v>
       </c>
       <c r="D101" t="n">
-        <v>43.6172</v>
+        <v>90.5117</v>
       </c>
       <c r="E101" t="n">
-        <v>17.0743</v>
+        <v>23.9506</v>
       </c>
       <c r="F101" t="n">
-        <v>27.9611</v>
+        <v>41.279</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>21.8716</v>
+        <v>86.35550000000001</v>
       </c>
       <c r="C102" t="n">
-        <v>48.8424</v>
+        <v>152.28</v>
       </c>
       <c r="D102" t="n">
-        <v>43.0829</v>
+        <v>78.4218</v>
       </c>
       <c r="E102" t="n">
-        <v>16.8578</v>
+        <v>23.5314</v>
       </c>
       <c r="F102" t="n">
-        <v>27.9836</v>
+        <v>40.9598</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>21.3341</v>
+        <v>85.6493</v>
       </c>
       <c r="C103" t="n">
-        <v>43.8491</v>
+        <v>152.454</v>
       </c>
       <c r="D103" t="n">
-        <v>42.6893</v>
+        <v>79.7124</v>
       </c>
       <c r="E103" t="n">
-        <v>16.5543</v>
+        <v>23.1437</v>
       </c>
       <c r="F103" t="n">
-        <v>27.2342</v>
+        <v>40.3277</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>20.7362</v>
+        <v>84.6767</v>
       </c>
       <c r="C104" t="n">
-        <v>39.2879</v>
+        <v>157.371</v>
       </c>
       <c r="D104" t="n">
-        <v>42.5543</v>
+        <v>72.93300000000001</v>
       </c>
       <c r="E104" t="n">
-        <v>16.067</v>
+        <v>22.7385</v>
       </c>
       <c r="F104" t="n">
-        <v>26.9126</v>
+        <v>40.1315</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>20.0587</v>
+        <v>84.614</v>
       </c>
       <c r="C105" t="n">
-        <v>38.6168</v>
+        <v>152.247</v>
       </c>
       <c r="D105" t="n">
-        <v>42.2223</v>
+        <v>68.2619</v>
       </c>
       <c r="E105" t="n">
-        <v>15.7065</v>
+        <v>22.4032</v>
       </c>
       <c r="F105" t="n">
-        <v>26.5732</v>
+        <v>39.4638</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>19.4144</v>
+        <v>83.9824</v>
       </c>
       <c r="C106" t="n">
-        <v>41.6184</v>
+        <v>163.808</v>
       </c>
       <c r="D106" t="n">
-        <v>41.6851</v>
+        <v>81.34350000000001</v>
       </c>
       <c r="E106" t="n">
-        <v>15.4296</v>
+        <v>22.0174</v>
       </c>
       <c r="F106" t="n">
-        <v>26.2862</v>
+        <v>39.0322</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>18.645</v>
+        <v>83.21259999999999</v>
       </c>
       <c r="C107" t="n">
-        <v>41.1232</v>
+        <v>152.218</v>
       </c>
       <c r="D107" t="n">
-        <v>45.7117</v>
+        <v>85.6456</v>
       </c>
       <c r="E107" t="n">
-        <v>15.1173</v>
+        <v>21.629</v>
       </c>
       <c r="F107" t="n">
-        <v>25.9159</v>
+        <v>38.6195</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>17.73</v>
+        <v>82.30759999999999</v>
       </c>
       <c r="C108" t="n">
-        <v>39.7261</v>
+        <v>156.177</v>
       </c>
       <c r="D108" t="n">
-        <v>45.0375</v>
+        <v>90.59399999999999</v>
       </c>
       <c r="E108" t="n">
-        <v>19.941</v>
+        <v>27.2867</v>
       </c>
       <c r="F108" t="n">
-        <v>30.284</v>
+        <v>44.776</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>16.5706</v>
+        <v>81.34139999999999</v>
       </c>
       <c r="C109" t="n">
-        <v>34.5568</v>
+        <v>161.106</v>
       </c>
       <c r="D109" t="n">
-        <v>44.604</v>
+        <v>85.5132</v>
       </c>
       <c r="E109" t="n">
-        <v>19.477</v>
+        <v>26.7523</v>
       </c>
       <c r="F109" t="n">
-        <v>29.8372</v>
+        <v>44.3164</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>24.6493</v>
+        <v>89.76439999999999</v>
       </c>
       <c r="C110" t="n">
-        <v>47.3106</v>
+        <v>156.963</v>
       </c>
       <c r="D110" t="n">
-        <v>44.1602</v>
+        <v>91.1567</v>
       </c>
       <c r="E110" t="n">
-        <v>19.0662</v>
+        <v>26.2635</v>
       </c>
       <c r="F110" t="n">
-        <v>29.4317</v>
+        <v>43.761</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>24.3087</v>
+        <v>89.8926</v>
       </c>
       <c r="C111" t="n">
-        <v>47.1031</v>
+        <v>162.597</v>
       </c>
       <c r="D111" t="n">
-        <v>43.7971</v>
+        <v>76.9933</v>
       </c>
       <c r="E111" t="n">
-        <v>18.7691</v>
+        <v>25.7675</v>
       </c>
       <c r="F111" t="n">
-        <v>29.6169</v>
+        <v>43.5208</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>23.9121</v>
+        <v>88.6164</v>
       </c>
       <c r="C112" t="n">
-        <v>46.7761</v>
+        <v>172.036</v>
       </c>
       <c r="D112" t="n">
-        <v>43.3579</v>
+        <v>82.2312</v>
       </c>
       <c r="E112" t="n">
-        <v>18.4003</v>
+        <v>25.3512</v>
       </c>
       <c r="F112" t="n">
-        <v>29.3137</v>
+        <v>43.186</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>23.4407</v>
+        <v>88.559</v>
       </c>
       <c r="C113" t="n">
-        <v>46.3358</v>
+        <v>189.407</v>
       </c>
       <c r="D113" t="n">
-        <v>42.8394</v>
+        <v>73.5804</v>
       </c>
       <c r="E113" t="n">
-        <v>17.8656</v>
+        <v>24.8787</v>
       </c>
       <c r="F113" t="n">
-        <v>28.4405</v>
+        <v>42.6892</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>22.9575</v>
+        <v>87.9796</v>
       </c>
       <c r="C114" t="n">
-        <v>45.9384</v>
+        <v>179.471</v>
       </c>
       <c r="D114" t="n">
-        <v>42.3028</v>
+        <v>74.742</v>
       </c>
       <c r="E114" t="n">
-        <v>17.449</v>
+        <v>24.4662</v>
       </c>
       <c r="F114" t="n">
-        <v>28.3465</v>
+        <v>42.0877</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>22.4449</v>
+        <v>87.42319999999999</v>
       </c>
       <c r="C115" t="n">
-        <v>44.928</v>
+        <v>187.93</v>
       </c>
       <c r="D115" t="n">
-        <v>42.462</v>
+        <v>73.7259</v>
       </c>
       <c r="E115" t="n">
-        <v>17.1134</v>
+        <v>23.987</v>
       </c>
       <c r="F115" t="n">
-        <v>28.0643</v>
+        <v>41.4585</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>21.9173</v>
+        <v>87.30629999999999</v>
       </c>
       <c r="C116" t="n">
-        <v>46.0291</v>
+        <v>183.209</v>
       </c>
       <c r="D116" t="n">
-        <v>42.1717</v>
+        <v>69.3665</v>
       </c>
       <c r="E116" t="n">
-        <v>16.7985</v>
+        <v>23.5784</v>
       </c>
       <c r="F116" t="n">
-        <v>27.7308</v>
+        <v>41.0821</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>21.4298</v>
+        <v>86.155</v>
       </c>
       <c r="C117" t="n">
-        <v>33.6264</v>
+        <v>203.88</v>
       </c>
       <c r="D117" t="n">
-        <v>41.4614</v>
+        <v>69.2266</v>
       </c>
       <c r="E117" t="n">
-        <v>16.464</v>
+        <v>23.2131</v>
       </c>
       <c r="F117" t="n">
-        <v>27.2688</v>
+        <v>40.6126</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>20.83</v>
+        <v>85.5971</v>
       </c>
       <c r="C118" t="n">
-        <v>43.1671</v>
+        <v>191.594</v>
       </c>
       <c r="D118" t="n">
-        <v>40.8368</v>
+        <v>66.6557</v>
       </c>
       <c r="E118" t="n">
-        <v>16.133</v>
+        <v>22.7606</v>
       </c>
       <c r="F118" t="n">
-        <v>27.1081</v>
+        <v>40.1325</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>20.2286</v>
+        <v>84.8985</v>
       </c>
       <c r="C119" t="n">
-        <v>44.0286</v>
+        <v>180.542</v>
       </c>
       <c r="D119" t="n">
-        <v>40.6895</v>
+        <v>66.21769999999999</v>
       </c>
       <c r="E119" t="n">
-        <v>15.8211</v>
+        <v>22.4004</v>
       </c>
       <c r="F119" t="n">
-        <v>26.7287</v>
+        <v>39.7898</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>19.5705</v>
+        <v>84.051</v>
       </c>
       <c r="C120" t="n">
-        <v>43.4949</v>
+        <v>189.317</v>
       </c>
       <c r="D120" t="n">
-        <v>40.5487</v>
+        <v>64.7029</v>
       </c>
       <c r="E120" t="n">
-        <v>15.5225</v>
+        <v>22.0286</v>
       </c>
       <c r="F120" t="n">
-        <v>26.3722</v>
+        <v>39.2677</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>18.8434</v>
+        <v>83.2814</v>
       </c>
       <c r="C121" t="n">
-        <v>39.0923</v>
+        <v>192.873</v>
       </c>
       <c r="D121" t="n">
-        <v>49.2164</v>
+        <v>86.3951</v>
       </c>
       <c r="E121" t="n">
-        <v>15.1968</v>
+        <v>21.6688</v>
       </c>
       <c r="F121" t="n">
-        <v>25.9225</v>
+        <v>38.7577</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>17.8388</v>
+        <v>82.4823</v>
       </c>
       <c r="C122" t="n">
-        <v>33.4795</v>
+        <v>201.227</v>
       </c>
       <c r="D122" t="n">
-        <v>47.7135</v>
+        <v>85.6178</v>
       </c>
       <c r="E122" t="n">
-        <v>14.8866</v>
+        <v>21.2648</v>
       </c>
       <c r="F122" t="n">
-        <v>25.6542</v>
+        <v>38.219</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>16.9398</v>
+        <v>81.5239</v>
       </c>
       <c r="C123" t="n">
-        <v>35.4697</v>
+        <v>192.707</v>
       </c>
       <c r="D123" t="n">
-        <v>47.2358</v>
+        <v>133.854</v>
       </c>
       <c r="E123" t="n">
-        <v>19.6585</v>
+        <v>26.6973</v>
       </c>
       <c r="F123" t="n">
-        <v>30.3674</v>
+        <v>44.4254</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>24.6935</v>
+        <v>90.6707</v>
       </c>
       <c r="C124" t="n">
-        <v>49.9706</v>
+        <v>208.005</v>
       </c>
       <c r="D124" t="n">
-        <v>46.6411</v>
+        <v>80.4301</v>
       </c>
       <c r="E124" t="n">
-        <v>19.2058</v>
+        <v>26.2105</v>
       </c>
       <c r="F124" t="n">
-        <v>30.036</v>
+        <v>43.8924</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>24.3612</v>
+        <v>89.9402</v>
       </c>
       <c r="C125" t="n">
-        <v>38.4729</v>
+        <v>210.413</v>
       </c>
       <c r="D125" t="n">
-        <v>46.338</v>
+        <v>78.883</v>
       </c>
       <c r="E125" t="n">
-        <v>18.8093</v>
+        <v>25.8792</v>
       </c>
       <c r="F125" t="n">
-        <v>29.5232</v>
+        <v>43.3435</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>23.9507</v>
+        <v>89.4087</v>
       </c>
       <c r="C126" t="n">
-        <v>46.3768</v>
+        <v>210.451</v>
       </c>
       <c r="D126" t="n">
-        <v>45.8176</v>
+        <v>78.7384</v>
       </c>
       <c r="E126" t="n">
-        <v>18.4147</v>
+        <v>25.3429</v>
       </c>
       <c r="F126" t="n">
-        <v>29.3357</v>
+        <v>42.9297</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>23.4916</v>
+        <v>88.7427</v>
       </c>
       <c r="C127" t="n">
-        <v>39.9525</v>
+        <v>213.202</v>
       </c>
       <c r="D127" t="n">
-        <v>44.7338</v>
+        <v>75.6503</v>
       </c>
       <c r="E127" t="n">
-        <v>18.05</v>
+        <v>24.9034</v>
       </c>
       <c r="F127" t="n">
-        <v>28.9398</v>
+        <v>42.4049</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>22.9943</v>
+        <v>87.9119</v>
       </c>
       <c r="C128" t="n">
-        <v>52.4676</v>
+        <v>213.543</v>
       </c>
       <c r="D128" t="n">
-        <v>44.1402</v>
+        <v>77.4041</v>
       </c>
       <c r="E128" t="n">
-        <v>17.6843</v>
+        <v>24.4744</v>
       </c>
       <c r="F128" t="n">
-        <v>28.6539</v>
+        <v>41.9354</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>22.5479</v>
+        <v>87.2552</v>
       </c>
       <c r="C129" t="n">
-        <v>38.9497</v>
+        <v>214.352</v>
       </c>
       <c r="D129" t="n">
-        <v>44.0648</v>
+        <v>87.7606</v>
       </c>
       <c r="E129" t="n">
-        <v>17.3302</v>
+        <v>24.0757</v>
       </c>
       <c r="F129" t="n">
-        <v>28.2447</v>
+        <v>41.6562</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>22.0373</v>
+        <v>86.63200000000001</v>
       </c>
       <c r="C130" t="n">
-        <v>40.1513</v>
+        <v>195.306</v>
       </c>
       <c r="D130" t="n">
-        <v>43.606</v>
+        <v>91.8883</v>
       </c>
       <c r="E130" t="n">
-        <v>17.0439</v>
+        <v>23.7045</v>
       </c>
       <c r="F130" t="n">
-        <v>27.9897</v>
+        <v>41.2005</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>21.4737</v>
+        <v>85.8413</v>
       </c>
       <c r="C131" t="n">
-        <v>44.7993</v>
+        <v>192.489</v>
       </c>
       <c r="D131" t="n">
-        <v>43.2044</v>
+        <v>93.815</v>
       </c>
       <c r="E131" t="n">
-        <v>16.7075</v>
+        <v>23.2839</v>
       </c>
       <c r="F131" t="n">
-        <v>27.6738</v>
+        <v>40.7328</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>20.9603</v>
+        <v>85.2723</v>
       </c>
       <c r="C132" t="n">
-        <v>46.5666</v>
+        <v>189.033</v>
       </c>
       <c r="D132" t="n">
-        <v>42.8387</v>
+        <v>83.4229</v>
       </c>
       <c r="E132" t="n">
-        <v>16.4042</v>
+        <v>22.927</v>
       </c>
       <c r="F132" t="n">
-        <v>27.5071</v>
+        <v>40.1842</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>20.385</v>
+        <v>84.7192</v>
       </c>
       <c r="C133" t="n">
-        <v>41.7332</v>
+        <v>191.832</v>
       </c>
       <c r="D133" t="n">
-        <v>42.3428</v>
+        <v>82.4901</v>
       </c>
       <c r="E133" t="n">
-        <v>16.016</v>
+        <v>22.5203</v>
       </c>
       <c r="F133" t="n">
-        <v>27.1476</v>
+        <v>39.6642</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>19.7507</v>
+        <v>84.41160000000001</v>
       </c>
       <c r="C134" t="n">
-        <v>40.8705</v>
+        <v>191.117</v>
       </c>
       <c r="D134" t="n">
-        <v>41.9811</v>
+        <v>86.086</v>
       </c>
       <c r="E134" t="n">
-        <v>15.5362</v>
+        <v>22.1071</v>
       </c>
       <c r="F134" t="n">
-        <v>26.3644</v>
+        <v>39.3302</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>19.006</v>
+        <v>83.3746</v>
       </c>
       <c r="C135" t="n">
-        <v>44.7118</v>
+        <v>207.828</v>
       </c>
       <c r="D135" t="n">
-        <v>49.3347</v>
+        <v>99.3385</v>
       </c>
       <c r="E135" t="n">
-        <v>15.2287</v>
+        <v>21.7246</v>
       </c>
       <c r="F135" t="n">
-        <v>26.1137</v>
+        <v>39.0591</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>18.1019</v>
+        <v>82.7321</v>
       </c>
       <c r="C136" t="n">
-        <v>42.9698</v>
+        <v>207.571</v>
       </c>
       <c r="D136" t="n">
-        <v>48.754</v>
+        <v>108.595</v>
       </c>
       <c r="E136" t="n">
-        <v>14.9431</v>
+        <v>21.3397</v>
       </c>
       <c r="F136" t="n">
-        <v>25.6994</v>
+        <v>38.3347</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>17.0961</v>
+        <v>81.9909</v>
       </c>
       <c r="C137" t="n">
-        <v>41.4858</v>
+        <v>204.114</v>
       </c>
       <c r="D137" t="n">
-        <v>48.4306</v>
+        <v>94.7501</v>
       </c>
       <c r="E137" t="n">
-        <v>19.7482</v>
+        <v>26.8522</v>
       </c>
       <c r="F137" t="n">
-        <v>29.8856</v>
+        <v>44.7179</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>24.7895</v>
+        <v>121.972</v>
       </c>
       <c r="C138" t="n">
-        <v>51.4396</v>
+        <v>209.156</v>
       </c>
       <c r="D138" t="n">
-        <v>47.2498</v>
+        <v>130.42</v>
       </c>
       <c r="E138" t="n">
-        <v>19.3092</v>
+        <v>26.3422</v>
       </c>
       <c r="F138" t="n">
-        <v>29.5197</v>
+        <v>44.2901</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>24.4365</v>
+        <v>118.347</v>
       </c>
       <c r="C139" t="n">
-        <v>49.8608</v>
+        <v>203.724</v>
       </c>
       <c r="D139" t="n">
-        <v>46.6299</v>
+        <v>120.371</v>
       </c>
       <c r="E139" t="n">
-        <v>18.9007</v>
+        <v>25.9196</v>
       </c>
       <c r="F139" t="n">
-        <v>29.2037</v>
+        <v>43.6069</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>24.0389</v>
+        <v>115.441</v>
       </c>
       <c r="C140" t="n">
-        <v>40.4231</v>
+        <v>203.816</v>
       </c>
       <c r="D140" t="n">
-        <v>45.9415</v>
+        <v>100.665</v>
       </c>
       <c r="E140" t="n">
-        <v>18.4768</v>
+        <v>25.4661</v>
       </c>
       <c r="F140" t="n">
-        <v>29.1965</v>
+        <v>43.2305</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>23.6121</v>
+        <v>114.437</v>
       </c>
       <c r="C141" t="n">
-        <v>44.7031</v>
+        <v>226.932</v>
       </c>
       <c r="D141" t="n">
-        <v>45.3649</v>
+        <v>93.7718</v>
       </c>
       <c r="E141" t="n">
-        <v>18.1169</v>
+        <v>25.0159</v>
       </c>
       <c r="F141" t="n">
-        <v>28.7669</v>
+        <v>42.64</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>23.143</v>
+        <v>119.074</v>
       </c>
       <c r="C142" t="n">
-        <v>51.5054</v>
+        <v>210.736</v>
       </c>
       <c r="D142" t="n">
-        <v>44.8422</v>
+        <v>93.77849999999999</v>
       </c>
       <c r="E142" t="n">
-        <v>17.7571</v>
+        <v>24.5904</v>
       </c>
       <c r="F142" t="n">
-        <v>28.5487</v>
+        <v>42.4904</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>22.6567</v>
+        <v>120.056</v>
       </c>
       <c r="C143" t="n">
-        <v>49.8344</v>
+        <v>203.499</v>
       </c>
       <c r="D143" t="n">
-        <v>44.3619</v>
+        <v>88.28279999999999</v>
       </c>
       <c r="E143" t="n">
-        <v>17.3911</v>
+        <v>24.1671</v>
       </c>
       <c r="F143" t="n">
-        <v>28.4385</v>
+        <v>41.783</v>
       </c>
     </row>
   </sheetData>

--- a/clang-x64/Running erasure.xlsx
+++ b/clang-x64/Running erasure.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>86.4451</v>
+        <v>18.207</v>
       </c>
       <c r="C2" t="n">
-        <v>124.729</v>
+        <v>31.1002</v>
       </c>
       <c r="D2" t="n">
-        <v>49.5287</v>
+        <v>30.3341</v>
       </c>
       <c r="E2" t="n">
-        <v>22.8676</v>
+        <v>13.404</v>
       </c>
       <c r="F2" t="n">
-        <v>39.4053</v>
+        <v>25.4372</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>86.59310000000001</v>
+        <v>17.9424</v>
       </c>
       <c r="C3" t="n">
-        <v>123.296</v>
+        <v>30.6523</v>
       </c>
       <c r="D3" t="n">
-        <v>50.2526</v>
+        <v>30.5031</v>
       </c>
       <c r="E3" t="n">
-        <v>22.2117</v>
+        <v>13.0995</v>
       </c>
       <c r="F3" t="n">
-        <v>39.2941</v>
+        <v>24.8786</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>85.2226</v>
+        <v>17.5546</v>
       </c>
       <c r="C4" t="n">
-        <v>123.148</v>
+        <v>30.7891</v>
       </c>
       <c r="D4" t="n">
-        <v>49.8111</v>
+        <v>30.6662</v>
       </c>
       <c r="E4" t="n">
-        <v>21.7162</v>
+        <v>12.9304</v>
       </c>
       <c r="F4" t="n">
-        <v>38.5165</v>
+        <v>24.6887</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>84.1682</v>
+        <v>17.202</v>
       </c>
       <c r="C5" t="n">
-        <v>121.823</v>
+        <v>30.0997</v>
       </c>
       <c r="D5" t="n">
-        <v>50.1189</v>
+        <v>30.8823</v>
       </c>
       <c r="E5" t="n">
-        <v>21.4631</v>
+        <v>12.9122</v>
       </c>
       <c r="F5" t="n">
-        <v>38.6517</v>
+        <v>25.1004</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>84.3837</v>
+        <v>16.8605</v>
       </c>
       <c r="C6" t="n">
-        <v>121.741</v>
+        <v>29.087</v>
       </c>
       <c r="D6" t="n">
-        <v>49.9484</v>
+        <v>30.9791</v>
       </c>
       <c r="E6" t="n">
-        <v>21.1492</v>
+        <v>12.6854</v>
       </c>
       <c r="F6" t="n">
-        <v>38.0793</v>
+        <v>24.8528</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>83.9453</v>
+        <v>16.0205</v>
       </c>
       <c r="C7" t="n">
-        <v>120.537</v>
+        <v>28.5663</v>
       </c>
       <c r="D7" t="n">
-        <v>51.0683</v>
+        <v>30.3298</v>
       </c>
       <c r="E7" t="n">
-        <v>20.6549</v>
+        <v>12.4114</v>
       </c>
       <c r="F7" t="n">
-        <v>37.432</v>
+        <v>24.3516</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>83.1002</v>
+        <v>15.5107</v>
       </c>
       <c r="C8" t="n">
-        <v>119.921</v>
+        <v>28.0739</v>
       </c>
       <c r="D8" t="n">
-        <v>51.0465</v>
+        <v>30.4152</v>
       </c>
       <c r="E8" t="n">
-        <v>20.2229</v>
+        <v>12.1964</v>
       </c>
       <c r="F8" t="n">
-        <v>36.9766</v>
+        <v>24.0671</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>82.1091</v>
+        <v>14.4867</v>
       </c>
       <c r="C9" t="n">
-        <v>118.649</v>
+        <v>27.5892</v>
       </c>
       <c r="D9" t="n">
-        <v>51.9071</v>
+        <v>30.4867</v>
       </c>
       <c r="E9" t="n">
-        <v>27.0053</v>
+        <v>18.8048</v>
       </c>
       <c r="F9" t="n">
-        <v>44.4026</v>
+        <v>28.03</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>89.8073</v>
+        <v>21.8206</v>
       </c>
       <c r="C10" t="n">
-        <v>127.014</v>
+        <v>34.7262</v>
       </c>
       <c r="D10" t="n">
-        <v>51.1075</v>
+        <v>30.5955</v>
       </c>
       <c r="E10" t="n">
-        <v>26.3377</v>
+        <v>18.4603</v>
       </c>
       <c r="F10" t="n">
-        <v>43.8081</v>
+        <v>27.8511</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>89.9851</v>
+        <v>21.4238</v>
       </c>
       <c r="C11" t="n">
-        <v>126.999</v>
+        <v>34.4098</v>
       </c>
       <c r="D11" t="n">
-        <v>51.5923</v>
+        <v>30.8641</v>
       </c>
       <c r="E11" t="n">
-        <v>26.1386</v>
+        <v>18.1331</v>
       </c>
       <c r="F11" t="n">
-        <v>43.59</v>
+        <v>27.6757</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>89.5376</v>
+        <v>21.3116</v>
       </c>
       <c r="C12" t="n">
-        <v>125.019</v>
+        <v>34.008</v>
       </c>
       <c r="D12" t="n">
-        <v>52.767</v>
+        <v>30.9754</v>
       </c>
       <c r="E12" t="n">
-        <v>25.2945</v>
+        <v>17.7603</v>
       </c>
       <c r="F12" t="n">
-        <v>43.0519</v>
+        <v>27.3053</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>88.6392</v>
+        <v>20.9188</v>
       </c>
       <c r="C13" t="n">
-        <v>125.802</v>
+        <v>33.7713</v>
       </c>
       <c r="D13" t="n">
-        <v>51.0993</v>
+        <v>30.883</v>
       </c>
       <c r="E13" t="n">
-        <v>25.06</v>
+        <v>17.2913</v>
       </c>
       <c r="F13" t="n">
-        <v>42.2326</v>
+        <v>27.2309</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>88.18389999999999</v>
+        <v>20.5139</v>
       </c>
       <c r="C14" t="n">
-        <v>126.088</v>
+        <v>33.2129</v>
       </c>
       <c r="D14" t="n">
-        <v>51.023</v>
+        <v>30.7888</v>
       </c>
       <c r="E14" t="n">
-        <v>24.7036</v>
+        <v>16.8692</v>
       </c>
       <c r="F14" t="n">
-        <v>41.6305</v>
+        <v>26.6967</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>87.8976</v>
+        <v>20.1312</v>
       </c>
       <c r="C15" t="n">
-        <v>122.413</v>
+        <v>32.873</v>
       </c>
       <c r="D15" t="n">
-        <v>52.3791</v>
+        <v>31.0037</v>
       </c>
       <c r="E15" t="n">
-        <v>24.2014</v>
+        <v>16.5539</v>
       </c>
       <c r="F15" t="n">
-        <v>41.3296</v>
+        <v>26.4917</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>87.1769</v>
+        <v>19.635</v>
       </c>
       <c r="C16" t="n">
-        <v>122.828</v>
+        <v>32.4725</v>
       </c>
       <c r="D16" t="n">
-        <v>52.4619</v>
+        <v>31.145</v>
       </c>
       <c r="E16" t="n">
-        <v>24.0877</v>
+        <v>16.2417</v>
       </c>
       <c r="F16" t="n">
-        <v>41.5404</v>
+        <v>26.096</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>86.6583</v>
+        <v>19.3583</v>
       </c>
       <c r="C17" t="n">
-        <v>123.999</v>
+        <v>31.779</v>
       </c>
       <c r="D17" t="n">
-        <v>52.0389</v>
+        <v>31.1738</v>
       </c>
       <c r="E17" t="n">
-        <v>23.5856</v>
+        <v>16.0272</v>
       </c>
       <c r="F17" t="n">
-        <v>40.9023</v>
+        <v>25.8045</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>85.6354</v>
+        <v>18.9201</v>
       </c>
       <c r="C18" t="n">
-        <v>123.246</v>
+        <v>31.568</v>
       </c>
       <c r="D18" t="n">
-        <v>52.4958</v>
+        <v>31.2394</v>
       </c>
       <c r="E18" t="n">
-        <v>22.9833</v>
+        <v>15.59</v>
       </c>
       <c r="F18" t="n">
-        <v>39.8422</v>
+        <v>25.5411</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>85.5213</v>
+        <v>18.3924</v>
       </c>
       <c r="C19" t="n">
-        <v>121.119</v>
+        <v>30.6079</v>
       </c>
       <c r="D19" t="n">
-        <v>52.5238</v>
+        <v>31.4096</v>
       </c>
       <c r="E19" t="n">
-        <v>22.382</v>
+        <v>15.1644</v>
       </c>
       <c r="F19" t="n">
-        <v>39.9739</v>
+        <v>25.2679</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>84.6418</v>
+        <v>17.9082</v>
       </c>
       <c r="C20" t="n">
-        <v>121.539</v>
+        <v>29.8355</v>
       </c>
       <c r="D20" t="n">
-        <v>52.492</v>
+        <v>31.5699</v>
       </c>
       <c r="E20" t="n">
-        <v>22.3749</v>
+        <v>14.9916</v>
       </c>
       <c r="F20" t="n">
-        <v>39.6057</v>
+        <v>25.262</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>84.0839</v>
+        <v>17.1711</v>
       </c>
       <c r="C21" t="n">
-        <v>121.726</v>
+        <v>29.8409</v>
       </c>
       <c r="D21" t="n">
-        <v>55.007</v>
+        <v>30.8411</v>
       </c>
       <c r="E21" t="n">
-        <v>21.5406</v>
+        <v>14.4208</v>
       </c>
       <c r="F21" t="n">
-        <v>38.4342</v>
+        <v>24.6664</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>83.3141</v>
+        <v>16.536</v>
       </c>
       <c r="C22" t="n">
-        <v>120.767</v>
+        <v>28.7272</v>
       </c>
       <c r="D22" t="n">
-        <v>55.5838</v>
+        <v>31.2355</v>
       </c>
       <c r="E22" t="n">
-        <v>20.9763</v>
+        <v>14.055</v>
       </c>
       <c r="F22" t="n">
-        <v>38.1593</v>
+        <v>24.8682</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>82.4893</v>
+        <v>15.7264</v>
       </c>
       <c r="C23" t="n">
-        <v>118.784</v>
+        <v>27.2237</v>
       </c>
       <c r="D23" t="n">
-        <v>53.3908</v>
+        <v>30.7194</v>
       </c>
       <c r="E23" t="n">
-        <v>27.371</v>
+        <v>19.6827</v>
       </c>
       <c r="F23" t="n">
-        <v>45.0289</v>
+        <v>28.5055</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>90.3867</v>
+        <v>22.6717</v>
       </c>
       <c r="C24" t="n">
-        <v>127.442</v>
+        <v>34.6066</v>
       </c>
       <c r="D24" t="n">
-        <v>54.8671</v>
+        <v>30.9469</v>
       </c>
       <c r="E24" t="n">
-        <v>26.759</v>
+        <v>19.1038</v>
       </c>
       <c r="F24" t="n">
-        <v>43.7196</v>
+        <v>28.1387</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>90.029</v>
+        <v>22.2589</v>
       </c>
       <c r="C25" t="n">
-        <v>128.149</v>
+        <v>34.2106</v>
       </c>
       <c r="D25" t="n">
-        <v>55.1534</v>
+        <v>31.3027</v>
       </c>
       <c r="E25" t="n">
-        <v>26.419</v>
+        <v>18.7797</v>
       </c>
       <c r="F25" t="n">
-        <v>44.8894</v>
+        <v>27.8114</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>89.2808</v>
+        <v>21.9813</v>
       </c>
       <c r="C26" t="n">
-        <v>126.873</v>
+        <v>33.7807</v>
       </c>
       <c r="D26" t="n">
-        <v>55.1371</v>
+        <v>31.598</v>
       </c>
       <c r="E26" t="n">
-        <v>25.8948</v>
+        <v>18.2896</v>
       </c>
       <c r="F26" t="n">
-        <v>43.9947</v>
+        <v>27.5997</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>89.0492</v>
+        <v>21.6885</v>
       </c>
       <c r="C27" t="n">
-        <v>126.608</v>
+        <v>33.3345</v>
       </c>
       <c r="D27" t="n">
-        <v>56.3471</v>
+        <v>31.1922</v>
       </c>
       <c r="E27" t="n">
-        <v>25.4809</v>
+        <v>18.0386</v>
       </c>
       <c r="F27" t="n">
-        <v>43.6189</v>
+        <v>27.3134</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>88.4023</v>
+        <v>21.2555</v>
       </c>
       <c r="C28" t="n">
-        <v>126.188</v>
+        <v>32.8482</v>
       </c>
       <c r="D28" t="n">
-        <v>52.2337</v>
+        <v>31.3435</v>
       </c>
       <c r="E28" t="n">
-        <v>24.9122</v>
+        <v>17.5465</v>
       </c>
       <c r="F28" t="n">
-        <v>41.7953</v>
+        <v>27.0352</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>87.9542</v>
+        <v>20.9179</v>
       </c>
       <c r="C29" t="n">
-        <v>125.146</v>
+        <v>32.4665</v>
       </c>
       <c r="D29" t="n">
-        <v>55.3393</v>
+        <v>31.4498</v>
       </c>
       <c r="E29" t="n">
-        <v>24.5177</v>
+        <v>17.2417</v>
       </c>
       <c r="F29" t="n">
-        <v>43.4117</v>
+        <v>26.7148</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>87.0408</v>
+        <v>20.386</v>
       </c>
       <c r="C30" t="n">
-        <v>124.48</v>
+        <v>31.4108</v>
       </c>
       <c r="D30" t="n">
-        <v>57.3512</v>
+        <v>31.5808</v>
       </c>
       <c r="E30" t="n">
-        <v>24.0098</v>
+        <v>16.9504</v>
       </c>
       <c r="F30" t="n">
-        <v>41.0724</v>
+        <v>26.4837</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>86.33799999999999</v>
+        <v>19.9017</v>
       </c>
       <c r="C31" t="n">
-        <v>124.044</v>
+        <v>31.3162</v>
       </c>
       <c r="D31" t="n">
-        <v>55.7383</v>
+        <v>31.3723</v>
       </c>
       <c r="E31" t="n">
-        <v>23.5424</v>
+        <v>16.549</v>
       </c>
       <c r="F31" t="n">
-        <v>42.1275</v>
+        <v>26.2201</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>86.1536</v>
+        <v>19.4127</v>
       </c>
       <c r="C32" t="n">
-        <v>123.544</v>
+        <v>31.2325</v>
       </c>
       <c r="D32" t="n">
-        <v>56.5413</v>
+        <v>31.3889</v>
       </c>
       <c r="E32" t="n">
-        <v>23.2356</v>
+        <v>16.1579</v>
       </c>
       <c r="F32" t="n">
-        <v>40.1568</v>
+        <v>25.8867</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>85.66030000000001</v>
+        <v>18.9655</v>
       </c>
       <c r="C33" t="n">
-        <v>125.642</v>
+        <v>30.0537</v>
       </c>
       <c r="D33" t="n">
-        <v>55.4948</v>
+        <v>31.6705</v>
       </c>
       <c r="E33" t="n">
-        <v>22.6798</v>
+        <v>15.9714</v>
       </c>
       <c r="F33" t="n">
-        <v>40.3544</v>
+        <v>25.6789</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>84.94459999999999</v>
+        <v>18.3838</v>
       </c>
       <c r="C34" t="n">
-        <v>123.72</v>
+        <v>29.8321</v>
       </c>
       <c r="D34" t="n">
-        <v>57.5559</v>
+        <v>31.7341</v>
       </c>
       <c r="E34" t="n">
-        <v>22.2421</v>
+        <v>15.6024</v>
       </c>
       <c r="F34" t="n">
-        <v>41.4854</v>
+        <v>25.3466</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>84.2794</v>
+        <v>17.7859</v>
       </c>
       <c r="C35" t="n">
-        <v>125.124</v>
+        <v>29.4389</v>
       </c>
       <c r="D35" t="n">
-        <v>61.9436</v>
+        <v>30.9274</v>
       </c>
       <c r="E35" t="n">
-        <v>21.7705</v>
+        <v>15.0584</v>
       </c>
       <c r="F35" t="n">
-        <v>41.4389</v>
+        <v>24.9706</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>83.5732</v>
+        <v>17.1167</v>
       </c>
       <c r="C36" t="n">
-        <v>122.84</v>
+        <v>28.7012</v>
       </c>
       <c r="D36" t="n">
-        <v>61.4872</v>
+        <v>30.9916</v>
       </c>
       <c r="E36" t="n">
-        <v>21.3076</v>
+        <v>14.657</v>
       </c>
       <c r="F36" t="n">
-        <v>39.1588</v>
+        <v>24.6134</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>82.7957</v>
+        <v>16.4463</v>
       </c>
       <c r="C37" t="n">
-        <v>118.88</v>
+        <v>27.6092</v>
       </c>
       <c r="D37" t="n">
-        <v>61.4097</v>
+        <v>30.9703</v>
       </c>
       <c r="E37" t="n">
-        <v>27.4852</v>
+        <v>19.8518</v>
       </c>
       <c r="F37" t="n">
-        <v>49.4803</v>
+        <v>28.7938</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>90.1216</v>
+        <v>23.2233</v>
       </c>
       <c r="C38" t="n">
-        <v>128.395</v>
+        <v>34.4886</v>
       </c>
       <c r="D38" t="n">
-        <v>62.3781</v>
+        <v>31.4928</v>
       </c>
       <c r="E38" t="n">
-        <v>27.0055</v>
+        <v>19.4637</v>
       </c>
       <c r="F38" t="n">
-        <v>44.7948</v>
+        <v>28.4619</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>89.9639</v>
+        <v>22.7985</v>
       </c>
       <c r="C39" t="n">
-        <v>128.928</v>
+        <v>34.1398</v>
       </c>
       <c r="D39" t="n">
-        <v>60.0624</v>
+        <v>30.9709</v>
       </c>
       <c r="E39" t="n">
-        <v>26.4479</v>
+        <v>19.0703</v>
       </c>
       <c r="F39" t="n">
-        <v>44.3881</v>
+        <v>28.145</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>89.5074</v>
+        <v>22.3672</v>
       </c>
       <c r="C40" t="n">
-        <v>134.951</v>
+        <v>33.8711</v>
       </c>
       <c r="D40" t="n">
-        <v>61.0518</v>
+        <v>31.1114</v>
       </c>
       <c r="E40" t="n">
-        <v>25.9293</v>
+        <v>18.5758</v>
       </c>
       <c r="F40" t="n">
-        <v>43.3978</v>
+        <v>27.8515</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>88.78579999999999</v>
+        <v>21.9661</v>
       </c>
       <c r="C41" t="n">
-        <v>127.747</v>
+        <v>33.4997</v>
       </c>
       <c r="D41" t="n">
-        <v>61.9046</v>
+        <v>31.0411</v>
       </c>
       <c r="E41" t="n">
-        <v>25.371</v>
+        <v>18.242</v>
       </c>
       <c r="F41" t="n">
-        <v>43.0058</v>
+        <v>27.5666</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>88.54949999999999</v>
+        <v>21.6076</v>
       </c>
       <c r="C42" t="n">
-        <v>126.947</v>
+        <v>33.0911</v>
       </c>
       <c r="D42" t="n">
-        <v>59.8995</v>
+        <v>31.1643</v>
       </c>
       <c r="E42" t="n">
-        <v>25.1034</v>
+        <v>17.8721</v>
       </c>
       <c r="F42" t="n">
-        <v>42.2677</v>
+        <v>27.2741</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>87.9547</v>
+        <v>21.1646</v>
       </c>
       <c r="C43" t="n">
-        <v>127.416</v>
+        <v>32.6084</v>
       </c>
       <c r="D43" t="n">
-        <v>65.3437</v>
+        <v>31.3108</v>
       </c>
       <c r="E43" t="n">
-        <v>24.6774</v>
+        <v>17.5498</v>
       </c>
       <c r="F43" t="n">
-        <v>43.0406</v>
+        <v>27.0169</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>87.069</v>
+        <v>20.6674</v>
       </c>
       <c r="C44" t="n">
-        <v>127.622</v>
+        <v>32.5534</v>
       </c>
       <c r="D44" t="n">
-        <v>61.29</v>
+        <v>31.2615</v>
       </c>
       <c r="E44" t="n">
-        <v>24.2534</v>
+        <v>17.1463</v>
       </c>
       <c r="F44" t="n">
-        <v>42.6011</v>
+        <v>26.7628</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>86.7441</v>
+        <v>20.2225</v>
       </c>
       <c r="C45" t="n">
-        <v>130.324</v>
+        <v>32.0849</v>
       </c>
       <c r="D45" t="n">
-        <v>60.5607</v>
+        <v>31.4582</v>
       </c>
       <c r="E45" t="n">
-        <v>23.788</v>
+        <v>16.7518</v>
       </c>
       <c r="F45" t="n">
-        <v>40.7226</v>
+        <v>26.4665</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>86.21769999999999</v>
+        <v>19.6902</v>
       </c>
       <c r="C46" t="n">
-        <v>129.238</v>
+        <v>31.3861</v>
       </c>
       <c r="D46" t="n">
-        <v>65.30289999999999</v>
+        <v>31.5787</v>
       </c>
       <c r="E46" t="n">
-        <v>23.2617</v>
+        <v>16.4375</v>
       </c>
       <c r="F46" t="n">
-        <v>41.5883</v>
+        <v>26.1386</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>85.5774</v>
+        <v>19.2328</v>
       </c>
       <c r="C47" t="n">
-        <v>125.56</v>
+        <v>31.4483</v>
       </c>
       <c r="D47" t="n">
-        <v>63.0092</v>
+        <v>31.6816</v>
       </c>
       <c r="E47" t="n">
-        <v>22.8591</v>
+        <v>16.1073</v>
       </c>
       <c r="F47" t="n">
-        <v>41.1374</v>
+        <v>25.9029</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>84.5215</v>
+        <v>18.6798</v>
       </c>
       <c r="C48" t="n">
-        <v>131.665</v>
+        <v>29.9253</v>
       </c>
       <c r="D48" t="n">
-        <v>60.4321</v>
+        <v>31.7179</v>
       </c>
       <c r="E48" t="n">
-        <v>22.3182</v>
+        <v>15.8104</v>
       </c>
       <c r="F48" t="n">
-        <v>42.8778</v>
+        <v>25.5957</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>84.181</v>
+        <v>18.1526</v>
       </c>
       <c r="C49" t="n">
-        <v>128.462</v>
+        <v>30.5743</v>
       </c>
       <c r="D49" t="n">
-        <v>65.2179</v>
+        <v>31.9876</v>
       </c>
       <c r="E49" t="n">
-        <v>21.842</v>
+        <v>15.3831</v>
       </c>
       <c r="F49" t="n">
-        <v>40.2234</v>
+        <v>25.2894</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>83.4158</v>
+        <v>17.5127</v>
       </c>
       <c r="C50" t="n">
-        <v>125.748</v>
+        <v>29.4281</v>
       </c>
       <c r="D50" t="n">
-        <v>79.13039999999999</v>
+        <v>31.0601</v>
       </c>
       <c r="E50" t="n">
-        <v>21.4537</v>
+        <v>14.9816</v>
       </c>
       <c r="F50" t="n">
-        <v>38.5529</v>
+        <v>24.9154</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>82.5016</v>
+        <v>16.7335</v>
       </c>
       <c r="C51" t="n">
-        <v>127.73</v>
+        <v>28.7202</v>
       </c>
       <c r="D51" t="n">
-        <v>75.5827</v>
+        <v>31.3094</v>
       </c>
       <c r="E51" t="n">
-        <v>27.0398</v>
+        <v>20.1824</v>
       </c>
       <c r="F51" t="n">
-        <v>47.799</v>
+        <v>28.881</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>81.9683</v>
+        <v>15.79</v>
       </c>
       <c r="C52" t="n">
-        <v>123.676</v>
+        <v>27.3913</v>
       </c>
       <c r="D52" t="n">
-        <v>75.9521</v>
+        <v>31.2772</v>
       </c>
       <c r="E52" t="n">
-        <v>26.5398</v>
+        <v>19.7051</v>
       </c>
       <c r="F52" t="n">
-        <v>45.2577</v>
+        <v>28.5365</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>90.12569999999999</v>
+        <v>23.0199</v>
       </c>
       <c r="C53" t="n">
-        <v>135.573</v>
+        <v>34.5104</v>
       </c>
       <c r="D53" t="n">
-        <v>68.2719</v>
+        <v>31.7223</v>
       </c>
       <c r="E53" t="n">
-        <v>26.213</v>
+        <v>19.3386</v>
       </c>
       <c r="F53" t="n">
-        <v>44.8686</v>
+        <v>28.3412</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>89.40900000000001</v>
+        <v>22.6946</v>
       </c>
       <c r="C54" t="n">
-        <v>135.836</v>
+        <v>34.2452</v>
       </c>
       <c r="D54" t="n">
-        <v>76.6217</v>
+        <v>32.1403</v>
       </c>
       <c r="E54" t="n">
-        <v>25.5564</v>
+        <v>18.9076</v>
       </c>
       <c r="F54" t="n">
-        <v>43.4777</v>
+        <v>28.0572</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>89.07340000000001</v>
+        <v>22.2718</v>
       </c>
       <c r="C55" t="n">
-        <v>126.341</v>
+        <v>34.0214</v>
       </c>
       <c r="D55" t="n">
-        <v>80.62649999999999</v>
+        <v>31.798</v>
       </c>
       <c r="E55" t="n">
-        <v>25.1806</v>
+        <v>18.4299</v>
       </c>
       <c r="F55" t="n">
-        <v>42.9038</v>
+        <v>27.7306</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>88.499</v>
+        <v>21.8324</v>
       </c>
       <c r="C56" t="n">
-        <v>125.893</v>
+        <v>33.6526</v>
       </c>
       <c r="D56" t="n">
-        <v>78.9586</v>
+        <v>32.1315</v>
       </c>
       <c r="E56" t="n">
-        <v>24.7153</v>
+        <v>18.0216</v>
       </c>
       <c r="F56" t="n">
-        <v>44.0015</v>
+        <v>27.4511</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>87.8434</v>
+        <v>21.4736</v>
       </c>
       <c r="C57" t="n">
-        <v>137.784</v>
+        <v>33.2865</v>
       </c>
       <c r="D57" t="n">
-        <v>74.8477</v>
+        <v>32.4653</v>
       </c>
       <c r="E57" t="n">
-        <v>24.3584</v>
+        <v>17.7153</v>
       </c>
       <c r="F57" t="n">
-        <v>44.2817</v>
+        <v>27.168</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>87.3009</v>
+        <v>21.0335</v>
       </c>
       <c r="C58" t="n">
-        <v>136.953</v>
+        <v>35.0274</v>
       </c>
       <c r="D58" t="n">
-        <v>72.30719999999999</v>
+        <v>32.4053</v>
       </c>
       <c r="E58" t="n">
-        <v>23.9072</v>
+        <v>17.3285</v>
       </c>
       <c r="F58" t="n">
-        <v>42.1978</v>
+        <v>26.9304</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>87.0031</v>
+        <v>20.4645</v>
       </c>
       <c r="C59" t="n">
-        <v>136.358</v>
+        <v>32.7547</v>
       </c>
       <c r="D59" t="n">
-        <v>65.2599</v>
+        <v>32.5056</v>
       </c>
       <c r="E59" t="n">
-        <v>23.5829</v>
+        <v>16.9252</v>
       </c>
       <c r="F59" t="n">
-        <v>41.2424</v>
+        <v>26.5913</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>86.12</v>
+        <v>19.9091</v>
       </c>
       <c r="C60" t="n">
-        <v>136.478</v>
+        <v>32.0034</v>
       </c>
       <c r="D60" t="n">
-        <v>80.2997</v>
+        <v>32.7926</v>
       </c>
       <c r="E60" t="n">
-        <v>23.1611</v>
+        <v>16.6297</v>
       </c>
       <c r="F60" t="n">
-        <v>40.7334</v>
+        <v>26.2944</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>85.3437</v>
+        <v>19.5268</v>
       </c>
       <c r="C61" t="n">
-        <v>136.536</v>
+        <v>33.4333</v>
       </c>
       <c r="D61" t="n">
-        <v>76.07089999999999</v>
+        <v>33.3888</v>
       </c>
       <c r="E61" t="n">
-        <v>22.7539</v>
+        <v>16.3133</v>
       </c>
       <c r="F61" t="n">
-        <v>40.4844</v>
+        <v>26.0361</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>85.0873</v>
+        <v>18.9018</v>
       </c>
       <c r="C62" t="n">
-        <v>137.295</v>
+        <v>30.6872</v>
       </c>
       <c r="D62" t="n">
-        <v>68.91889999999999</v>
+        <v>33.5897</v>
       </c>
       <c r="E62" t="n">
-        <v>22.3707</v>
+        <v>15.9663</v>
       </c>
       <c r="F62" t="n">
-        <v>43.791</v>
+        <v>25.7462</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>84.11020000000001</v>
+        <v>18.339</v>
       </c>
       <c r="C63" t="n">
-        <v>122.255</v>
+        <v>33.7534</v>
       </c>
       <c r="D63" t="n">
-        <v>74.9157</v>
+        <v>33.8238</v>
       </c>
       <c r="E63" t="n">
-        <v>21.9636</v>
+        <v>15.4956</v>
       </c>
       <c r="F63" t="n">
-        <v>40.9145</v>
+        <v>25.4091</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>83.6498</v>
+        <v>17.6789</v>
       </c>
       <c r="C64" t="n">
-        <v>136.3</v>
+        <v>31.5303</v>
       </c>
       <c r="D64" t="n">
-        <v>97.29430000000001</v>
+        <v>37.7737</v>
       </c>
       <c r="E64" t="n">
-        <v>21.5138</v>
+        <v>15.1265</v>
       </c>
       <c r="F64" t="n">
-        <v>38.9271</v>
+        <v>25.0724</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>82.86490000000001</v>
+        <v>17.0178</v>
       </c>
       <c r="C65" t="n">
-        <v>136.879</v>
+        <v>33.1199</v>
       </c>
       <c r="D65" t="n">
-        <v>90.8321</v>
+        <v>38.1428</v>
       </c>
       <c r="E65" t="n">
-        <v>21.137</v>
+        <v>14.809</v>
       </c>
       <c r="F65" t="n">
-        <v>38.3948</v>
+        <v>24.721</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>81.7594</v>
+        <v>16.1468</v>
       </c>
       <c r="C66" t="n">
-        <v>135.663</v>
+        <v>30.7111</v>
       </c>
       <c r="D66" t="n">
-        <v>91.54389999999999</v>
+        <v>38.3601</v>
       </c>
       <c r="E66" t="n">
-        <v>27.1752</v>
+        <v>20.2574</v>
       </c>
       <c r="F66" t="n">
-        <v>44.8036</v>
+        <v>28.7295</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>90.1575</v>
+        <v>23.2271</v>
       </c>
       <c r="C67" t="n">
-        <v>142.292</v>
+        <v>38.283</v>
       </c>
       <c r="D67" t="n">
-        <v>82.28319999999999</v>
+        <v>38.156</v>
       </c>
       <c r="E67" t="n">
-        <v>26.5259</v>
+        <v>20.1304</v>
       </c>
       <c r="F67" t="n">
-        <v>44.9217</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>89.7667</v>
+        <v>22.8925</v>
       </c>
       <c r="C68" t="n">
-        <v>138.345</v>
+        <v>38.0173</v>
       </c>
       <c r="D68" t="n">
-        <v>88.2938</v>
+        <v>38.3107</v>
       </c>
       <c r="E68" t="n">
-        <v>26.1123</v>
+        <v>19.4172</v>
       </c>
       <c r="F68" t="n">
-        <v>43.8468</v>
+        <v>28.1992</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>89.0951</v>
+        <v>22.4484</v>
       </c>
       <c r="C69" t="n">
-        <v>144.678</v>
+        <v>37.7479</v>
       </c>
       <c r="D69" t="n">
-        <v>89.8746</v>
+        <v>38.8515</v>
       </c>
       <c r="E69" t="n">
-        <v>25.5324</v>
+        <v>18.8775</v>
       </c>
       <c r="F69" t="n">
-        <v>43.3335</v>
+        <v>27.8852</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>88.8523</v>
+        <v>21.904</v>
       </c>
       <c r="C70" t="n">
-        <v>144.303</v>
+        <v>37.3018</v>
       </c>
       <c r="D70" t="n">
-        <v>87.1807</v>
+        <v>38.8192</v>
       </c>
       <c r="E70" t="n">
-        <v>25.1612</v>
+        <v>18.2976</v>
       </c>
       <c r="F70" t="n">
-        <v>46.8068</v>
+        <v>27.6053</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>88.26260000000001</v>
+        <v>21.5066</v>
       </c>
       <c r="C71" t="n">
-        <v>141.905</v>
+        <v>36.9628</v>
       </c>
       <c r="D71" t="n">
-        <v>72.735</v>
+        <v>38.761</v>
       </c>
       <c r="E71" t="n">
-        <v>24.5568</v>
+        <v>18.0085</v>
       </c>
       <c r="F71" t="n">
-        <v>43.5162</v>
+        <v>27.2587</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>87.9438</v>
+        <v>21.1367</v>
       </c>
       <c r="C72" t="n">
-        <v>125.174</v>
+        <v>35.6943</v>
       </c>
       <c r="D72" t="n">
-        <v>71.8034</v>
+        <v>38.8953</v>
       </c>
       <c r="E72" t="n">
-        <v>24.0501</v>
+        <v>17.4644</v>
       </c>
       <c r="F72" t="n">
-        <v>42.6208</v>
+        <v>26.9865</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>86.8326</v>
+        <v>20.663</v>
       </c>
       <c r="C73" t="n">
-        <v>130.685</v>
+        <v>44.3219</v>
       </c>
       <c r="D73" t="n">
-        <v>88.5489</v>
+        <v>38.9307</v>
       </c>
       <c r="E73" t="n">
-        <v>23.6565</v>
+        <v>17.1344</v>
       </c>
       <c r="F73" t="n">
-        <v>41.6165</v>
+        <v>26.699</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>86.3566</v>
+        <v>20.1267</v>
       </c>
       <c r="C74" t="n">
-        <v>148.232</v>
+        <v>43.7646</v>
       </c>
       <c r="D74" t="n">
-        <v>92.7149</v>
+        <v>39.1447</v>
       </c>
       <c r="E74" t="n">
-        <v>23.2895</v>
+        <v>16.8268</v>
       </c>
       <c r="F74" t="n">
-        <v>41.0084</v>
+        <v>26.4675</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>85.6683</v>
+        <v>19.5306</v>
       </c>
       <c r="C75" t="n">
-        <v>146.184</v>
+        <v>44.6435</v>
       </c>
       <c r="D75" t="n">
-        <v>90.066</v>
+        <v>39.2408</v>
       </c>
       <c r="E75" t="n">
-        <v>22.8484</v>
+        <v>16.4039</v>
       </c>
       <c r="F75" t="n">
-        <v>40.4308</v>
+        <v>26.1077</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>85.122</v>
+        <v>19.0855</v>
       </c>
       <c r="C76" t="n">
-        <v>143.606</v>
+        <v>47.5815</v>
       </c>
       <c r="D76" t="n">
-        <v>81.3954</v>
+        <v>39.102</v>
       </c>
       <c r="E76" t="n">
-        <v>22.4521</v>
+        <v>16.2418</v>
       </c>
       <c r="F76" t="n">
-        <v>41.2877</v>
+        <v>25.8461</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>84.45959999999999</v>
+        <v>18.508</v>
       </c>
       <c r="C77" t="n">
-        <v>150.21</v>
+        <v>43.5055</v>
       </c>
       <c r="D77" t="n">
-        <v>77.7308</v>
+        <v>39.3161</v>
       </c>
       <c r="E77" t="n">
-        <v>22.0833</v>
+        <v>15.8183</v>
       </c>
       <c r="F77" t="n">
-        <v>39.662</v>
+        <v>25.4975</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>84.0441</v>
+        <v>17.9396</v>
       </c>
       <c r="C78" t="n">
-        <v>139.42</v>
+        <v>39.0234</v>
       </c>
       <c r="D78" t="n">
-        <v>102.62</v>
+        <v>46.3613</v>
       </c>
       <c r="E78" t="n">
-        <v>21.6399</v>
+        <v>15.3402</v>
       </c>
       <c r="F78" t="n">
-        <v>39.1258</v>
+        <v>25.2546</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>82.8419</v>
+        <v>17.1743</v>
       </c>
       <c r="C79" t="n">
-        <v>141.493</v>
+        <v>34.4576</v>
       </c>
       <c r="D79" t="n">
-        <v>95.7379</v>
+        <v>45.8825</v>
       </c>
       <c r="E79" t="n">
-        <v>21.2405</v>
+        <v>15.0548</v>
       </c>
       <c r="F79" t="n">
-        <v>38.4773</v>
+        <v>24.8846</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>82.00449999999999</v>
+        <v>16.3389</v>
       </c>
       <c r="C80" t="n">
-        <v>144.52</v>
+        <v>41.2086</v>
       </c>
       <c r="D80" t="n">
-        <v>97.4161</v>
+        <v>45.711</v>
       </c>
       <c r="E80" t="n">
-        <v>26.914</v>
+        <v>20.1698</v>
       </c>
       <c r="F80" t="n">
-        <v>44.8397</v>
+        <v>28.8393</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>90.3556</v>
+        <v>23.4684</v>
       </c>
       <c r="C81" t="n">
-        <v>150.398</v>
+        <v>37.2964</v>
       </c>
       <c r="D81" t="n">
-        <v>97.0324</v>
+        <v>45.0961</v>
       </c>
       <c r="E81" t="n">
-        <v>26.3139</v>
+        <v>19.5636</v>
       </c>
       <c r="F81" t="n">
-        <v>44.1629</v>
+        <v>28.4402</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>90.2427</v>
+        <v>23.0166</v>
       </c>
       <c r="C82" t="n">
-        <v>146.638</v>
+        <v>36.9723</v>
       </c>
       <c r="D82" t="n">
-        <v>95.5917</v>
+        <v>44.5182</v>
       </c>
       <c r="E82" t="n">
-        <v>25.8865</v>
+        <v>19.1315</v>
       </c>
       <c r="F82" t="n">
-        <v>43.7278</v>
+        <v>28.1426</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>89.7773</v>
+        <v>22.6697</v>
       </c>
       <c r="C83" t="n">
-        <v>149.57</v>
+        <v>36.415</v>
       </c>
       <c r="D83" t="n">
-        <v>82.8475</v>
+        <v>44.0776</v>
       </c>
       <c r="E83" t="n">
-        <v>25.4566</v>
+        <v>18.7071</v>
       </c>
       <c r="F83" t="n">
-        <v>43.7031</v>
+        <v>27.8998</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>89.6623</v>
+        <v>22.0857</v>
       </c>
       <c r="C84" t="n">
-        <v>150.571</v>
+        <v>35.8237</v>
       </c>
       <c r="D84" t="n">
-        <v>81.4049</v>
+        <v>43.6305</v>
       </c>
       <c r="E84" t="n">
-        <v>24.9149</v>
+        <v>18.4331</v>
       </c>
       <c r="F84" t="n">
-        <v>42.6893</v>
+        <v>27.5422</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>88.5539</v>
+        <v>21.6271</v>
       </c>
       <c r="C85" t="n">
-        <v>149.282</v>
+        <v>35.2858</v>
       </c>
       <c r="D85" t="n">
-        <v>79.8419</v>
+        <v>43.262</v>
       </c>
       <c r="E85" t="n">
-        <v>24.5379</v>
+        <v>17.9766</v>
       </c>
       <c r="F85" t="n">
-        <v>42.3054</v>
+        <v>27.2847</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>87.6892</v>
+        <v>21.1902</v>
       </c>
       <c r="C86" t="n">
-        <v>150.104</v>
+        <v>34.7261</v>
       </c>
       <c r="D86" t="n">
-        <v>99.50530000000001</v>
+        <v>43.107</v>
       </c>
       <c r="E86" t="n">
-        <v>24.2673</v>
+        <v>17.6278</v>
       </c>
       <c r="F86" t="n">
-        <v>42.3965</v>
+        <v>26.9781</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>87.10250000000001</v>
+        <v>20.689</v>
       </c>
       <c r="C87" t="n">
-        <v>149.921</v>
+        <v>41.3991</v>
       </c>
       <c r="D87" t="n">
-        <v>105.674</v>
+        <v>42.6707</v>
       </c>
       <c r="E87" t="n">
-        <v>23.8039</v>
+        <v>17.2405</v>
       </c>
       <c r="F87" t="n">
-        <v>41.5768</v>
+        <v>26.7214</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>86.6151</v>
+        <v>20.2208</v>
       </c>
       <c r="C88" t="n">
-        <v>154.983</v>
+        <v>37.9521</v>
       </c>
       <c r="D88" t="n">
-        <v>101.447</v>
+        <v>42.3076</v>
       </c>
       <c r="E88" t="n">
-        <v>23.4246</v>
+        <v>16.9419</v>
       </c>
       <c r="F88" t="n">
-        <v>40.7935</v>
+        <v>26.4722</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>85.8805</v>
+        <v>19.6928</v>
       </c>
       <c r="C89" t="n">
-        <v>148.565</v>
+        <v>43.8876</v>
       </c>
       <c r="D89" t="n">
-        <v>92.2749</v>
+        <v>41.9118</v>
       </c>
       <c r="E89" t="n">
-        <v>22.9928</v>
+        <v>16.5686</v>
       </c>
       <c r="F89" t="n">
-        <v>40.427</v>
+        <v>26.163</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>85.2269</v>
+        <v>19.1451</v>
       </c>
       <c r="C90" t="n">
-        <v>121.599</v>
+        <v>42.9083</v>
       </c>
       <c r="D90" t="n">
-        <v>86.13330000000001</v>
+        <v>41.6211</v>
       </c>
       <c r="E90" t="n">
-        <v>22.6016</v>
+        <v>16.2006</v>
       </c>
       <c r="F90" t="n">
-        <v>40.1272</v>
+        <v>25.8929</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>84.76990000000001</v>
+        <v>18.6922</v>
       </c>
       <c r="C91" t="n">
-        <v>123.737</v>
+        <v>41.1131</v>
       </c>
       <c r="D91" t="n">
-        <v>86.99469999999999</v>
+        <v>41.5574</v>
       </c>
       <c r="E91" t="n">
-        <v>22.2475</v>
+        <v>15.82</v>
       </c>
       <c r="F91" t="n">
-        <v>39.8855</v>
+        <v>25.5793</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>84.0133</v>
+        <v>18.07</v>
       </c>
       <c r="C92" t="n">
-        <v>119.732</v>
+        <v>34.0639</v>
       </c>
       <c r="D92" t="n">
-        <v>95.7773</v>
+        <v>46.9569</v>
       </c>
       <c r="E92" t="n">
-        <v>21.8485</v>
+        <v>15.4625</v>
       </c>
       <c r="F92" t="n">
-        <v>39.1291</v>
+        <v>25.2733</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>83.21639999999999</v>
+        <v>17.4061</v>
       </c>
       <c r="C93" t="n">
-        <v>118.624</v>
+        <v>40.8972</v>
       </c>
       <c r="D93" t="n">
-        <v>90.40949999999999</v>
+        <v>46.5762</v>
       </c>
       <c r="E93" t="n">
-        <v>21.4256</v>
+        <v>15.1137</v>
       </c>
       <c r="F93" t="n">
-        <v>38.6287</v>
+        <v>25.021</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>82.3335</v>
+        <v>16.6077</v>
       </c>
       <c r="C94" t="n">
-        <v>149.531</v>
+        <v>36.7434</v>
       </c>
       <c r="D94" t="n">
-        <v>92.12649999999999</v>
+        <v>46.0232</v>
       </c>
       <c r="E94" t="n">
-        <v>27.0803</v>
+        <v>20.2131</v>
       </c>
       <c r="F94" t="n">
-        <v>44.6572</v>
+        <v>29.0525</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>90.80419999999999</v>
+        <v>23.4187</v>
       </c>
       <c r="C95" t="n">
-        <v>173.968</v>
+        <v>47.1568</v>
       </c>
       <c r="D95" t="n">
-        <v>88.40940000000001</v>
+        <v>45.1621</v>
       </c>
       <c r="E95" t="n">
-        <v>26.6066</v>
+        <v>19.7316</v>
       </c>
       <c r="F95" t="n">
-        <v>44.2164</v>
+        <v>28.7131</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>90.1097</v>
+        <v>23.0614</v>
       </c>
       <c r="C96" t="n">
-        <v>141.379</v>
+        <v>35.6078</v>
       </c>
       <c r="D96" t="n">
-        <v>88.7017</v>
+        <v>44.5661</v>
       </c>
       <c r="E96" t="n">
-        <v>26.029</v>
+        <v>19.2443</v>
       </c>
       <c r="F96" t="n">
-        <v>43.8045</v>
+        <v>28.4537</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>89.616</v>
+        <v>22.6575</v>
       </c>
       <c r="C97" t="n">
-        <v>159.13</v>
+        <v>35.1997</v>
       </c>
       <c r="D97" t="n">
-        <v>81.4717</v>
+        <v>44.0925</v>
       </c>
       <c r="E97" t="n">
-        <v>25.4879</v>
+        <v>18.8113</v>
       </c>
       <c r="F97" t="n">
-        <v>43.1965</v>
+        <v>27.8708</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>88.9842</v>
+        <v>22.2387</v>
       </c>
       <c r="C98" t="n">
-        <v>157.796</v>
+        <v>34.7923</v>
       </c>
       <c r="D98" t="n">
-        <v>80.5185</v>
+        <v>43.6539</v>
       </c>
       <c r="E98" t="n">
-        <v>25.0889</v>
+        <v>18.441</v>
       </c>
       <c r="F98" t="n">
-        <v>42.6532</v>
+        <v>27.6256</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>88.2175</v>
+        <v>21.8212</v>
       </c>
       <c r="C99" t="n">
-        <v>152.964</v>
+        <v>34.2908</v>
       </c>
       <c r="D99" t="n">
-        <v>83.7385</v>
+        <v>43.4914</v>
       </c>
       <c r="E99" t="n">
-        <v>24.6615</v>
+        <v>18.0306</v>
       </c>
       <c r="F99" t="n">
-        <v>42.2509</v>
+        <v>27.3406</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>87.74169999999999</v>
+        <v>21.2641</v>
       </c>
       <c r="C100" t="n">
-        <v>158.112</v>
+        <v>33.8405</v>
       </c>
       <c r="D100" t="n">
-        <v>77.7394</v>
+        <v>42.5467</v>
       </c>
       <c r="E100" t="n">
-        <v>24.3721</v>
+        <v>17.6632</v>
       </c>
       <c r="F100" t="n">
-        <v>41.7406</v>
+        <v>27.0908</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>86.6797</v>
+        <v>20.9232</v>
       </c>
       <c r="C101" t="n">
-        <v>165.894</v>
+        <v>40.9446</v>
       </c>
       <c r="D101" t="n">
-        <v>90.5117</v>
+        <v>42.6377</v>
       </c>
       <c r="E101" t="n">
-        <v>23.9506</v>
+        <v>17.3078</v>
       </c>
       <c r="F101" t="n">
-        <v>41.279</v>
+        <v>26.8696</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>86.35550000000001</v>
+        <v>20.4992</v>
       </c>
       <c r="C102" t="n">
-        <v>152.28</v>
+        <v>43.8154</v>
       </c>
       <c r="D102" t="n">
-        <v>78.4218</v>
+        <v>41.9095</v>
       </c>
       <c r="E102" t="n">
-        <v>23.5314</v>
+        <v>16.9583</v>
       </c>
       <c r="F102" t="n">
-        <v>40.9598</v>
+        <v>26.4808</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>85.6493</v>
+        <v>20.0205</v>
       </c>
       <c r="C103" t="n">
-        <v>152.454</v>
+        <v>42.041</v>
       </c>
       <c r="D103" t="n">
-        <v>79.7124</v>
+        <v>41.7491</v>
       </c>
       <c r="E103" t="n">
-        <v>23.1437</v>
+        <v>16.6036</v>
       </c>
       <c r="F103" t="n">
-        <v>40.3277</v>
+        <v>26.2747</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>84.6767</v>
+        <v>19.4654</v>
       </c>
       <c r="C104" t="n">
-        <v>157.371</v>
+        <v>41.4318</v>
       </c>
       <c r="D104" t="n">
-        <v>72.93300000000001</v>
+        <v>41.4901</v>
       </c>
       <c r="E104" t="n">
-        <v>22.7385</v>
+        <v>16.2597</v>
       </c>
       <c r="F104" t="n">
-        <v>40.1315</v>
+        <v>25.9891</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>84.614</v>
+        <v>18.9089</v>
       </c>
       <c r="C105" t="n">
-        <v>152.247</v>
+        <v>37.6813</v>
       </c>
       <c r="D105" t="n">
-        <v>68.2619</v>
+        <v>40.7685</v>
       </c>
       <c r="E105" t="n">
-        <v>22.4032</v>
+        <v>15.9205</v>
       </c>
       <c r="F105" t="n">
-        <v>39.4638</v>
+        <v>25.6551</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>83.9824</v>
+        <v>18.2534</v>
       </c>
       <c r="C106" t="n">
-        <v>163.808</v>
+        <v>39.5164</v>
       </c>
       <c r="D106" t="n">
-        <v>81.34350000000001</v>
+        <v>40.4453</v>
       </c>
       <c r="E106" t="n">
-        <v>22.0174</v>
+        <v>15.5669</v>
       </c>
       <c r="F106" t="n">
-        <v>39.0322</v>
+        <v>25.3772</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>83.21259999999999</v>
+        <v>17.6933</v>
       </c>
       <c r="C107" t="n">
-        <v>152.218</v>
+        <v>39.1894</v>
       </c>
       <c r="D107" t="n">
-        <v>85.6456</v>
+        <v>44.4674</v>
       </c>
       <c r="E107" t="n">
-        <v>21.629</v>
+        <v>15.195</v>
       </c>
       <c r="F107" t="n">
-        <v>38.6195</v>
+        <v>25.0583</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>82.30759999999999</v>
+        <v>16.9313</v>
       </c>
       <c r="C108" t="n">
-        <v>156.177</v>
+        <v>37.3667</v>
       </c>
       <c r="D108" t="n">
-        <v>90.59399999999999</v>
+        <v>43.7566</v>
       </c>
       <c r="E108" t="n">
-        <v>27.2867</v>
+        <v>20.2931</v>
       </c>
       <c r="F108" t="n">
-        <v>44.776</v>
+        <v>28.7741</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>81.34139999999999</v>
+        <v>15.8903</v>
       </c>
       <c r="C109" t="n">
-        <v>161.106</v>
+        <v>34.3083</v>
       </c>
       <c r="D109" t="n">
-        <v>85.5132</v>
+        <v>43.4549</v>
       </c>
       <c r="E109" t="n">
-        <v>26.7523</v>
+        <v>19.7456</v>
       </c>
       <c r="F109" t="n">
-        <v>44.3164</v>
+        <v>28.4348</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>89.76439999999999</v>
+        <v>23.2406</v>
       </c>
       <c r="C110" t="n">
-        <v>156.963</v>
+        <v>42.2787</v>
       </c>
       <c r="D110" t="n">
-        <v>91.1567</v>
+        <v>43.1137</v>
       </c>
       <c r="E110" t="n">
-        <v>26.2635</v>
+        <v>19.3471</v>
       </c>
       <c r="F110" t="n">
-        <v>43.761</v>
+        <v>28.2007</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>89.8926</v>
+        <v>22.8489</v>
       </c>
       <c r="C111" t="n">
-        <v>162.597</v>
+        <v>42.1235</v>
       </c>
       <c r="D111" t="n">
-        <v>76.9933</v>
+        <v>42.5204</v>
       </c>
       <c r="E111" t="n">
-        <v>25.7675</v>
+        <v>18.9421</v>
       </c>
       <c r="F111" t="n">
-        <v>43.5208</v>
+        <v>27.96</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>88.6164</v>
+        <v>22.4998</v>
       </c>
       <c r="C112" t="n">
-        <v>172.036</v>
+        <v>41.3777</v>
       </c>
       <c r="D112" t="n">
-        <v>82.2312</v>
+        <v>42.0509</v>
       </c>
       <c r="E112" t="n">
-        <v>25.3512</v>
+        <v>18.5299</v>
       </c>
       <c r="F112" t="n">
-        <v>43.186</v>
+        <v>27.672</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>88.559</v>
+        <v>21.9197</v>
       </c>
       <c r="C113" t="n">
-        <v>189.407</v>
+        <v>41.1425</v>
       </c>
       <c r="D113" t="n">
-        <v>73.5804</v>
+        <v>41.7757</v>
       </c>
       <c r="E113" t="n">
-        <v>24.8787</v>
+        <v>18.0903</v>
       </c>
       <c r="F113" t="n">
-        <v>42.6892</v>
+        <v>27.394</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>87.9796</v>
+        <v>21.4575</v>
       </c>
       <c r="C114" t="n">
-        <v>179.471</v>
+        <v>40.4312</v>
       </c>
       <c r="D114" t="n">
-        <v>74.742</v>
+        <v>41.2865</v>
       </c>
       <c r="E114" t="n">
-        <v>24.4662</v>
+        <v>17.7067</v>
       </c>
       <c r="F114" t="n">
-        <v>42.0877</v>
+        <v>27.148</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>87.42319999999999</v>
+        <v>20.9629</v>
       </c>
       <c r="C115" t="n">
-        <v>187.93</v>
+        <v>43.2824</v>
       </c>
       <c r="D115" t="n">
-        <v>73.7259</v>
+        <v>41.2891</v>
       </c>
       <c r="E115" t="n">
-        <v>23.987</v>
+        <v>17.387</v>
       </c>
       <c r="F115" t="n">
-        <v>41.4585</v>
+        <v>26.9102</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>87.30629999999999</v>
+        <v>20.5149</v>
       </c>
       <c r="C116" t="n">
-        <v>183.209</v>
+        <v>42.1851</v>
       </c>
       <c r="D116" t="n">
-        <v>69.3665</v>
+        <v>40.9203</v>
       </c>
       <c r="E116" t="n">
-        <v>23.5784</v>
+        <v>17.0308</v>
       </c>
       <c r="F116" t="n">
-        <v>41.0821</v>
+        <v>26.6362</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>86.155</v>
+        <v>20.0222</v>
       </c>
       <c r="C117" t="n">
-        <v>203.88</v>
+        <v>33.2174</v>
       </c>
       <c r="D117" t="n">
-        <v>69.2266</v>
+        <v>40.3685</v>
       </c>
       <c r="E117" t="n">
-        <v>23.2131</v>
+        <v>16.6661</v>
       </c>
       <c r="F117" t="n">
-        <v>40.6126</v>
+        <v>26.2993</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>85.5971</v>
+        <v>19.4784</v>
       </c>
       <c r="C118" t="n">
-        <v>191.594</v>
+        <v>41.1334</v>
       </c>
       <c r="D118" t="n">
-        <v>66.6557</v>
+        <v>39.6476</v>
       </c>
       <c r="E118" t="n">
-        <v>22.7606</v>
+        <v>16.3374</v>
       </c>
       <c r="F118" t="n">
-        <v>40.1325</v>
+        <v>26.0681</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>84.8985</v>
+        <v>18.9754</v>
       </c>
       <c r="C119" t="n">
-        <v>180.542</v>
+        <v>39.1201</v>
       </c>
       <c r="D119" t="n">
-        <v>66.21769999999999</v>
+        <v>39.6714</v>
       </c>
       <c r="E119" t="n">
-        <v>22.4004</v>
+        <v>15.9359</v>
       </c>
       <c r="F119" t="n">
-        <v>39.7898</v>
+        <v>25.7169</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>84.051</v>
+        <v>18.3402</v>
       </c>
       <c r="C120" t="n">
-        <v>189.317</v>
+        <v>36.2454</v>
       </c>
       <c r="D120" t="n">
-        <v>64.7029</v>
+        <v>39.3521</v>
       </c>
       <c r="E120" t="n">
-        <v>22.0286</v>
+        <v>15.5889</v>
       </c>
       <c r="F120" t="n">
-        <v>39.2677</v>
+        <v>25.6256</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>83.2814</v>
+        <v>17.7036</v>
       </c>
       <c r="C121" t="n">
-        <v>192.873</v>
+        <v>35.4345</v>
       </c>
       <c r="D121" t="n">
-        <v>86.3951</v>
+        <v>47.7242</v>
       </c>
       <c r="E121" t="n">
-        <v>21.6688</v>
+        <v>15.2598</v>
       </c>
       <c r="F121" t="n">
-        <v>38.7577</v>
+        <v>25.1641</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>82.4823</v>
+        <v>17.0424</v>
       </c>
       <c r="C122" t="n">
-        <v>201.227</v>
+        <v>37.9853</v>
       </c>
       <c r="D122" t="n">
-        <v>85.6178</v>
+        <v>47.1557</v>
       </c>
       <c r="E122" t="n">
-        <v>21.2648</v>
+        <v>14.903</v>
       </c>
       <c r="F122" t="n">
-        <v>38.219</v>
+        <v>24.8485</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>81.5239</v>
+        <v>16.1942</v>
       </c>
       <c r="C123" t="n">
-        <v>192.707</v>
+        <v>34.538</v>
       </c>
       <c r="D123" t="n">
-        <v>133.854</v>
+        <v>45.7867</v>
       </c>
       <c r="E123" t="n">
-        <v>26.6973</v>
+        <v>19.8916</v>
       </c>
       <c r="F123" t="n">
-        <v>44.4254</v>
+        <v>28.5946</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>90.6707</v>
+        <v>23.2967</v>
       </c>
       <c r="C124" t="n">
-        <v>208.005</v>
+        <v>49.027</v>
       </c>
       <c r="D124" t="n">
-        <v>80.4301</v>
+        <v>45.6743</v>
       </c>
       <c r="E124" t="n">
-        <v>26.2105</v>
+        <v>19.4662</v>
       </c>
       <c r="F124" t="n">
-        <v>43.8924</v>
+        <v>28.2967</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>89.9402</v>
+        <v>22.8935</v>
       </c>
       <c r="C125" t="n">
-        <v>210.413</v>
+        <v>49.6141</v>
       </c>
       <c r="D125" t="n">
-        <v>78.883</v>
+        <v>45.1569</v>
       </c>
       <c r="E125" t="n">
-        <v>25.8792</v>
+        <v>19.0015</v>
       </c>
       <c r="F125" t="n">
-        <v>43.3435</v>
+        <v>28.027</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>89.4087</v>
+        <v>22.4758</v>
       </c>
       <c r="C126" t="n">
-        <v>210.451</v>
+        <v>40.7035</v>
       </c>
       <c r="D126" t="n">
-        <v>78.7384</v>
+        <v>44.4139</v>
       </c>
       <c r="E126" t="n">
-        <v>25.3429</v>
+        <v>18.6146</v>
       </c>
       <c r="F126" t="n">
-        <v>42.9297</v>
+        <v>27.721</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>88.7427</v>
+        <v>22.117</v>
       </c>
       <c r="C127" t="n">
-        <v>213.202</v>
+        <v>45.2036</v>
       </c>
       <c r="D127" t="n">
-        <v>75.6503</v>
+        <v>43.7424</v>
       </c>
       <c r="E127" t="n">
-        <v>24.9034</v>
+        <v>18.192</v>
       </c>
       <c r="F127" t="n">
-        <v>42.4049</v>
+        <v>27.4653</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>87.9119</v>
+        <v>21.6773</v>
       </c>
       <c r="C128" t="n">
-        <v>213.543</v>
+        <v>38.5475</v>
       </c>
       <c r="D128" t="n">
-        <v>77.4041</v>
+        <v>43.1697</v>
       </c>
       <c r="E128" t="n">
-        <v>24.4744</v>
+        <v>17.8284</v>
       </c>
       <c r="F128" t="n">
-        <v>41.9354</v>
+        <v>27.2457</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>87.2552</v>
+        <v>21.1412</v>
       </c>
       <c r="C129" t="n">
-        <v>214.352</v>
+        <v>47.2854</v>
       </c>
       <c r="D129" t="n">
-        <v>87.7606</v>
+        <v>42.8942</v>
       </c>
       <c r="E129" t="n">
-        <v>24.0757</v>
+        <v>17.4962</v>
       </c>
       <c r="F129" t="n">
-        <v>41.6562</v>
+        <v>27.1142</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>86.63200000000001</v>
+        <v>20.7008</v>
       </c>
       <c r="C130" t="n">
-        <v>195.306</v>
+        <v>43.4328</v>
       </c>
       <c r="D130" t="n">
-        <v>91.8883</v>
+        <v>42.4587</v>
       </c>
       <c r="E130" t="n">
-        <v>23.7045</v>
+        <v>17.1342</v>
       </c>
       <c r="F130" t="n">
-        <v>41.2005</v>
+        <v>26.819</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>85.8413</v>
+        <v>20.1933</v>
       </c>
       <c r="C131" t="n">
-        <v>192.489</v>
+        <v>39.7812</v>
       </c>
       <c r="D131" t="n">
-        <v>93.815</v>
+        <v>42.0112</v>
       </c>
       <c r="E131" t="n">
-        <v>23.2839</v>
+        <v>16.8229</v>
       </c>
       <c r="F131" t="n">
-        <v>40.7328</v>
+        <v>26.5468</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>85.2723</v>
+        <v>19.5876</v>
       </c>
       <c r="C132" t="n">
-        <v>189.033</v>
+        <v>37.1862</v>
       </c>
       <c r="D132" t="n">
-        <v>83.4229</v>
+        <v>41.7029</v>
       </c>
       <c r="E132" t="n">
-        <v>22.927</v>
+        <v>16.4021</v>
       </c>
       <c r="F132" t="n">
-        <v>40.1842</v>
+        <v>26.095</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>84.7192</v>
+        <v>19.071</v>
       </c>
       <c r="C133" t="n">
-        <v>191.832</v>
+        <v>44.5729</v>
       </c>
       <c r="D133" t="n">
-        <v>82.4901</v>
+        <v>41.4645</v>
       </c>
       <c r="E133" t="n">
-        <v>22.5203</v>
+        <v>16.0719</v>
       </c>
       <c r="F133" t="n">
-        <v>39.6642</v>
+        <v>26.0184</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>84.41160000000001</v>
+        <v>18.4869</v>
       </c>
       <c r="C134" t="n">
-        <v>191.117</v>
+        <v>41.4199</v>
       </c>
       <c r="D134" t="n">
-        <v>86.086</v>
+        <v>41.284</v>
       </c>
       <c r="E134" t="n">
-        <v>22.1071</v>
+        <v>15.7091</v>
       </c>
       <c r="F134" t="n">
-        <v>39.3302</v>
+        <v>25.7406</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>83.3746</v>
+        <v>17.986</v>
       </c>
       <c r="C135" t="n">
-        <v>207.828</v>
+        <v>39.8504</v>
       </c>
       <c r="D135" t="n">
-        <v>99.3385</v>
+        <v>48.1077</v>
       </c>
       <c r="E135" t="n">
-        <v>21.7246</v>
+        <v>15.357</v>
       </c>
       <c r="F135" t="n">
-        <v>39.0591</v>
+        <v>25.4236</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>82.7321</v>
+        <v>17.173</v>
       </c>
       <c r="C136" t="n">
-        <v>207.571</v>
+        <v>36.4638</v>
       </c>
       <c r="D136" t="n">
-        <v>108.595</v>
+        <v>47.158</v>
       </c>
       <c r="E136" t="n">
-        <v>21.3397</v>
+        <v>15.0309</v>
       </c>
       <c r="F136" t="n">
-        <v>38.3347</v>
+        <v>25.63</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>81.9909</v>
+        <v>16.3874</v>
       </c>
       <c r="C137" t="n">
-        <v>204.114</v>
+        <v>41.5658</v>
       </c>
       <c r="D137" t="n">
-        <v>94.7501</v>
+        <v>46.8551</v>
       </c>
       <c r="E137" t="n">
-        <v>26.8522</v>
+        <v>19.9719</v>
       </c>
       <c r="F137" t="n">
-        <v>44.7179</v>
+        <v>28.8739</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>121.972</v>
+        <v>23.3695</v>
       </c>
       <c r="C138" t="n">
-        <v>209.156</v>
+        <v>35.2165</v>
       </c>
       <c r="D138" t="n">
-        <v>130.42</v>
+        <v>46.3115</v>
       </c>
       <c r="E138" t="n">
-        <v>26.3422</v>
+        <v>19.5893</v>
       </c>
       <c r="F138" t="n">
-        <v>44.2901</v>
+        <v>28.5629</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>118.347</v>
+        <v>22.9769</v>
       </c>
       <c r="C139" t="n">
-        <v>203.724</v>
+        <v>42.3662</v>
       </c>
       <c r="D139" t="n">
-        <v>120.371</v>
+        <v>45.6992</v>
       </c>
       <c r="E139" t="n">
-        <v>25.9196</v>
+        <v>19.1319</v>
       </c>
       <c r="F139" t="n">
-        <v>43.6069</v>
+        <v>28.2742</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>115.441</v>
+        <v>22.6013</v>
       </c>
       <c r="C140" t="n">
-        <v>203.816</v>
+        <v>44.4029</v>
       </c>
       <c r="D140" t="n">
-        <v>100.665</v>
+        <v>44.9868</v>
       </c>
       <c r="E140" t="n">
-        <v>25.4661</v>
+        <v>18.721</v>
       </c>
       <c r="F140" t="n">
-        <v>43.2305</v>
+        <v>27.8103</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>114.437</v>
+        <v>22.1759</v>
       </c>
       <c r="C141" t="n">
-        <v>226.932</v>
+        <v>38.7359</v>
       </c>
       <c r="D141" t="n">
-        <v>93.7718</v>
+        <v>44.3679</v>
       </c>
       <c r="E141" t="n">
-        <v>25.0159</v>
+        <v>18.319</v>
       </c>
       <c r="F141" t="n">
-        <v>42.64</v>
+        <v>27.516</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>119.074</v>
+        <v>21.6647</v>
       </c>
       <c r="C142" t="n">
-        <v>210.736</v>
+        <v>49.7632</v>
       </c>
       <c r="D142" t="n">
-        <v>93.77849999999999</v>
+        <v>43.8578</v>
       </c>
       <c r="E142" t="n">
-        <v>24.5904</v>
+        <v>17.9163</v>
       </c>
       <c r="F142" t="n">
-        <v>42.4904</v>
+        <v>27.2322</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>120.056</v>
+        <v>21.1924</v>
       </c>
       <c r="C143" t="n">
-        <v>203.499</v>
+        <v>40.2964</v>
       </c>
       <c r="D143" t="n">
-        <v>88.28279999999999</v>
+        <v>43.2283</v>
       </c>
       <c r="E143" t="n">
-        <v>24.1671</v>
+        <v>17.5951</v>
       </c>
       <c r="F143" t="n">
-        <v>41.783</v>
+        <v>26.9331</v>
       </c>
     </row>
   </sheetData>
